--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -2488,16 +2488,16 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>19.16</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="63">
@@ -2521,16 +2521,16 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
+          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>6.06</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="64">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KRDMD</t>
+          <t>KRDMB</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>38.56</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="87">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>KRDMB</t>
+          <t>KRDMD</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>113.6</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="89">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>20</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>36.7</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>38.24</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>47.78</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>17.65</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>2.42</v>
+        <v>181.6</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>12.47</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>70.05</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>16.81</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>40.9</v>
+        <v>70.05</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>14.43</v>
+        <v>142.7</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>17.2</v>
+        <v>34.08</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>3.75</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>142.7</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>37.7</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>34.08</v>
+        <v>162.9</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>7.86</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>162.9</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>167.4</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>105.9</v>
+        <v>41.74</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>181.6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>18.65</v>
+        <v>167.4</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>67.09999999999999</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>20.68</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>41.74</v>
+        <v>20.68</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>72.09999999999999</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>17.11</v>
+        <v>18.65</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ISBTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>417997.5</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="12">
@@ -838,7 +838,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>ISBTR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>13.74</v>
+        <v>417997.5</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2915000</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="14">
@@ -2488,16 +2488,16 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
+          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>6.06</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="63">
@@ -2521,16 +2521,16 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>19.16</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="64">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>17.11</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>17.2</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>105.9</v>
+        <v>167.4</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>67.09999999999999</v>
+        <v>142.7</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>3.75</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>181.6</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="592">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>36.7</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="594">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>70.05</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>142.7</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>34.08</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>40.9</v>
+        <v>162.9</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>12.47</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>2.42</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>162.9</v>
+        <v>70.05</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>47.78</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>72.09999999999999</v>
+        <v>41.74</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>7.86</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>41.74</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>20</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>167.4</v>
+        <v>18.65</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>16.81</v>
+        <v>20.68</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>17.65</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>20.68</v>
+        <v>20</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>37.7</v>
+        <v>181.6</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>18.65</v>
+        <v>34.08</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.284465</v>
+        <v>3.287993</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>59.865902</v>
+        <v>59.734573</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.694062</v>
+        <v>3.698805</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44.110245</v>
+        <v>44.395364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5.493287</v>
+        <v>5.51244</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.848312</v>
+        <v>0.853064</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.255265</v>
+        <v>1.261835</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>104.987852</v>
+        <v>104.857329</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.175092</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.972155</v>
+        <v>1.964561</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.171472</v>
+        <v>1.15462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.231844</v>
+        <v>1.204933</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.309287</v>
+        <v>0.306784</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.973323</v>
+        <v>0.947202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.5515060000000001</v>
+        <v>0.555307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8.923401999999999</v>
+        <v>8.925490999999999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>36.6776</v>
+        <v>36.604215</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.584917</v>
+        <v>10.585152</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20.27232</v>
+        <v>20.270019</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.09957000000000001</v>
+        <v>0.099694</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.507181</v>
+        <v>0.508149</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>50.460192</v>
+        <v>50.547923</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.501618</v>
+        <v>0.50182</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.897795</v>
+        <v>0.90071</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.350469</v>
+        <v>0.350686</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>101.179752</v>
+        <v>101.410226</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.378175</v>
+        <v>0.377991</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6.598827</v>
+        <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.148665</v>
+        <v>0.148943</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.223992</v>
+        <v>0.223636</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.331767</v>
+        <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>17.81099</v>
+        <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3.682533</v>
+        <v>3.680804</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1.090773</v>
+        <v>1.070168</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>18.204762</v>
+        <v>18.171726</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.129996</v>
+        <v>0.130129</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.960569</v>
+        <v>0.9558449999999999</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3.330895</v>
+        <v>3.334538</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2.091252</v>
+        <v>2.094923</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1.988006</v>
+        <v>1.972682</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.651884</v>
+        <v>1.643992</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2.416761</v>
+        <v>2.388073</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1.627319</v>
+        <v>1.619681</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1.718317</v>
+        <v>1.711743</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.940707</v>
+        <v>0.936064</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.109873</v>
+        <v>1.115056</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>6.052204</v>
+        <v>6.058867</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1.537491</v>
+        <v>1.542755</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3.02479</v>
+        <v>3.006525</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.268687</v>
+        <v>3.271435</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1.362604</v>
+        <v>1.369086</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7.677539</v>
+        <v>7.650922</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2.351931</v>
+        <v>2.351107</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1.290802</v>
+        <v>1.295474</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1.630806</v>
+        <v>1.59895</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1.567281</v>
+        <v>1.568971</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1.263949</v>
+        <v>1.264891</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1.458721</v>
+        <v>1.460482</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1.531975</v>
+        <v>1.530026</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.536707</v>
+        <v>1.53831</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2484,20 +2484,20 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4.552408</v>
+        <v>4.513604</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>19.16</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="63">
@@ -2517,20 +2517,20 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1.580083</v>
+        <v>1.56672</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
+          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>6.06</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="64">
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1.239157</v>
+        <v>1.22532</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1.049131</v>
+        <v>1.049625</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1.724206</v>
+        <v>1.720815</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1.531915</v>
+        <v>1.530228</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1.273878</v>
+        <v>1.273737</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1.306602</v>
+        <v>1.30794</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3.366299</v>
+        <v>3.353749</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2.33216</v>
+        <v>2.334765</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1.982151</v>
+        <v>1.964564</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1.390139</v>
+        <v>1.380843</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3.860719</v>
+        <v>3.784127</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>3.670979</v>
+        <v>3.628347</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4.771132</v>
+        <v>4.770315</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1.283626</v>
+        <v>1.277663</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3.509238</v>
+        <v>3.495631</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.691448</v>
+        <v>0.677146</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.104452</v>
+        <v>0.104585</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.362375</v>
+        <v>0.36261</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.112431</v>
+        <v>0.112549</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.47393</v>
+        <v>0.474512</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.13049</v>
+        <v>0.130627</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3.053927</v>
+        <v>3.057388</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1.280533</v>
+        <v>1.277348</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3309,11 +3309,11 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>7.414444</v>
+        <v>7.386533</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>KRDMA</t>
+          <t>KRDMD</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>41.18</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="88">
@@ -3342,11 +3342,11 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5.085314</v>
+        <v>5.066379</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>KRDMD</t>
+          <t>KRDMA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>38.56</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="89">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1.088374</v>
+        <v>1.08143</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1.37116</v>
+        <v>1.370017</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>3.663235</v>
+        <v>3.649702</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2.29702</v>
+        <v>2.299389</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>7.128632</v>
+        <v>7.125172</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>5.636667</v>
+        <v>5.642548</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>6.56569</v>
+        <v>6.516193</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1.201837</v>
+        <v>1.201962</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>8.036825</v>
+        <v>8.04541</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>16.585807</v>
+        <v>16.61241</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1.183699</v>
+        <v>1.176714</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>13.834236</v>
+        <v>13.83428</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1.371739</v>
+        <v>1.369048</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>4.159412</v>
+        <v>4.139253</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1.365562</v>
+        <v>1.368731</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>5.056675</v>
+        <v>4.93684</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1.210592</v>
+        <v>1.212809</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>9.433381000000001</v>
+        <v>9.325125</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1.780064</v>
+        <v>1.770784</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4.596404</v>
+        <v>4.571949</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.960806</v>
+        <v>0.961456</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.257164</v>
+        <v>0.25368</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>84.768767</v>
+        <v>84.15931399999999</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1.746553</v>
+        <v>1.752133</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>3.35579</v>
+        <v>3.354445</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.634282</v>
+        <v>0.632935</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1.852694</v>
+        <v>1.851774</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>4.880412</v>
+        <v>4.885546</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.1316</v>
+        <v>0.131745</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>13.639566</v>
+        <v>13.60642</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1.193825</v>
+        <v>1.193044</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1.350832</v>
+        <v>1.350797</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1.276987</v>
+        <v>1.278345</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1.145398</v>
+        <v>1.138894</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1.27937</v>
+        <v>1.268821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1.237507</v>
+        <v>1.238856</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1.059859</v>
+        <v>1.056685</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1.235963</v>
+        <v>1.235468</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1.164208</v>
+        <v>1.143848</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>2.351052</v>
+        <v>2.355904</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1.958529</v>
+        <v>1.977979</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1.823617</v>
+        <v>1.822592</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>2.735081</v>
+        <v>2.737792</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>8.065237</v>
+        <v>8.073271999999999</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>7.257606</v>
+        <v>7.258081</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>739.184916</v>
+        <v>739.900908</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.468502</v>
+        <v>0.458639</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.971469</v>
+        <v>0.972933</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.344649</v>
+        <v>0.345048</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.214519</v>
+        <v>0.21487</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1.624074</v>
+        <v>1.630702</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.191923</v>
+        <v>0.191656</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>72.491456</v>
+        <v>72.542602</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>32.552303</v>
+        <v>32.639002</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>2.452197</v>
+        <v>2.454717</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.091484</v>
+        <v>0.091585</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>5.670125</v>
+        <v>5.674687</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1.282857</v>
+        <v>0</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1.420678</v>
+        <v>1.422197</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>5.113099</v>
+        <v>5.09422</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.716835</v>
+        <v>0.717074</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>10.908602</v>
+        <v>10.931084</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1.101588</v>
+        <v>1.102745</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>5.329139</v>
+        <v>5.328929</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1.833272</v>
+        <v>1.834879</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0.437611</v>
+        <v>0.438878</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1.642028</v>
+        <v>1.644793</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>11.819561</v>
+        <v>11.825729</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.294546</v>
+        <v>0.291524</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0.556958</v>
+        <v>0.554417</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0.806389</v>
+        <v>0.807243</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>13.129253</v>
+        <v>12.93956</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>3.303177</v>
+        <v>3.299748</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>12.901579</v>
+        <v>12.647386</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>37.732235</v>
+        <v>37.767585</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1.643006</v>
+        <v>1.629124</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>3.413375</v>
+        <v>3.417401</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>2.431215</v>
+        <v>2.412756</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>10.448937</v>
+        <v>10.447986</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>4.92383</v>
+        <v>4.875516</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1.3364</v>
+        <v>1.337004</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>8.203797</v>
+        <v>8.153606999999999</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1374.310895</v>
+        <v>1374.961004</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0.158642</v>
+        <v>0.158702</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1.98971</v>
+        <v>1.990557</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>7.52194</v>
+        <v>0</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>2.633451</v>
+        <v>2.628981</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1.476957</v>
+        <v>1.459453</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1.492745</v>
+        <v>1.490428</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1.546182</v>
+        <v>1.550178</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>4.416088</v>
+        <v>4.43419</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>4.694335</v>
+        <v>4.702206</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>4.709588</v>
+        <v>4.712697</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>5.077783</v>
+        <v>5.092525</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>3.931481</v>
+        <v>3.936111</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2.460992</v>
+        <v>2.477515</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>16.438797</v>
+        <v>16.333136</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2.605937</v>
+        <v>2.553111</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1.125167</v>
+        <v>1.126443</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>22.038093</v>
+        <v>22.051114</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>11.281919</v>
+        <v>11.29313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>8.535353000000001</v>
+        <v>8.536136000000001</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>15.251003</v>
+        <v>15.128004</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>17.290429</v>
+        <v>17.300056</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1.288899</v>
+        <v>1.290398</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>2.773471</v>
+        <v>2.731275</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>19.827354</v>
+        <v>19.830752</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1.815179</v>
+        <v>1.817181</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1.732014</v>
+        <v>1.72251</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0.546689</v>
+        <v>0.548049</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1.481431</v>
+        <v>1.450201</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>14.068122</v>
+        <v>14.011034</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1.322676</v>
+        <v>1.322281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>7.561792</v>
+        <v>7.570458</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>11.305042</v>
+        <v>11.18479</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>2.382664</v>
+        <v>2.38511</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0.886001</v>
+        <v>0.875368</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0.436882</v>
+        <v>0.432185</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>12.07007</v>
+        <v>0</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1.604305</v>
+        <v>1.60711</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>4.324415</v>
+        <v>4.286488</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>5.3508</v>
+        <v>0</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0.106174</v>
+        <v>0.106236</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>6.27813</v>
+        <v>6.240926</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>5.000515</v>
+        <v>5.011578</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>8.214195999999999</v>
+        <v>8.209652</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>5.209476</v>
+        <v>5.204615</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>7.199025</v>
+        <v>7.200016</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>11.237954</v>
+        <v>11.234573</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>8.175319</v>
+        <v>8.189164999999999</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>7.278643</v>
+        <v>7.218859</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>6.428849</v>
+        <v>6.365313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1.001989</v>
+        <v>1.002983</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>2.874332</v>
+        <v>2.813686</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>47.284463</v>
+        <v>46.386414</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>4.117318</v>
+        <v>4.115432</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1.386657</v>
+        <v>1.390904</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0.959535</v>
+        <v>0.959093</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1.459113</v>
+        <v>1.45724</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>3.747833</v>
+        <v>3.767521</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1.391492</v>
+        <v>1.395989</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1.993164</v>
+        <v>1.988873</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>4.041729</v>
+        <v>4.020065</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1.352733</v>
+        <v>1.353093</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>8.601331999999999</v>
+        <v>8.507913</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>0.095987</v>
+        <v>0.095746</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1.335588</v>
+        <v>1.340484</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>0.234938</v>
+        <v>0.233064</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>0.34493</v>
+        <v>0.344813</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>0.207505</v>
+        <v>0.207507</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>2.217564</v>
+        <v>2.219941</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>0.159252</v>
+        <v>0.159268</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>0.105325</v>
+        <v>0.105431</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>2.357033</v>
+        <v>2.344488</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1574.418896</v>
+        <v>1576.534304</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>382.72089</v>
+        <v>383.130375</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>0.93116</v>
+        <v>0.93241</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1.800242</v>
+        <v>1.777669</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>0.9929210000000001</v>
+        <v>0.9927589999999999</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1.237266</v>
+        <v>1.239947</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>5.314844</v>
+        <v>5.320311</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1.530216</v>
+        <v>1.533274</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>4.365298</v>
+        <v>4.370147</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>5.406213</v>
+        <v>5.405773</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>6.880403</v>
+        <v>6.843938</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>5.878096</v>
+        <v>5.884822</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1.976279</v>
+        <v>1.980199</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1.66996</v>
+        <v>1.667355</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>0.184351</v>
+        <v>0.18452</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1.397373</v>
+        <v>1.373026</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>14.729972</v>
+        <v>14.686765</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>0.5118740000000001</v>
+        <v>0.501676</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1.293093</v>
+        <v>1.292004</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>125.472909</v>
+        <v>125.596805</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>118.546968</v>
+        <v>118.670164</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>189.245509</v>
+        <v>188.981975</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>2.125119</v>
+        <v>2.135518</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>8.638832000000001</v>
+        <v>8.701845</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>12.801279</v>
+        <v>12.722556</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>1.483855</v>
+        <v>1.480491</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>5.590944</v>
+        <v>5.597223</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>0.223117</v>
+        <v>0.22286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>0.980785</v>
+        <v>0.979186</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>5.031448</v>
+        <v>5.000688</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>9.326025</v>
+        <v>9.327446999999999</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>4.340755</v>
+        <v>4.346177</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>3.132323</v>
+        <v>3.114821</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>16.479029</v>
+        <v>16.45892</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>3.656722</v>
+        <v>3.641961</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>31.747174</v>
+        <v>31.824589</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>13.363601</v>
+        <v>13.364751</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>5.861162</v>
+        <v>5.822088</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>17.133133</v>
+        <v>17.128351</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>6.839687</v>
+        <v>0</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>8.705015</v>
+        <v>8.621024</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>5.218592</v>
+        <v>5.224192</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>12.961727</v>
+        <v>12.92347</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>9.088735</v>
+        <v>9.061170000000001</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>9.060510000000001</v>
+        <v>9.028551</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1.409356</v>
+        <v>1.41076</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>7.594211</v>
+        <v>7.590347</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>1.213425</v>
+        <v>1.21184</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>1.647283</v>
+        <v>1.645639</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>4.261696</v>
+        <v>4.266345</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>0.836978</v>
+        <v>0.837597</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>8.891059</v>
+        <v>8.887432</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>19.871453</v>
+        <v>19.79689</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>74.419353</v>
+        <v>74.459807</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>6.719554</v>
+        <v>0</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>7.601755</v>
+        <v>7.602894</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>3.700552</v>
+        <v>3.704556</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>0.180099</v>
+        <v>0.180292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1.190102</v>
+        <v>1.189705</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>12.299533</v>
+        <v>12.24857</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>5.968003</v>
+        <v>5.96765</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>2.148745</v>
+        <v>2.150835</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>6.22741</v>
+        <v>6.207875</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>5.885204</v>
+        <v>5.807732</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>5.773894</v>
+        <v>5.745876</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>2.177646</v>
+        <v>2.161707</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>1.695733</v>
+        <v>1.690623</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>4.91838</v>
+        <v>4.920545</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>1.636247</v>
+        <v>1.638286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>2.855243</v>
+        <v>2.82747</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>1.243891</v>
+        <v>1.242513</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>3.374783</v>
+        <v>3.394423</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>1.504586</v>
+        <v>1.512504</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>2.195743</v>
+        <v>2.191001</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>1.227191</v>
+        <v>1.216824</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>4.346322</v>
+        <v>4.306568</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>4.055911</v>
+        <v>4.015467</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>4.278237</v>
+        <v>4.283547</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>1.41784</v>
+        <v>1.404657</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>0.21193</v>
+        <v>0.212021</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>6.408674</v>
+        <v>6.403898</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>4.492381</v>
+        <v>4.497135</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>1.545026</v>
+        <v>1.545735</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>3.246188</v>
+        <v>3.183093</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>0.8948159999999999</v>
+        <v>0.88413</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>1.878596</v>
+        <v>1.875415</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>0.994227</v>
+        <v>0.986273</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1.30087</v>
+        <v>1.29082</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1.583872</v>
+        <v>1.593433</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>20.107298</v>
+        <v>20.125397</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>1.287578</v>
+        <v>1.288914</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>1.365654</v>
+        <v>1.367102</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>2.930956</v>
+        <v>2.934</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>3.92567</v>
+        <v>3.931083</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>0.135097</v>
+        <v>0.135347</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>20.00221</v>
+        <v>19.992466</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>1.087154</v>
+        <v>1.089603</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>2.71156</v>
+        <v>2.714601</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>4.79066</v>
+        <v>4.764146</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>1.976881</v>
+        <v>1.965567</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>1.973514</v>
+        <v>1.977436</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>2.455542</v>
+        <v>2.43733</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>20.931628</v>
+        <v>20.943665</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>7.693809</v>
+        <v>7.700578</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>7.166629</v>
+        <v>7.173881</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>1.082438</v>
+        <v>1.079163</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>1.434763</v>
+        <v>1.42332</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>0.701936</v>
+        <v>0.70533</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>1.61505</v>
+        <v>1.616768</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>11.382713</v>
+        <v>11.297137</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>1.385275</v>
+        <v>1.388546</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>1.166731</v>
+        <v>1.162644</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>25.994744</v>
+        <v>25.456628</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>2.202406</v>
+        <v>2.168786</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>1.746197</v>
+        <v>1.747974</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>0.816046</v>
+        <v>0.818504</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>1.020256</v>
+        <v>1.018888</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>0.26748</v>
+        <v>0.267765</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>1.56147</v>
+        <v>1.565227</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>1.965139</v>
+        <v>1.965705</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>1.934308</v>
+        <v>1.931968</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>5.714713</v>
+        <v>5.653882</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>2.097242</v>
+        <v>2.092677</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>1.410962</v>
+        <v>1.396462</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>16.261863</v>
+        <v>15.933228</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>15.863149</v>
+        <v>15.905151</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>1.340059</v>
+        <v>1.341443</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>7.738723</v>
+        <v>7.747506</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>9.200832</v>
+        <v>9.212342</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>1.859091</v>
+        <v>1.861391</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>23.91606</v>
+        <v>23.817809</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>1.221281</v>
+        <v>1.219552</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>1.976396</v>
+        <v>1.982417</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>1.500095</v>
+        <v>1.488165</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>5.121594</v>
+        <v>5.06909</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>5.252357</v>
+        <v>5.206657</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>0.999272</v>
+        <v>0.980401</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>2.910547</v>
+        <v>2.849717</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>1.398074</v>
+        <v>0</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>5.467095</v>
+        <v>0</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>5.815557</v>
+        <v>5.847798</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>11.720529</v>
+        <v>11.525336</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>5.381792</v>
+        <v>5.387781</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>6.979205</v>
+        <v>6.988012</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>1.275642</v>
+        <v>1.270321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>1.023918</v>
+        <v>1.021331</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>1.168383</v>
+        <v>1.155729</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>1.421546</v>
+        <v>1.419353</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>1.55055</v>
+        <v>1.545814</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>22.11523</v>
+        <v>22.205202</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>1.638639</v>
+        <v>1.62768</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>11.690379</v>
+        <v>11.818762</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>5.168271</v>
+        <v>5.173093</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>1.71039</v>
+        <v>1.712237</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>1.214276</v>
+        <v>1.207635</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>1.655639</v>
+        <v>1.65551</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>1.312598</v>
+        <v>1.312591</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>4.474864</v>
+        <v>4.478938</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>3.296571</v>
+        <v>3.298687</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>2.939728</v>
+        <v>2.941055</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>0.191225</v>
+        <v>0.191184</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>1.082835</v>
+        <v>1.083895</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>19.156952</v>
+        <v>0</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>3.823186</v>
+        <v>3.816968</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>7.708098</v>
+        <v>7.709003</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>10.813028</v>
+        <v>10.631905</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>22.538447</v>
+        <v>22.498311</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>2.702843</v>
+        <v>2.681677</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>3.604897</v>
+        <v>3.601045</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>4.767281</v>
+        <v>4.767119</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>12.410896</v>
+        <v>12.156205</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>12.293393</v>
+        <v>12.217811</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>0.565842</v>
+        <v>0.565242</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>6.003766</v>
+        <v>6.009894</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>0.151846</v>
+        <v>0.152003</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>3.181899</v>
+        <v>3.136683</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>4.696533</v>
+        <v>4.696504</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>1.74515</v>
+        <v>1.743954</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         </is>
       </c>
       <c r="D426" t="n">
-        <v>12.690233</v>
+        <v>12.648677</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>3.068942</v>
+        <v>3.044968</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         </is>
       </c>
       <c r="D428" t="n">
-        <v>25.275429</v>
+        <v>25.122459</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>23.016883</v>
+        <v>22.955153</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>8.966885</v>
+        <v>8.865109</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>13.171209</v>
+        <v>13.185789</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>0.144591</v>
+        <v>0.144745</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>6.716883</v>
+        <v>6.694868</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>1.285666</v>
+        <v>1.274001</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>3.144634</v>
+        <v>3.129966</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>1.30068</v>
+        <v>1.302163</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         </is>
       </c>
       <c r="D437" t="n">
-        <v>3.275826</v>
+        <v>3.218803</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         </is>
       </c>
       <c r="D438" t="n">
-        <v>2.098247</v>
+        <v>2.098424</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>4.561373</v>
+        <v>4.613301</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>5.595189</v>
+        <v>5.596667</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         </is>
       </c>
       <c r="D441" t="n">
-        <v>1.362857</v>
+        <v>1.335654</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>2.250951</v>
+        <v>2.251128</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>2.814925</v>
+        <v>2.814105</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>1.692389</v>
+        <v>1.694436</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         </is>
       </c>
       <c r="D445" t="n">
-        <v>1.294445</v>
+        <v>1.279611</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="D446" t="n">
-        <v>3.292996</v>
+        <v>3.329608</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         </is>
       </c>
       <c r="D447" t="n">
-        <v>1.496575</v>
+        <v>1.495871</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         </is>
       </c>
       <c r="D448" t="n">
-        <v>1.555081</v>
+        <v>1.551838</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         </is>
       </c>
       <c r="D449" t="n">
-        <v>1.735248</v>
+        <v>1.739387</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         </is>
       </c>
       <c r="D450" t="n">
-        <v>3.979664</v>
+        <v>3.941605</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         </is>
       </c>
       <c r="D451" t="n">
-        <v>1.549668</v>
+        <v>1.530421</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         </is>
       </c>
       <c r="D452" t="n">
-        <v>4.826576</v>
+        <v>4.831835</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         </is>
       </c>
       <c r="D453" t="n">
-        <v>4.389866</v>
+        <v>4.300187</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         </is>
       </c>
       <c r="D454" t="n">
-        <v>1.450343</v>
+        <v>1.451882</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="D455" t="n">
-        <v>1.546977</v>
+        <v>1.548636</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>1.125161</v>
+        <v>1.126645</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         </is>
       </c>
       <c r="D457" t="n">
-        <v>1.704467</v>
+        <v>1.692555</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         </is>
       </c>
       <c r="D458" t="n">
-        <v>10.238163</v>
+        <v>10.234144</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         </is>
       </c>
       <c r="D459" t="n">
-        <v>1.351488</v>
+        <v>1.352907</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>1.678629</v>
+        <v>1.671323</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         </is>
       </c>
       <c r="D461" t="n">
-        <v>2.120303</v>
+        <v>2.122374</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         </is>
       </c>
       <c r="D462" t="n">
-        <v>2.087256</v>
+        <v>2.089675</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         </is>
       </c>
       <c r="D463" t="n">
-        <v>5.338799</v>
+        <v>5.344636</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         </is>
       </c>
       <c r="D464" t="n">
-        <v>2.896794</v>
+        <v>2.899877</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>3.014966</v>
+        <v>3.018579</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         </is>
       </c>
       <c r="D466" t="n">
-        <v>6.104462</v>
+        <v>6.111509</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         </is>
       </c>
       <c r="D467" t="n">
-        <v>2.160216</v>
+        <v>2.162779</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         </is>
       </c>
       <c r="D468" t="n">
-        <v>2.029076</v>
+        <v>2.031339</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         </is>
       </c>
       <c r="D469" t="n">
-        <v>1.237862</v>
+        <v>1.23918</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         </is>
       </c>
       <c r="D470" t="n">
-        <v>2.891147</v>
+        <v>2.894925</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         </is>
       </c>
       <c r="D471" t="n">
-        <v>1.012015</v>
+        <v>1.009461</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         </is>
       </c>
       <c r="D472" t="n">
-        <v>1.496275</v>
+        <v>1.479579</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         </is>
       </c>
       <c r="D473" t="n">
-        <v>1.531235</v>
+        <v>1.539406</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         </is>
       </c>
       <c r="D474" t="n">
-        <v>1.108902</v>
+        <v>1.110091</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>1.052326</v>
+        <v>1.050661</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         </is>
       </c>
       <c r="D476" t="n">
-        <v>20.148889</v>
+        <v>19.817134</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>1.545072</v>
+        <v>1.546437</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>1.660112</v>
+        <v>1.662268</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>31.785141</v>
+        <v>31.669306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="D480" t="n">
-        <v>8.322934</v>
+        <v>8.324707</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="D481" t="n">
-        <v>2.088212</v>
+        <v>2.090602</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         </is>
       </c>
       <c r="D482" t="n">
-        <v>6.080029</v>
+        <v>6.086627</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         </is>
       </c>
       <c r="D483" t="n">
-        <v>6.426158</v>
+        <v>6.432725</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         </is>
       </c>
       <c r="D484" t="n">
-        <v>1.63878</v>
+        <v>1.639114</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         </is>
       </c>
       <c r="D485" t="n">
-        <v>1.735773</v>
+        <v>1.736167</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         </is>
       </c>
       <c r="D486" t="n">
-        <v>1.056318</v>
+        <v>1.055002</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         </is>
       </c>
       <c r="D487" t="n">
-        <v>1.549057</v>
+        <v>1.544778</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         </is>
       </c>
       <c r="D488" t="n">
-        <v>7.188074</v>
+        <v>7.195849</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         </is>
       </c>
       <c r="D489" t="n">
-        <v>5.6598</v>
+        <v>5.653105</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         </is>
       </c>
       <c r="D490" t="n">
-        <v>3.194847</v>
+        <v>3.130578</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         </is>
       </c>
       <c r="D491" t="n">
-        <v>1.639605</v>
+        <v>1.636753</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         </is>
       </c>
       <c r="D492" t="n">
-        <v>1.974896</v>
+        <v>1.976849</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         </is>
       </c>
       <c r="D493" t="n">
-        <v>4.942944</v>
+        <v>4.896618</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         </is>
       </c>
       <c r="D494" t="n">
-        <v>13.715329</v>
+        <v>13.726731</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         </is>
       </c>
       <c r="D495" t="n">
-        <v>5.679378</v>
+        <v>5.597159</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="D496" t="n">
-        <v>1.399804</v>
+        <v>1.391466</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         </is>
       </c>
       <c r="D497" t="n">
-        <v>3.877391</v>
+        <v>3.846405</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         </is>
       </c>
       <c r="D498" t="n">
-        <v>4.598085</v>
+        <v>4.603168</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         </is>
       </c>
       <c r="D499" t="n">
-        <v>1.529312</v>
+        <v>1.530922</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         </is>
       </c>
       <c r="D500" t="n">
-        <v>2.014754</v>
+        <v>1.995073</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         </is>
       </c>
       <c r="D501" t="n">
-        <v>5.733019</v>
+        <v>5.625668</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -17004,7 +17004,7 @@
         </is>
       </c>
       <c r="D502" t="n">
-        <v>2.393887</v>
+        <v>2.390785</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         </is>
       </c>
       <c r="D503" t="n">
-        <v>1.568706</v>
+        <v>1.569655</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         </is>
       </c>
       <c r="D504" t="n">
-        <v>1.329268</v>
+        <v>1.32917</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="D505" t="n">
-        <v>1.725435</v>
+        <v>1.718411</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         </is>
       </c>
       <c r="D506" t="n">
-        <v>3.46398</v>
+        <v>3.463641</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         </is>
       </c>
       <c r="D507" t="n">
-        <v>1.645987</v>
+        <v>1.635976</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         </is>
       </c>
       <c r="D508" t="n">
-        <v>1.301055</v>
+        <v>1.300076</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         </is>
       </c>
       <c r="D509" t="n">
-        <v>1.361884</v>
+        <v>1.356684</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         </is>
       </c>
       <c r="D510" t="n">
-        <v>1.474362</v>
+        <v>1.476078</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         </is>
       </c>
       <c r="D511" t="n">
-        <v>1.290693</v>
+        <v>1.301993</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         </is>
       </c>
       <c r="D513" t="n">
-        <v>1.477426</v>
+        <v>1.475287</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         </is>
       </c>
       <c r="D514" t="n">
-        <v>1.557711</v>
+        <v>1.548362</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         </is>
       </c>
       <c r="D515" t="n">
-        <v>1.380209</v>
+        <v>1.378763</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="D516" t="n">
-        <v>190.540209</v>
+        <v>188.543132</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         </is>
       </c>
       <c r="D517" t="n">
-        <v>0.555719</v>
+        <v>0.5560079999999999</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         </is>
       </c>
       <c r="D518" t="n">
-        <v>0.388771</v>
+        <v>0.388222</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>21.145473</v>
+        <v>21.047335</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         </is>
       </c>
       <c r="D520" t="n">
-        <v>1.118147</v>
+        <v>1.118623</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         </is>
       </c>
       <c r="D521" t="n">
-        <v>9.214416999999999</v>
+        <v>9.134988</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         </is>
       </c>
       <c r="D522" t="n">
-        <v>2.581372</v>
+        <v>2.534503</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         </is>
       </c>
       <c r="D523" t="n">
-        <v>2.324464</v>
+        <v>2.317579</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         </is>
       </c>
       <c r="D524" t="n">
-        <v>0.630206</v>
+        <v>0.633931</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         </is>
       </c>
       <c r="D525" t="n">
-        <v>49.9</v>
+        <v>49.977166</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         </is>
       </c>
       <c r="D526" t="n">
-        <v>0.380674</v>
+        <v>0.381072</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         </is>
       </c>
       <c r="D527" t="n">
-        <v>0.737536</v>
+        <v>0.725486</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         </is>
       </c>
       <c r="D528" t="n">
-        <v>0.217593</v>
+        <v>0.217835</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         </is>
       </c>
       <c r="D529" t="n">
-        <v>46.516279</v>
+        <v>46.614849</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="D530" t="n">
-        <v>4.223429</v>
+        <v>0</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         </is>
       </c>
       <c r="D531" t="n">
-        <v>0.507507</v>
+        <v>0.507964</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         </is>
       </c>
       <c r="D532" t="n">
-        <v>38.009551</v>
+        <v>37.889569</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         </is>
       </c>
       <c r="D533" t="n">
-        <v>6.070703</v>
+        <v>6.070182</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         </is>
       </c>
       <c r="D534" t="n">
-        <v>2.604817</v>
+        <v>2.584446</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         </is>
       </c>
       <c r="D535" t="n">
-        <v>40.342741</v>
+        <v>40.101826</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         </is>
       </c>
       <c r="D536" t="n">
-        <v>1.215826</v>
+        <v>1.217543</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="D537" t="n">
-        <v>0.459097</v>
+        <v>0.459563</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         </is>
       </c>
       <c r="D538" t="n">
-        <v>0.282546</v>
+        <v>0.282194</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         </is>
       </c>
       <c r="D539" t="n">
-        <v>6.414749</v>
+        <v>6.31752</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         </is>
       </c>
       <c r="D540" t="n">
-        <v>2.684585</v>
+        <v>2.661103</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         </is>
       </c>
       <c r="D541" t="n">
-        <v>2.206825</v>
+        <v>2.189949</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="D542" t="n">
-        <v>0.125783</v>
+        <v>0.125587</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         </is>
       </c>
       <c r="D543" t="n">
-        <v>0.115098</v>
+        <v>0.114937</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="D544" t="n">
-        <v>0.060542</v>
+        <v>0.060595</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         </is>
       </c>
       <c r="D545" t="n">
-        <v>0.04979</v>
+        <v>0.049907</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         </is>
       </c>
       <c r="D546" t="n">
-        <v>73.589037</v>
+        <v>73.61566500000001</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         </is>
       </c>
       <c r="D547" t="n">
-        <v>0.720617</v>
+        <v>0.722868</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         </is>
       </c>
       <c r="D548" t="n">
-        <v>1.350052</v>
+        <v>1.349038</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         </is>
       </c>
       <c r="D549" t="n">
-        <v>5.161043</v>
+        <v>0</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         </is>
       </c>
       <c r="D550" t="n">
-        <v>6.076144</v>
+        <v>0</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         </is>
       </c>
       <c r="D551" t="n">
-        <v>64.673044</v>
+        <v>64.79174500000001</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         </is>
       </c>
       <c r="D552" t="n">
-        <v>27.321137</v>
+        <v>27.285575</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         </is>
       </c>
       <c r="D553" t="n">
-        <v>28.788047</v>
+        <v>28.508894</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         </is>
       </c>
       <c r="D554" t="n">
-        <v>1.640007</v>
+        <v>1.641753</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         </is>
       </c>
       <c r="D555" t="n">
-        <v>1.264267</v>
+        <v>1.265635</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         </is>
       </c>
       <c r="D556" t="n">
-        <v>18.442113</v>
+        <v>18.349652</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         </is>
       </c>
       <c r="D557" t="n">
-        <v>0.151084</v>
+        <v>0.150994</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         </is>
       </c>
       <c r="D558" t="n">
-        <v>1.321914</v>
+        <v>1.311888</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         </is>
       </c>
       <c r="D559" t="n">
-        <v>1.342079</v>
+        <v>1.34198</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         </is>
       </c>
       <c r="D560" t="n">
-        <v>1.813469</v>
+        <v>1.8089</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         </is>
       </c>
       <c r="D561" t="n">
-        <v>1.396708</v>
+        <v>1.398008</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         </is>
       </c>
       <c r="D562" t="n">
-        <v>885.369249</v>
+        <v>886.213994</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         </is>
       </c>
       <c r="D563" t="n">
-        <v>1.981275</v>
+        <v>1.983827</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         </is>
       </c>
       <c r="D564" t="n">
-        <v>12.25879</v>
+        <v>0</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         </is>
       </c>
       <c r="D565" t="n">
-        <v>10.316817</v>
+        <v>10.328808</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         </is>
       </c>
       <c r="D566" t="n">
-        <v>20.182428</v>
+        <v>20.190456</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         </is>
       </c>
       <c r="D567" t="n">
-        <v>10.16116</v>
+        <v>10.145977</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         </is>
       </c>
       <c r="D568" t="n">
-        <v>27.101478</v>
+        <v>27.108292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         </is>
       </c>
       <c r="D569" t="n">
-        <v>1.978682</v>
+        <v>1.983949</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         </is>
       </c>
       <c r="D570" t="n">
-        <v>2.344508</v>
+        <v>2.305334</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         </is>
       </c>
       <c r="D571" t="n">
-        <v>0.578139</v>
+        <v>0.568951</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         </is>
       </c>
       <c r="D572" t="n">
-        <v>1.642014</v>
+        <v>1.64084</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         </is>
       </c>
       <c r="D573" t="n">
-        <v>1.354018</v>
+        <v>1.325514</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         </is>
       </c>
       <c r="D574" t="n">
-        <v>1.145372</v>
+        <v>1.146599</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         </is>
       </c>
       <c r="D575" t="n">
-        <v>2.628577</v>
+        <v>2.626797</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         </is>
       </c>
       <c r="D576" t="n">
-        <v>1.978912</v>
+        <v>1.978669</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="D577" t="n">
-        <v>2.35893</v>
+        <v>2.371877</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         </is>
       </c>
       <c r="D578" t="n">
-        <v>0.156125</v>
+        <v>0.156393</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         </is>
       </c>
       <c r="D579" t="n">
-        <v>5.780168</v>
+        <v>5.690418</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="D580" t="n">
-        <v>29.709946</v>
+        <v>29.754937</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         </is>
       </c>
       <c r="D581" t="n">
-        <v>6.525034</v>
+        <v>6.531726</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="D582" t="n">
-        <v>1.787931</v>
+        <v>1.763796</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         </is>
       </c>
       <c r="D583" t="n">
-        <v>1.518105</v>
+        <v>1.521948</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         </is>
       </c>
       <c r="D584" t="n">
-        <v>3.342841</v>
+        <v>3.299164</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         </is>
       </c>
       <c r="D585" t="n">
-        <v>5.082504</v>
+        <v>5.088301</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -19776,20 +19776,20 @@
         </is>
       </c>
       <c r="D586" t="n">
-        <v>0.9505940000000001</v>
+        <v>0.9376679999999999</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>2.42</v>
+        <v>34.08</v>
       </c>
     </row>
     <row r="587">
@@ -19809,20 +19809,20 @@
         </is>
       </c>
       <c r="D587" t="n">
-        <v>0.996287</v>
+        <v>0.994175</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>105.9</v>
+        <v>167.4</v>
       </c>
     </row>
     <row r="588">
@@ -19842,20 +19842,20 @@
         </is>
       </c>
       <c r="D588" t="n">
-        <v>1.008194</v>
+        <v>1.009184</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>167.4</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="589">
@@ -19875,20 +19875,20 @@
         </is>
       </c>
       <c r="D589" t="n">
-        <v>1.007052</v>
+        <v>1.00808</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>142.7</v>
+        <v>70.05</v>
       </c>
     </row>
     <row r="590">
@@ -19908,20 +19908,20 @@
         </is>
       </c>
       <c r="D590" t="n">
-        <v>0.942653</v>
+        <v>0.924366</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>12.47</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="591">
@@ -19941,20 +19941,20 @@
         </is>
       </c>
       <c r="D591" t="n">
-        <v>1.029918</v>
+        <v>1.03103</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>3.75</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="592">
@@ -19974,20 +19974,20 @@
         </is>
       </c>
       <c r="D592" t="n">
-        <v>1.227323</v>
+        <v>1.229267</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>14.43</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="593">
@@ -20007,20 +20007,20 @@
         </is>
       </c>
       <c r="D593" t="n">
-        <v>13.756393</v>
+        <v>13.704364</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>72.09999999999999</v>
+        <v>162.9</v>
       </c>
     </row>
     <row r="594">
@@ -20040,20 +20040,20 @@
         </is>
       </c>
       <c r="D594" t="n">
-        <v>1.103288</v>
+        <v>1.103925</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>38.24</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="595">
@@ -20073,20 +20073,20 @@
         </is>
       </c>
       <c r="D595" t="n">
-        <v>4.827133</v>
+        <v>4.834086</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>16.81</v>
+        <v>20.68</v>
       </c>
     </row>
     <row r="596">
@@ -20106,20 +20106,20 @@
         </is>
       </c>
       <c r="D596" t="n">
-        <v>13.521607</v>
+        <v>13.529873</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>7.86</v>
+        <v>181.6</v>
       </c>
     </row>
     <row r="597">
@@ -20139,20 +20139,20 @@
         </is>
       </c>
       <c r="D597" t="n">
-        <v>13.896296</v>
+        <v>13.806077</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>40.9</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="598">
@@ -20172,20 +20172,20 @@
         </is>
       </c>
       <c r="D598" t="n">
-        <v>1781.002291</v>
+        <v>1758.596071</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>162.9</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="599">
@@ -20205,20 +20205,20 @@
         </is>
       </c>
       <c r="D599" t="n">
-        <v>1.741769</v>
+        <v>1.742684</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>47.78</v>
+        <v>18.65</v>
       </c>
     </row>
     <row r="600">
@@ -20238,20 +20238,20 @@
         </is>
       </c>
       <c r="D600" t="n">
-        <v>0.135031</v>
+        <v>0.135176</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>36.7</v>
+        <v>41.74</v>
       </c>
     </row>
     <row r="601">
@@ -20271,20 +20271,20 @@
         </is>
       </c>
       <c r="D601" t="n">
-        <v>3.826659</v>
+        <v>0</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>70.05</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="602">
@@ -20304,20 +20304,20 @@
         </is>
       </c>
       <c r="D602" t="n">
-        <v>0.42972</v>
+        <v>0.429661</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>17.2</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="603">
@@ -20337,20 +20337,20 @@
         </is>
       </c>
       <c r="D603" t="n">
-        <v>2.04252</v>
+        <v>2.040465</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>41.74</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="604">
@@ -20370,20 +20370,20 @@
         </is>
       </c>
       <c r="D604" t="n">
-        <v>0.909887</v>
+        <v>0.91282</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>17.65</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="605">
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="D605" t="n">
-        <v>0.099494</v>
+        <v>0.099579</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -20436,20 +20436,20 @@
         </is>
       </c>
       <c r="D606" t="n">
-        <v>2.281743</v>
+        <v>2.26418</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>17.11</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="607">
@@ -20469,20 +20469,20 @@
         </is>
       </c>
       <c r="D607" t="n">
-        <v>1.941615</v>
+        <v>1.939184</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>18.65</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="608">
@@ -20502,20 +20502,20 @@
         </is>
       </c>
       <c r="D608" t="n">
-        <v>24.498392</v>
+        <v>24.534669</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>20.68</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="609">
@@ -20535,20 +20535,20 @@
         </is>
       </c>
       <c r="D609" t="n">
-        <v>0.384714</v>
+        <v>0.384889</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>37.7</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="610">
@@ -20568,7 +20568,7 @@
         </is>
       </c>
       <c r="D610" t="n">
-        <v>9.047644999999999</v>
+        <v>9.033566</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -20601,20 +20601,20 @@
         </is>
       </c>
       <c r="D611" t="n">
-        <v>2.749376</v>
+        <v>2.765998</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>181.6</v>
+        <v>142.7</v>
       </c>
     </row>
     <row r="612">
@@ -20634,20 +20634,20 @@
         </is>
       </c>
       <c r="D612" t="n">
-        <v>3.893896</v>
+        <v>3.89066</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>34.08</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="613">
@@ -20667,7 +20667,7 @@
         </is>
       </c>
       <c r="D613" t="n">
-        <v>5.573989</v>
+        <v>5.558157</v>
       </c>
     </row>
     <row r="614">
@@ -20687,7 +20687,7 @@
         </is>
       </c>
       <c r="D614" t="n">
-        <v>0.81841</v>
+        <v>0.803215</v>
       </c>
     </row>
     <row r="615">
@@ -20707,7 +20707,7 @@
         </is>
       </c>
       <c r="D615" t="n">
-        <v>3.658904</v>
+        <v>3.646026</v>
       </c>
     </row>
     <row r="616">
@@ -20727,7 +20727,7 @@
         </is>
       </c>
       <c r="D616" t="n">
-        <v>8.166957999999999</v>
+        <v>8.168438999999999</v>
       </c>
     </row>
     <row r="617">
@@ -20747,7 +20747,7 @@
         </is>
       </c>
       <c r="D617" t="n">
-        <v>5.463008</v>
+        <v>5.437755</v>
       </c>
     </row>
     <row r="618">
@@ -20767,7 +20767,7 @@
         </is>
       </c>
       <c r="D618" t="n">
-        <v>2.372487</v>
+        <v>2.364657</v>
       </c>
     </row>
     <row r="619">
@@ -20787,7 +20787,7 @@
         </is>
       </c>
       <c r="D619" t="n">
-        <v>37.139478</v>
+        <v>37.159909</v>
       </c>
     </row>
     <row r="620">
@@ -20807,7 +20807,7 @@
         </is>
       </c>
       <c r="D620" t="n">
-        <v>5.205223</v>
+        <v>5.148981</v>
       </c>
     </row>
     <row r="621">
@@ -20827,7 +20827,7 @@
         </is>
       </c>
       <c r="D621" t="n">
-        <v>1.586671</v>
+        <v>1.586717</v>
       </c>
     </row>
     <row r="622">
@@ -20847,7 +20847,7 @@
         </is>
       </c>
       <c r="D622" t="n">
-        <v>7.408109</v>
+        <v>7.376133</v>
       </c>
     </row>
     <row r="623">
@@ -20867,7 +20867,7 @@
         </is>
       </c>
       <c r="D623" t="n">
-        <v>0.162351</v>
+        <v>0.162593</v>
       </c>
     </row>
     <row r="624">
@@ -20887,7 +20887,7 @@
         </is>
       </c>
       <c r="D624" t="n">
-        <v>0.895625</v>
+        <v>0.891055</v>
       </c>
     </row>
     <row r="625">
@@ -20907,7 +20907,7 @@
         </is>
       </c>
       <c r="D625" t="n">
-        <v>2.796855</v>
+        <v>2.799163</v>
       </c>
     </row>
     <row r="626">
@@ -20927,7 +20927,7 @@
         </is>
       </c>
       <c r="D626" t="n">
-        <v>1.259536</v>
+        <v>1.262614</v>
       </c>
     </row>
     <row r="627">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="D627" t="n">
-        <v>4.788484</v>
+        <v>4.756612</v>
       </c>
     </row>
     <row r="628">
@@ -20967,7 +20967,7 @@
         </is>
       </c>
       <c r="D628" t="n">
-        <v>12.631623</v>
+        <v>12.521267</v>
       </c>
     </row>
     <row r="629">
@@ -20987,7 +20987,7 @@
         </is>
       </c>
       <c r="D629" t="n">
-        <v>10.887886</v>
+        <v>10.955059</v>
       </c>
     </row>
     <row r="630">
@@ -21007,7 +21007,7 @@
         </is>
       </c>
       <c r="D630" t="n">
-        <v>647.817507</v>
+        <v>648.3061269999999</v>
       </c>
     </row>
     <row r="631">
@@ -21027,7 +21027,7 @@
         </is>
       </c>
       <c r="D631" t="n">
-        <v>2.12137</v>
+        <v>2.124484</v>
       </c>
     </row>
     <row r="632">
@@ -21047,7 +21047,7 @@
         </is>
       </c>
       <c r="D632" t="n">
-        <v>4.794206</v>
+        <v>4.799443</v>
       </c>
     </row>
     <row r="633">
@@ -21067,7 +21067,7 @@
         </is>
       </c>
       <c r="D633" t="n">
-        <v>1.701563</v>
+        <v>1.697569</v>
       </c>
     </row>
     <row r="634">
@@ -21087,7 +21087,7 @@
         </is>
       </c>
       <c r="D634" t="n">
-        <v>3.754617</v>
+        <v>3.735902</v>
       </c>
     </row>
     <row r="635">
@@ -21107,7 +21107,7 @@
         </is>
       </c>
       <c r="D635" t="n">
-        <v>6.982867</v>
+        <v>6.990803</v>
       </c>
     </row>
     <row r="636">
@@ -21127,7 +21127,7 @@
         </is>
       </c>
       <c r="D636" t="n">
-        <v>12.093704</v>
+        <v>12.156584</v>
       </c>
     </row>
     <row r="637">
@@ -21147,7 +21147,7 @@
         </is>
       </c>
       <c r="D637" t="n">
-        <v>6.988164</v>
+        <v>6.920333</v>
       </c>
     </row>
     <row r="638">
@@ -21167,7 +21167,7 @@
         </is>
       </c>
       <c r="D638" t="n">
-        <v>1.374824</v>
+        <v>1.373756</v>
       </c>
     </row>
     <row r="639">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="D639" t="n">
-        <v>14.260898</v>
+        <v>14.285907</v>
       </c>
     </row>
     <row r="640">
@@ -21207,7 +21207,7 @@
         </is>
       </c>
       <c r="D640" t="n">
-        <v>10.852397</v>
+        <v>10.807724</v>
       </c>
     </row>
     <row r="641">
@@ -21227,7 +21227,7 @@
         </is>
       </c>
       <c r="D641" t="n">
-        <v>11.468232</v>
+        <v>11.406442</v>
       </c>
     </row>
     <row r="642">
@@ -21247,7 +21247,7 @@
         </is>
       </c>
       <c r="D642" t="n">
-        <v>6.308955</v>
+        <v>6.203812</v>
       </c>
     </row>
     <row r="643">
@@ -21267,7 +21267,7 @@
         </is>
       </c>
       <c r="D643" t="n">
-        <v>18.193192</v>
+        <v>18.230839</v>
       </c>
     </row>
     <row r="644">
@@ -21287,7 +21287,7 @@
         </is>
       </c>
       <c r="D644" t="n">
-        <v>31.682463</v>
+        <v>31.51946</v>
       </c>
     </row>
     <row r="645">
@@ -21307,7 +21307,7 @@
         </is>
       </c>
       <c r="D645" t="n">
-        <v>22.152035</v>
+        <v>22.158015</v>
       </c>
     </row>
     <row r="646">
@@ -21327,7 +21327,7 @@
         </is>
       </c>
       <c r="D646" t="n">
-        <v>9.964447</v>
+        <v>9.975789000000001</v>
       </c>
     </row>
     <row r="647">
@@ -21347,7 +21347,7 @@
         </is>
       </c>
       <c r="D647" t="n">
-        <v>49.752794</v>
+        <v>49.678496</v>
       </c>
     </row>
     <row r="648">
@@ -21367,7 +21367,7 @@
         </is>
       </c>
       <c r="D648" t="n">
-        <v>4.210325</v>
+        <v>4.191552</v>
       </c>
     </row>
     <row r="649">
@@ -21387,7 +21387,7 @@
         </is>
       </c>
       <c r="D649" t="n">
-        <v>1.168719</v>
+        <v>1.167923</v>
       </c>
     </row>
   </sheetData>

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>366.5</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2585</v>
+        <v>2592.5</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>93.75</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>133.1</v>
+        <v>132.5</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>187.5</v>
+        <v>187.2</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>231</v>
+        <v>232.4</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>385.75</v>
+        <v>383.75</v>
       </c>
     </row>
     <row r="10">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.175653</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>302.5</v>
+        <v>301.75</v>
       </c>
     </row>
     <row r="11">
@@ -838,7 +838,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2915000</v>
+        <v>14.05</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>14.11</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>68.90000000000001</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>170.7</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>115.6</v>
+        <v>115.8</v>
       </c>
     </row>
     <row r="17">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>45.96</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>32.52</v>
+        <v>32.22</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>87.55</v>
+        <v>87.34999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>36.24</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>293.75</v>
+        <v>292.75</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>39.08</v>
+        <v>38.98</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>108.7</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>62.85</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="26">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>93.45</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>59.7</v>
+        <v>59.35</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1558</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="29">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>6.60776</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>228.1</v>
+        <v>228.7</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>490</v>
+        <v>488.5</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>97.7</v>
+        <v>97.05</v>
       </c>
     </row>
     <row r="32">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>15.329052</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>291</v>
+        <v>289.75</v>
       </c>
     </row>
     <row r="33">
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>17.817226</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>44.06</v>
+        <v>43.36</v>
       </c>
     </row>
     <row r="34">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3.680804</v>
+        <v>3.680715</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>44.42</v>
+        <v>44.32</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>13</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="36">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>104.5</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="38">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>654.5</v>
+        <v>653.5</v>
       </c>
     </row>
     <row r="39">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>20.6</v>
+        <v>20.66</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>676.5</v>
+        <v>672.5</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>10987.5</v>
+        <v>11360</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>20.84</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="45">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>99</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>77.40000000000001</v>
+        <v>77.45</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>267.75</v>
+        <v>268.5</v>
       </c>
     </row>
     <row r="49">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>111.6</v>
+        <v>110.9</v>
       </c>
     </row>
     <row r="51">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>625.5</v>
+        <v>622</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>440.75</v>
+        <v>440</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>32</v>
+        <v>31.86</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>170.2</v>
+        <v>169.5</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>17.68</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>32.86</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="58">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>116.1</v>
+        <v>115.8</v>
       </c>
     </row>
     <row r="59">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>226</v>
+        <v>217.9</v>
       </c>
     </row>
     <row r="60">
@@ -2418,7 +2418,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1.530026</v>
+        <v>1.529063</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.65</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6.09</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="62">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>19.51</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>103.2</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>109.4</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>257.75</v>
+        <v>256.25</v>
       </c>
     </row>
     <row r="66">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>33.04</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>199.7</v>
+        <v>201.3</v>
       </c>
     </row>
     <row r="68">
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1.273737</v>
+        <v>1.273736</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.6</v>
+        <v>32.54</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>182.4</v>
+        <v>182.1</v>
       </c>
     </row>
     <row r="70">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>95.95</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="73">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>82.34999999999999</v>
+        <v>82.15000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>28</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>40.48</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>34.18</v>
+        <v>33.84</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1987</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>170</v>
+        <v>171.5</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>36.06</v>
+        <v>35.96</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>138.4</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>218.6</v>
+        <v>217.3</v>
       </c>
     </row>
     <row r="83">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1681</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="84">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KRDMD</t>
+          <t>KRDMA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>39.06</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="85">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KRDMB</t>
+          <t>KRDMD</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>115</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="86">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KRDMA</t>
+          <t>KRDMB</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>41.22</v>
+        <v>114.6</v>
       </c>
     </row>
     <row r="87">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.42</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="88">
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5.066379</v>
+        <v>5.064265</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.32</v>
+        <v>19.39</v>
       </c>
     </row>
     <row r="89">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>224.6</v>
+        <v>224.8</v>
       </c>
     </row>
     <row r="90">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1235</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>49.38</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>247.6</v>
+        <v>247.5</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>445.5</v>
+        <v>445.75</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>107.2</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="95">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>6.516193</v>
+        <v>6.512748</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>101.6</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="96">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>133.8</v>
+        <v>133.5</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>610.5</v>
+        <v>609</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>10.97</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="99">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>66.75</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="100">
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>13.83428</v>
+        <v>13.804557</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>347.5</v>
+        <v>354.25</v>
       </c>
     </row>
     <row r="101">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>108.5</v>
+        <v>106.9</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>216.9</v>
+        <v>218.5</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>112.6</v>
+        <v>113.5</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>203.5</v>
+        <v>204.6</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>85.55</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1644</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>22.06</v>
+        <v>21.94</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>36.24</v>
+        <v>36.32</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>106.6</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>351.25</v>
+        <v>351</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>8.109999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>142.1</v>
+        <v>142.3</v>
       </c>
     </row>
     <row r="113">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>323.75</v>
+        <v>324.5</v>
       </c>
     </row>
     <row r="114">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>48.78</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>13.63</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>42.62</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="117">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="118">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>13.33</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="119">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>5.84</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="120">
@@ -4398,7 +4398,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1.350797</v>
+        <v>1.350795</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="121">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>197.6</v>
+        <v>196.5</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>11.67</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>215</v>
+        <v>214.4</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>26.28</v>
+        <v>26.08</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>308</v>
+        <v>307.5</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>13.39</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="127">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>15.6</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="128">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>10.53</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>13.43</v>
+        <v>13.45</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>48.66</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="131">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>15.04</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="133">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>53</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="135">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>91.45</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>28.28</v>
+        <v>28.16</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>233.1</v>
+        <v>231.4</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>13847.5</v>
+        <v>13785</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>70.75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="141">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>320.75</v>
+        <v>317.5</v>
       </c>
     </row>
     <row r="142">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>145</v>
+        <v>144.9</v>
       </c>
     </row>
     <row r="144">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>58</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>47.2</v>
+        <v>46.58</v>
       </c>
     </row>
     <row r="147">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>6.23</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="148">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>47.68</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>86.95</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="150">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>57.65</v>
+        <v>57.75</v>
       </c>
     </row>
     <row r="151">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="152">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>18.07</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="153">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.08</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="154">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>60.8</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>84.09999999999999</v>
+        <v>83.05</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>11.81</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="157">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="158">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>35.12</v>
+        <v>35.26</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>14.19</v>
+        <v>14.17</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>81.84999999999999</v>
+        <v>81.75</v>
       </c>
     </row>
     <row r="161">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>37.68</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8.15</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="163">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>152</v>
+        <v>152.6</v>
       </c>
     </row>
     <row r="164">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>174.2</v>
+        <v>175.4</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>20.26</v>
+        <v>20.24</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>6.87</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>39.02</v>
+        <v>39.06</v>
       </c>
     </row>
     <row r="168">
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>10.447986</v>
+        <v>10.401183</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>58.8</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>20.62</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>4905</v>
+        <v>4892.5</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>25.76</v>
+        <v>25.62</v>
       </c>
     </row>
     <row r="173">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>69.25</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>3680</v>
+        <v>3692.5</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5650</v>
+        <v>5647.5</v>
       </c>
     </row>
     <row r="176">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
+        <v>7.416827</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>136</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1513</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>15.86</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>82.7</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="180">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>11.08</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="181">
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>4.43419</v>
+        <v>4.436246</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>642</v>
+        <v>627.5</v>
       </c>
     </row>
     <row r="182">
@@ -6444,7 +6444,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>4.702206</v>
+        <v>4.692303</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>96.5</v>
+        <v>95.84999999999999</v>
       </c>
     </row>
     <row r="183">
@@ -6477,7 +6477,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>4.712697</v>
+        <v>4.713458</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>14.12</v>
+        <v>14.66</v>
       </c>
     </row>
     <row r="184">
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>5.092525</v>
+        <v>5.088501</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>23.26</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="185">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>20.42</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="186">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>61.9</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>32.24</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>147.5</v>
+        <v>146.7</v>
       </c>
     </row>
     <row r="189">
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>9.67</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="190">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>40.04</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>252.25</v>
+        <v>254.5</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>13.42</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="193">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>28.5</v>
+        <v>28.38</v>
       </c>
     </row>
     <row r="194">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>13.95</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="196">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="199">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>26.34</v>
+        <v>26.36</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.52</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>30.74</v>
+        <v>30.62</v>
       </c>
     </row>
     <row r="202">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="203">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>19.34</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>84.7</v>
+        <v>84.34999999999999</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>19.49</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>45.12</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="207">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>144.4</v>
+        <v>144.2</v>
       </c>
     </row>
     <row r="208">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>116.4</v>
+        <v>117</v>
       </c>
     </row>
     <row r="209">
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0</v>
+        <v>11.952216</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>4.47</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>65.40000000000001</v>
+        <v>65.65000000000001</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>42.96</v>
+        <v>42.92</v>
       </c>
     </row>
     <row r="212">
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0</v>
+        <v>5.344285</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>6</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="213">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>79</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="214">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>41.04</v>
+        <v>41.98</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>32.04</v>
+        <v>32.18</v>
       </c>
     </row>
     <row r="216">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>12.52</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>72.95</v>
+        <v>73.05</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>623</v>
+        <v>638.5</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>11.21</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="221">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>14.59</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="222">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>40.42</v>
+        <v>40.26</v>
       </c>
     </row>
     <row r="223">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>54.15</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>7.48</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="225">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>134.8</v>
+        <v>133.7</v>
       </c>
     </row>
     <row r="227">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>16.67</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="229">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>8.85</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="230">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.09</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>39.68</v>
+        <v>39.46</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>17.28</v>
+        <v>17.31</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="234">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>12.23</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>42.28</v>
+        <v>41.64</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>107.5</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>61.3</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="239">
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="H239" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="240">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="241">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>39.24</v>
+        <v>39.16</v>
       </c>
     </row>
     <row r="242">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>31.32</v>
+        <v>31.34</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>89.15000000000001</v>
+        <v>89.05</v>
       </c>
     </row>
     <row r="244">
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>2.344488</v>
+        <v>2.344484</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>21.14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="245">
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="246">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.23</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="247">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>85.59999999999999</v>
+        <v>85.95</v>
       </c>
     </row>
     <row r="248">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>6.25</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="249">
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>0.9927589999999999</v>
+        <v>0.992144</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="250">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>409</v>
+        <v>411.25</v>
       </c>
     </row>
     <row r="251">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>35.82</v>
+        <v>35.66</v>
       </c>
     </row>
     <row r="252">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>260.75</v>
+        <v>260</v>
       </c>
     </row>
     <row r="253">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>21.4</v>
+        <v>20.38</v>
       </c>
     </row>
     <row r="254">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>24</v>
+        <v>23.92</v>
       </c>
     </row>
     <row r="255">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>1147</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>18.83</v>
+        <v>18.58</v>
       </c>
     </row>
     <row r="257">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="258">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>71.8</v>
+        <v>71.05</v>
       </c>
     </row>
     <row r="259">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>52.55</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="260">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>12.82</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="261">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.34</v>
+        <v>28.94</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>125.7</v>
+        <v>126.1</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>11.7</v>
+        <v>11.87</v>
       </c>
     </row>
     <row r="265">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>17.76</v>
+        <v>17.83</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>17.89</v>
+        <v>18.01</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>13.59</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="269">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>5.96</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="270">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>59.7</v>
+        <v>58.95</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>24.68</v>
+        <v>24.64</v>
       </c>
     </row>
     <row r="272">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>8.23</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="273">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>12.57</v>
+        <v>12.44</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>7.71</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>40.1</v>
+        <v>40.18</v>
       </c>
     </row>
     <row r="276">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>32.78</v>
+        <v>32.76</v>
       </c>
     </row>
     <row r="277">
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="H277" t="n">
-        <v>14.46</v>
+        <v>15.41</v>
       </c>
     </row>
     <row r="278">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.28</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>105.2</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="280">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="281">
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>6.37</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="282">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>25.36</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="284">
@@ -9810,7 +9810,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>0</v>
+        <v>6.836331</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>24.46</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="285">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>22.52</v>
+        <v>22.56</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>6.19</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="287">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>6.23</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="289">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>20.48</v>
+        <v>20.58</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>727</v>
+        <v>724.5</v>
       </c>
     </row>
     <row r="292">
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>11.56</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="293">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>43.88</v>
+        <v>44.94</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>53.9</v>
+        <v>53.95</v>
       </c>
     </row>
     <row r="295">
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>988</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="296">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>44.32</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>23.66</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="299">
@@ -10305,7 +10305,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>0</v>
+        <v>6.737157</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>215.9</v>
+        <v>212.3</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>9.65</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="301">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>7.21</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="303">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>80.45</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="305">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>5.96765</v>
+        <v>5.947925</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>17.49</v>
+        <v>18.56</v>
       </c>
     </row>
     <row r="307">
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="308">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>9.859999999999999</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="310">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>117.5</v>
+        <v>117</v>
       </c>
     </row>
     <row r="311">
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="312">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>7.14</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="313">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>6.42</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>39.54</v>
+        <v>40.86</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>15.88</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>15.37</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>11.06</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>91.95</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="320">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>5.98</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="321">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>428</v>
+        <v>432.25</v>
       </c>
     </row>
     <row r="322">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>6.22</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>246</v>
+        <v>240.2</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>12.15</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>7.9</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>13.72</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>325.5</v>
+        <v>323.25</v>
       </c>
     </row>
     <row r="330">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>100.9</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>32.4</v>
+        <v>32.38</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>14.53</v>
+        <v>14.62</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>16.88</v>
+        <v>16.76</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>61.85</v>
+        <v>62</v>
       </c>
     </row>
     <row r="336">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="337">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.77</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="338">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>142.9</v>
+        <v>143.7</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>14.05</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="340">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>22.42</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>27.04</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>29.36</v>
+        <v>29.24</v>
       </c>
     </row>
     <row r="344">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="345">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>17.53</v>
+        <v>17.55</v>
       </c>
     </row>
     <row r="346">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>10.69</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="347">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>11.99</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.34</v>
+        <v>25.18</v>
       </c>
     </row>
     <row r="349">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="H349" t="n">
-        <v>12.66</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="350">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>5.42</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="351">
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="H351" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="352">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>260.75</v>
+        <v>261.75</v>
       </c>
     </row>
     <row r="355">
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="H355" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="356">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>38.1</v>
+        <v>37.92</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>12.26</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="358">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>6.6</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>150</v>
+        <v>148.6</v>
       </c>
     </row>
     <row r="363">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>23.42</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="364">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>18.69</v>
+        <v>18.71</v>
       </c>
     </row>
     <row r="365">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="H365" t="n">
-        <v>58.3</v>
+        <v>58.35</v>
       </c>
     </row>
     <row r="366">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>21.02</v>
+        <v>20.56</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>120.2</v>
+        <v>119.2</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>15.02</v>
+        <v>15.01</v>
       </c>
     </row>
     <row r="369">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>23.14</v>
+        <v>22.96</v>
       </c>
     </row>
     <row r="370">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>7.23</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>6.69</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="372">
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>15.905151</v>
+        <v>15.904746</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>15.81</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="373">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>299.5</v>
+        <v>300</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>64.75</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>65</v>
+        <v>64.55</v>
       </c>
     </row>
     <row r="377">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>90.55</v>
+        <v>90.05</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>63.95</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>39.92</v>
+        <v>39.82</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>16.73</v>
+        <v>16.82</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>19.83</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>101</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="384">
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="H384" t="n">
-        <v>52.3</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="385">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>109</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="386">
@@ -13176,7 +13176,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>0</v>
+        <v>1.399667</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="H386" t="n">
-        <v>6.6</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="387">
@@ -13209,7 +13209,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>0</v>
+        <v>5.460848</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>4.85</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="388">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>5.57</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="389">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>34.3</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="390">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="H390" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="391">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>12.92</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="392">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>9.32</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="393">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="395">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.22</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="396">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="397">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>14.28</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="398">
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="H398" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="399">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>9.800000000000001</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>147.4</v>
+        <v>147.2</v>
       </c>
     </row>
     <row r="401">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="H401" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="402">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>12.07</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="403">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>183.7</v>
+        <v>182.2</v>
       </c>
     </row>
     <row r="404">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="405">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>29.96</v>
+        <v>29.98</v>
       </c>
     </row>
     <row r="406">
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>4.7</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="407">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>90.09999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>27.86</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="409">
@@ -13968,7 +13968,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>0</v>
+        <v>19.16876</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>3.816968</v>
+        <v>3.817787</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>26.1</v>
+        <v>26.06</v>
       </c>
     </row>
     <row r="412">
@@ -14034,7 +14034,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>7.709202</v>
+        <v>7.698754</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>10.631905</v>
+        <v>10.629152</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>19.97</v>
+        <v>19.96</v>
       </c>
     </row>
     <row r="414">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>46.56</v>
+        <v>46.64</v>
       </c>
     </row>
     <row r="416">
@@ -14166,7 +14166,7 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>3.601045</v>
+        <v>3.536201</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.23</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="417">
@@ -14199,7 +14199,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>4.767119</v>
+        <v>4.754033</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>45.4</v>
+        <v>47.26</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>8.449999999999999</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="420">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>28.3</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="421">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>39.64</v>
+        <v>38.98</v>
       </c>
     </row>
     <row r="422">
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="H422" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="423">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>15.34</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="424">
@@ -14430,7 +14430,7 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>4.696504</v>
+        <v>4.701613</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>46.4</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="425">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>21.84</v>
+        <v>21.76</v>
       </c>
     </row>
     <row r="426">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.14</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>21.24</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="429">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>8.93</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="430">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>11.26</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="431">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>313.5</v>
+        <v>311.75</v>
       </c>
     </row>
     <row r="433">
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>6.658232</v>
+        <v>6.658168</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.59</v>
+        <v>14.58</v>
       </c>
     </row>
     <row r="434">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>7.58</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="435">
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="436">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>10.04</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="437">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>7.36</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="438">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>12.85</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="439">
@@ -14925,7 +14925,7 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>4.613301</v>
+        <v>4.613261</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>10.53</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="440">
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="441">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>6.07</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="442">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="443">
@@ -15057,7 +15057,7 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>2.814105</v>
+        <v>2.807704</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>99.45</v>
+        <v>99.34999999999999</v>
       </c>
     </row>
     <row r="444">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>40.16</v>
+        <v>40.04</v>
       </c>
     </row>
     <row r="445">
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="H445" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="446">
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="D446" t="n">
-        <v>3.329608</v>
+        <v>3.329603</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>27.18</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="447">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>27.5</v>
+        <v>27.44</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>27.22</v>
+        <v>27.14</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>1521</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="450">
@@ -15301,7 +15301,7 @@
         </is>
       </c>
       <c r="H450" t="n">
-        <v>118.3</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="451">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>179.4</v>
+        <v>181.3</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>13.52</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="454">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>22.24</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>17.34</v>
+        <v>17.37</v>
       </c>
     </row>
     <row r="457">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>19.68</v>
+        <v>19.94</v>
       </c>
     </row>
     <row r="458">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="H458" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="459">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>12.65</v>
+        <v>12.89</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>37.7</v>
+        <v>37.76</v>
       </c>
     </row>
     <row r="461">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>81.5</v>
+        <v>81.45</v>
       </c>
     </row>
     <row r="462">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="464">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>31.8</v>
+        <v>31.64</v>
       </c>
     </row>
     <row r="465">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="H465" t="n">
-        <v>11.03</v>
+        <v>11</v>
       </c>
     </row>
     <row r="466">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="468">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>24.9</v>
+        <v>24.92</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>35.58</v>
+        <v>35.52</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>31.28</v>
+        <v>31.94</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>42.8</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="472">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="473">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>12.72</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="474">
@@ -16113,7 +16113,7 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>1.050661</v>
+        <v>1.050635</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="476">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>14.14</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="477">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>26.96</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>8.17</v>
+        <v>8.210000000000001</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.41</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="481">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>13.72</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="482">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>82.25</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="484">
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="485">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>96.45</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="487">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>17.84</v>
+        <v>17.77</v>
       </c>
     </row>
     <row r="488">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>10.31</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="489">
@@ -16588,7 +16588,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="490">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>26.56</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="491">
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="H491" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="492">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>34.2</v>
+        <v>34.14</v>
       </c>
     </row>
     <row r="494">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>49.76</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="495">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>10.63</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="497">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="499">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="501">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>40.14</v>
+        <v>39.82</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.54</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="503">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="H504" t="n">
-        <v>8.65</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="505">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>8.460000000000001</v>
+        <v>8.539999999999999</v>
       </c>
     </row>
     <row r="506">
@@ -17248,7 +17248,7 @@
         </is>
       </c>
       <c r="H509" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="510">
@@ -17281,7 +17281,7 @@
         </is>
       </c>
       <c r="H510" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="511">
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="512">
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="H512" t="n">
-        <v>34.24</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="513">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="H513" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="514">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="516">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>16.19</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>14.36</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>218.6</v>
+        <v>215.1</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>144.5</v>
+        <v>144.2</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>12.77</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>73.05</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="523">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>4.66</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="524">
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>7.62</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="526">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>13.81</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="527">
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="H528" t="n">
-        <v>16.41</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="529">
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="H529" t="n">
-        <v>13.96</v>
+        <v>14</v>
       </c>
     </row>
     <row r="530">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="D530" t="n">
-        <v>0</v>
+        <v>4.223164</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         </is>
       </c>
       <c r="H530" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="531">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="532">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.22</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="534">
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="H534" t="n">
-        <v>4.35</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="535">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>6.08</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="536">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>22.9</v>
+        <v>22.74</v>
       </c>
     </row>
     <row r="537">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.18</v>
+        <v>25.34</v>
       </c>
     </row>
     <row r="538">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>156</v>
+        <v>155.7</v>
       </c>
     </row>
     <row r="539">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>61.85</v>
+        <v>61.75</v>
       </c>
     </row>
     <row r="540">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>25.48</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="542">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>14.9</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="544">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>33.16</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="546">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>16.04</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="547">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>27.82</v>
+        <v>27.76</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>52.5</v>
+        <v>52.05</v>
       </c>
     </row>
     <row r="549">
@@ -18555,7 +18555,7 @@
         </is>
       </c>
       <c r="D549" t="n">
-        <v>0</v>
+        <v>5.15619</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="H549" t="n">
-        <v>9.99</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="550">
@@ -18588,7 +18588,7 @@
         </is>
       </c>
       <c r="D550" t="n">
-        <v>0</v>
+        <v>6.071366</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         </is>
       </c>
       <c r="H551" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="552">
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="H553" t="n">
-        <v>46</v>
+        <v>47.36</v>
       </c>
     </row>
     <row r="554">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="H558" t="n">
-        <v>119.3</v>
+        <v>118.7</v>
       </c>
     </row>
     <row r="559">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>28.48</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="562">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="H562" t="n">
-        <v>23.88</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="563">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="H563" t="n">
-        <v>26.58</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="564">
@@ -19050,7 +19050,7 @@
         </is>
       </c>
       <c r="D564" t="n">
-        <v>0</v>
+        <v>12.184879</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>6.51</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="569">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="H569" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="570">
@@ -19261,7 +19261,7 @@
         </is>
       </c>
       <c r="H570" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="571">
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>8.529999999999999</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="572">
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>4.85</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="573">
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="H573" t="n">
-        <v>18.43</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="574">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>26.58</v>
+        <v>26.42</v>
       </c>
     </row>
     <row r="575">
@@ -19459,7 +19459,7 @@
         </is>
       </c>
       <c r="H576" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="577">
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="H577" t="n">
-        <v>5.94</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="578">
@@ -19558,7 +19558,7 @@
         </is>
       </c>
       <c r="H579" t="n">
-        <v>12.23</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="580">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.289999999999999</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="581">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.64</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="582">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H582" t="n">
-        <v>10.11</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="583">
@@ -19690,7 +19690,7 @@
         </is>
       </c>
       <c r="H583" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="584">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>3.79</v>
+        <v>105.1</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>105.6</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>165.1</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>33.74</v>
+        <v>16.64</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>17.81</v>
+        <v>183.9</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>46.86</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>66.15000000000001</v>
+        <v>162.7</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>17.34</v>
+        <v>68.05</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>2.44</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>21.06</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>12.58</v>
+        <v>17.28</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>18.88</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>38.36</v>
+        <v>38.04</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>70.09999999999999</v>
+        <v>14.42</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>128.5</v>
+        <v>72.67</v>
       </c>
     </row>
     <row r="601">
@@ -20271,20 +20271,20 @@
         </is>
       </c>
       <c r="D601" t="n">
-        <v>0</v>
+        <v>3.829855</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>17.18</v>
+        <v>40.62</v>
       </c>
     </row>
     <row r="602">
@@ -20317,7 +20317,7 @@
         </is>
       </c>
       <c r="H602" t="n">
-        <v>37.12</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>16.48</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>41.14</v>
+        <v>47.46</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>7.91</v>
+        <v>33.74</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>20.28</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>182.6</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>72.86</v>
+        <v>21.44</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>166.3</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>41.8</v>
+        <v>17.19</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>14.45</v>
+        <v>164.3</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>38.04</v>
+        <v>18.85</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>374.25</v>
+        <v>377.25</v>
       </c>
     </row>
     <row r="3">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>94.7</v>
+        <v>94.95</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>136.7</v>
+        <v>137.7</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>191.2</v>
+        <v>191.1</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>231</v>
+        <v>231.7</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>388.25</v>
+        <v>387.5</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>308.25</v>
+        <v>308.75</v>
       </c>
     </row>
     <row r="11">
@@ -805,7 +805,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ISBTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>420000</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="12">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>14.52</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISBTR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2915000</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>71.75</v>
+        <v>71.65000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>175.5</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>114.9</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="17">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>47.28</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>33.18</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>88.65000000000001</v>
+        <v>88.84999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>295</v>
+        <v>293.5</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>39.6</v>
+        <v>39.64</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>110.4</v>
+        <v>111.1</v>
       </c>
     </row>
     <row r="24">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>80.45</v>
+        <v>82.25</v>
       </c>
     </row>
     <row r="25">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>64.09999999999999</v>
+        <v>64.25</v>
       </c>
     </row>
     <row r="26">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>95.84999999999999</v>
+        <v>95.65000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>60</v>
+        <v>60.25</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1565</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>231.6</v>
+        <v>226.9</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>98.05</v>
+        <v>97.55</v>
       </c>
     </row>
     <row r="32">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>297</v>
+        <v>296.5</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>44</v>
+        <v>44.16</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>45.04</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>12.99</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="36">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>105.3</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="38">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>652.5</v>
+        <v>652</v>
       </c>
     </row>
     <row r="39">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>20.94</v>
+        <v>20.92</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>674</v>
+        <v>677.5</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>11435</v>
+        <v>11407.5</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1524</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>21.06</v>
+        <v>21.18</v>
       </c>
     </row>
     <row r="45">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>98.90000000000001</v>
+        <v>98.84999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>78.09999999999999</v>
+        <v>78.15000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>276</v>
+        <v>276.5</v>
       </c>
     </row>
     <row r="49">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>110.6</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="51">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>31.84</v>
+        <v>31.92</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>173.5</v>
+        <v>173.3</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>17.27</v>
+        <v>17.28</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>33.28</v>
+        <v>33.26</v>
       </c>
     </row>
     <row r="58">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>215.8</v>
+        <v>213</v>
       </c>
     </row>
     <row r="60">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.609999999999999</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="61">
@@ -2455,16 +2455,16 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
+          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6.08</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="62">
@@ -2488,16 +2488,16 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>20.08</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>104.3</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>110</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>258.25</v>
+        <v>257</v>
       </c>
     </row>
     <row r="66">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>32.88</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>202.2</v>
+        <v>203</v>
       </c>
     </row>
     <row r="68">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.74</v>
+        <v>32.54</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>183.7</v>
+        <v>183.4</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>13</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="71">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>94.65000000000001</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1298</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="73">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>124.1</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="74">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>82.84999999999999</v>
+        <v>83.05</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>28.2</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>40.94</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>34.14</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1998</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>172</v>
+        <v>172.2</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>36.4</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>137.8</v>
+        <v>141.4</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>218</v>
+        <v>217.1</v>
       </c>
     </row>
     <row r="83">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1680</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="84">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>41.24</v>
+        <v>41.26</v>
       </c>
     </row>
     <row r="85">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>39.6</v>
+        <v>40.66</v>
       </c>
     </row>
     <row r="86">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.36</v>
+        <v>25.16</v>
       </c>
     </row>
     <row r="88">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.23</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="89">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>223.5</v>
+        <v>223.4</v>
       </c>
     </row>
     <row r="90">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1225</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>49.6</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>246.4</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>447.75</v>
+        <v>449.25</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>109.6</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="95">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>134.6</v>
+        <v>134.9</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>608.5</v>
+        <v>609.5</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>11.04</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="99">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>64.65000000000001</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>354.5</v>
+        <v>354.25</v>
       </c>
     </row>
     <row r="101">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>108.8</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>222.8</v>
+        <v>220.9</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>114.6</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>205.3</v>
+        <v>205.2</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>84.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1679</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>22.26</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>36.64</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>108.7</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>352.75</v>
+        <v>353</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>8.17</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>141.6</v>
+        <v>143</v>
       </c>
     </row>
     <row r="113">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>324.5</v>
+        <v>324.75</v>
       </c>
     </row>
     <row r="114">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>48.98</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>13.9</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>42.36</v>
+        <v>42.64</v>
       </c>
     </row>
     <row r="117">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="118">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>13.8</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="119">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>5.85</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="120">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>195.8</v>
+        <v>195.7</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>11.9</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>216.1</v>
+        <v>216</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>26.12</v>
+        <v>25.84</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>13.49</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="127">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>15.63</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="128">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>10.48</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>13.46</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>48.88</v>
+        <v>49.16</v>
       </c>
     </row>
     <row r="131">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>15.11</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>113.5</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="134">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>54.2</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="135">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>92.15000000000001</v>
+        <v>92.05</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>28.58</v>
+        <v>29.04</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>232</v>
+        <v>232.7</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>13890</v>
+        <v>13872.5</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>70.25</v>
+        <v>70.05</v>
       </c>
     </row>
     <row r="141">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>320.25</v>
+        <v>317.5</v>
       </c>
     </row>
     <row r="142">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>9.82</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="145">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>58.95</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>46.44</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="147">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>6.25</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="148">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>48</v>
+        <v>47.86</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>87.05</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="150">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>57.85</v>
+        <v>57.95</v>
       </c>
     </row>
     <row r="151">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="152">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>17.65</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="153">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.109999999999999</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="154">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>61.25</v>
+        <v>61.05</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>84.45</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>12.08</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="157">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="158">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>35.48</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>14.26</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>82.15000000000001</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="161">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>38.34</v>
+        <v>38.28</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8.32</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="163">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>152.7</v>
+        <v>153.7</v>
       </c>
     </row>
     <row r="164">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>175.6</v>
+        <v>175.5</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>6.94</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>39.22</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="168">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>58.6</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>21.2</v>
+        <v>21.38</v>
       </c>
     </row>
     <row r="171">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>25.8</v>
+        <v>25.76</v>
       </c>
     </row>
     <row r="173">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>68.90000000000001</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>3702.5</v>
+        <v>3707.5</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5672.5</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>136.5</v>
+        <v>136.8</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1525</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>16.08</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>83.25</v>
+        <v>82.34999999999999</v>
       </c>
     </row>
     <row r="180">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>10.94</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="181">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>631.5</v>
+        <v>635</v>
       </c>
     </row>
     <row r="182">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>94.75</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>14.58</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="184">
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>23.36</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="185">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>20.5</v>
+        <v>20.56</v>
       </c>
     </row>
     <row r="186">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>61.8</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>32.14</v>
+        <v>32.12</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>146.6</v>
+        <v>145.9</v>
       </c>
     </row>
     <row r="189">
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>9.08</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="190">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>39.9</v>
+        <v>39.96</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>256.5</v>
+        <v>256.25</v>
       </c>
     </row>
     <row r="192">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>28.66</v>
+        <v>28.68</v>
       </c>
     </row>
     <row r="194">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>13.8</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>28.38</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="196">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="199">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>26.52</v>
+        <v>26.48</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.86</v>
+        <v>23.66</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>30.86</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="202">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>3.66</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="203">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>19.65</v>
+        <v>19.63</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>84.95</v>
+        <v>84.34999999999999</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>19.6</v>
+        <v>19.66</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>45.32</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="207">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>144.9</v>
+        <v>144</v>
       </c>
     </row>
     <row r="208">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>118.5</v>
+        <v>117.8</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>4.51</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>65.84999999999999</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>43</v>
+        <v>43.02</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>5.94</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="213">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>79.5</v>
+        <v>80.45</v>
       </c>
     </row>
     <row r="214">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>41.54</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>32.18</v>
+        <v>31.98</v>
       </c>
     </row>
     <row r="216">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="217">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>12.37</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="218">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>629.5</v>
+        <v>623</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>11.4</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="221">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>14.66</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="222">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>40.88</v>
+        <v>40.96</v>
       </c>
     </row>
     <row r="223">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>55.05</v>
+        <v>55</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>7.42</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="225">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>134.8</v>
+        <v>136.2</v>
       </c>
     </row>
     <row r="227">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>8.949999999999999</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="230">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>39.52</v>
+        <v>39.44</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>17.39</v>
+        <v>17.97</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>540</v>
+        <v>538.5</v>
       </c>
     </row>
     <row r="234">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>12.36</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>41.42</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>108.2</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>60.9</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="239">
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="H239" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="240">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="241">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>39.5</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="242">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>31.34</v>
+        <v>31.52</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>89.75</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>21.46</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="245">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.3</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="247">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>86.5</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="248">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>413</v>
+        <v>414.5</v>
       </c>
     </row>
     <row r="251">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="252">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>261.25</v>
+        <v>263</v>
       </c>
     </row>
     <row r="253">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>20.48</v>
+        <v>20.42</v>
       </c>
     </row>
     <row r="254">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>24.14</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="255">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>18.6</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="257">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="258">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>71.65000000000001</v>
+        <v>71.55</v>
       </c>
     </row>
     <row r="259">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>12.88</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="261">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="262">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.62</v>
+        <v>28.68</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>124.1</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>11.85</v>
+        <v>11.86</v>
       </c>
     </row>
     <row r="265">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>17.9</v>
+        <v>18.01</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>18.06</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>13.74</v>
+        <v>13.81</v>
       </c>
     </row>
     <row r="269">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>5.98</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="270">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>59.45</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>24.82</v>
+        <v>24.92</v>
       </c>
     </row>
     <row r="272">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>8.210000000000001</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="273">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>12.43</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>7.68</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>40.4</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="276">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>32.94</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="277">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.37</v>
+        <v>11.33</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>109.4</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="280">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="281">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>25.32</v>
+        <v>25.34</v>
       </c>
     </row>
     <row r="284">
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>24.7</v>
+        <v>24.74</v>
       </c>
     </row>
     <row r="285">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>22.7</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>6.2</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="287">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="288">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>6.16</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="289">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>20.72</v>
+        <v>20.82</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>732</v>
+        <v>734.5</v>
       </c>
     </row>
     <row r="292">
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>11.64</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="293">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>45.38</v>
+        <v>45.56</v>
       </c>
     </row>
     <row r="294">
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>999.5</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="296">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>44.56</v>
+        <v>44.94</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>18.85</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>23.94</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>217</v>
+        <v>214.9</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>9.710000000000001</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="301">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>7.27</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="303">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>81.05</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="305">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="306">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="H308" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="309">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>10.02</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="310">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>7.19</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="313">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>6.34</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>40.54</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="315">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>15.23</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>10.7</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>93.05</v>
+        <v>93</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>255.25</v>
+        <v>251.5</v>
       </c>
     </row>
     <row r="320">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>5.94</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="321">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="324">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>6.26</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>243.8</v>
+        <v>241.5</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>12.24</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>7.9</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>14.47</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>325.75</v>
+        <v>326.75</v>
       </c>
     </row>
     <row r="330">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>102.8</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="332">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>14.89</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>16.94</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>62.8</v>
+        <v>63.05</v>
       </c>
     </row>
     <row r="336">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="337">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.81</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="338">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>145.2</v>
+        <v>144.7</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>14.1</v>
+        <v>14.17</v>
       </c>
     </row>
     <row r="340">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>22.4</v>
+        <v>22.48</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>27.42</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>29.8</v>
+        <v>29.94</v>
       </c>
     </row>
     <row r="344">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="345">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>17.74</v>
+        <v>17.77</v>
       </c>
     </row>
     <row r="346">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>10.69</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="347">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>12.25</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.12</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="349">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="H349" t="n">
-        <v>12.72</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="350">
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="H351" t="n">
-        <v>4.23</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="352">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="H352" t="n">
-        <v>10.08</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="353">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>264.25</v>
+        <v>266.75</v>
       </c>
     </row>
     <row r="355">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>38.66</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>12.22</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="358">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>6.61</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>8.869999999999999</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>147.4</v>
+        <v>148.4</v>
       </c>
     </row>
     <row r="363">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>18.94</v>
+        <v>18.83</v>
       </c>
     </row>
     <row r="365">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="H365" t="n">
-        <v>58.95</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="366">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>20.76</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>120.7</v>
+        <v>121.1</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>15.05</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="369">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>23.16</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="370">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>7.24</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>6.72</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="372">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>15.89</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="373">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>300.75</v>
+        <v>301.5</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>65.5</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>65</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="377">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>90.34999999999999</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>64.90000000000001</v>
+        <v>65.25</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>40.06</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.1</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>19.86</v>
+        <v>19.96</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>99.90000000000001</v>
+        <v>98.95</v>
       </c>
     </row>
     <row r="384">
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="H384" t="n">
-        <v>53.1</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="385">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>109</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="386">
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="388">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>5.53</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="389">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>34.32</v>
+        <v>34.14</v>
       </c>
     </row>
     <row r="390">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="H390" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="391">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>12.99</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="392">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>9.42</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="393">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>4.09</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>5.31</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="395">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.23</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="396">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>14.58</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="398">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>9.99</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>148</v>
+        <v>148.7</v>
       </c>
     </row>
     <row r="401">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>12.16</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="403">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>183.8</v>
+        <v>183.2</v>
       </c>
     </row>
     <row r="404">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>43.02</v>
+        <v>43</v>
       </c>
     </row>
     <row r="405">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>30.14</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="406">
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>4.67</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="407">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>90.75</v>
+        <v>90.45</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>27.9</v>
+        <v>27.86</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>117.4</v>
+        <v>117.6</v>
       </c>
     </row>
     <row r="410">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>6.75</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="411">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>26.24</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="412">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>20.06</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="414">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>47.16</v>
+        <v>47.04</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.3</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="417">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>46.92</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>8.48</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="420">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>28.3</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="421">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>39.62</v>
+        <v>39.54</v>
       </c>
     </row>
     <row r="422">
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="H422" t="n">
-        <v>4.11</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="423">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>15.33</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="424">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>46.94</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="425">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>21.92</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.7</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="427">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.27</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>21.36</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="429">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>8.9</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="430">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>11.39</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="431">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="432">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>311.75</v>
+        <v>312.25</v>
       </c>
     </row>
     <row r="433">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.67</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="434">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>7.55</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="435">
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="436">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>10.25</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="437">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>7.39</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="438">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>12.91</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="439">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>10.54</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="440">
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="441">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>6.09</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="442">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="443">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>101.2</v>
+        <v>104.9</v>
       </c>
     </row>
     <row r="444">
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="H445" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="446">
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>27.58</v>
+        <v>27.52</v>
       </c>
     </row>
     <row r="447">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>27.64</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>1533</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="450">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>180.4</v>
+        <v>179.5</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>13.44</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="454">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>5.15</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>22.18</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>17.48</v>
+        <v>17.53</v>
       </c>
     </row>
     <row r="457">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="458">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>13.25</v>
+        <v>13.13</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>37.62</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="461">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>81.95</v>
+        <v>81.84999999999999</v>
       </c>
     </row>
     <row r="462">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="464">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>31.86</v>
+        <v>31.84</v>
       </c>
     </row>
     <row r="465">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="468">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>25.16</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>35.7</v>
+        <v>35.66</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>31.04</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>43.98</v>
+        <v>43.54</v>
       </c>
     </row>
     <row r="472">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="473">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>12.79</v>
+        <v>12.77</v>
       </c>
     </row>
     <row r="474">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>14.11</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="477">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="478">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>27.18</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>8.23</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.4</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="481">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>13.67</v>
+        <v>13.88</v>
       </c>
     </row>
     <row r="482">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.14</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="484">
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="485">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="486">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>97.05</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="487">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>17.85</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="488">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="489">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>26.1</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="491">
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="H491" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="492">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>34.26</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="494">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>49.64</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="495">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>10.23</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="497">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="499">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="501">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>39.9</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.62</v>
+        <v>24.64</v>
       </c>
     </row>
     <row r="503">
@@ -17050,7 +17050,7 @@
         </is>
       </c>
       <c r="H503" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="504">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="H504" t="n">
-        <v>8.6</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="505">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>8.630000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="506">
@@ -17149,7 +17149,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="507">
@@ -17248,7 +17248,7 @@
         </is>
       </c>
       <c r="H509" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="510">
@@ -17281,7 +17281,7 @@
         </is>
       </c>
       <c r="H510" t="n">
-        <v>4.21</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="511">
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="H512" t="n">
-        <v>34.9</v>
+        <v>34.74</v>
       </c>
     </row>
     <row r="513">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="H513" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="514">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>6.7</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="515">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>9.09</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="516">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>16.26</v>
+        <v>16.23</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>14.33</v>
+        <v>14.27</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>214.1</v>
+        <v>215.3</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>144.9</v>
+        <v>145.1</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>12.67</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>73.15000000000001</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="523">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>4.63</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="524">
@@ -17743,7 +17743,7 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="525">
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>7.64</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="526">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>13.9</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="527">
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="H528" t="n">
-        <v>16.9</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="529">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="532">
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="533">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="534">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>6.13</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="536">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>22.84</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="537">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.36</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="538">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>154.1</v>
+        <v>153.6</v>
       </c>
     </row>
     <row r="539">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>62.3</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="540">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>25.56</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="542">
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="H542" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="543">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="544">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>33.5</v>
+        <v>33.32</v>
       </c>
     </row>
     <row r="546">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>16.05</v>
+        <v>16.03</v>
       </c>
     </row>
     <row r="547">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>27.82</v>
+        <v>27.62</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
     </row>
     <row r="549">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="H549" t="n">
-        <v>10</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="550">
@@ -18634,7 +18634,7 @@
         </is>
       </c>
       <c r="H551" t="n">
-        <v>43.36</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="552">
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="H553" t="n">
-        <v>46.72</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="554">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="H554" t="n">
-        <v>4.67</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="555">
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="H557" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="558">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="H558" t="n">
-        <v>118.2</v>
+        <v>119.4</v>
       </c>
     </row>
     <row r="559">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>28.92</v>
+        <v>28.84</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="562">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="H562" t="n">
-        <v>23.58</v>
+        <v>23.94</v>
       </c>
     </row>
     <row r="563">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="H563" t="n">
-        <v>27.06</v>
+        <v>27.08</v>
       </c>
     </row>
     <row r="564">
@@ -19063,7 +19063,7 @@
         </is>
       </c>
       <c r="H564" t="n">
-        <v>12.79</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="565">
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="H565" t="n">
-        <v>7.95</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="566">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>6.41</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="569">
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="573">
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="H573" t="n">
-        <v>18.45</v>
+        <v>18.55</v>
       </c>
     </row>
     <row r="574">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>26.48</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="575">
@@ -19459,7 +19459,7 @@
         </is>
       </c>
       <c r="H576" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="577">
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="H577" t="n">
-        <v>5.95</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="578">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.630000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="581">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.64</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="582">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H582" t="n">
-        <v>10.14</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="583">
@@ -19690,7 +19690,7 @@
         </is>
       </c>
       <c r="H583" t="n">
-        <v>6.42</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="584">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>17.07</v>
+        <v>74.22</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>164.7</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>12.62</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>17.44</v>
+        <v>34.14</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>163</v>
+        <v>38.38</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>44.98</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>105.4</v>
+        <v>38.28</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>3.83</v>
+        <v>17.05</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>38.04</v>
+        <v>20.56</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>66.55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>2.45</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>17.2</v>
+        <v>16.96</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>70.09999999999999</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>7.98</v>
+        <v>162.9</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>34.08</v>
+        <v>40.82</v>
       </c>
     </row>
     <row r="602">
@@ -20317,7 +20317,7 @@
         </is>
       </c>
       <c r="H602" t="n">
-        <v>18.95</v>
+        <v>19.18</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>40.7</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>17.28</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>38.18</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>184.2</v>
+        <v>17.31</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>47.96</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>20.18</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>21.44</v>
+        <v>161.1</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>38.86</v>
+        <v>21.26</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>73.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>14.62</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>377.25</v>
+        <v>379.25</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2580</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>94.95</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>191.1</v>
+        <v>191.5</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>231.7</v>
+        <v>232.6</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>387.5</v>
+        <v>386.5</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>308.75</v>
+        <v>309.5</v>
       </c>
     </row>
     <row r="11">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>71.65000000000001</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>174.9</v>
+        <v>174.7</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>114.3</v>
+        <v>114.6</v>
       </c>
     </row>
     <row r="17">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>47.2</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>33.38</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>88.84999999999999</v>
+        <v>88.65000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>293.5</v>
+        <v>292.5</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>39.64</v>
+        <v>39.82</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>111.1</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="24">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>82.25</v>
+        <v>81.84999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>64.25</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>95.65000000000001</v>
+        <v>95.84999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>60.25</v>
+        <v>60.45</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1580</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>226.9</v>
+        <v>227.8</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>493</v>
+        <v>491.75</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>97.55</v>
+        <v>97.25</v>
       </c>
     </row>
     <row r="32">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>296.5</v>
+        <v>296.75</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>44.16</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>45.34</v>
+        <v>45.46</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>12.9</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="36">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>106.5</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="38">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="39">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>20.92</v>
+        <v>20.94</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>677.5</v>
+        <v>678</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>11407.5</v>
+        <v>11427.5</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1550</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>21.18</v>
+        <v>21.26</v>
       </c>
     </row>
     <row r="45">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>98.84999999999999</v>
+        <v>98.75</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>78.15000000000001</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>276.5</v>
+        <v>276</v>
       </c>
     </row>
     <row r="49">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>109.6</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="51">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>444</v>
+        <v>443.5</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>31.92</v>
+        <v>31.96</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>173.3</v>
+        <v>173.6</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>17.28</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>33.26</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="58">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>116.5</v>
+        <v>116.1</v>
       </c>
     </row>
     <row r="59">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>213</v>
+        <v>214.3</v>
       </c>
     </row>
     <row r="60">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.65</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2455,16 +2455,16 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>20.16</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="62">
@@ -2488,16 +2488,16 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
+          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>6.09</v>
+        <v>20.18</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>104.2</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>110.6</v>
+        <v>110.1</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>257</v>
+        <v>257.25</v>
       </c>
     </row>
     <row r="66">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>203</v>
+        <v>202.4</v>
       </c>
     </row>
     <row r="68">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.54</v>
+        <v>32.48</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>183.4</v>
+        <v>183</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>13.07</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="71">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>93.7</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1295</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="73">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>125.4</v>
+        <v>125.6</v>
       </c>
     </row>
     <row r="74">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>83.05</v>
+        <v>82.75</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>27.96</v>
+        <v>28.02</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>41.2</v>
+        <v>41.22</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>34.3</v>
+        <v>34.14</v>
       </c>
     </row>
     <row r="78">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>172.2</v>
+        <v>171.5</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>36.44</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>141.4</v>
+        <v>139.8</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>217.1</v>
+        <v>217</v>
       </c>
     </row>
     <row r="83">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1690</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="84">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>41.26</v>
+        <v>41.28</v>
       </c>
     </row>
     <row r="85">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>40.66</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="86">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>114.6</v>
+        <v>113.9</v>
       </c>
     </row>
     <row r="87">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.16</v>
+        <v>25.28</v>
       </c>
     </row>
     <row r="88">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.35</v>
+        <v>19.34</v>
       </c>
     </row>
     <row r="89">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>223.4</v>
+        <v>224.8</v>
       </c>
     </row>
     <row r="90">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>50.45</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>244</v>
+        <v>244.2</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>449.25</v>
+        <v>446.5</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>109.7</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="95">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>100.7</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="96">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>134.9</v>
+        <v>135.4</v>
       </c>
     </row>
     <row r="97">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>11.05</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="99">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>108.6</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>220.9</v>
+        <v>219.2</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>114.4</v>
+        <v>114.5</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>205.2</v>
+        <v>205.1</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>84.09999999999999</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1671</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>36.7</v>
+        <v>36.68</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>108.9</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>8.140000000000001</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>143</v>
+        <v>144.9</v>
       </c>
     </row>
     <row r="113">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>324.75</v>
+        <v>326.5</v>
       </c>
     </row>
     <row r="114">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>48.92</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>13.95</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>42.64</v>
+        <v>42.52</v>
       </c>
     </row>
     <row r="117">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="118">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>13.54</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="119">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>5.9</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="120">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>195.7</v>
+        <v>197.4</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>11.91</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>216</v>
+        <v>217.5</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>25.84</v>
+        <v>25.82</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>13.69</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="127">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>15.64</v>
+        <v>15.74</v>
       </c>
     </row>
     <row r="128">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>10.65</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>13.56</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>49.16</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="131">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>15.23</v>
+        <v>15.21</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>113.2</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="134">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>53.75</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="135">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>92.05</v>
+        <v>91.84999999999999</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>29.04</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>232.7</v>
+        <v>231.8</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>13872.5</v>
+        <v>13812.5</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>70.05</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="141">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>317.5</v>
+        <v>319</v>
       </c>
     </row>
     <row r="142">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>144.7</v>
+        <v>145.1</v>
       </c>
     </row>
     <row r="144">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>9.800000000000001</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="145">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>58.85</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>46.28</v>
+        <v>46.04</v>
       </c>
     </row>
     <row r="147">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>47.86</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>87.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="150">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>57.95</v>
+        <v>58</v>
       </c>
     </row>
     <row r="151">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>17.75</v>
+        <v>17.72</v>
       </c>
     </row>
     <row r="153">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.09</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="154">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>61.05</v>
+        <v>60.65</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>84.59999999999999</v>
+        <v>84.45</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>12.2</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="157">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="158">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>35.5</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="159">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>81.8</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="161">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>38.28</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8.43</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="163">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>153.7</v>
+        <v>153.3</v>
       </c>
     </row>
     <row r="164">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>175.5</v>
+        <v>175.4</v>
       </c>
     </row>
     <row r="165">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>6.99</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="167">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>4.82</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>58.1</v>
+        <v>58.35</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>21.38</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>4922.5</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>25.76</v>
+        <v>25.58</v>
       </c>
     </row>
     <row r="173">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>69.3</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>3707.5</v>
+        <v>3717.5</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5670</v>
+        <v>5702.5</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>136.8</v>
+        <v>136.9</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>16.14</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>82.34999999999999</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="180">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>11.05</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="181">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>635</v>
+        <v>639.5</v>
       </c>
     </row>
     <row r="182">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>90.40000000000001</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>14.63</v>
+        <v>14.57</v>
       </c>
     </row>
     <row r="184">
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>23.4</v>
+        <v>23.38</v>
       </c>
     </row>
     <row r="185">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>61.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>32.12</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>145.9</v>
+        <v>145.6</v>
       </c>
     </row>
     <row r="189">
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>9.09</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="190">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>39.96</v>
+        <v>39.64</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>256.25</v>
+        <v>256.5</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>13.63</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="193">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>13.94</v>
+        <v>13.81</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>28.34</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="196">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="199">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>26.48</v>
+        <v>26.52</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.66</v>
+        <v>23.48</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>30.9</v>
+        <v>30.94</v>
       </c>
     </row>
     <row r="202">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="203">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>19.63</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>84.34999999999999</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>19.66</v>
+        <v>19.67</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>45.1</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="207">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>144</v>
+        <v>144.2</v>
       </c>
     </row>
     <row r="208">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>117.8</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>4.52</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>43.02</v>
+        <v>43</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>5.97</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="213">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>80.45</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="214">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>31.98</v>
+        <v>32.04</v>
       </c>
     </row>
     <row r="216">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="217">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>12.41</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>73.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>11.49</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="221">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>14.65</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="222">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>40.96</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="223">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>55</v>
+        <v>55.05</v>
       </c>
     </row>
     <row r="224">
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>8.01</v>
+        <v>8</v>
       </c>
     </row>
     <row r="226">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>136.2</v>
+        <v>136</v>
       </c>
     </row>
     <row r="227">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>16.68</v>
+        <v>16.71</v>
       </c>
     </row>
     <row r="229">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.15</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>39.44</v>
+        <v>39.28</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>17.97</v>
+        <v>17.79</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>538.5</v>
+        <v>536.5</v>
       </c>
     </row>
     <row r="234">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>12.38</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>41.46</v>
+        <v>41.78</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>107.9</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>61.8</v>
+        <v>61.55</v>
       </c>
     </row>
     <row r="239">
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="H239" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="240">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="241">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>39.52</v>
+        <v>39.48</v>
       </c>
     </row>
     <row r="242">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>31.52</v>
+        <v>31.46</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>21.34</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="245">
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="246">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.34</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="247">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>86.2</v>
+        <v>86</v>
       </c>
     </row>
     <row r="248">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="250">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>414.5</v>
+        <v>414</v>
       </c>
     </row>
     <row r="251">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>35.7</v>
+        <v>35.86</v>
       </c>
     </row>
     <row r="252">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>263</v>
+        <v>262.25</v>
       </c>
     </row>
     <row r="253">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>20.42</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="254">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>24.22</v>
+        <v>24.26</v>
       </c>
     </row>
     <row r="255">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>1149</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>18.67</v>
+        <v>18.69</v>
       </c>
     </row>
     <row r="257">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>71.55</v>
+        <v>71.75</v>
       </c>
     </row>
     <row r="259">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="260">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>12.84</v>
+        <v>12.79</v>
       </c>
     </row>
     <row r="261">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.68</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>125.5</v>
+        <v>125</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>11.86</v>
+        <v>11.72</v>
       </c>
     </row>
     <row r="265">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>18.01</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>17.86</v>
+        <v>17.85</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>13.81</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="269">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>5.99</v>
+        <v>6</v>
       </c>
     </row>
     <row r="270">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>59.1</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>24.92</v>
+        <v>24.88</v>
       </c>
     </row>
     <row r="272">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>12.45</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>7.67</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>40.72</v>
+        <v>40.48</v>
       </c>
     </row>
     <row r="276">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.33</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>109.8</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="280">
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>6.41</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="282">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>25.34</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="284">
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>24.74</v>
+        <v>24.82</v>
       </c>
     </row>
     <row r="285">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>22.84</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="286">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>58.4</v>
+        <v>58.45</v>
       </c>
     </row>
     <row r="288">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>6.17</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="289">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>7.9</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>20.82</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>734.5</v>
+        <v>733.5</v>
       </c>
     </row>
     <row r="292">
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>11.65</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="293">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>45.56</v>
+        <v>46.16</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>54.25</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="295">
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>1010</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="296">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>44.94</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>18.84</v>
+        <v>18.83</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>23.9</v>
+        <v>23.86</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>214.9</v>
+        <v>214.7</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="301">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>7.35</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="303">
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="H303" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="304">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="305">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="306">
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="308">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="H308" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="309">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>10.06</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="310">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>116</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="311">
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="312">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>7.2</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="313">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>15.45</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>15.3</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>10.42</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>93</v>
+        <v>93.05</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>251.5</v>
+        <v>256.5</v>
       </c>
     </row>
     <row r="320">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>5.93</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="321">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>434</v>
+        <v>431.25</v>
       </c>
     </row>
     <row r="322">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>6.27</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>241.5</v>
+        <v>244.7</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>12.19</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>7.95</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>14.37</v>
+        <v>14.26</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>326.75</v>
+        <v>327</v>
       </c>
     </row>
     <row r="330">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>40.16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="331">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>104.8</v>
+        <v>104.1</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>32.68</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>14.97</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>16.9</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>63.05</v>
+        <v>62.85</v>
       </c>
     </row>
     <row r="336">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="337">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="338">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>144.7</v>
+        <v>144.4</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>14.17</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="340">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>22.48</v>
+        <v>22.56</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>27.4</v>
+        <v>27.26</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>29.94</v>
+        <v>30.08</v>
       </c>
     </row>
     <row r="344">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>17.77</v>
+        <v>17.69</v>
       </c>
     </row>
     <row r="346">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>10.64</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="347">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>12.17</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.2</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="349">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="H349" t="n">
-        <v>12.76</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="350">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>5.49</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="351">
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="H351" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="352">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="H352" t="n">
-        <v>10.14</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="353">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>266.75</v>
+        <v>267.5</v>
       </c>
     </row>
     <row r="355">
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="H355" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>38.7</v>
+        <v>38.64</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>12.19</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="358">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="H358" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="359">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>6.66</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>8.83</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>148.4</v>
+        <v>148</v>
       </c>
     </row>
     <row r="363">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>18.83</v>
+        <v>18.82</v>
       </c>
     </row>
     <row r="365">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="H365" t="n">
-        <v>59.2</v>
+        <v>59</v>
       </c>
     </row>
     <row r="366">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>20.7</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>121.1</v>
+        <v>121</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>15.08</v>
+        <v>15.07</v>
       </c>
     </row>
     <row r="369">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>23.08</v>
+        <v>23.02</v>
       </c>
     </row>
     <row r="370">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>7.21</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>6.71</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="372">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>15.88</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="373">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>301.5</v>
+        <v>302.75</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>65.2</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="377">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>7.35</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="378">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>90.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>65.25</v>
+        <v>65.34999999999999</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>40.2</v>
+        <v>40.24</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.03</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>19.96</v>
+        <v>19.85</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>98.95</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="384">
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="H384" t="n">
-        <v>53.5</v>
+        <v>53.65</v>
       </c>
     </row>
     <row r="385">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>108.9</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="386">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="H386" t="n">
-        <v>6.62</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="387">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>5.57</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="389">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>34.14</v>
+        <v>34.72</v>
       </c>
     </row>
     <row r="390">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="H390" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="391">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>13.04</v>
+        <v>13.08</v>
       </c>
     </row>
     <row r="392">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>4.11</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>5.39</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="395">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.36</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="396">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="397">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>9.949999999999999</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>148.7</v>
+        <v>148.6</v>
       </c>
     </row>
     <row r="401">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>12.21</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="403">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>183.2</v>
+        <v>183.4</v>
       </c>
     </row>
     <row r="404">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="405">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>30.26</v>
+        <v>30.24</v>
       </c>
     </row>
     <row r="406">
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>4.95</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="407">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>90.45</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>27.86</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>117.6</v>
+        <v>117.5</v>
       </c>
     </row>
     <row r="410">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>6.74</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="411">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>26.32</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="412">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>20.16</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="414">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>47.04</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.28</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="417">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>46.68</v>
+        <v>46.82</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>8.449999999999999</v>
+        <v>8.470000000000001</v>
       </c>
     </row>
     <row r="420">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>28.34</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="421">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>39.54</v>
+        <v>39.48</v>
       </c>
     </row>
     <row r="422">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>46.98</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="425">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>21.9</v>
+        <v>21.82</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.69</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="427">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.26</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>21.4</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="429">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>8.859999999999999</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="430">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>11.47</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="431">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="432">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>312.25</v>
+        <v>317.75</v>
       </c>
     </row>
     <row r="433">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>7.56</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="435">
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="436">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>10.28</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="437">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>7.4</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="438">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>12.92</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="439">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>10.57</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="440">
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="441">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>6.07</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="442">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>104.9</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="444">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>40.1</v>
+        <v>40.14</v>
       </c>
     </row>
     <row r="445">
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>27.52</v>
+        <v>27.48</v>
       </c>
     </row>
     <row r="447">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>27.64</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>27.96</v>
+        <v>27.84</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>1535</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="450">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>179.5</v>
+        <v>181.3</v>
       </c>
     </row>
     <row r="452">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>5.18</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>22.1</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>17.53</v>
+        <v>17.54</v>
       </c>
     </row>
     <row r="457">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>19.9</v>
+        <v>20.56</v>
       </c>
     </row>
     <row r="458">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="H458" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="459">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>13.13</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>37.7</v>
+        <v>37.36</v>
       </c>
     </row>
     <row r="461">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>81.84999999999999</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="462">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="464">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>31.84</v>
+        <v>32</v>
       </c>
     </row>
     <row r="465">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
     </row>
     <row r="468">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>25.3</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>35.66</v>
+        <v>35.68</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>43.54</v>
+        <v>43.42</v>
       </c>
     </row>
     <row r="472">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>12.77</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="474">
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="476">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>13.85</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="477">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="478">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>27.1</v>
+        <v>27.12</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>8.25</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.38</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="481">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>13.88</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="482">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.21</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>83.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="484">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>96.2</v>
+        <v>96.65000000000001</v>
       </c>
     </row>
     <row r="487">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>18.09</v>
+        <v>18.33</v>
       </c>
     </row>
     <row r="488">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="489">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>25.96</v>
+        <v>26.36</v>
       </c>
     </row>
     <row r="491">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>34.2</v>
+        <v>34.18</v>
       </c>
     </row>
     <row r="494">
@@ -16786,7 +16786,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="496">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>10.21</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="497">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="499">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="501">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>39.68</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.64</v>
+        <v>24.56</v>
       </c>
     </row>
     <row r="503">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="H504" t="n">
-        <v>8.59</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="505">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>8.6</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="506">
@@ -17149,7 +17149,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="507">
@@ -17248,7 +17248,7 @@
         </is>
       </c>
       <c r="H509" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="510">
@@ -17281,7 +17281,7 @@
         </is>
       </c>
       <c r="H510" t="n">
-        <v>4.31</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="511">
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="512">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="H513" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="514">
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="H516" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="517">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>16.23</v>
+        <v>16.17</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>14.27</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>215.3</v>
+        <v>216.4</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>145.1</v>
+        <v>147.8</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>12.57</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>72.8</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="523">
@@ -17743,7 +17743,7 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="525">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>13.98</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="527">
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="H528" t="n">
-        <v>17.08</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="529">
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="H529" t="n">
-        <v>13.92</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="530">
@@ -17941,7 +17941,7 @@
         </is>
       </c>
       <c r="H530" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="531">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.28</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="534">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>6.12</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="536">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.3</v>
+        <v>25.18</v>
       </c>
     </row>
     <row r="538">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>153.6</v>
+        <v>153</v>
       </c>
     </row>
     <row r="539">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>62.4</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="540">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="H540" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="541">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>25.7</v>
+        <v>25.52</v>
       </c>
     </row>
     <row r="542">
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="H542" t="n">
-        <v>4.48</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="543">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>15.2</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="544">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>16.03</v>
+        <v>16</v>
       </c>
     </row>
     <row r="547">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>27.62</v>
+        <v>27.76</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>52</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="549">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="H549" t="n">
-        <v>10.12</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="550">
@@ -18634,7 +18634,7 @@
         </is>
       </c>
       <c r="H551" t="n">
-        <v>43.26</v>
+        <v>43.36</v>
       </c>
     </row>
     <row r="552">
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="H553" t="n">
-        <v>46.5</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="554">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="H554" t="n">
-        <v>4.71</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="555">
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="H556" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="557">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>28.84</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="562">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="H562" t="n">
-        <v>23.94</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="563">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="H563" t="n">
-        <v>27.08</v>
+        <v>26.98</v>
       </c>
     </row>
     <row r="564">
@@ -19063,7 +19063,7 @@
         </is>
       </c>
       <c r="H564" t="n">
-        <v>12.81</v>
+        <v>13</v>
       </c>
     </row>
     <row r="565">
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="H565" t="n">
-        <v>8.039999999999999</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="566">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>6.49</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="569">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="H569" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="570">
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>8.470000000000001</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="572">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>26.58</v>
+        <v>26.72</v>
       </c>
     </row>
     <row r="575">
@@ -19558,7 +19558,7 @@
         </is>
       </c>
       <c r="H579" t="n">
-        <v>12.3</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="580">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.5</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="581">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.67</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="582">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H582" t="n">
-        <v>10.15</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="583">
@@ -19690,7 +19690,7 @@
         </is>
       </c>
       <c r="H583" t="n">
-        <v>6.4</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="584">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>128.5</v>
+        <v>37.98</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>74.22</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>47.6</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>105.4</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>34.14</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>38.38</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>12.64</v>
+        <v>17.32</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>38.28</v>
+        <v>66.75</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>17.05</v>
+        <v>47.36</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>20.56</v>
+        <v>105.7</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>8</v>
+        <v>38.36</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>3.82</v>
+        <v>183.7</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>16.96</v>
+        <v>38.26</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>66.7</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>162.9</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>40.82</v>
+        <v>159</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>19.18</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>183.8</v>
+        <v>19.14</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>37.96</v>
+        <v>17.51</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>44.98</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>17.31</v>
+        <v>162.6</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>14.59</v>
+        <v>20.44</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>2.46</v>
+        <v>74.34</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>161.1</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>21.26</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>70.09999999999999</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>17.5</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>379.25</v>
+        <v>381.25</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2590</v>
+        <v>2592.5</v>
       </c>
     </row>
     <row r="5">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>137.7</v>
+        <v>137.3</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>191.5</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>232.6</v>
+        <v>235.5</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>386.5</v>
+        <v>386.75</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>309.5</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -805,7 +805,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISBTR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2915000</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="12">
@@ -871,7 +871,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISBTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>420000</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>71.90000000000001</v>
+        <v>71.95</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>174.7</v>
+        <v>175.2</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>114.6</v>
+        <v>114.7</v>
       </c>
     </row>
     <row r="17">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>47.28</v>
+        <v>47.18</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>33.6</v>
+        <v>33.48</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>88.65000000000001</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>38.2</v>
+        <v>38.12</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>292.5</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>39.82</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>110.4</v>
+        <v>110.8</v>
       </c>
     </row>
     <row r="24">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>60.45</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1576</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>227.8</v>
+        <v>228.9</v>
       </c>
     </row>
     <row r="30">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>296.75</v>
+        <v>295.75</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>44.26</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>45.46</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>12.98</v>
+        <v>12.96</v>
       </c>
     </row>
     <row r="36">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>654</v>
+        <v>653.5</v>
       </c>
     </row>
     <row r="39">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>20.94</v>
+        <v>21.06</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>678</v>
+        <v>678.5</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>11427.5</v>
+        <v>11332.5</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1563</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>21.26</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="45">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>98.75</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>78.25</v>
+        <v>78.84999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>276</v>
+        <v>275.75</v>
       </c>
     </row>
     <row r="49">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>443.5</v>
+        <v>444.25</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>31.96</v>
+        <v>31.94</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>173.6</v>
+        <v>173.5</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>17.24</v>
+        <v>17.19</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>33.44</v>
+        <v>34.06</v>
       </c>
     </row>
     <row r="58">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>214.3</v>
+        <v>215</v>
       </c>
     </row>
     <row r="60">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.640000000000001</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="61">
@@ -2455,16 +2455,16 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
+          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6.1</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="62">
@@ -2488,16 +2488,16 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>20.18</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>104.4</v>
+        <v>104.3</v>
       </c>
     </row>
     <row r="64">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>257.25</v>
+        <v>258.5</v>
       </c>
     </row>
     <row r="66">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>202.4</v>
+        <v>202.6</v>
       </c>
     </row>
     <row r="68">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.48</v>
+        <v>32.44</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>183</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>13.12</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="71">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>94.5</v>
+        <v>93.65000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1289</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="73">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>82.75</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>28.02</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>41.22</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>34.14</v>
+        <v>34.02</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>171.5</v>
+        <v>171.8</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>36.36</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>139.8</v>
+        <v>140</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>217</v>
+        <v>217.3</v>
       </c>
     </row>
     <row r="83">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1677</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="84">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KRDMA</t>
+          <t>KRDMD</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>41.28</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="85">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KRDMD</t>
+          <t>KRDMA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>40.7</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="86">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>113.9</v>
+        <v>114.1</v>
       </c>
     </row>
     <row r="87">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.28</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="88">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.34</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="89">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>224.8</v>
+        <v>224.9</v>
       </c>
     </row>
     <row r="90">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1229</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>50.2</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>244.2</v>
+        <v>246.1</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>446.5</v>
+        <v>447</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>109.6</v>
+        <v>109.9</v>
       </c>
     </row>
     <row r="95">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>135.4</v>
+        <v>135.3</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>609.5</v>
+        <v>612.5</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>11.13</v>
+        <v>11.12</v>
       </c>
     </row>
     <row r="99">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>64.59999999999999</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>354.25</v>
+        <v>354.5</v>
       </c>
     </row>
     <row r="101">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>219.2</v>
+        <v>219</v>
       </c>
     </row>
     <row r="103">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>205.1</v>
+        <v>205.4</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>83.95</v>
+        <v>83.25</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1682</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>22.4</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>36.68</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>108.5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>352</v>
+        <v>352.75</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>8.18</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>144.9</v>
+        <v>144.6</v>
       </c>
     </row>
     <row r="113">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>326.5</v>
+        <v>325.5</v>
       </c>
     </row>
     <row r="114">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>48.9</v>
+        <v>49.02</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>13.93</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="116">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="118">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>13.56</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="119">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>5.93</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="120">
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="121">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>197.4</v>
+        <v>197.2</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>11.98</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>217.5</v>
+        <v>216.3</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>25.82</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="125">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>13.9</v>
+        <v>13.81</v>
       </c>
     </row>
     <row r="127">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>15.74</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="128">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>10.67</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>13.51</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>49.2</v>
+        <v>49.24</v>
       </c>
     </row>
     <row r="131">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>15.21</v>
+        <v>15.18</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>112.7</v>
+        <v>113.1</v>
       </c>
     </row>
     <row r="134">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>53.55</v>
+        <v>53.45</v>
       </c>
     </row>
     <row r="135">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>91.84999999999999</v>
+        <v>91.95</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>28.7</v>
+        <v>28.64</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>231.8</v>
+        <v>232.1</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>13812.5</v>
+        <v>13692.5</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>70.59999999999999</v>
+        <v>70.75</v>
       </c>
     </row>
     <row r="141">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>319</v>
+        <v>319.5</v>
       </c>
     </row>
     <row r="142">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>145.1</v>
+        <v>146.1</v>
       </c>
     </row>
     <row r="144">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>9.789999999999999</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="145">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>58.65</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>46.04</v>
+        <v>46.62</v>
       </c>
     </row>
     <row r="147">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>6.32</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="148">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>47.78</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>87.59999999999999</v>
+        <v>87.34999999999999</v>
       </c>
     </row>
     <row r="150">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>58</v>
+        <v>57.85</v>
       </c>
     </row>
     <row r="151">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="152">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>17.72</v>
+        <v>17.71</v>
       </c>
     </row>
     <row r="153">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.1</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>60.65</v>
+        <v>60.25</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>84.45</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>12.03</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="157">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>35.48</v>
+        <v>35.52</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>14.24</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>81.5</v>
+        <v>81.95</v>
       </c>
     </row>
     <row r="161">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>38.18</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8.460000000000001</v>
+        <v>8.539999999999999</v>
       </c>
     </row>
     <row r="163">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>153.3</v>
+        <v>153</v>
       </c>
     </row>
     <row r="164">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>175.4</v>
+        <v>175.5</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>20.4</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>6.94</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>39.3</v>
+        <v>39.12</v>
       </c>
     </row>
     <row r="168">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>58.35</v>
+        <v>58.05</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>21.2</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>4920</v>
+        <v>4937.5</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>25.58</v>
+        <v>25.54</v>
       </c>
     </row>
     <row r="173">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>3717.5</v>
+        <v>3712.5</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5702.5</v>
+        <v>5692.5</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>136.9</v>
+        <v>136.7</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1528</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>16.16</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>81.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="180">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>11.01</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="181">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>639.5</v>
+        <v>637.5</v>
       </c>
     </row>
     <row r="182">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>91.7</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>14.57</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="184">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>20.56</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="186">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>32.14</v>
+        <v>31.98</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>145.6</v>
+        <v>144.8</v>
       </c>
     </row>
     <row r="189">
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>9.02</v>
+        <v>9</v>
       </c>
     </row>
     <row r="190">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>39.64</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>256.5</v>
+        <v>257.5</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>13.6</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="193">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>28.68</v>
+        <v>28.76</v>
       </c>
     </row>
     <row r="194">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>13.81</v>
+        <v>13.88</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>28.4</v>
+        <v>28.38</v>
       </c>
     </row>
     <row r="196">
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="197">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="198">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>26.52</v>
+        <v>26.54</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.48</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>30.94</v>
+        <v>30.88</v>
       </c>
     </row>
     <row r="202">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>19.5</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>84.2</v>
+        <v>84.34999999999999</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>19.67</v>
+        <v>19.65</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>45.04</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="207">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>144.2</v>
+        <v>144.4</v>
       </c>
     </row>
     <row r="208">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>116.6</v>
+        <v>115.9</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>65.90000000000001</v>
+        <v>65.95</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>5.94</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="213">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>80.2</v>
+        <v>80.34999999999999</v>
       </c>
     </row>
     <row r="214">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>41.1</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>32.04</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="216">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="217">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>12.39</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>73.59999999999999</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>11.43</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="221">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>40.92</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="223">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>7.39</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="225">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>16.71</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="229">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>8.94</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="230">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.16</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>39.28</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>17.79</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>536.5</v>
+        <v>537.5</v>
       </c>
     </row>
     <row r="234">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>12.41</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>41.78</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>108.9</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>61.55</v>
+        <v>61.25</v>
       </c>
     </row>
     <row r="239">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="241">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>39.48</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="242">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>31.46</v>
+        <v>31.66</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>89.90000000000001</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>21.14</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="245">
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="246">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.35</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="247">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>414</v>
+        <v>412.5</v>
       </c>
     </row>
     <row r="251">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>35.86</v>
+        <v>35.96</v>
       </c>
     </row>
     <row r="252">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>262.25</v>
+        <v>262.75</v>
       </c>
     </row>
     <row r="253">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>20.7</v>
+        <v>21.26</v>
       </c>
     </row>
     <row r="254">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>24.26</v>
+        <v>24.24</v>
       </c>
     </row>
     <row r="255">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>18.69</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="257">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>4.59</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="258">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>71.75</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="259">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>12.79</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="261">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>29.1</v>
+        <v>28.72</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>11.72</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="265">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>18.04</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>17.85</v>
+        <v>17.92</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>13.83</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="269">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>6</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="270">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>58.4</v>
+        <v>58.25</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>24.88</v>
+        <v>24.78</v>
       </c>
     </row>
     <row r="272">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>12.43</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>7.74</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>40.48</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="276">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>32.9</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="277">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.35</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>110.5</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="280">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="281">
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>6.4</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="282">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>25.44</v>
+        <v>25.62</v>
       </c>
     </row>
     <row r="284">
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>24.82</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="285">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>22.86</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>6.19</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="287">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>58.45</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="288">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>6.15</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="289">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>7.92</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>20.98</v>
+        <v>21.02</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>733.5</v>
+        <v>735</v>
       </c>
     </row>
     <row r="292">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>46.16</v>
+        <v>45.22</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>54.5</v>
+        <v>54.45</v>
       </c>
     </row>
     <row r="295">
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>1013</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="296">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>44.9</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>18.83</v>
+        <v>18.82</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>23.86</v>
+        <v>24.04</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>214.7</v>
+        <v>215.5</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>9.710000000000001</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="301">
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="H301" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="302">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>7.37</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="303">
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="H303" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="304">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>81.59999999999999</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="305">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="306">
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="308">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="H308" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="309">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>115.6</v>
+        <v>115.4</v>
       </c>
     </row>
     <row r="311">
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="312">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>6.3</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>40.7</v>
+        <v>40.44</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>15.36</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>15.35</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>93.05</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>256.5</v>
+        <v>263</v>
       </c>
     </row>
     <row r="320">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>5.91</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="321">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>431.25</v>
+        <v>433</v>
       </c>
     </row>
     <row r="322">
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="H322" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="323">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>6.25</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>244.7</v>
+        <v>246.6</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>12.23</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>7.99</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>14.26</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="329">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>40</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="331">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>104.1</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>32.82</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>15.08</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>16.97</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>62.85</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="336">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="337">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.83</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="338">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>144.4</v>
+        <v>144.1</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>14.14</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="340">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>22.56</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>27.26</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="343">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>17.69</v>
+        <v>17.72</v>
       </c>
     </row>
     <row r="346">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>10.66</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="347">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>11.98</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.26</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="349">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>5.47</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="351">
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="H351" t="n">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="352">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="H352" t="n">
-        <v>10.26</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="353">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>267.5</v>
+        <v>266</v>
       </c>
     </row>
     <row r="355">
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="H355" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="356">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>38.64</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>12.21</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="358">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="H358" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="359">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>6.65</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>8.77</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>148</v>
+        <v>147.4</v>
       </c>
     </row>
     <row r="363">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>23.56</v>
+        <v>23.62</v>
       </c>
     </row>
     <row r="364">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>18.82</v>
+        <v>18.83</v>
       </c>
     </row>
     <row r="365">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="H365" t="n">
-        <v>59</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="366">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>20.74</v>
+        <v>20.58</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>121</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>15.07</v>
+        <v>15.13</v>
       </c>
     </row>
     <row r="369">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>23.02</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="370">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>7.17</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>6.75</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="372">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>15.91</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="373">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>302.75</v>
+        <v>303.75</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>65.7</v>
+        <v>65.75</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>65.40000000000001</v>
+        <v>65.25</v>
       </c>
     </row>
     <row r="377">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>7.26</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="378">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>89.90000000000001</v>
+        <v>89.95</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>65.34999999999999</v>
+        <v>65.65000000000001</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>40.24</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.09</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>19.85</v>
+        <v>19.88</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>100.5</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="384">
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="H384" t="n">
-        <v>53.65</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="385">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>108.8</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="386">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="H386" t="n">
-        <v>6.59</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="387">
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="388">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>5.56</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="389">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>34.72</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="390">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>9.390000000000001</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="393">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>4.09</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>5.4</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="395">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.41</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="396">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="397">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>14.43</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="398">
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="H398" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="399">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>9.93</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>148.6</v>
+        <v>148.2</v>
       </c>
     </row>
     <row r="401">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>12.22</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="403">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>42.9</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="405">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>30.24</v>
+        <v>30.28</v>
       </c>
     </row>
     <row r="406">
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="407">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>90.40000000000001</v>
+        <v>90.45</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>117.5</v>
+        <v>117.1</v>
       </c>
     </row>
     <row r="410">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>6.72</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="411">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="412">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>47.1</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.26</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="417">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>46.82</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>8.470000000000001</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="420">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>28.3</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="421">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>15.36</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="424">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>47.3</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="425">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>21.82</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.71</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="427">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.28</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>21.34</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="429">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>8.82</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="430">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>11.4</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="431">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>317.75</v>
+        <v>318.75</v>
       </c>
     </row>
     <row r="433">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.73</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="434">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>7.58</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="435">
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="436">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>10.25</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="437">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>7.41</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="438">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>12.95</v>
+        <v>12.96</v>
       </c>
     </row>
     <row r="439">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>10.59</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="440">
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="441">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>6.14</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="442">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="443">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>103.8</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="444">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>40.14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="445">
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="H445" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="446">
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>27.48</v>
+        <v>27.46</v>
       </c>
     </row>
     <row r="447">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>27.6</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>27.84</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>1533</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="450">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>181.3</v>
+        <v>181.1</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>13.41</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="454">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>21.86</v>
+        <v>22</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>17.54</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="457">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>20.56</v>
+        <v>20.38</v>
       </c>
     </row>
     <row r="458">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="H458" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="459">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>13.07</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>37.36</v>
+        <v>37.16</v>
       </c>
     </row>
     <row r="461">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>81.8</v>
+        <v>81.75</v>
       </c>
     </row>
     <row r="462">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="464">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="H465" t="n">
-        <v>11.04</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="466">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>25.14</v>
+        <v>25.02</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>35.68</v>
+        <v>35.56</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>31.5</v>
+        <v>31.06</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>43.42</v>
+        <v>43.34</v>
       </c>
     </row>
     <row r="472">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="473">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>12.75</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="474">
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="476">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>13.76</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="477">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="478">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>27.12</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>8.300000000000001</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.37</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="481">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>13.91</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="482">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.2</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="484">
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="485">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="486">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>96.65000000000001</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="487">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>18.33</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="488">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>10.42</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="489">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>26.36</v>
+        <v>26.38</v>
       </c>
     </row>
     <row r="491">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>49.42</v>
+        <v>49.48</v>
       </c>
     </row>
     <row r="495">
@@ -16786,7 +16786,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="496">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>3.24</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="499">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="501">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>39.9</v>
+        <v>40.14</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.56</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="503">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="H504" t="n">
-        <v>8.619999999999999</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="505">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>8.59</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="506">
@@ -17149,7 +17149,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="507">
@@ -17248,7 +17248,7 @@
         </is>
       </c>
       <c r="H509" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="510">
@@ -17281,7 +17281,7 @@
         </is>
       </c>
       <c r="H510" t="n">
-        <v>4.24</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="511">
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="512">
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="H512" t="n">
-        <v>34.74</v>
+        <v>34.72</v>
       </c>
     </row>
     <row r="513">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="H513" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="514">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>6.71</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="515">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>9.1</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="516">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>16.17</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>14.55</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>216.4</v>
+        <v>215.8</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>147.8</v>
+        <v>146.2</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>12.52</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>72.59999999999999</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="523">
@@ -17743,7 +17743,7 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="525">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>13.97</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="527">
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="H528" t="n">
-        <v>16.97</v>
+        <v>16.98</v>
       </c>
     </row>
     <row r="529">
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="H529" t="n">
-        <v>13.96</v>
+        <v>13.88</v>
       </c>
     </row>
     <row r="530">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="532">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.32</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="534">
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="H534" t="n">
-        <v>4.44</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="535">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>6.14</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="536">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>22.9</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="537">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.18</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="538">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>153</v>
+        <v>156.3</v>
       </c>
     </row>
     <row r="539">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>62.9</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="540">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="H540" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="541">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>25.52</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="542">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>15.15</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="544">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>33.32</v>
+        <v>33.14</v>
       </c>
     </row>
     <row r="546">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>16</v>
+        <v>15.98</v>
       </c>
     </row>
     <row r="547">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>27.76</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>51.85</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="549">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="H549" t="n">
-        <v>10.14</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="550">
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="H553" t="n">
-        <v>46.9</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="554">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="H554" t="n">
-        <v>4.69</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="555">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="H558" t="n">
-        <v>119.4</v>
+        <v>120.2</v>
       </c>
     </row>
     <row r="559">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>28.7</v>
+        <v>28.72</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="562">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="H562" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="563">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="H563" t="n">
-        <v>26.98</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="564">
@@ -19063,7 +19063,7 @@
         </is>
       </c>
       <c r="H564" t="n">
-        <v>13</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="565">
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="H565" t="n">
-        <v>7.99</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="566">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>6.6</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="569">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="H569" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="570">
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>8.51</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="572">
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="H573" t="n">
-        <v>18.55</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="574">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>26.72</v>
+        <v>26.64</v>
       </c>
     </row>
     <row r="575">
@@ -19459,7 +19459,7 @@
         </is>
       </c>
       <c r="H576" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="577">
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="H577" t="n">
-        <v>5.96</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="578">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.34</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="581">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.68</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="582">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H582" t="n">
-        <v>10.09</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="583">
@@ -19690,7 +19690,7 @@
         </is>
       </c>
       <c r="H583" t="n">
-        <v>6.43</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="584">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>37.98</v>
+        <v>38.22</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>12.66</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>34.24</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>14.56</v>
+        <v>40.66</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>44.98</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>17.12</v>
+        <v>17.48</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>17.32</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>66.75</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>47.36</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>105.7</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>38.36</v>
+        <v>17.37</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>183.7</v>
+        <v>17.59</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>38.26</v>
+        <v>34.44</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>3.82</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>40.92</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>159</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>16.99</v>
+        <v>157.9</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>19.14</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>17.51</v>
+        <v>74.31</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>128.5</v>
+        <v>21.38</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>162.6</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>20.44</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>74.34</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>70.09999999999999</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>2.48</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>8.01</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>21.36</v>
+        <v>162.7</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>381.25</v>
+        <v>378.5</v>
       </c>
     </row>
     <row r="3">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2592.5</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>95.09999999999999</v>
+        <v>94.95</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>137.3</v>
+        <v>137.5</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>191.6</v>
+        <v>191.2</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>235.5</v>
+        <v>233.9</v>
       </c>
     </row>
     <row r="9">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>310</v>
+        <v>309.75</v>
       </c>
     </row>
     <row r="11">
@@ -838,7 +838,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>14.56</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2915000</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>71.95</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>175.2</v>
+        <v>175.3</v>
       </c>
     </row>
     <row r="16">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>47.18</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>33.48</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>88.8</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>38.12</v>
+        <v>38.22</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>292</v>
+        <v>288.25</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>39.76</v>
+        <v>39.66</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>110.8</v>
+        <v>110.7</v>
       </c>
     </row>
     <row r="24">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>81.84999999999999</v>
+        <v>81.55</v>
       </c>
     </row>
     <row r="25">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>95.84999999999999</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>60.4</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1573</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>228.9</v>
+        <v>230.6</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>491.75</v>
+        <v>489.5</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>97.25</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="32">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>295.75</v>
+        <v>295.5</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>44.2</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>45.38</v>
+        <v>45.28</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>12.96</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="36">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>106.4</v>
+        <v>106.6</v>
       </c>
     </row>
     <row r="38">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>653.5</v>
+        <v>654</v>
       </c>
     </row>
     <row r="39">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>21.06</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>678.5</v>
+        <v>677.5</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>11332.5</v>
+        <v>11202.5</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1560</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>21.24</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="45">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>98.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>78.84999999999999</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>275.75</v>
+        <v>275</v>
       </c>
     </row>
     <row r="49">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>110.2</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="51">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>9.09</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>444.25</v>
+        <v>444</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>31.94</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>173.5</v>
+        <v>173.3</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>17.19</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>34.06</v>
+        <v>33.52</v>
       </c>
     </row>
     <row r="58">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>215</v>
+        <v>212.8</v>
       </c>
     </row>
     <row r="60">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.66</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="61">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>20.16</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="62">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>104.3</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>110.1</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="65">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>32.9</v>
+        <v>32.94</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>202.6</v>
+        <v>202.4</v>
       </c>
     </row>
     <row r="68">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.44</v>
+        <v>32.36</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>182.9</v>
+        <v>182.1</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>12.98</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="71">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>93.65000000000001</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1324</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="73">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>125.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="74">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>82.7</v>
+        <v>82.55</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>27.96</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>41.38</v>
+        <v>41.28</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>34.02</v>
+        <v>33.94</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>171.8</v>
+        <v>170.9</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>36.44</v>
+        <v>36.32</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>140</v>
+        <v>139.5</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>217.3</v>
+        <v>216.8</v>
       </c>
     </row>
     <row r="83">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KRDMD</t>
+          <t>KRDMA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>40.46</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="85">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KRDMA</t>
+          <t>KRDMD</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>41.3</v>
+        <v>40.34</v>
       </c>
     </row>
     <row r="86">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>114.1</v>
+        <v>113.9</v>
       </c>
     </row>
     <row r="87">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.4</v>
+        <v>25.42</v>
       </c>
     </row>
     <row r="88">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.43</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="89">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>224.9</v>
+        <v>224.2</v>
       </c>
     </row>
     <row r="90">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1212</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="91">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>246.1</v>
+        <v>246.4</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>447</v>
+        <v>445.75</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>109.9</v>
+        <v>110.3</v>
       </c>
     </row>
     <row r="95">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>100.4</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="96">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>612.5</v>
+        <v>611</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>11.12</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="99">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>64.09999999999999</v>
+        <v>64.25</v>
       </c>
     </row>
     <row r="100">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>354.5</v>
+        <v>354.25</v>
       </c>
     </row>
     <row r="101">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>108.3</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>219</v>
+        <v>219.4</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>114.5</v>
+        <v>114</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>205.4</v>
+        <v>204.9</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>83.25</v>
+        <v>82.34999999999999</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1673</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>22.32</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>36.56</v>
+        <v>36.42</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>107</v>
+        <v>108.1</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>352.75</v>
+        <v>351.5</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>8.16</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>144.6</v>
+        <v>145.8</v>
       </c>
     </row>
     <row r="113">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>325.5</v>
+        <v>324.25</v>
       </c>
     </row>
     <row r="114">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>49.02</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>13.94</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>42.52</v>
+        <v>42.32</v>
       </c>
     </row>
     <row r="117">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="118">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>13.54</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="119">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>5.9</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="120">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>197.2</v>
+        <v>196.9</v>
       </c>
     </row>
     <row r="122">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>216.3</v>
+        <v>215.7</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>25.92</v>
+        <v>25.72</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>309</v>
+        <v>307.75</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>13.81</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="127">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>15.8</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="128">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>10.74</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>13.53</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>49.24</v>
+        <v>49.12</v>
       </c>
     </row>
     <row r="131">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>15.18</v>
+        <v>15.13</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>113.1</v>
+        <v>113</v>
       </c>
     </row>
     <row r="134">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>53.45</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="135">
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="136">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>91.95</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>28.64</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>232.1</v>
+        <v>232</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>13692.5</v>
+        <v>13735</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>70.75</v>
+        <v>70.65000000000001</v>
       </c>
     </row>
     <row r="141">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>319.5</v>
+        <v>320.5</v>
       </c>
     </row>
     <row r="142">
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>290</v>
+        <v>289.75</v>
       </c>
     </row>
     <row r="143">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>146.1</v>
+        <v>145.6</v>
       </c>
     </row>
     <row r="144">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>9.82</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="145">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>46.62</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="147">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>47.6</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>87.34999999999999</v>
+        <v>87.25</v>
       </c>
     </row>
     <row r="150">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>57.85</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="151">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="152">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>17.71</v>
+        <v>17.98</v>
       </c>
     </row>
     <row r="153">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="154">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>60.25</v>
+        <v>60.45</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>84.40000000000001</v>
+        <v>84</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>12.13</v>
+        <v>12.32</v>
       </c>
     </row>
     <row r="157">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>35.52</v>
+        <v>35.38</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>14.23</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>81.95</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>38.08</v>
+        <v>38.06</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8.539999999999999</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="163">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>175.5</v>
+        <v>175.1</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>20.34</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>7.01</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>39.12</v>
+        <v>39.06</v>
       </c>
     </row>
     <row r="168">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>58.05</v>
+        <v>58</v>
       </c>
     </row>
     <row r="170">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>4937.5</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="172">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>3712.5</v>
+        <v>3717.5</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5692.5</v>
+        <v>5695</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>136.7</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1525</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>16.22</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>82.09999999999999</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="180">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>11.02</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="181">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>637.5</v>
+        <v>633.5</v>
       </c>
     </row>
     <row r="182">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>92.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>14.68</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="184">
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>23.38</v>
+        <v>23.06</v>
       </c>
     </row>
     <row r="185">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>20.6</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="186">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>61.9</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>31.98</v>
+        <v>31.84</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>144.8</v>
+        <v>146.9</v>
       </c>
     </row>
     <row r="189">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>39.7</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>257.5</v>
+        <v>254.5</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>13.59</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="193">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>28.76</v>
+        <v>28.68</v>
       </c>
     </row>
     <row r="194">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>13.88</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>28.38</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="196">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="198">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="199">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>26.54</v>
+        <v>26.46</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.44</v>
+        <v>23.54</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>30.88</v>
+        <v>30.82</v>
       </c>
     </row>
     <row r="202">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="203">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>19.44</v>
+        <v>19.42</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>84.34999999999999</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>19.65</v>
+        <v>19.67</v>
       </c>
     </row>
     <row r="206">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>144.4</v>
+        <v>144.1</v>
       </c>
     </row>
     <row r="208">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>115.9</v>
+        <v>116.2</v>
       </c>
     </row>
     <row r="209">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>65.95</v>
+        <v>65.75</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>43.1</v>
+        <v>42.98</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>5.98</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="213">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>80.34999999999999</v>
+        <v>80.15000000000001</v>
       </c>
     </row>
     <row r="214">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>40.72</v>
+        <v>40.76</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>32.1</v>
+        <v>31.86</v>
       </c>
     </row>
     <row r="216">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="217">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>12.38</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>73.3</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>622</v>
+        <v>646</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>11.39</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="221">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>14.7</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="222">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>41.04</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="223">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>55.05</v>
+        <v>55.15</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>7.35</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="225">
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>8</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="226">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="227">
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="H227" t="n">
-        <v>2800</v>
+        <v>2802.5</v>
       </c>
     </row>
     <row r="228">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>16.7</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="229">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>8.99</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="230">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>39.58</v>
+        <v>39.12</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>17.76</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>537.5</v>
+        <v>535</v>
       </c>
     </row>
     <row r="234">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>16.36</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="235">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>12.47</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>41.92</v>
+        <v>41.74</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>108.4</v>
+        <v>109.3</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>61.25</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="239">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="241">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>39.52</v>
+        <v>39.48</v>
       </c>
     </row>
     <row r="242">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>31.66</v>
+        <v>31.74</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>90.25</v>
+        <v>90.15000000000001</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>21.08</v>
+        <v>20.92</v>
       </c>
     </row>
     <row r="245">
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="246">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>86</v>
+        <v>86.05</v>
       </c>
     </row>
     <row r="248">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>6.33</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="249">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="250">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>412.5</v>
+        <v>412.25</v>
       </c>
     </row>
     <row r="251">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>262.75</v>
+        <v>261.25</v>
       </c>
     </row>
     <row r="253">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>21.26</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="254">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>24.24</v>
+        <v>24.16</v>
       </c>
     </row>
     <row r="255">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>1153</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>18.64</v>
+        <v>18.57</v>
       </c>
     </row>
     <row r="257">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>4.6</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="258">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>71.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="259">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>13.17</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="261">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="262">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.72</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>11.73</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="265">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>18.14</v>
+        <v>17.89</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>17.92</v>
+        <v>17.96</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>13.9</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="269">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>58.25</v>
+        <v>58.05</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>24.78</v>
+        <v>24.58</v>
       </c>
     </row>
     <row r="272">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>8.23</v>
+        <v>8.220000000000001</v>
       </c>
     </row>
     <row r="273">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>12.45</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>7.7</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>40.46</v>
+        <v>40.12</v>
       </c>
     </row>
     <row r="276">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>32.82</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="277">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.29</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>110.4</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="280">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="281">
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>20.98</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="283">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>25.62</v>
+        <v>25.58</v>
       </c>
     </row>
     <row r="284">
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>24.8</v>
+        <v>24.78</v>
       </c>
     </row>
     <row r="285">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>22.84</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>6.2</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="287">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>58.4</v>
+        <v>58.25</v>
       </c>
     </row>
     <row r="288">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>7.91</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>21.02</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>735</v>
+        <v>733.5</v>
       </c>
     </row>
     <row r="292">
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>11.63</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="293">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>45.22</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>54.45</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="295">
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>1000</v>
+        <v>999.5</v>
       </c>
     </row>
     <row r="296">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>18.82</v>
+        <v>18.77</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>24.04</v>
+        <v>23.92</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>215.5</v>
+        <v>215.2</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>9.69</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="301">
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="H301" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="302">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>7.35</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="303">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>84.7</v>
+        <v>84.95</v>
       </c>
     </row>
     <row r="305">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
     </row>
     <row r="306">
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="308">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="H308" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="309">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>115.4</v>
+        <v>115.9</v>
       </c>
     </row>
     <row r="311">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>7.21</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="313">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>6.27</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>40.44</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>15.17</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>15.44</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>10.24</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>93.2</v>
+        <v>93</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>263</v>
+        <v>261.5</v>
       </c>
     </row>
     <row r="320">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>5.89</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="321">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="324">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>6.26</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>246.6</v>
+        <v>245.9</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>12.2</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>8.1</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>14.19</v>
+        <v>14.06</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>327</v>
+        <v>325.75</v>
       </c>
     </row>
     <row r="330">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>39.98</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="331">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>98.25</v>
+        <v>98.55</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>32.8</v>
+        <v>32.96</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>15.03</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>16.93</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>62.9</v>
+        <v>63.15</v>
       </c>
     </row>
     <row r="336">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="337">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.84</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="338">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>144.1</v>
+        <v>143.7</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>14.15</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="340">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="H340" t="n">
-        <v>208.8</v>
+        <v>207.9</v>
       </c>
     </row>
     <row r="341">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>22.52</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>27.2</v>
+        <v>27.04</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>30.08</v>
+        <v>29.98</v>
       </c>
     </row>
     <row r="344">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>5.26</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="345">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>17.72</v>
+        <v>17.77</v>
       </c>
     </row>
     <row r="346">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>10.64</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="347">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>12.08</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.5</v>
+        <v>25.42</v>
       </c>
     </row>
     <row r="349">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="H349" t="n">
-        <v>12.8</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="350">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>5.48</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="351">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="H352" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="353">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="355">
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="H355" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>38.5</v>
+        <v>38.38</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>12.19</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="358">
@@ -12298,7 +12298,7 @@
         </is>
       </c>
       <c r="H359" t="n">
-        <v>16.28</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="360">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>8.779999999999999</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>147.4</v>
+        <v>147.9</v>
       </c>
     </row>
     <row r="363">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>23.62</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="364">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="H365" t="n">
-        <v>58.8</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="366">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>20.58</v>
+        <v>20.64</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>120.8</v>
+        <v>120.7</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>15.13</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="369">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>23.04</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="370">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>7.15</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>6.76</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="372">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>15.9</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="373">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>303.75</v>
+        <v>302.75</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>65.75</v>
+        <v>65.55</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>65.25</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="377">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>7.27</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="378">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>89.95</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>65.65000000000001</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>40.2</v>
+        <v>40.18</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.07</v>
+        <v>17.13</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>19.88</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>100.7</v>
+        <v>98.95</v>
       </c>
     </row>
     <row r="384">
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="H384" t="n">
-        <v>54.2</v>
+        <v>53.95</v>
       </c>
     </row>
     <row r="385">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="H386" t="n">
-        <v>6.62</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="387">
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="388">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>34.38</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="390">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>13.08</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="392">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>9.359999999999999</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="393">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>4.12</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>5.69</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="395">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.49</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="396">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="397">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>14.32</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="398">
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="H398" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="399">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>9.880000000000001</v>
+        <v>10</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>148.2</v>
+        <v>147.9</v>
       </c>
     </row>
     <row r="401">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>12.26</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="403">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>42.82</v>
+        <v>42.76</v>
       </c>
     </row>
     <row r="405">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>30.28</v>
+        <v>30.14</v>
       </c>
     </row>
     <row r="406">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>90.45</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>27.9</v>
+        <v>28.16</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>117.1</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="410">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>6.71</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="411">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>26.4</v>
+        <v>26.34</v>
       </c>
     </row>
     <row r="412">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>20.1</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="414">
@@ -14113,7 +14113,7 @@
         </is>
       </c>
       <c r="H414" t="n">
-        <v>6.24</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="415">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>46.96</v>
+        <v>46.82</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.24</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="417">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>47.28</v>
+        <v>46.42</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>8.51</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="420">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="421">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>39.48</v>
+        <v>39.42</v>
       </c>
     </row>
     <row r="422">
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="H422" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="423">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>15.37</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="424">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>47.52</v>
+        <v>48.32</v>
       </c>
     </row>
     <row r="425">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>21.88</v>
+        <v>21.94</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.72</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="427">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>21.36</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="429">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>11.41</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="431">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>318.75</v>
+        <v>316.5</v>
       </c>
     </row>
     <row r="433">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.76</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="434">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>7.63</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="435">
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="436">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>10.13</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="437">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>12.96</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="439">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>6.13</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="442">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="443">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>103.3</v>
+        <v>103.4</v>
       </c>
     </row>
     <row r="444">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>40</v>
+        <v>40.08</v>
       </c>
     </row>
     <row r="445">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>27.54</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>27.9</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>1529</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="450">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>181.1</v>
+        <v>180.5</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>13.43</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="454">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>5.15</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>17.58</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="457">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>20.38</v>
+        <v>20.44</v>
       </c>
     </row>
     <row r="458">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="H458" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="459">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>12.98</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>37.16</v>
+        <v>37.14</v>
       </c>
     </row>
     <row r="461">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>81.75</v>
+        <v>81.55</v>
       </c>
     </row>
     <row r="462">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="464">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>32</v>
+        <v>31.92</v>
       </c>
     </row>
     <row r="465">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="H465" t="n">
-        <v>11.03</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="466">
@@ -15829,7 +15829,7 @@
         </is>
       </c>
       <c r="H466" t="n">
-        <v>96</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="467">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="468">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>25.02</v>
+        <v>24.96</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>35.56</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>31.06</v>
+        <v>31.26</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>43.34</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="472">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="473">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>12.73</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="474">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>13.73</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="477">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>8.32</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.39</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="481">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>13.87</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="482">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.17</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>82.5</v>
+        <v>82.55</v>
       </c>
     </row>
     <row r="484">
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="485">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="486">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>96.2</v>
+        <v>96.05</v>
       </c>
     </row>
     <row r="487">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>18.04</v>
+        <v>17.97</v>
       </c>
     </row>
     <row r="488">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>10.38</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="489">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>26.38</v>
+        <v>26.42</v>
       </c>
     </row>
     <row r="491">
@@ -16687,7 +16687,7 @@
         </is>
       </c>
       <c r="H492" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="493">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>34.18</v>
+        <v>34.08</v>
       </c>
     </row>
     <row r="494">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>49.48</v>
+        <v>49.16</v>
       </c>
     </row>
     <row r="495">
@@ -16786,7 +16786,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="496">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="497">
@@ -16852,7 +16852,7 @@
         </is>
       </c>
       <c r="H497" t="n">
-        <v>222.5</v>
+        <v>223.1</v>
       </c>
     </row>
     <row r="498">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="499">
@@ -16918,7 +16918,7 @@
         </is>
       </c>
       <c r="H499" t="n">
-        <v>12.6</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="500">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="501">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>40.14</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.54</v>
+        <v>24.46</v>
       </c>
     </row>
     <row r="503">
@@ -17050,7 +17050,7 @@
         </is>
       </c>
       <c r="H503" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="504">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="H504" t="n">
-        <v>8.69</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="505">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>8.66</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="506">
@@ -17149,7 +17149,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="507">
@@ -17281,7 +17281,7 @@
         </is>
       </c>
       <c r="H510" t="n">
-        <v>4.68</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="511">
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="H512" t="n">
-        <v>34.72</v>
+        <v>34.42</v>
       </c>
     </row>
     <row r="513">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="H513" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="514">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>6.7</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="515">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>9.109999999999999</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="516">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>16.16</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>14.5</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>215.8</v>
+        <v>214.7</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>146.2</v>
+        <v>146</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>12.5</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="523">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="524">
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>7.63</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="526">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>13.98</v>
+        <v>14.03</v>
       </c>
     </row>
     <row r="527">
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="H528" t="n">
-        <v>16.98</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="529">
@@ -17941,7 +17941,7 @@
         </is>
       </c>
       <c r="H530" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="531">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="532">
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>5.21</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="533">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.36</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="534">
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="H534" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="535">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>6.11</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="536">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>22.86</v>
+        <v>22.74</v>
       </c>
     </row>
     <row r="537">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.32</v>
+        <v>25.34</v>
       </c>
     </row>
     <row r="538">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>156.3</v>
+        <v>156.7</v>
       </c>
     </row>
     <row r="539">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>62.5</v>
+        <v>62.35</v>
       </c>
     </row>
     <row r="540">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>25.6</v>
+        <v>25.64</v>
       </c>
     </row>
     <row r="542">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>15.12</v>
+        <v>15.41</v>
       </c>
     </row>
     <row r="544">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="H544" t="n">
-        <v>8.75</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="545">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>33.14</v>
+        <v>33.02</v>
       </c>
     </row>
     <row r="546">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>15.98</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="547">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>27.6</v>
+        <v>27.98</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>53.9</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="549">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="H549" t="n">
-        <v>10.12</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="550">
@@ -18634,7 +18634,7 @@
         </is>
       </c>
       <c r="H551" t="n">
-        <v>43.36</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="552">
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="H553" t="n">
-        <v>47.02</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="554">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="H554" t="n">
-        <v>4.72</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="555">
@@ -18766,7 +18766,7 @@
         </is>
       </c>
       <c r="H555" t="n">
-        <v>56</v>
+        <v>56.65</v>
       </c>
     </row>
     <row r="556">
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="H556" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="557">
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="H557" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="558">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="H558" t="n">
-        <v>120.2</v>
+        <v>119.6</v>
       </c>
     </row>
     <row r="559">
@@ -18898,7 +18898,7 @@
         </is>
       </c>
       <c r="H559" t="n">
-        <v>61.4</v>
+        <v>62.95</v>
       </c>
     </row>
     <row r="560">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>28.72</v>
+        <v>28.94</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="562">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="H562" t="n">
-        <v>23.9</v>
+        <v>23.76</v>
       </c>
     </row>
     <row r="563">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="H563" t="n">
-        <v>26.94</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="564">
@@ -19063,7 +19063,7 @@
         </is>
       </c>
       <c r="H564" t="n">
-        <v>13.04</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="565">
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="H565" t="n">
-        <v>8.039999999999999</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="566">
@@ -19129,7 +19129,7 @@
         </is>
       </c>
       <c r="H566" t="n">
-        <v>58.85</v>
+        <v>57.95</v>
       </c>
     </row>
     <row r="567">
@@ -19162,7 +19162,7 @@
         </is>
       </c>
       <c r="H567" t="n">
-        <v>78.34999999999999</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="568">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>6.63</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="569">
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>8.49</v>
+        <v>8.470000000000001</v>
       </c>
     </row>
     <row r="572">
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="573">
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="H573" t="n">
-        <v>18.49</v>
+        <v>18.47</v>
       </c>
     </row>
     <row r="574">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>26.64</v>
+        <v>26.52</v>
       </c>
     </row>
     <row r="575">
@@ -19426,7 +19426,7 @@
         </is>
       </c>
       <c r="H575" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="576">
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="H577" t="n">
-        <v>5.95</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="578">
@@ -19525,7 +19525,7 @@
         </is>
       </c>
       <c r="H578" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="579">
@@ -19558,7 +19558,7 @@
         </is>
       </c>
       <c r="H579" t="n">
-        <v>12.29</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="580">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.49</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="581">
@@ -19690,7 +19690,7 @@
         </is>
       </c>
       <c r="H583" t="n">
-        <v>6.42</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="584">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="H584" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="585">
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="H585" t="n">
-        <v>21.24</v>
+        <v>22.02</v>
       </c>
     </row>
     <row r="586">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>38.22</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>14.64</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>66.5</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>40.66</v>
+        <v>105.6</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>70.09999999999999</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>17.48</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>183.8</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>47.62</v>
+        <v>181.8</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>2.5</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>38.16</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>17.37</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>17.59</v>
+        <v>34.28</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>34.44</v>
+        <v>17.59</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>8.01</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>12.73</v>
+        <v>14.47</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>18.96</v>
+        <v>156.8</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>157.9</v>
+        <v>18.86</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>17.01</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>74.31</v>
+        <v>159.1</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>21.38</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>105.5</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>38.1</v>
+        <v>17.35</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>3.84</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>128.5</v>
+        <v>38.02</v>
       </c>
     </row>
     <row r="610">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>20.52</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>162.7</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>378.5</v>
+        <v>379.75</v>
       </c>
     </row>
     <row r="3">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>94.95</v>
+        <v>94.75</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>137.5</v>
+        <v>136.9</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>191.2</v>
+        <v>190.8</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>233.9</v>
+        <v>234.6</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>386.75</v>
+        <v>386.25</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>309.75</v>
+        <v>308.75</v>
       </c>
     </row>
     <row r="11">
@@ -805,7 +805,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ISBTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>420000</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="12">
@@ -838,7 +838,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2915000</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>ISBTR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>14.56</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>72.09999999999999</v>
+        <v>72.15000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>175.3</v>
+        <v>175.1</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>114.7</v>
+        <v>114.9</v>
       </c>
     </row>
     <row r="17">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>47.14</v>
+        <v>46.84</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>33.5</v>
+        <v>33.26</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>88.7</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>38.22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>288.25</v>
+        <v>282.25</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>39.66</v>
+        <v>39.62</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>110.7</v>
+        <v>110.1</v>
       </c>
     </row>
     <row r="24">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>81.55</v>
+        <v>81.34999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="26">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>95.7</v>
+        <v>95.55</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>60.2</v>
+        <v>59.85</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1569</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>230.6</v>
+        <v>232.1</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>489.5</v>
+        <v>487.5</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>96.7</v>
+        <v>96.55</v>
       </c>
     </row>
     <row r="32">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>295.5</v>
+        <v>294.75</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>43.98</v>
+        <v>44.08</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>45.28</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>12.94</v>
+        <v>12.89</v>
       </c>
     </row>
     <row r="36">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>106.6</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>21</v>
+        <v>21.02</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>677.5</v>
+        <v>675.5</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>11202.5</v>
+        <v>11122.5</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1547</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>21.3</v>
+        <v>21.32</v>
       </c>
     </row>
     <row r="45">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>98.40000000000001</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>78.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>275</v>
+        <v>274.5</v>
       </c>
     </row>
     <row r="49">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>109.6</v>
+        <v>109.4</v>
       </c>
     </row>
     <row r="51">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="53">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>31.9</v>
+        <v>31.84</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>173.3</v>
+        <v>172.6</v>
       </c>
     </row>
     <row r="56">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>33.52</v>
+        <v>33.48</v>
       </c>
     </row>
     <row r="58">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>116.1</v>
+        <v>115.9</v>
       </c>
     </row>
     <row r="59">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>212.8</v>
+        <v>211</v>
       </c>
     </row>
     <row r="60">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.65</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2455,16 +2455,16 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>20.1</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="62">
@@ -2488,16 +2488,16 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
+          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>6.11</v>
+        <v>20.04</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>104.4</v>
+        <v>104.3</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>109.5</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>258.5</v>
+        <v>261.75</v>
       </c>
     </row>
     <row r="66">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>32.94</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>202.4</v>
+        <v>202.1</v>
       </c>
     </row>
     <row r="68">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>182.1</v>
+        <v>181.9</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>13.01</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="71">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>93.2</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1317</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="73">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>82.55</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>27.92</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>41.28</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>33.94</v>
+        <v>33.82</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>170.9</v>
+        <v>170.1</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>36.32</v>
+        <v>36.26</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>139.5</v>
+        <v>140.9</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>216.8</v>
+        <v>217.1</v>
       </c>
     </row>
     <row r="83">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1690</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="84">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KRDMA</t>
+          <t>KRDMD</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>41.3</v>
+        <v>40.34</v>
       </c>
     </row>
     <row r="85">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KRDMD</t>
+          <t>KRDMA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>40.34</v>
+        <v>41.28</v>
       </c>
     </row>
     <row r="86">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.42</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="88">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1218</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>50.05</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>246.4</v>
+        <v>246.1</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>445.75</v>
+        <v>445.25</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>110.3</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="95">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>135.3</v>
+        <v>134.5</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>11.11</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="99">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>64.25</v>
+        <v>64</v>
       </c>
     </row>
     <row r="100">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>107.8</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>219.4</v>
+        <v>219</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>114</v>
+        <v>113.9</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>204.9</v>
+        <v>205.1</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>82.34999999999999</v>
+        <v>81.75</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1672</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>22.22</v>
+        <v>22.16</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>36.42</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>108.1</v>
+        <v>107.3</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>351.5</v>
+        <v>348</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>8.17</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>145.8</v>
+        <v>145.3</v>
       </c>
     </row>
     <row r="113">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>324.25</v>
+        <v>325</v>
       </c>
     </row>
     <row r="114">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>48.76</v>
+        <v>48.78</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>13.93</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>42.32</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="117">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>4.02</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="118">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="120">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>196.9</v>
+        <v>196.1</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>11.94</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>215.7</v>
+        <v>215.5</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>25.72</v>
+        <v>25.88</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>307.75</v>
+        <v>305.5</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>13.67</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="127">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>15.77</v>
+        <v>15.74</v>
       </c>
     </row>
     <row r="128">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>10.84</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>13.56</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>49.12</v>
+        <v>49.08</v>
       </c>
     </row>
     <row r="131">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>15.13</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="133">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>53.15</v>
+        <v>52.95</v>
       </c>
     </row>
     <row r="135">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>91.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>28.4</v>
+        <v>28.24</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>232</v>
+        <v>229.9</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>13735</v>
+        <v>13715</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>70.65000000000001</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="141">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>320.5</v>
+        <v>320.25</v>
       </c>
     </row>
     <row r="142">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>145.6</v>
+        <v>144.9</v>
       </c>
     </row>
     <row r="144">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>9.800000000000001</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="145">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>58.6</v>
+        <v>58.45</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>46.8</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="147">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="148">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>47.52</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>87.25</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="150">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>57.5</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="151">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>17.98</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="153">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>60.45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>12.32</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="157">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="158">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>35.38</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>14.18</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>81.90000000000001</v>
+        <v>82.15000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>38.06</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8.49</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="163">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="164">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>175.1</v>
+        <v>174.8</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>20.36</v>
+        <v>20.42</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="167">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>4.82</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>58</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>21.16</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>4950</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>25.54</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="173">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>69.5</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>3717.5</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5695</v>
+        <v>5675</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>136.5</v>
+        <v>136</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1515</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>16.15</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>82.3</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="180">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>10.96</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="181">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>633.5</v>
+        <v>631</v>
       </c>
     </row>
     <row r="182">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>92.40000000000001</v>
+        <v>92.65000000000001</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>14.69</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="184">
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>23.06</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="185">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>20.52</v>
+        <v>20.62</v>
       </c>
     </row>
     <row r="186">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>61.4</v>
+        <v>61.25</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>31.84</v>
+        <v>31.92</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>146.9</v>
+        <v>145.9</v>
       </c>
     </row>
     <row r="189">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>39.4</v>
+        <v>39.12</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>254.5</v>
+        <v>255</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>13.6</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="193">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>28.68</v>
+        <v>28.66</v>
       </c>
     </row>
     <row r="194">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>13.99</v>
+        <v>14</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>28.32</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="196">
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="197">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>26.46</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.54</v>
+        <v>23.58</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>30.82</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="202">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="203">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>19.42</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>84.7</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>19.67</v>
+        <v>19.63</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>45.14</v>
+        <v>45</v>
       </c>
     </row>
     <row r="207">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>116.2</v>
+        <v>116.8</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>65.75</v>
+        <v>65.55</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>42.98</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>5.94</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="213">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>80.15000000000001</v>
+        <v>80.25</v>
       </c>
     </row>
     <row r="214">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>40.76</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>31.86</v>
+        <v>31.78</v>
       </c>
     </row>
     <row r="216">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="217">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>12.4</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>73.2</v>
+        <v>73.05</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>11.38</v>
+        <v>11.33</v>
       </c>
     </row>
     <row r="221">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>14.68</v>
+        <v>14.66</v>
       </c>
     </row>
     <row r="222">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>40.92</v>
+        <v>40.78</v>
       </c>
     </row>
     <row r="223">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>55.15</v>
+        <v>54.95</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>7.23</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="225">
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>8.02</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="226">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>135</v>
+        <v>134.6</v>
       </c>
     </row>
     <row r="227">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>16.68</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="229">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>8.970000000000001</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="230">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.15</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>39.12</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>17.75</v>
+        <v>17.73</v>
       </c>
     </row>
     <row r="233">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>12.41</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>41.74</v>
+        <v>41.76</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>109.3</v>
+        <v>108.1</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>61.3</v>
+        <v>61.45</v>
       </c>
     </row>
     <row r="239">
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="H239" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="240">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="241">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>39.48</v>
+        <v>39.36</v>
       </c>
     </row>
     <row r="242">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>31.74</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>90.15000000000001</v>
+        <v>89.95</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>20.92</v>
+        <v>21.46</v>
       </c>
     </row>
     <row r="245">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.36</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="247">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>86.05</v>
+        <v>86</v>
       </c>
     </row>
     <row r="248">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="250">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>412.25</v>
+        <v>410.5</v>
       </c>
     </row>
     <row r="251">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>35.96</v>
+        <v>35.84</v>
       </c>
     </row>
     <row r="252">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>261.25</v>
+        <v>260.75</v>
       </c>
     </row>
     <row r="253">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>20.9</v>
+        <v>20.54</v>
       </c>
     </row>
     <row r="254">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>24.16</v>
+        <v>24.18</v>
       </c>
     </row>
     <row r="255">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>1144</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>18.57</v>
+        <v>18.56</v>
       </c>
     </row>
     <row r="257">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>4.59</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="258">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>71.59999999999999</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="259">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>13.4</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="261">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.8</v>
+        <v>28.76</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>125</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>11.67</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="265">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>132.6</v>
+        <v>124.7</v>
       </c>
     </row>
     <row r="266">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>17.89</v>
+        <v>17.68</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>17.96</v>
+        <v>17.89</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>13.91</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="269">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>5.99</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="270">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>58.05</v>
+        <v>57.95</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>24.58</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="272">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>8.220000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="273">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>7.64</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>40.12</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="276">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>32.8</v>
+        <v>32.76</v>
       </c>
     </row>
     <row r="277">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.2</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>109.8</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="280">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="281">
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>6.39</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="282">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>25.58</v>
+        <v>25.42</v>
       </c>
     </row>
     <row r="284">
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>24.78</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="285">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>22.82</v>
+        <v>22.78</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>6.19</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="287">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>58.25</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="288">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>7.88</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>20.8</v>
+        <v>20.78</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>733.5</v>
+        <v>732</v>
       </c>
     </row>
     <row r="292">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>45.14</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>54.9</v>
+        <v>55</v>
       </c>
     </row>
     <row r="295">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>44.84</v>
+        <v>44.76</v>
       </c>
     </row>
     <row r="297">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>23.92</v>
+        <v>23.94</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>215.2</v>
+        <v>214.7</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>9.68</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="301">
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="H301" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="302">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>7.37</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="303">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>84.95</v>
+        <v>85.55</v>
       </c>
     </row>
     <row r="305">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>5</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="306">
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="308">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>10.08</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="310">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>115.9</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="311">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>7.22</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="313">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>6.3</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>40.3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>15.23</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>15.4</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>10.29</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>93</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>261.5</v>
+        <v>260.5</v>
       </c>
     </row>
     <row r="320">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>5.87</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="321">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="322">
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="H322" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="323">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="324">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>6.25</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>245.9</v>
+        <v>247.1</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>12.18</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>8.07</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>14.06</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="329">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>39.84</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="331">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>98.55</v>
+        <v>98.05</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>32.96</v>
+        <v>32.84</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>14.94</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>16.86</v>
+        <v>16.88</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>63.15</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="336">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.81</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="338">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>143.7</v>
+        <v>146.5</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>14.09</v>
+        <v>14.11</v>
       </c>
     </row>
     <row r="340">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>22.5</v>
+        <v>22.44</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>27.04</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>29.98</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="344">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>5.25</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="345">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>17.77</v>
+        <v>17.81</v>
       </c>
     </row>
     <row r="346">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>10.62</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="347">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>12.03</v>
+        <v>12.04</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.42</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="349">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="H349" t="n">
-        <v>12.78</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="350">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>5.43</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="351">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="H352" t="n">
-        <v>10.24</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="353">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="355">
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="H355" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="356">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>38.38</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>12.16</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="358">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="H358" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="359">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>6.66</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="361">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>147.9</v>
+        <v>148.4</v>
       </c>
     </row>
     <row r="363">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>23.52</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="364">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>18.83</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="365">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="H365" t="n">
-        <v>58.65</v>
+        <v>58.55</v>
       </c>
     </row>
     <row r="366">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>20.64</v>
+        <v>20.66</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>120.7</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>15.1</v>
+        <v>15.04</v>
       </c>
     </row>
     <row r="369">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>7.12</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>6.75</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="372">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>15.87</v>
+        <v>15.85</v>
       </c>
     </row>
     <row r="373">
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="H373" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="374">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>302.75</v>
+        <v>302.5</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>65.55</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>65.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="377">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>7.26</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="378">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>90.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>65.3</v>
+        <v>65.75</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>40.18</v>
+        <v>40.28</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.13</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>19.95</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>98.95</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="384">
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="H384" t="n">
-        <v>53.95</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="385">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>108.3</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="386">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="H386" t="n">
-        <v>6.54</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="387">
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>4.89</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="388">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>34.4</v>
+        <v>34.42</v>
       </c>
     </row>
     <row r="390">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>13.05</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="392">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>9.35</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="393">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>5.73</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="395">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.38</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="396">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="397">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>14.31</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="398">
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="H398" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="399">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>147.9</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="401">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="H401" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="402">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>12.23</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="403">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>183.4</v>
+        <v>183</v>
       </c>
     </row>
     <row r="404">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>42.76</v>
+        <v>42.92</v>
       </c>
     </row>
     <row r="405">
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="407">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>90.25</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>28.16</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>116.6</v>
+        <v>116.5</v>
       </c>
     </row>
     <row r="410">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>6.73</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="411">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>26.34</v>
+        <v>26.36</v>
       </c>
     </row>
     <row r="412">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>20.16</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="414">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>46.82</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.2</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="417">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>46.42</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>8.460000000000001</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="420">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>28.3</v>
+        <v>28.16</v>
       </c>
     </row>
     <row r="421">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>39.42</v>
+        <v>39.24</v>
       </c>
     </row>
     <row r="422">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>15.35</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="424">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>48.32</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="425">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>21.94</v>
+        <v>21.84</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.71</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="427">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.3</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>21.34</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="429">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>8.890000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="430">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>11.38</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="431">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="432">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>316.5</v>
+        <v>316.25</v>
       </c>
     </row>
     <row r="433">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.73</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="434">
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="436">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="437">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>7.4</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="438">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>12.93</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="439">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>10.6</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="440">
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="441">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>6.11</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="442">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>103.4</v>
+        <v>102.6</v>
       </c>
     </row>
     <row r="444">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>40.08</v>
+        <v>40</v>
       </c>
     </row>
     <row r="445">
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="H445" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="446">
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>27.46</v>
+        <v>27.52</v>
       </c>
     </row>
     <row r="447">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>27.5</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>27.72</v>
+        <v>27.64</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>1526</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="450">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>180.5</v>
+        <v>180.8</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>13.36</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
     </row>
     <row r="454">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>5.18</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>17.5</v>
+        <v>17.45</v>
       </c>
     </row>
     <row r="457">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>20.44</v>
+        <v>20.32</v>
       </c>
     </row>
     <row r="458">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="H458" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="459">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>12.95</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>37.14</v>
+        <v>37.18</v>
       </c>
     </row>
     <row r="461">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>81.55</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="462">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="464">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>31.92</v>
+        <v>31.88</v>
       </c>
     </row>
     <row r="465">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="468">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>24.96</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>35.48</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>31.26</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>43.28</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="472">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="473">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>12.71</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="474">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>13.87</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="477">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="478">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>27.1</v>
+        <v>26.98</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>8.4</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.35</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="481">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>13.89</v>
+        <v>14.03</v>
       </c>
     </row>
     <row r="482">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.16</v>
+        <v>11.15</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>82.55</v>
+        <v>82.25</v>
       </c>
     </row>
     <row r="484">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="486">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>96.05</v>
+        <v>95.84999999999999</v>
       </c>
     </row>
     <row r="487">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>17.97</v>
+        <v>17.93</v>
       </c>
     </row>
     <row r="488">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>10.39</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="489">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>26.42</v>
+        <v>26.12</v>
       </c>
     </row>
     <row r="491">
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="H491" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="492">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>34.08</v>
+        <v>34</v>
       </c>
     </row>
     <row r="494">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>49.16</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="495">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>10.19</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="497">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="499">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="501">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>39.9</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.46</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="503">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="H504" t="n">
-        <v>8.94</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="505">
@@ -17149,7 +17149,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="507">
@@ -17248,7 +17248,7 @@
         </is>
       </c>
       <c r="H509" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="510">
@@ -17281,7 +17281,7 @@
         </is>
       </c>
       <c r="H510" t="n">
-        <v>5.09</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="511">
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="H512" t="n">
-        <v>34.42</v>
+        <v>34.16</v>
       </c>
     </row>
     <row r="513">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>6.71</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="515">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>9.09</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="516">
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="H516" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="517">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>16.08</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>14.59</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>214.7</v>
+        <v>215.8</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>146</v>
+        <v>145.6</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>12.66</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>72.8</v>
+        <v>72.75</v>
       </c>
     </row>
     <row r="523">
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>7.68</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="526">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>14.03</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="527">
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="H528" t="n">
-        <v>16.97</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="529">
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="H529" t="n">
-        <v>13.88</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="530">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="532">
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="533">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.31</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="534">
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="H534" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="535">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>6.09</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="536">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>22.74</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="537">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.34</v>
+        <v>25.36</v>
       </c>
     </row>
     <row r="538">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>156.7</v>
+        <v>156.5</v>
       </c>
     </row>
     <row r="539">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>62.35</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="540">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>25.64</v>
+        <v>25.52</v>
       </c>
     </row>
     <row r="542">
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="H542" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="543">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>15.41</v>
+        <v>15.29</v>
       </c>
     </row>
     <row r="544">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>33.02</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="546">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>15.94</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="547">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>27.98</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>55.6</v>
+        <v>55.55</v>
       </c>
     </row>
     <row r="549">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="H549" t="n">
-        <v>10.14</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="550">
@@ -18634,7 +18634,7 @@
         </is>
       </c>
       <c r="H551" t="n">
-        <v>43.04</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="552">
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="H553" t="n">
-        <v>46.98</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="554">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="H554" t="n">
-        <v>4.68</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="555">
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="H556" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="557">
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="H557" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="558">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>28.94</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="561">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="H563" t="n">
-        <v>26.7</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="564">
@@ -19063,7 +19063,7 @@
         </is>
       </c>
       <c r="H564" t="n">
-        <v>12.97</v>
+        <v>13.13</v>
       </c>
     </row>
     <row r="565">
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="H565" t="n">
-        <v>8.029999999999999</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="566">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>6.64</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="569">
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>8.470000000000001</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="572">
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="573">
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="H573" t="n">
-        <v>18.47</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="574">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>26.52</v>
+        <v>26.64</v>
       </c>
     </row>
     <row r="575">
@@ -19459,7 +19459,7 @@
         </is>
       </c>
       <c r="H576" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="577">
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="H577" t="n">
-        <v>5.96</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="578">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.67</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="582">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H582" t="n">
-        <v>10.21</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="583">
@@ -19690,7 +19690,7 @@
         </is>
       </c>
       <c r="H583" t="n">
-        <v>6.4</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="584">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>3.83</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>12.65</v>
+        <v>38.74</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>38.16</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>105.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>38.16</v>
+        <v>20.46</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>46.6</v>
+        <v>17.72</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>67.09999999999999</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>181.8</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>17.47</v>
+        <v>17.32</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>21.34</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>40.42</v>
+        <v>182.8</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>34.28</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>17.59</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>20.5</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>14.47</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>156.8</v>
+        <v>159.8</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>18.86</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>128.5</v>
+        <v>17.13</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>159.1</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>2.48</v>
+        <v>105.3</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>70.40000000000001</v>
+        <v>21.42</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>17.35</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>74.2</v>
+        <v>156</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>38.02</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>44.98</v>
+        <v>66.84999999999999</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>8.01</v>
+        <v>73.87</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>17.01</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>379.75</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2595</v>
+        <v>2592.5</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>94.75</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>190.8</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>234.6</v>
+        <v>234.1</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>386.25</v>
+        <v>386.75</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>308.75</v>
+        <v>309.25</v>
       </c>
     </row>
     <row r="11">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>14.45</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="13">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>420000</v>
+        <v>419915</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>72.15000000000001</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>175.1</v>
+        <v>174.7</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>114.9</v>
+        <v>115.7</v>
       </c>
     </row>
     <row r="17">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>46.84</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>33.26</v>
+        <v>33.34</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>38</v>
+        <v>38.06</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>282.25</v>
+        <v>283.75</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>39.62</v>
+        <v>39.66</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>110.1</v>
+        <v>110.7</v>
       </c>
     </row>
     <row r="24">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>81.34999999999999</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="25">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>63.9</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>95.55</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>59.85</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1571</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>232.1</v>
+        <v>229.6</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>487.5</v>
+        <v>488</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>96.55</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>294.75</v>
+        <v>297.5</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>44.08</v>
+        <v>43.96</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>45.4</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>12.89</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="36">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>106</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="38">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>21.02</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>675.5</v>
+        <v>679.5</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>11122.5</v>
+        <v>11090</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1560</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>21.32</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="45">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>98.25</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>78.09999999999999</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>274.5</v>
+        <v>275.75</v>
       </c>
     </row>
     <row r="49">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>36.96</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>109.4</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="51">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>9.300000000000001</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="52">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>631</v>
+        <v>631.5</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>444</v>
+        <v>445.25</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>31.84</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>172.6</v>
+        <v>173</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>17.14</v>
+        <v>17.19</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>33.48</v>
+        <v>33.56</v>
       </c>
     </row>
     <row r="58">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>115.9</v>
+        <v>116.1</v>
       </c>
     </row>
     <row r="59">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>211</v>
+        <v>211.3</v>
       </c>
     </row>
     <row r="60">
@@ -2455,16 +2455,16 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
+          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6.11</v>
+        <v>20.08</v>
       </c>
     </row>
     <row r="62">
@@ -2488,16 +2488,16 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>20.04</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>104.3</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="64">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>261.75</v>
+        <v>262.25</v>
       </c>
     </row>
     <row r="66">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.36</v>
+        <v>32.32</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>181.9</v>
+        <v>182</v>
       </c>
     </row>
     <row r="70">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>92.5</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="73">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>127.8</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="74">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>82.40000000000001</v>
+        <v>82.65000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>27.88</v>
+        <v>27.86</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>40.9</v>
+        <v>40.82</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>33.82</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>170.1</v>
+        <v>170.6</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>36.26</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>140.9</v>
+        <v>140.4</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>217.1</v>
+        <v>216.9</v>
       </c>
     </row>
     <row r="83">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1677</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="84">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KRDMD</t>
+          <t>KRDMB</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>40.34</v>
+        <v>113.9</v>
       </c>
     </row>
     <row r="85">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KRDMA</t>
+          <t>KRDMD</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>41.28</v>
+        <v>40.32</v>
       </c>
     </row>
     <row r="86">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KRDMB</t>
+          <t>KRDMA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>113.9</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="87">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.44</v>
+        <v>25.46</v>
       </c>
     </row>
     <row r="88">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.38</v>
+        <v>19.45</v>
       </c>
     </row>
     <row r="89">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>224.2</v>
+        <v>224</v>
       </c>
     </row>
     <row r="90">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1213</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>246.1</v>
+        <v>248.3</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>445.25</v>
+        <v>445</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>110.2</v>
+        <v>111.3</v>
       </c>
     </row>
     <row r="95">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>100.5</v>
+        <v>100.9</v>
       </c>
     </row>
     <row r="96">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>134.5</v>
+        <v>134.8</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>11.08</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="99">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>64</v>
+        <v>64.45</v>
       </c>
     </row>
     <row r="100">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>354.25</v>
+        <v>354.5</v>
       </c>
     </row>
     <row r="101">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>107.6</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="102">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>113.9</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>205.1</v>
+        <v>204.8</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>81.75</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1668</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>22.16</v>
+        <v>22.26</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>36.36</v>
+        <v>36.38</v>
       </c>
     </row>
     <row r="109">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>348</v>
+        <v>345.5</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>8.49</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>145.3</v>
+        <v>145.9</v>
       </c>
     </row>
     <row r="113">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="114">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>48.78</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>13.94</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>42.34</v>
+        <v>42.58</v>
       </c>
     </row>
     <row r="117">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="118">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>13.51</v>
+        <v>13.55</v>
       </c>
     </row>
     <row r="119">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>5.85</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="120">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>196.1</v>
+        <v>196</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>11.9</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>215.5</v>
+        <v>215.2</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>25.88</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>305.5</v>
+        <v>306.25</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>13.7</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="127">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>15.74</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="128">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>10.75</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>13.6</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>49.08</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="131">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>113</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="134">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>52.95</v>
+        <v>53</v>
       </c>
     </row>
     <row r="135">
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="136">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>91.09999999999999</v>
+        <v>91.34999999999999</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>28.24</v>
+        <v>28.26</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>229.9</v>
+        <v>232.9</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>13715</v>
+        <v>13797.5</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>70.8</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="141">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>320.25</v>
+        <v>319.75</v>
       </c>
     </row>
     <row r="142">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>144.9</v>
+        <v>144.7</v>
       </c>
     </row>
     <row r="144">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>9.75</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="145">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>58.45</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>47.14</v>
+        <v>47.06</v>
       </c>
     </row>
     <row r="147">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>6.3</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="148">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>87.09999999999999</v>
+        <v>87.15000000000001</v>
       </c>
     </row>
     <row r="150">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="151">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="152">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>17.91</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="153">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>83.8</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>12.26</v>
+        <v>12.32</v>
       </c>
     </row>
     <row r="157">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>35.14</v>
+        <v>36.04</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>14.14</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>82.15000000000001</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="161">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8.43</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="163">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>152</v>
+        <v>152.6</v>
       </c>
     </row>
     <row r="164">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>174.8</v>
+        <v>175.2</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>20.42</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>6.91</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>39.06</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="168">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>57.7</v>
+        <v>58.25</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>21.08</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>4990</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>25.3</v>
+        <v>25.42</v>
       </c>
     </row>
     <row r="173">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>69.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="174">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5675</v>
+        <v>5687.5</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>136</v>
+        <v>136.4</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1520</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>16.12</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>81.40000000000001</v>
+        <v>81.45</v>
       </c>
     </row>
     <row r="180">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>10.98</v>
+        <v>11</v>
       </c>
     </row>
     <row r="181">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>631</v>
+        <v>631.5</v>
       </c>
     </row>
     <row r="182">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>92.65000000000001</v>
+        <v>93.84999999999999</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>14.65</v>
+        <v>14.57</v>
       </c>
     </row>
     <row r="184">
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>22.86</v>
+        <v>22.94</v>
       </c>
     </row>
     <row r="185">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>20.62</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="186">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>61.25</v>
+        <v>61.35</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>31.92</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>145.9</v>
+        <v>147.3</v>
       </c>
     </row>
     <row r="189">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>39.12</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>13.56</v>
+        <v>13.46</v>
       </c>
     </row>
     <row r="193">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>28.66</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="194">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>14</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="195">
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="197">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.58</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>30.74</v>
+        <v>30.78</v>
       </c>
     </row>
     <row r="202">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="203">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>19.43</v>
+        <v>19.45</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>84.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>19.63</v>
+        <v>19.83</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>45</v>
+        <v>44.86</v>
       </c>
     </row>
     <row r="207">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>144.1</v>
+        <v>145.6</v>
       </c>
     </row>
     <row r="208">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>116.8</v>
+        <v>116.7</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>65.55</v>
+        <v>65.75</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>42.82</v>
+        <v>42.88</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>5.9</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="213">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>31.78</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="216">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>12.42</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>73.05</v>
+        <v>73.34999999999999</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>11.33</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="221">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>14.66</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="222">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>40.78</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="223">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>54.95</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>7.25</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="225">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>134.6</v>
+        <v>134.3</v>
       </c>
     </row>
     <row r="227">
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="H227" t="n">
-        <v>2802.5</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="228">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>16.67</v>
+        <v>16.69</v>
       </c>
     </row>
     <row r="229">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>8.94</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="230">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.14</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>39.2</v>
+        <v>39.04</v>
       </c>
     </row>
     <row r="232">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="234">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>16.33</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="235">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>12.38</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>41.76</v>
+        <v>41.64</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>108.1</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>61.45</v>
+        <v>61.55</v>
       </c>
     </row>
     <row r="239">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="241">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>39.36</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="242">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>31.5</v>
+        <v>31.66</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>89.95</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>21.46</v>
+        <v>21.42</v>
       </c>
     </row>
     <row r="245">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.37</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="247">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>86</v>
+        <v>86.15000000000001</v>
       </c>
     </row>
     <row r="248">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>6.31</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="249">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="250">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>410.5</v>
+        <v>412.5</v>
       </c>
     </row>
     <row r="251">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>35.84</v>
+        <v>36</v>
       </c>
     </row>
     <row r="252">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>260.75</v>
+        <v>261.25</v>
       </c>
     </row>
     <row r="253">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>20.54</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="254">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>24.18</v>
+        <v>24.36</v>
       </c>
     </row>
     <row r="255">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>1139</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>18.56</v>
+        <v>18.54</v>
       </c>
     </row>
     <row r="257">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="258">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>71.7</v>
+        <v>71.65000000000001</v>
       </c>
     </row>
     <row r="259">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>52.8</v>
+        <v>52.85</v>
       </c>
     </row>
     <row r="260">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>13.36</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="261">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.76</v>
+        <v>28.78</v>
       </c>
     </row>
     <row r="263">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>11.64</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="265">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>17.68</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>17.89</v>
+        <v>18.03</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>13.9</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="269">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>57.95</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>24.6</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="272">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>12.41</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>7.68</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="276">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>32.76</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="277">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.22</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>108.9</v>
+        <v>109.4</v>
       </c>
     </row>
     <row r="280">
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>6.38</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="282">
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>21.14</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="283">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>25.42</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="284">
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>24.7</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="285">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>22.78</v>
+        <v>22.74</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>6.18</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="287">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>58.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="288">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>6.18</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="289">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>7.86</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>20.78</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="292">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>45.44</v>
+        <v>45.82</v>
       </c>
     </row>
     <row r="294">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>44.76</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>18.77</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>23.94</v>
+        <v>23.92</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>214.7</v>
+        <v>215.4</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>9.69</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="301">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>7.47</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="303">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>85.55</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="305">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="306">
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="308">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="H308" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="309">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>10.04</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="310">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>115.1</v>
+        <v>114.8</v>
       </c>
     </row>
     <row r="311">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>6.26</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>40</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>15.2</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>15.38</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>10.28</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>92.59999999999999</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>260.5</v>
+        <v>261.75</v>
       </c>
     </row>
     <row r="320">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>434</v>
+        <v>436.75</v>
       </c>
     </row>
     <row r="322">
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="H322" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="323">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="324">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>6.21</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>247.1</v>
+        <v>248</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>12.17</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>8.050000000000001</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>13.99</v>
+        <v>14.06</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>325.75</v>
+        <v>326.25</v>
       </c>
     </row>
     <row r="330">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>98.05</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>32.84</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>14.9</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>16.88</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="336">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="337">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.8</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="338">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="H340" t="n">
-        <v>207.9</v>
+        <v>205.9</v>
       </c>
     </row>
     <row r="341">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>22.44</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>27.16</v>
+        <v>27.26</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="344">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>5.32</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="345">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>17.81</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="346">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>10.58</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="347">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>12.04</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.6</v>
+        <v>25.54</v>
       </c>
     </row>
     <row r="349">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>5.41</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="351">
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="H351" t="n">
-        <v>4.23</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="352">
@@ -12100,7 +12100,7 @@
         </is>
       </c>
       <c r="H353" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="354">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>265</v>
+        <v>265.5</v>
       </c>
     </row>
     <row r="355">
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="H355" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>38.24</v>
+        <v>38.28</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>12.13</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="358">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="H358" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="359">
@@ -12298,7 +12298,7 @@
         </is>
       </c>
       <c r="H359" t="n">
-        <v>16.3</v>
+        <v>16.23</v>
       </c>
     </row>
     <row r="360">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>6.71</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>8.710000000000001</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>148.4</v>
+        <v>148.8</v>
       </c>
     </row>
     <row r="363">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>23.46</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="364">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>18.78</v>
+        <v>18.82</v>
       </c>
     </row>
     <row r="365">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="H365" t="n">
-        <v>58.55</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="366">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>20.66</v>
+        <v>21.02</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>120.8</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>15.04</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="369">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="370">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>6.73</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="372">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>15.85</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="373">
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="H373" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="374">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>65.59999999999999</v>
+        <v>65.65000000000001</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>64.90000000000001</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="377">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>7.27</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="378">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>89.90000000000001</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>65.75</v>
+        <v>66.15000000000001</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>40.28</v>
+        <v>40.18</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.11</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>19.93</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>100.2</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="384">
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="H384" t="n">
-        <v>53.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="385">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>108.4</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="386">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="H386" t="n">
-        <v>6.52</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="387">
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="388">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>5.54</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="389">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>34.42</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="390">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="H390" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="391">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>13.06</v>
+        <v>13.09</v>
       </c>
     </row>
     <row r="392">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>9.300000000000001</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="393">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>5.64</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="395">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.33</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="396">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>14.25</v>
+        <v>14.26</v>
       </c>
     </row>
     <row r="398">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>9.94</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>147.5</v>
+        <v>147.9</v>
       </c>
     </row>
     <row r="401">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="H401" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="402">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>183</v>
+        <v>183.1</v>
       </c>
     </row>
     <row r="404">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>42.92</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="405">
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="407">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>89.90000000000001</v>
+        <v>90</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>28.12</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>116.5</v>
+        <v>116.4</v>
       </c>
     </row>
     <row r="410">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="414">
@@ -14113,7 +14113,7 @@
         </is>
       </c>
       <c r="H414" t="n">
-        <v>6.15</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="415">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>46.52</v>
+        <v>46.66</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.21</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="417">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>46.7</v>
+        <v>46.78</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>8.41</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="420">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>28.16</v>
+        <v>28.26</v>
       </c>
     </row>
     <row r="421">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>15.32</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="424">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>47.52</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="425">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>21.84</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.65</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="427">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.25</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>21.2</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="429">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>8.9</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="430">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>11.37</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="431">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="432">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>316.25</v>
+        <v>314</v>
       </c>
     </row>
     <row r="433">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>7.62</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="435">
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="436">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>10.08</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="437">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>7.38</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="438">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>10.61</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="440">
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="441">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>102.6</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="444">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>40</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="445">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>27.36</v>
+        <v>27.34</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>27.64</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>1519</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="450">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>180.8</v>
+        <v>181.8</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>13.35</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="454">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>22.1</v>
+        <v>22.08</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>17.45</v>
+        <v>17.51</v>
       </c>
     </row>
     <row r="457">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>20.32</v>
+        <v>20.24</v>
       </c>
     </row>
     <row r="458">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>12.92</v>
+        <v>12.96</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>37.18</v>
+        <v>37.14</v>
       </c>
     </row>
     <row r="461">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>81.59999999999999</v>
+        <v>81.75</v>
       </c>
     </row>
     <row r="462">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="464">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>31.88</v>
+        <v>31.96</v>
       </c>
     </row>
     <row r="465">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="H465" t="n">
-        <v>10.91</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="466">
@@ -15829,7 +15829,7 @@
         </is>
       </c>
       <c r="H466" t="n">
-        <v>96.09999999999999</v>
+        <v>96.15000000000001</v>
       </c>
     </row>
     <row r="467">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="468">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>24.9</v>
+        <v>25.04</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>35.4</v>
+        <v>35.44</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>30.9</v>
+        <v>31.28</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>42.78</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="472">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="473">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>12.68</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="474">
@@ -16093,7 +16093,7 @@
         </is>
       </c>
       <c r="H474" t="n">
-        <v>396.75</v>
+        <v>393.75</v>
       </c>
     </row>
     <row r="475">
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="476">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>13.77</v>
+        <v>13.47</v>
       </c>
     </row>
     <row r="477">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="478">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>26.98</v>
+        <v>27</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>8.33</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.33</v>
+        <v>12.32</v>
       </c>
     </row>
     <row r="481">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>14.03</v>
+        <v>14</v>
       </c>
     </row>
     <row r="482">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.15</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>82.25</v>
+        <v>81.75</v>
       </c>
     </row>
     <row r="484">
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="485">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="486">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>95.84999999999999</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="487">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>17.93</v>
+        <v>17.89</v>
       </c>
     </row>
     <row r="488">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>10.37</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="489">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>26.12</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="491">
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="H491" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="492">
@@ -16687,7 +16687,7 @@
         </is>
       </c>
       <c r="H492" t="n">
-        <v>73.09999999999999</v>
+        <v>75</v>
       </c>
     </row>
     <row r="493">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="494">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>48.94</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="495">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>10.16</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="497">
@@ -16852,7 +16852,7 @@
         </is>
       </c>
       <c r="H497" t="n">
-        <v>223.1</v>
+        <v>224</v>
       </c>
     </row>
     <row r="498">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="499">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="501">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>39.7</v>
+        <v>39.82</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.4</v>
+        <v>24.52</v>
       </c>
     </row>
     <row r="503">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="H504" t="n">
-        <v>8.960000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="505">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>8.6</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="506">
@@ -17149,7 +17149,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="507">
@@ -17182,7 +17182,7 @@
         </is>
       </c>
       <c r="H507" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="508">
@@ -17248,7 +17248,7 @@
         </is>
       </c>
       <c r="H509" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="510">
@@ -17281,7 +17281,7 @@
         </is>
       </c>
       <c r="H510" t="n">
-        <v>5.12</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="511">
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="512">
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="H512" t="n">
-        <v>34.16</v>
+        <v>34.08</v>
       </c>
     </row>
     <row r="513">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>6.7</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="515">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>9.07</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="516">
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="H516" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="517">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>16.1</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>14.82</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>215.8</v>
+        <v>217.1</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>145.6</v>
+        <v>146.1</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>12.59</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>72.75</v>
+        <v>72.84999999999999</v>
       </c>
     </row>
     <row r="523">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>13.97</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="527">
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="H528" t="n">
-        <v>17.09</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="529">
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="H529" t="n">
-        <v>13.8</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="530">
@@ -17941,7 +17941,7 @@
         </is>
       </c>
       <c r="H530" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="531">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="532">
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>5.18</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="533">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.32</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="534">
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="H534" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="535">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>6.07</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="536">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>22.7</v>
+        <v>22.78</v>
       </c>
     </row>
     <row r="537">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.36</v>
+        <v>25.38</v>
       </c>
     </row>
     <row r="538">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>156.5</v>
+        <v>154.3</v>
       </c>
     </row>
     <row r="539">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>62.3</v>
+        <v>62.35</v>
       </c>
     </row>
     <row r="540">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>25.52</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="542">
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="H542" t="n">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="543">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>15.29</v>
+        <v>15.18</v>
       </c>
     </row>
     <row r="544">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>33.1</v>
+        <v>33.36</v>
       </c>
     </row>
     <row r="546">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>15.87</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="547">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>27.92</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>55.55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="549">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="H549" t="n">
-        <v>10.15</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="550">
@@ -18601,7 +18601,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>11.01</v>
+        <v>11</v>
       </c>
     </row>
     <row r="551">
@@ -18634,7 +18634,7 @@
         </is>
       </c>
       <c r="H551" t="n">
-        <v>42.9</v>
+        <v>42.94</v>
       </c>
     </row>
     <row r="552">
@@ -18667,7 +18667,7 @@
         </is>
       </c>
       <c r="H552" t="n">
-        <v>156</v>
+        <v>159.5</v>
       </c>
     </row>
     <row r="553">
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="H553" t="n">
-        <v>46.88</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="554">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="H554" t="n">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="555">
@@ -18766,7 +18766,7 @@
         </is>
       </c>
       <c r="H555" t="n">
-        <v>56.65</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="556">
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="H556" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="557">
@@ -18898,7 +18898,7 @@
         </is>
       </c>
       <c r="H559" t="n">
-        <v>62.95</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="560">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>28.8</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="562">
@@ -19063,7 +19063,7 @@
         </is>
       </c>
       <c r="H564" t="n">
-        <v>13.13</v>
+        <v>13.08</v>
       </c>
     </row>
     <row r="565">
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="H565" t="n">
-        <v>8.02</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="566">
@@ -19129,7 +19129,7 @@
         </is>
       </c>
       <c r="H566" t="n">
-        <v>57.95</v>
+        <v>57.85</v>
       </c>
     </row>
     <row r="567">
@@ -19162,7 +19162,7 @@
         </is>
       </c>
       <c r="H567" t="n">
-        <v>82.2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="568">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>6.65</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="569">
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>8.51</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="572">
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="573">
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="H573" t="n">
-        <v>18.5</v>
+        <v>18.47</v>
       </c>
     </row>
     <row r="574">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>26.64</v>
+        <v>26.66</v>
       </c>
     </row>
     <row r="575">
@@ -19459,7 +19459,7 @@
         </is>
       </c>
       <c r="H576" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="577">
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="H577" t="n">
-        <v>5.97</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="578">
@@ -19525,7 +19525,7 @@
         </is>
       </c>
       <c r="H578" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="579">
@@ -19558,7 +19558,7 @@
         </is>
       </c>
       <c r="H579" t="n">
-        <v>12.4</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="580">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.5</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="581">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.69</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="582">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H582" t="n">
-        <v>10.19</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="583">
@@ -19690,7 +19690,7 @@
         </is>
       </c>
       <c r="H583" t="n">
-        <v>6.39</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="584">
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="H585" t="n">
-        <v>22.02</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="586">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>18.9</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>38.74</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="588">
@@ -19855,7 +19855,7 @@
         </is>
       </c>
       <c r="H588" t="n">
-        <v>40.16</v>
+        <v>40.04</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>8</v>
+        <v>157.5</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>20.46</v>
+        <v>73.66</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>17.72</v>
+        <v>17.56</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>38.1</v>
+        <v>17.34</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>2.51</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>17.32</v>
+        <v>21.28</v>
       </c>
     </row>
     <row r="595">
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="H595" t="n">
-        <v>47.54</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>182.8</v>
+        <v>34.94</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>38.2</v>
+        <v>160.8</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>3.82</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>128.5</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>44.98</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>159.8</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>70.40000000000001</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>17.13</v>
+        <v>38.22</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>34.48</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>105.3</v>
+        <v>183.5</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>21.42</v>
+        <v>66.55</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>14.46</v>
+        <v>20.48</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>156</v>
+        <v>17.73</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>12.63</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>66.84999999999999</v>
+        <v>17.05</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>73.87</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>17.58</v>
+        <v>38.52</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>381</v>
+        <v>379.25</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2592.5</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>95</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>136.9</v>
+        <v>136.6</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>191</v>
+        <v>190.7</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>234.1</v>
+        <v>233.5</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>386.75</v>
+        <v>385.5</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>309.25</v>
+        <v>308.75</v>
       </c>
     </row>
     <row r="11">
@@ -805,7 +805,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISBTR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2915000</v>
+        <v>419915</v>
       </c>
     </row>
     <row r="12">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>14.5</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISBTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>419915</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>174.7</v>
+        <v>174.2</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>115.7</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="17">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>47.1</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>33.34</v>
+        <v>33.12</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>88.5</v>
+        <v>88.15000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>38.06</v>
+        <v>37.92</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>283.75</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>39.66</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>110.7</v>
+        <v>110.8</v>
       </c>
     </row>
     <row r="24">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>64.09999999999999</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>96.09999999999999</v>
+        <v>96.05</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>59.6</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1587</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>229.6</v>
+        <v>234.5</v>
       </c>
     </row>
     <row r="30">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>96.40000000000001</v>
+        <v>95.95</v>
       </c>
     </row>
     <row r="32">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>297.5</v>
+        <v>296.25</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>43.96</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>45.58</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>12.94</v>
+        <v>12.96</v>
       </c>
     </row>
     <row r="36">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>105.9</v>
+        <v>105.7</v>
       </c>
     </row>
     <row r="38">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>654</v>
+        <v>654.5</v>
       </c>
     </row>
     <row r="39">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>21.08</v>
+        <v>21.06</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>679.5</v>
+        <v>677.5</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>11090</v>
+        <v>11085</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1565</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>21.3</v>
+        <v>21.28</v>
       </c>
     </row>
     <row r="45">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>98.09999999999999</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>275.75</v>
+        <v>274</v>
       </c>
     </row>
     <row r="49">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>109.5</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>631.5</v>
+        <v>630</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>445.25</v>
+        <v>443.75</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>31.8</v>
+        <v>31.84</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>173</v>
+        <v>172.9</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>17.19</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>33.56</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="58">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>211.3</v>
+        <v>212.3</v>
       </c>
     </row>
     <row r="60">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.640000000000001</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>20.08</v>
+        <v>20.02</v>
       </c>
     </row>
     <row r="62">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>6.11</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>104.4</v>
+        <v>104.1</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>109.2</v>
+        <v>109.9</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>262.25</v>
+        <v>260.75</v>
       </c>
     </row>
     <row r="66">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>32.8</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>202.1</v>
+        <v>202.2</v>
       </c>
     </row>
     <row r="68">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.32</v>
+        <v>32.24</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>182</v>
+        <v>181.9</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>12.98</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="71">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>93.59999999999999</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="72">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>127.7</v>
+        <v>127.6</v>
       </c>
     </row>
     <row r="74">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>82.65000000000001</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>27.86</v>
+        <v>27.82</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>40.82</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>33.8</v>
+        <v>34.06</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2000</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>170.6</v>
+        <v>170</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>36.36</v>
+        <v>36.34</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>140.4</v>
+        <v>140.1</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>216.9</v>
+        <v>216.7</v>
       </c>
     </row>
     <row r="83">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1690</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="84">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>113.9</v>
+        <v>113.8</v>
       </c>
     </row>
     <row r="85">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>40.32</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="86">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>41.32</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="87">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.46</v>
+        <v>25.42</v>
       </c>
     </row>
     <row r="88">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.45</v>
+        <v>19.41</v>
       </c>
     </row>
     <row r="89">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>224</v>
+        <v>223.8</v>
       </c>
     </row>
     <row r="90">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>50.1</v>
+        <v>49.96</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>248.3</v>
+        <v>246.5</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>111.3</v>
+        <v>110.7</v>
       </c>
     </row>
     <row r="95">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>100.9</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="96">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>134.8</v>
+        <v>134.7</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>64.45</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="100">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>354.5</v>
+        <v>354.75</v>
       </c>
     </row>
     <row r="101">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>107.5</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>219</v>
+        <v>217.2</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>114.3</v>
+        <v>113.7</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>204.8</v>
+        <v>203.8</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>82.2</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1672</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>22.26</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>36.38</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>107.3</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>345.5</v>
+        <v>344</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>8.300000000000001</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="112">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>326</v>
+        <v>324.25</v>
       </c>
     </row>
     <row r="114">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>48.82</v>
+        <v>48.86</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>13.91</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>42.58</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="117">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>13.55</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="119">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>5.84</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="120">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>196</v>
+        <v>195.8</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>11.93</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>215.2</v>
+        <v>216.3</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>25.92</v>
+        <v>25.98</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>306.25</v>
+        <v>306</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>13.62</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="127">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>15.78</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="128">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>10.98</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>13.65</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>49.3</v>
+        <v>49.36</v>
       </c>
     </row>
     <row r="131">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>15.19</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>113.2</v>
+        <v>113.1</v>
       </c>
     </row>
     <row r="134">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>53</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="135">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>91.34999999999999</v>
+        <v>91</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>28.26</v>
+        <v>28.22</v>
       </c>
     </row>
     <row r="138">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>13797.5</v>
+        <v>13745</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>70.90000000000001</v>
+        <v>70.34999999999999</v>
       </c>
     </row>
     <row r="141">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>144.7</v>
+        <v>140.8</v>
       </c>
     </row>
     <row r="144">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>58.6</v>
+        <v>58.45</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>47.06</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="147">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>47.6</v>
+        <v>47.36</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>87.15000000000001</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="150">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>57.7</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="151">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="152">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>17.88</v>
+        <v>17.74</v>
       </c>
     </row>
     <row r="153">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.1</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>60</v>
+        <v>59.75</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>84.2</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>12.32</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="157">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>36.04</v>
+        <v>36.14</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>14.16</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>82.59999999999999</v>
+        <v>82.75</v>
       </c>
     </row>
     <row r="161">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>38</v>
+        <v>38.04</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8.51</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="163">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>152.6</v>
+        <v>152.4</v>
       </c>
     </row>
     <row r="164">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>175.2</v>
+        <v>175.6</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>20.52</v>
+        <v>20.42</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>39.2</v>
+        <v>39.24</v>
       </c>
     </row>
     <row r="168">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>4.81</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>58.25</v>
+        <v>58.05</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>21.12</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>5100</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>25.42</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="173">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>3710</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5687.5</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>136.4</v>
+        <v>136.6</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1522</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>16.2</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="179">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>11</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="181">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>631.5</v>
+        <v>629.5</v>
       </c>
     </row>
     <row r="182">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>93.84999999999999</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>14.57</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="184">
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>22.94</v>
+        <v>22.98</v>
       </c>
     </row>
     <row r="185">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>20.6</v>
+        <v>20.56</v>
       </c>
     </row>
     <row r="186">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>61.35</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>32.14</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>147.3</v>
+        <v>146.7</v>
       </c>
     </row>
     <row r="189">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>39.2</v>
+        <v>39.14</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>254</v>
+        <v>252.25</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>13.46</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="193">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>28.7</v>
+        <v>28.64</v>
       </c>
     </row>
     <row r="194">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>13.98</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>28.28</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="196">
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="197">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="198">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>26.6</v>
+        <v>26.56</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.7</v>
+        <v>23.54</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>30.78</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="202">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>19.45</v>
+        <v>19.41</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>84.90000000000001</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>19.83</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>44.86</v>
+        <v>44.94</v>
       </c>
     </row>
     <row r="207">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>145.6</v>
+        <v>146.9</v>
       </c>
     </row>
     <row r="208">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>116.7</v>
+        <v>115.8</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>4.52</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>65.75</v>
+        <v>65.65000000000001</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>42.88</v>
+        <v>42.54</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>5.87</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="213">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>80.25</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="214">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>40.98</v>
+        <v>40.78</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>31.9</v>
+        <v>31.84</v>
       </c>
     </row>
     <row r="216">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="217">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>12.43</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>73.34999999999999</v>
+        <v>73.15000000000001</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>651</v>
+        <v>651.5</v>
       </c>
     </row>
     <row r="220">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>14.68</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="222">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>41.14</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="223">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>54.9</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>7.18</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="225">
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>7.99</v>
+        <v>8</v>
       </c>
     </row>
     <row r="226">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>134.3</v>
+        <v>133.7</v>
       </c>
     </row>
     <row r="227">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>16.69</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="229">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.15</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>39.04</v>
+        <v>38.88</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>17.73</v>
+        <v>17.78</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>537</v>
+        <v>536.5</v>
       </c>
     </row>
     <row r="234">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>12.35</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>41.64</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>108.2</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>61.55</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="239">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>39.76</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="242">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.38</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="247">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>86.15000000000001</v>
+        <v>86</v>
       </c>
     </row>
     <row r="248">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>6.33</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="249">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="250">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>412.5</v>
+        <v>412.75</v>
       </c>
     </row>
     <row r="251">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>261.25</v>
+        <v>262.25</v>
       </c>
     </row>
     <row r="253">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>20.7</v>
+        <v>20.38</v>
       </c>
     </row>
     <row r="254">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>24.36</v>
+        <v>24.26</v>
       </c>
     </row>
     <row r="255">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>18.54</v>
+        <v>18.52</v>
       </c>
     </row>
     <row r="257">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>4.58</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="258">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>52.85</v>
+        <v>52.55</v>
       </c>
     </row>
     <row r="260">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>13.17</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="261">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="262">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.78</v>
+        <v>28.72</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>126.4</v>
+        <v>126.5</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>11.6</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="265">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>124.7</v>
+        <v>124.2</v>
       </c>
     </row>
     <row r="266">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>17.7</v>
+        <v>17.72</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>18.03</v>
+        <v>18.02</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>13.92</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="269">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>24.68</v>
+        <v>26.04</v>
       </c>
     </row>
     <row r="272">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>8.199999999999999</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="273">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>12.43</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>7.65</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>40</v>
+        <v>39.94</v>
       </c>
     </row>
     <row r="276">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.23</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>109.4</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="280">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="281">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>25.56</v>
+        <v>25.54</v>
       </c>
     </row>
     <row r="284">
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>24.76</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="285">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>22.74</v>
+        <v>22.78</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>6.19</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="287">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>58.4</v>
+        <v>58.25</v>
       </c>
     </row>
     <row r="288">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>6.17</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="289">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>20.74</v>
+        <v>20.68</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>735</v>
+        <v>731</v>
       </c>
     </row>
     <row r="292">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>45.82</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>55</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="295">
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>999.5</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="296">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>45.1</v>
+        <v>44.94</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>18.8</v>
+        <v>18.79</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>23.92</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>215.4</v>
+        <v>214.8</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>9.710000000000001</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="301">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>7.49</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="303">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>86.09999999999999</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="305">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>4.99</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="306">
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="308">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>10.05</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="310">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>114.8</v>
+        <v>115</v>
       </c>
     </row>
     <row r="311">
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="312">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>7.15</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="313">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>6.28</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>39.68</v>
+        <v>39.96</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>15.31</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>15.36</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>10.31</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>92.7</v>
+        <v>92.34999999999999</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>261.75</v>
+        <v>260.25</v>
       </c>
     </row>
     <row r="320">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>5.84</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="321">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>436.75</v>
+        <v>433.25</v>
       </c>
     </row>
     <row r="322">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="324">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>6.24</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>248</v>
+        <v>247.7</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>12.2</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>8.07</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>14.06</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>326.25</v>
+        <v>325.25</v>
       </c>
     </row>
     <row r="330">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>39.58</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="331">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>98.40000000000001</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="332">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>14.94</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="334">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>63.4</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="336">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="338">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>146.5</v>
+        <v>147.2</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>14.11</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="340">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>22.52</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>27.26</v>
+        <v>27.12</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>29.9</v>
+        <v>29.66</v>
       </c>
     </row>
     <row r="344">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>5.33</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="345">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>17.76</v>
+        <v>17.62</v>
       </c>
     </row>
     <row r="346">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>10.64</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="347">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>12.05</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.54</v>
+        <v>25.52</v>
       </c>
     </row>
     <row r="349">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="H349" t="n">
-        <v>12.74</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="350">
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="H351" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="352">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="H352" t="n">
-        <v>10.25</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="353">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>265.5</v>
+        <v>265.75</v>
       </c>
     </row>
     <row r="355">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>38.28</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>12.15</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="358">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="H358" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="359">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>6.73</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>8.779999999999999</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>148.8</v>
+        <v>148.7</v>
       </c>
     </row>
     <row r="363">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>23.5</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="364">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>18.82</v>
+        <v>18.79</v>
       </c>
     </row>
     <row r="365">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="H365" t="n">
-        <v>58.75</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="366">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>21.02</v>
+        <v>20.94</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>120.5</v>
+        <v>121.5</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>15.08</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="369">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>7.13</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>6.76</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="372">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>15.94</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="373">
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="H373" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="374">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>302.5</v>
+        <v>302</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>65.65000000000001</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>64.5</v>
+        <v>64.55</v>
       </c>
     </row>
     <row r="377">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>7.26</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="378">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>66.15000000000001</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>40.18</v>
+        <v>40.22</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.18</v>
+        <v>17.19</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>19.95</v>
+        <v>19.92</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>100.6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="384">
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="H384" t="n">
-        <v>53.8</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="385">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>108.7</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="386">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>5.52</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="389">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>34.5</v>
+        <v>34.18</v>
       </c>
     </row>
     <row r="390">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="H390" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="391">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>13.09</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="392">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>5.61</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="395">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.34</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="396">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="397">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>14.26</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="398">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>9.949999999999999</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>147.9</v>
+        <v>147.7</v>
       </c>
     </row>
     <row r="401">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="H401" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="402">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>12.18</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="403">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>183.1</v>
+        <v>183.4</v>
       </c>
     </row>
     <row r="404">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>42.9</v>
+        <v>42.96</v>
       </c>
     </row>
     <row r="405">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>30.14</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="406">
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>4.92</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="407">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>90</v>
+        <v>89.95</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>28.1</v>
+        <v>27.98</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>116.4</v>
+        <v>115.8</v>
       </c>
     </row>
     <row r="410">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>6.71</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="411">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>26.36</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="412">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>20</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="414">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>46.66</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.22</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="417">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>46.78</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>8.43</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="420">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>28.26</v>
+        <v>28.14</v>
       </c>
     </row>
     <row r="421">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>39.24</v>
+        <v>39.28</v>
       </c>
     </row>
     <row r="422">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>15.36</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="424">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>21.9</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.67</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="427">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.28</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>21.16</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="429">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>8.93</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="430">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>11.39</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="431">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="432">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="433">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.7</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="434">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>7.68</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="435">
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="436">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>10.1</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="437">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>7.37</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="438">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>12.91</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="439">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>10.64</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="440">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>6.08</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="442">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>106.5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="444">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>39.98</v>
+        <v>39.96</v>
       </c>
     </row>
     <row r="445">
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>27.52</v>
+        <v>27.46</v>
       </c>
     </row>
     <row r="447">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>27.34</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>27.78</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>1527</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="450">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>181.8</v>
+        <v>181.1</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>13.4</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="454">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>22.08</v>
+        <v>22</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>17.51</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="457">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>20.24</v>
+        <v>20.28</v>
       </c>
     </row>
     <row r="458">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>12.96</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>37.14</v>
+        <v>37.26</v>
       </c>
     </row>
     <row r="461">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>81.75</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
     <row r="462">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="464">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>31.96</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="465">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="H465" t="n">
-        <v>10.97</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="466">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>25.04</v>
+        <v>24.98</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>35.44</v>
+        <v>35.46</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>31.28</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>42.6</v>
+        <v>42.58</v>
       </c>
     </row>
     <row r="472">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="473">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>12.72</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="474">
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="476">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>13.47</v>
+        <v>13.66</v>
       </c>
     </row>
     <row r="477">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="478">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>27</v>
+        <v>27.04</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>8.41</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.32</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="481">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>14</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="482">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.18</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>81.75</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="484">
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="485">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>96.09999999999999</v>
+        <v>95.84999999999999</v>
       </c>
     </row>
     <row r="487">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>17.89</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="488">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>10.48</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="489">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>26.88</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="491">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>48.98</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="495">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>10.24</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="497">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="499">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="501">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>39.82</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.52</v>
+        <v>24.46</v>
       </c>
     </row>
     <row r="503">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>8.609999999999999</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="506">
@@ -17149,7 +17149,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="507">
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="512">
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="H512" t="n">
-        <v>34.08</v>
+        <v>34.16</v>
       </c>
     </row>
     <row r="513">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="H513" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="514">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>9.1</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="516">
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="H516" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="517">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>14.69</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>217.1</v>
+        <v>216.6</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>146.1</v>
+        <v>145.6</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>12.62</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>72.84999999999999</v>
+        <v>73.05</v>
       </c>
     </row>
     <row r="523">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="524">
@@ -17743,7 +17743,7 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="525">
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>7.63</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="526">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>14.08</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="527">
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="H528" t="n">
-        <v>17.24</v>
+        <v>17.04</v>
       </c>
     </row>
     <row r="529">
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="H529" t="n">
-        <v>13.89</v>
+        <v>13.88</v>
       </c>
     </row>
     <row r="530">
@@ -17941,7 +17941,7 @@
         </is>
       </c>
       <c r="H530" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="531">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="532">
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>5.16</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="533">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.34</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="534">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>6.14</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="536">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>22.78</v>
+        <v>22.64</v>
       </c>
     </row>
     <row r="537">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.38</v>
+        <v>25.24</v>
       </c>
     </row>
     <row r="538">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>154.3</v>
+        <v>154.2</v>
       </c>
     </row>
     <row r="539">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>62.35</v>
+        <v>62.25</v>
       </c>
     </row>
     <row r="540">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="H540" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="541">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>25.6</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="542">
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="H542" t="n">
-        <v>4.35</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="543">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>15.18</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="544">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>33.36</v>
+        <v>33.56</v>
       </c>
     </row>
     <row r="546">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>15.9</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="547">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>27.88</v>
+        <v>27.76</v>
       </c>
     </row>
     <row r="548">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="H549" t="n">
-        <v>10.24</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="550">
@@ -18634,7 +18634,7 @@
         </is>
       </c>
       <c r="H551" t="n">
-        <v>42.94</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="552">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="H554" t="n">
-        <v>4.72</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="555">
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="H557" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="558">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>28.3</v>
+        <v>28.38</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="562">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="H562" t="n">
-        <v>23.76</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="563">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="H563" t="n">
-        <v>26.88</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="564">
@@ -19063,7 +19063,7 @@
         </is>
       </c>
       <c r="H564" t="n">
-        <v>13.08</v>
+        <v>13</v>
       </c>
     </row>
     <row r="565">
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="H565" t="n">
-        <v>7.94</v>
+        <v>8</v>
       </c>
     </row>
     <row r="566">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>6.59</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="569">
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>8.52</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="572">
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>4.65</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="573">
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="H573" t="n">
-        <v>18.47</v>
+        <v>18.45</v>
       </c>
     </row>
     <row r="574">
@@ -19459,7 +19459,7 @@
         </is>
       </c>
       <c r="H576" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="577">
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="H577" t="n">
-        <v>5.98</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="578">
@@ -19558,7 +19558,7 @@
         </is>
       </c>
       <c r="H579" t="n">
-        <v>12.29</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="580">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.44</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="581">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.72</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="582">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H582" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="583">
@@ -19690,7 +19690,7 @@
         </is>
       </c>
       <c r="H583" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="584">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>12.64</v>
+        <v>156.3</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>128.5</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>40.04</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>157.5</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>73.66</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>17.56</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>17.34</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>14.41</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>21.28</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="595">
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="H595" t="n">
-        <v>47.02</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>34.94</v>
+        <v>18.89</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>160.8</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>2.53</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>44.98</v>
+        <v>73.97</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>38.18</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>3.82</v>
+        <v>184.8</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>105.5</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>38.22</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>18.91</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>183.5</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>66.55</v>
+        <v>39.86</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>20.48</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>17.73</v>
+        <v>66.34999999999999</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>7.99</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>17.05</v>
+        <v>34.74</v>
       </c>
     </row>
     <row r="611">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>38.52</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>379.25</v>
+        <v>377.5</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2595</v>
+        <v>2592.5</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>94.5</v>
+        <v>94.45</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>136.6</v>
+        <v>136.4</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>190.7</v>
+        <v>190.2</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>233.5</v>
+        <v>233.4</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>385.5</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>308.75</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11">
@@ -805,7 +805,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ISBTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>419915</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="12">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>14.46</v>
+        <v>14.44</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISBTR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2915000</v>
+        <v>419915</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>72.2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>174.2</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>115.3</v>
+        <v>115.2</v>
       </c>
     </row>
     <row r="17">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>46.88</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>33.12</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>88.15000000000001</v>
+        <v>88.05</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>37.92</v>
+        <v>37.76</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>283</v>
+        <v>279.75</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>39.5</v>
+        <v>39.46</v>
       </c>
     </row>
     <row r="23">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>81.40000000000001</v>
+        <v>81.45</v>
       </c>
     </row>
     <row r="25">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>64</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>96.05</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>59.25</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1580</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>234.5</v>
+        <v>232.8</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>488</v>
+        <v>484.75</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>95.95</v>
+        <v>96.25</v>
       </c>
     </row>
     <row r="32">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>296.25</v>
+        <v>296.75</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>43.7</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>45.38</v>
+        <v>45.28</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>12.96</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="36">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>105.7</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="38">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>654.5</v>
+        <v>655</v>
       </c>
     </row>
     <row r="39">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>21.06</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>677.5</v>
+        <v>677</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>11085</v>
+        <v>11105</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1567</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>21.28</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="45">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>98.25</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>274</v>
+        <v>274.75</v>
       </c>
     </row>
     <row r="49">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>109</v>
+        <v>109.3</v>
       </c>
     </row>
     <row r="51">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>630</v>
+        <v>630.5</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>443.75</v>
+        <v>443</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>31.84</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>172.9</v>
+        <v>172.5</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>17.15</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>33.4</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="58">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>116.1</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>212.3</v>
+        <v>213.3</v>
       </c>
     </row>
     <row r="60">
@@ -2455,16 +2455,16 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>20.02</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="62">
@@ -2488,16 +2488,16 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
+          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>6.09</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>104.1</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>109.9</v>
+        <v>110.3</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>260.75</v>
+        <v>260.5</v>
       </c>
     </row>
     <row r="66">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>32.82</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>202.2</v>
+        <v>202.3</v>
       </c>
     </row>
     <row r="68">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.24</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>181.9</v>
+        <v>181.8</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>12.95</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="71">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>94.3</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>127.6</v>
+        <v>128.2</v>
       </c>
     </row>
     <row r="74">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>82.2</v>
+        <v>81.95</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>27.82</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>40.58</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>34.06</v>
+        <v>34.04</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>170</v>
+        <v>170.3</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>36.34</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>140.1</v>
+        <v>140.6</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>216.7</v>
+        <v>216.4</v>
       </c>
     </row>
     <row r="83">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1688</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="84">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KRDMB</t>
+          <t>KRDMA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>113.8</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="85">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KRDMD</t>
+          <t>KRDMB</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>40.16</v>
+        <v>113.3</v>
       </c>
     </row>
     <row r="86">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KRDMA</t>
+          <t>KRDMD</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>41.34</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="87">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.42</v>
+        <v>25.46</v>
       </c>
     </row>
     <row r="88">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.41</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="89">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>223.8</v>
+        <v>223.7</v>
       </c>
     </row>
     <row r="90">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1214</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>49.96</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>246.5</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>444</v>
+        <v>442.75</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>110.7</v>
+        <v>111.1</v>
       </c>
     </row>
     <row r="95">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>134.7</v>
+        <v>134.8</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>612</v>
+        <v>611.5</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>11</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="99">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>64.3</v>
+        <v>64.34999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>107.2</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>217.2</v>
+        <v>217.6</v>
       </c>
     </row>
     <row r="103">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>203.8</v>
+        <v>203.3</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>83.3</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>22.1</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>36.36</v>
+        <v>36.32</v>
       </c>
     </row>
     <row r="109">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>344</v>
+        <v>344.25</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>8.289999999999999</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>145.9</v>
+        <v>146</v>
       </c>
     </row>
     <row r="113">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>324.25</v>
+        <v>325</v>
       </c>
     </row>
     <row r="114">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>48.86</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>13.84</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="116">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="118">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>13.62</v>
+        <v>13.66</v>
       </c>
     </row>
     <row r="119">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>195.8</v>
+        <v>196.6</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>11.88</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>216.3</v>
+        <v>216.4</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>25.98</v>
+        <v>26.04</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>306</v>
+        <v>306.75</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>13.68</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="127">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>15.76</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="128">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>10.66</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>13.61</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>49.36</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="131">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>15.16</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>113.1</v>
+        <v>113.8</v>
       </c>
     </row>
     <row r="134">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>52.75</v>
+        <v>52.85</v>
       </c>
     </row>
     <row r="135">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>91</v>
+        <v>91.05</v>
       </c>
     </row>
     <row r="137">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>232.9</v>
+        <v>232.8</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>13745</v>
+        <v>13825</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>70.34999999999999</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="141">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>319.75</v>
+        <v>321</v>
       </c>
     </row>
     <row r="142">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>140.8</v>
+        <v>139.3</v>
       </c>
     </row>
     <row r="144">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>9.82</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="145">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>58.45</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>46.88</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="147">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>87.09999999999999</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="150">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="152">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>17.74</v>
+        <v>17.72</v>
       </c>
     </row>
     <row r="153">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>59.75</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>84.09999999999999</v>
+        <v>84.15000000000001</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>12.2</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="157">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>36.14</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>14.14</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="160">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>38.04</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8.52</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="163">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>175.6</v>
+        <v>175.1</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>20.42</v>
+        <v>20.46</v>
       </c>
     </row>
     <row r="166">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>39.24</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="168">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>58.05</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>21.14</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>5050</v>
+        <v>5065</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>25.26</v>
+        <v>25.16</v>
       </c>
     </row>
     <row r="173">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>70.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>3700</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5670</v>
+        <v>5680</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>136.6</v>
+        <v>136.4</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1520</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>16.12</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>81.45</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="180">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>11.01</v>
+        <v>11</v>
       </c>
     </row>
     <row r="181">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>629.5</v>
+        <v>629</v>
       </c>
     </row>
     <row r="182">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>93.3</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>14.56</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="184">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>20.56</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="186">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>61.3</v>
+        <v>61.25</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>32.16</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>146.7</v>
+        <v>145.3</v>
       </c>
     </row>
     <row r="189">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>39.14</v>
+        <v>38.88</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>252.25</v>
+        <v>252.5</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>13.41</v>
+        <v>13.45</v>
       </c>
     </row>
     <row r="193">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>14.02</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="196">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="199">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.54</v>
+        <v>23.64</v>
       </c>
     </row>
     <row r="201">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>19.41</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>84.5</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>19.87</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>44.94</v>
+        <v>44.86</v>
       </c>
     </row>
     <row r="207">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>146.9</v>
+        <v>146.8</v>
       </c>
     </row>
     <row r="208">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>115.8</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>4.51</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>65.65000000000001</v>
+        <v>65.75</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>42.54</v>
+        <v>42.64</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>5.88</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="213">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>40.78</v>
+        <v>41</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>31.84</v>
+        <v>31.86</v>
       </c>
     </row>
     <row r="216">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="217">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>12.42</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>73.15000000000001</v>
+        <v>73.25</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>651.5</v>
+        <v>641</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>11.37</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="221">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>14.69</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="222">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>41.18</v>
+        <v>41.16</v>
       </c>
     </row>
     <row r="223">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>54.8</v>
+        <v>54.85</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>7.32</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="225">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>133.7</v>
+        <v>133.1</v>
       </c>
     </row>
     <row r="227">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>16.62</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="229">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>38.88</v>
+        <v>38.82</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>17.78</v>
+        <v>17.79</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>536.5</v>
+        <v>531</v>
       </c>
     </row>
     <row r="234">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>12.28</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>41.6</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>107.8</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>61.6</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="239">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="241">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>39.6</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="242">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>90.09999999999999</v>
+        <v>90.34999999999999</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>21.42</v>
+        <v>21.56</v>
       </c>
     </row>
     <row r="245">
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="246">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>6.32</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="249">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="250">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>36</v>
+        <v>36.02</v>
       </c>
     </row>
     <row r="252">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>20.38</v>
+        <v>20.32</v>
       </c>
     </row>
     <row r="254">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>18.52</v>
+        <v>18.61</v>
       </c>
     </row>
     <row r="257">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>71.65000000000001</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="259">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>52.55</v>
+        <v>52.45</v>
       </c>
     </row>
     <row r="260">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>13.1</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="261">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="262">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.72</v>
+        <v>28.62</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>126.5</v>
+        <v>126.3</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>11.55</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="265">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>124.2</v>
+        <v>120.4</v>
       </c>
     </row>
     <row r="266">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>17.72</v>
+        <v>17.79</v>
       </c>
     </row>
     <row r="267">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>13.96</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="269">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>58.4</v>
+        <v>58.35</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>26.04</v>
+        <v>27.24</v>
       </c>
     </row>
     <row r="272">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>8.16</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="273">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>12.39</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>7.62</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>39.94</v>
+        <v>39.96</v>
       </c>
     </row>
     <row r="276">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>32.74</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="277">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.24</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>109.6</v>
+        <v>110</v>
       </c>
     </row>
     <row r="280">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>25.54</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="284">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>22.78</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>6.18</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="287">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>6.15</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="289">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>8</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>20.68</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="291">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>45.96</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>54.9</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="295">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>44.94</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>18.79</v>
+        <v>18.77</v>
       </c>
     </row>
     <row r="298">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>214.8</v>
+        <v>214</v>
       </c>
     </row>
     <row r="300">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>7.54</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="303">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>84.8</v>
+        <v>84.84999999999999</v>
       </c>
     </row>
     <row r="305">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="306">
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="308">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="H308" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="309">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>10.06</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="310">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>115</v>
+        <v>115.4</v>
       </c>
     </row>
     <row r="311">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>7.21</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="313">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>6.41</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>39.96</v>
+        <v>40.22</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>15.17</v>
+        <v>15.18</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>15.42</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="317">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>92.34999999999999</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="319">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>433.25</v>
+        <v>432</v>
       </c>
     </row>
     <row r="322">
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="H322" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="323">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>6.25</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>247.7</v>
+        <v>246.1</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>12.16</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>8.26</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>14.24</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>325.25</v>
+        <v>326.25</v>
       </c>
     </row>
     <row r="330">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>39.6</v>
+        <v>39.54</v>
       </c>
     </row>
     <row r="331">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>100.4</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>32.8</v>
+        <v>32.88</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>14.87</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>16.93</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>63.3</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="336">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="337">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.8</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="338">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>147.2</v>
+        <v>147.4</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>14.01</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="340">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>27.12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>29.66</v>
+        <v>29.78</v>
       </c>
     </row>
     <row r="344">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>5.34</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="345">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>17.62</v>
+        <v>17.63</v>
       </c>
     </row>
     <row r="346">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>10.6</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="347">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>12.07</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.52</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="349">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>5.37</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="351">
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="H351" t="n">
-        <v>4.2</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="352">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="H352" t="n">
-        <v>10.26</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="353">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>38.24</v>
+        <v>38.76</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>12.13</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="358">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="H358" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="359">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>6.72</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>8.91</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>148.7</v>
+        <v>149</v>
       </c>
     </row>
     <row r="363">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>23.44</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="364">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>18.79</v>
+        <v>19.01</v>
       </c>
     </row>
     <row r="365">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="H365" t="n">
-        <v>58.4</v>
+        <v>58.45</v>
       </c>
     </row>
     <row r="366">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>20.94</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>121.5</v>
+        <v>122.1</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>15.03</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="369">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>22.8</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="370">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>7.28</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>6.74</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="372">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>65.3</v>
+        <v>65.34999999999999</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>64.55</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="377">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>7.22</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="378">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>89.7</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>65.7</v>
+        <v>65.84999999999999</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>40.22</v>
+        <v>40.26</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.19</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>19.92</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>100</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="384">
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="H384" t="n">
-        <v>54.2</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="385">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="H386" t="n">
-        <v>6.54</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="387">
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>4.88</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="388">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>5.45</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="389">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>34.18</v>
+        <v>34.44</v>
       </c>
     </row>
     <row r="390">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="H390" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="391">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>13.1</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="392">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>9.359999999999999</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="393">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>5.58</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="395">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.3</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="396">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="397">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>14.24</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="398">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>9.93</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>147.7</v>
+        <v>148</v>
       </c>
     </row>
     <row r="401">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>12.19</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="403">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>183.4</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="404">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>30.3</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="406">
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>4.91</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="407">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>89.95</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>27.98</v>
+        <v>28.08</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>115.8</v>
+        <v>115.7</v>
       </c>
     </row>
     <row r="410">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>6.7</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="411">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>26.32</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="412">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>20.12</v>
+        <v>20.08</v>
       </c>
     </row>
     <row r="414">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>46.5</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.21</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="417">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>47.32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>8.42</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="420">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>28.14</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="421">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>39.28</v>
+        <v>39.38</v>
       </c>
     </row>
     <row r="422">
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="H422" t="n">
-        <v>4.11</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="423">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>15.31</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="424">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>47.68</v>
+        <v>47.82</v>
       </c>
     </row>
     <row r="425">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>21.92</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.65</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="427">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.26</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>21.14</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="429">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>11.4</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="431">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="432">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="433">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.65</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="434">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>7.6</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="435">
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="436">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>7.36</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="438">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>12.9</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="439">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>10.6</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="440">
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="441">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>6.07</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="442">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="443">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>39.96</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="445">
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="H445" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="446">
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>27.46</v>
+        <v>27.48</v>
       </c>
     </row>
     <row r="447">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>27.3</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>28.4</v>
+        <v>28.98</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>1520</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="450">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>181.1</v>
+        <v>180.5</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>13.35</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="454">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>5.13</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>22</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>17.5</v>
+        <v>17.56</v>
       </c>
     </row>
     <row r="457">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>20.28</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="458">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="H458" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="459">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>12.94</v>
+        <v>13</v>
       </c>
     </row>
     <row r="460">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>81.65000000000001</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="462">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="464">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>31.9</v>
+        <v>31.98</v>
       </c>
     </row>
     <row r="465">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="H465" t="n">
-        <v>10.94</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="466">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="468">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>24.98</v>
+        <v>25.16</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>35.46</v>
+        <v>36.04</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>42.58</v>
+        <v>42.68</v>
       </c>
     </row>
     <row r="472">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="473">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>12.71</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="474">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>13.66</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="477">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="478">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>27.04</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>8.44</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.21</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="481">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>13.93</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="482">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.17</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>82.2</v>
+        <v>82</v>
       </c>
     </row>
     <row r="484">
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="485">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="486">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>95.84999999999999</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="487">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>17.8</v>
+        <v>17.85</v>
       </c>
     </row>
     <row r="488">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>10.58</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="489">
@@ -16588,7 +16588,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="490">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>28.7</v>
+        <v>28.66</v>
       </c>
     </row>
     <row r="491">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>34.1</v>
+        <v>34.08</v>
       </c>
     </row>
     <row r="494">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>48.96</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="495">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="497">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>3.08</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="499">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="501">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>39.68</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.46</v>
+        <v>24.52</v>
       </c>
     </row>
     <row r="503">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="H504" t="n">
-        <v>9</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="505">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>8.550000000000001</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="506">
@@ -17149,7 +17149,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="507">
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="512">
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="H512" t="n">
-        <v>34.16</v>
+        <v>34.42</v>
       </c>
     </row>
     <row r="513">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="H513" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="514">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>6.69</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="515">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>9.08</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="516">
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="H516" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="517">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>16.13</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>14.75</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>216.6</v>
+        <v>217.2</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>145.6</v>
+        <v>146.7</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>12.61</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>73.05</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="523">
@@ -17743,7 +17743,7 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>4.23</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="525">
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="H528" t="n">
-        <v>17.04</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="529">
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="H529" t="n">
-        <v>13.88</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="530">
@@ -17941,7 +17941,7 @@
         </is>
       </c>
       <c r="H530" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="531">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="532">
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="533">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.35</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="534">
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="H534" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="535">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>6.13</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="536">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>22.64</v>
+        <v>22.72</v>
       </c>
     </row>
     <row r="537">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.24</v>
+        <v>25.38</v>
       </c>
     </row>
     <row r="538">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>154.2</v>
+        <v>153.9</v>
       </c>
     </row>
     <row r="539">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>62.25</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="540">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="H540" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="541">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>25.56</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="542">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>33.56</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="546">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>15.87</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="547">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>27.76</v>
+        <v>27.74</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="549">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="H549" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="550">
@@ -18634,7 +18634,7 @@
         </is>
       </c>
       <c r="H551" t="n">
-        <v>42.86</v>
+        <v>42.94</v>
       </c>
     </row>
     <row r="552">
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="H553" t="n">
-        <v>46.98</v>
+        <v>46.86</v>
       </c>
     </row>
     <row r="554">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="H554" t="n">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="555">
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="H556" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="557">
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="H557" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="558">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="H558" t="n">
-        <v>119.6</v>
+        <v>119.9</v>
       </c>
     </row>
     <row r="559">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>28.38</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="562">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="H562" t="n">
-        <v>23.52</v>
+        <v>23.82</v>
       </c>
     </row>
     <row r="563">
@@ -19063,7 +19063,7 @@
         </is>
       </c>
       <c r="H564" t="n">
-        <v>13</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="565">
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="H565" t="n">
-        <v>8</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="566">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>6.55</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="569">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="H569" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="570">
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>4.64</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="573">
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="H573" t="n">
-        <v>18.45</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="574">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>26.66</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="575">
@@ -19459,7 +19459,7 @@
         </is>
       </c>
       <c r="H576" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="577">
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="H577" t="n">
-        <v>5.89</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="578">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.390000000000001</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="581">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.67</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="582">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H582" t="n">
-        <v>10.2</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="583">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>156.3</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>44.98</v>
+        <v>17.61</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>8.01</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="589">
@@ -19888,7 +19888,7 @@
         </is>
       </c>
       <c r="H589" t="n">
-        <v>17.1</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>38.2</v>
+        <v>47.04</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>2.51</v>
+        <v>18.79</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>17.7</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>21.4</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>14.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>47.22</v>
+        <v>38.14</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>18.89</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>3.81</v>
+        <v>34.88</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>20.4</v>
+        <v>155.4</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>73.97</v>
+        <v>21.48</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>128.5</v>
+        <v>20.46</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>184.8</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="602">
@@ -20317,7 +20317,7 @@
         </is>
       </c>
       <c r="H602" t="n">
-        <v>161.5</v>
+        <v>160.5</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>17.3</v>
+        <v>105.2</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>12.61</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>17.57</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>39.86</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>105.4</v>
+        <v>17.81</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>66.34999999999999</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>38.44</v>
+        <v>183.7</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>34.74</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>70.40000000000001</v>
+        <v>74.06999999999999</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>38.16</v>
+        <v>65.55</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>377.5</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2592.5</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>94.45</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>190.2</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>233.4</v>
+        <v>234.3</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>385</v>
+        <v>383.25</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>309</v>
+        <v>310.25</v>
       </c>
     </row>
     <row r="11">
@@ -805,7 +805,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2915000</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="12">
@@ -838,7 +838,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>14.44</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="13">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>72</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>174.5</v>
+        <v>175.3</v>
       </c>
     </row>
     <row r="16">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>46.68</v>
+        <v>46.78</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>32.82</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>88.05</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>37.76</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>279.75</v>
+        <v>278.25</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>39.46</v>
+        <v>39.24</v>
       </c>
     </row>
     <row r="23">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>81.45</v>
+        <v>81.75</v>
       </c>
     </row>
     <row r="25">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>64.09999999999999</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="26">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>95.90000000000001</v>
+        <v>95.84999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>59.3</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>232.8</v>
+        <v>229.8</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>484.75</v>
+        <v>488</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>96.25</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="32">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>296.75</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>43.98</v>
+        <v>44.02</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>45.28</v>
+        <v>45.26</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>12.99</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="36">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>105.9</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="38">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="39">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>21.08</v>
+        <v>21.06</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>11105</v>
+        <v>11082.5</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>21.34</v>
+        <v>21.32</v>
       </c>
     </row>
     <row r="45">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>98.3</v>
+        <v>98.55</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>79.2</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>274.75</v>
+        <v>277.25</v>
       </c>
     </row>
     <row r="49">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>109.3</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="51">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>630.5</v>
+        <v>631</v>
       </c>
     </row>
     <row r="53">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>31.82</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>172.5</v>
+        <v>172.6</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>17.01</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>33.54</v>
+        <v>33.52</v>
       </c>
     </row>
     <row r="58">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>116</v>
+        <v>116.3</v>
       </c>
     </row>
     <row r="59">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>213.3</v>
+        <v>213.4</v>
       </c>
     </row>
     <row r="60">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.619999999999999</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="61">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>20</v>
+        <v>20.02</v>
       </c>
     </row>
     <row r="63">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>110.3</v>
+        <v>110.9</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>260.5</v>
+        <v>261</v>
       </c>
     </row>
     <row r="66">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>202.3</v>
+        <v>202.4</v>
       </c>
     </row>
     <row r="68">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.5</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>181.8</v>
+        <v>181.7</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>12.87</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="71">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>94</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="73">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>128.2</v>
+        <v>127.9</v>
       </c>
     </row>
     <row r="74">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>81.95</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>27.78</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>40.4</v>
+        <v>40.26</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>34.04</v>
+        <v>34.16</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1998</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="79">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>36.4</v>
+        <v>36.64</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>140.6</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>216.4</v>
+        <v>217.4</v>
       </c>
     </row>
     <row r="83">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1691</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="84">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KRDMA</t>
+          <t>KRDMD</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>41.32</v>
+        <v>39.92</v>
       </c>
     </row>
     <row r="85">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KRDMD</t>
+          <t>KRDMA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>39.98</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="87">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.46</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="88">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.38</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="89">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>223.7</v>
+        <v>224</v>
       </c>
     </row>
     <row r="90">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1218</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>49.94</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>244</v>
+        <v>243.4</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>442.75</v>
+        <v>444</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>111.1</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="95">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>100.7</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="96">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>134.8</v>
+        <v>134.9</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>611.5</v>
+        <v>612.5</v>
       </c>
     </row>
     <row r="98">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>64.34999999999999</v>
+        <v>63.85</v>
       </c>
     </row>
     <row r="100">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>107.4</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>217.6</v>
+        <v>218</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>113.7</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>203.3</v>
+        <v>203.2</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1668</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>22.06</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>36.32</v>
+        <v>36.28</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>108.6</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>344.25</v>
+        <v>343.75</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>146</v>
+        <v>145.4</v>
       </c>
     </row>
     <row r="113">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>325</v>
+        <v>324.5</v>
       </c>
     </row>
     <row r="114">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>48.94</v>
+        <v>49.08</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>13.8</v>
+        <v>13.82</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>42.5</v>
+        <v>42.46</v>
       </c>
     </row>
     <row r="117">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="118">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>13.66</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="119">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>5.87</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="120">
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="121">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>196.6</v>
+        <v>196.9</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>11.89</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>216.4</v>
+        <v>217</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>26.04</v>
+        <v>26.12</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>306.75</v>
+        <v>306.25</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>13.69</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="127">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>15.9</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="128">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>10.68</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>13.59</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>49.34</v>
+        <v>49.48</v>
       </c>
     </row>
     <row r="131">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>15.15</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>113.8</v>
+        <v>113.5</v>
       </c>
     </row>
     <row r="134">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>52.85</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="135">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>91.05</v>
+        <v>91</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>28.22</v>
+        <v>28.26</v>
       </c>
     </row>
     <row r="138">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>13825</v>
+        <v>13932.5</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>70.3</v>
+        <v>70.34999999999999</v>
       </c>
     </row>
     <row r="141">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="142">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>139.3</v>
+        <v>138.7</v>
       </c>
     </row>
     <row r="144">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>9.84</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="145">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>58.5</v>
+        <v>58.45</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>46.9</v>
+        <v>46.84</v>
       </c>
     </row>
     <row r="147">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="148">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>47.36</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>87.7</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="150">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>17.72</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="153">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.119999999999999</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="154">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>59.5</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>84.15000000000001</v>
+        <v>84</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>12.23</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="157">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>14.15</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>82.75</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="161">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>38.16</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8.56</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="163">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>152.4</v>
+        <v>152.5</v>
       </c>
     </row>
     <row r="164">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>175.1</v>
+        <v>175.6</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>20.46</v>
+        <v>20.44</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>6.91</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>39.2</v>
+        <v>39.36</v>
       </c>
     </row>
     <row r="168">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>4.89</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>58.1</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>21.1</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>5065</v>
+        <v>5045</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>25.16</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="173">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>70.40000000000001</v>
+        <v>71.25</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>3710</v>
+        <v>3715</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5680</v>
+        <v>5672.5</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>136.4</v>
+        <v>136.3</v>
       </c>
     </row>
     <row r="177">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>16.08</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>82.2</v>
+        <v>82.45</v>
       </c>
     </row>
     <row r="180">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>94.09999999999999</v>
+        <v>93.65000000000001</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>14.7</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="184">
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>22.98</v>
+        <v>22.96</v>
       </c>
     </row>
     <row r="185">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>20.74</v>
+        <v>20.64</v>
       </c>
     </row>
     <row r="186">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>61.25</v>
+        <v>61.35</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>32.2</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>145.3</v>
+        <v>147.1</v>
       </c>
     </row>
     <row r="189">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>38.88</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>252.5</v>
+        <v>252.75</v>
       </c>
     </row>
     <row r="192">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>28.64</v>
+        <v>28.66</v>
       </c>
     </row>
     <row r="194">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>14.04</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>28.5</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="196">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>26.56</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.64</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="201">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>19.48</v>
+        <v>19.21</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>84.7</v>
+        <v>84.75</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>19.84</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>44.86</v>
+        <v>45.26</v>
       </c>
     </row>
     <row r="207">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>146.8</v>
+        <v>147.4</v>
       </c>
     </row>
     <row r="208">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>114.2</v>
+        <v>112.1</v>
       </c>
     </row>
     <row r="209">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>65.75</v>
+        <v>65.65000000000001</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>42.64</v>
+        <v>42.68</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>5.99</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="213">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>80.09999999999999</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="214">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>41</v>
+        <v>41.08</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>31.86</v>
+        <v>31.84</v>
       </c>
     </row>
     <row r="216">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="217">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>12.43</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>73.25</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>641</v>
+        <v>633.5</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>11.47</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="221">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>14.74</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="222">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>41.16</v>
+        <v>41.12</v>
       </c>
     </row>
     <row r="223">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>54.85</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>7.42</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="225">
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>8</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="226">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>133.1</v>
+        <v>133</v>
       </c>
     </row>
     <row r="227">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>16.68</v>
+        <v>16.64</v>
       </c>
     </row>
     <row r="229">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>8.93</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="230">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.14</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>38.82</v>
+        <v>38.78</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>17.79</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>531</v>
+        <v>530.5</v>
       </c>
     </row>
     <row r="234">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>12.25</v>
+        <v>12.27</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>41.54</v>
+        <v>41.68</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>107.9</v>
+        <v>108</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>61.7</v>
+        <v>61.75</v>
       </c>
     </row>
     <row r="239">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>39.78</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="242">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>31.66</v>
+        <v>31.52</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>90.34999999999999</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>21.56</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="245">
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="246">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>86</v>
+        <v>86.05</v>
       </c>
     </row>
     <row r="248">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>6.31</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="249">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="250">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>412.75</v>
+        <v>413.5</v>
       </c>
     </row>
     <row r="251">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>36.02</v>
+        <v>36</v>
       </c>
     </row>
     <row r="252">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>262.25</v>
+        <v>261.25</v>
       </c>
     </row>
     <row r="253">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>20.32</v>
+        <v>20.28</v>
       </c>
     </row>
     <row r="254">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>24.26</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="255">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>18.61</v>
+        <v>18.66</v>
       </c>
     </row>
     <row r="257">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>4.59</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="258">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>52.45</v>
+        <v>52.35</v>
       </c>
     </row>
     <row r="260">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>13.12</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="261">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="262">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.62</v>
+        <v>28.68</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>126.3</v>
+        <v>126.5</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>11.56</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="265">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>120.4</v>
+        <v>123.4</v>
       </c>
     </row>
     <row r="266">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>17.79</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>18.02</v>
+        <v>18.01</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>14.02</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="269">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>5.98</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="270">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>58.35</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>27.24</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="272">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>8.18</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="273">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>12.4</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>7.65</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>39.96</v>
+        <v>39.92</v>
       </c>
     </row>
     <row r="276">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>32.68</v>
+        <v>32.72</v>
       </c>
     </row>
     <row r="277">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>110</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="280">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>25.66</v>
+        <v>25.72</v>
       </c>
     </row>
     <row r="284">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>22.84</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>6.21</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="287">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>58.25</v>
+        <v>58.55</v>
       </c>
     </row>
     <row r="288">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>6.16</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="289">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>8.09</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>20.7</v>
+        <v>20.72</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>731</v>
+        <v>732.5</v>
       </c>
     </row>
     <row r="292">
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>11.6</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="293">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>45.38</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>55.1</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="295">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>46.1</v>
+        <v>46.56</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>18.77</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>23.88</v>
+        <v>23.86</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>214</v>
+        <v>217.7</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>9.68</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="301">
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="H301" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="302">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>7.59</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="303">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>84.84999999999999</v>
+        <v>85.05</v>
       </c>
     </row>
     <row r="305">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="306">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="H308" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="309">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>10.07</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="310">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>115.4</v>
+        <v>114.6</v>
       </c>
     </row>
     <row r="311">
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="312">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>7.22</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="313">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>6.31</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>40.22</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>15.18</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>15.5</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>10.1</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>92.09999999999999</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>260.25</v>
+        <v>258</v>
       </c>
     </row>
     <row r="320">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="322">
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="H322" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="323">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="324">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>6.26</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>246.1</v>
+        <v>246.9</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>12.17</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>8.31</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>14.29</v>
+        <v>14.33</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>326.25</v>
+        <v>326.5</v>
       </c>
     </row>
     <row r="330">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>39.54</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="331">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>100.6</v>
+        <v>98.59999999999999</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>32.88</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>14.85</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>17.03</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>63.5</v>
+        <v>63.65</v>
       </c>
     </row>
     <row r="336">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>147.4</v>
+        <v>149.2</v>
       </c>
     </row>
     <row r="339">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>22.5</v>
+        <v>22.56</v>
       </c>
     </row>
     <row r="342">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>29.78</v>
+        <v>29.66</v>
       </c>
     </row>
     <row r="344">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="345">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>17.63</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="346">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>10.61</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="347">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.66</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="349">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="H349" t="n">
-        <v>12.73</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="350">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>5.36</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="351">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>265.75</v>
+        <v>264</v>
       </c>
     </row>
     <row r="355">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>38.76</v>
+        <v>38.64</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>12.12</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="358">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="H358" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="359">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>6.73</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>8.869999999999999</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>149</v>
+        <v>149.4</v>
       </c>
     </row>
     <row r="363">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>23.5</v>
+        <v>23.54</v>
       </c>
     </row>
     <row r="364">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>19.01</v>
+        <v>19.13</v>
       </c>
     </row>
     <row r="365">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>21.24</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>122.1</v>
+        <v>125</v>
       </c>
     </row>
     <row r="368">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>22.84</v>
+        <v>22.94</v>
       </c>
     </row>
     <row r="370">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>7.34</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>6.73</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="372">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>15.9</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="373">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>300</v>
+        <v>300.5</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>65.34999999999999</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>64.40000000000001</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="377">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>7.27</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="378">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>89.90000000000001</v>
+        <v>89.84999999999999</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>65.84999999999999</v>
+        <v>66</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>40.26</v>
+        <v>40.24</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.2</v>
+        <v>17.26</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>19.9</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>101.3</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="384">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>108.6</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="386">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="H386" t="n">
-        <v>6.55</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="387">
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="388">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>5.46</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="389">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>34.44</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="390">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>13.07</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="392">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>5.7</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="395">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="397">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>14.36</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="398">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>183.8</v>
+        <v>186</v>
       </c>
     </row>
     <row r="404">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>42.96</v>
+        <v>42.84</v>
       </c>
     </row>
     <row r="405">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>30.26</v>
+        <v>30.36</v>
       </c>
     </row>
     <row r="406">
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>4.89</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="407">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>90.25</v>
+        <v>90.05</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>28.08</v>
+        <v>28.14</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>115.7</v>
+        <v>116.8</v>
       </c>
     </row>
     <row r="410">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>6.76</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="411">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>26.4</v>
+        <v>26.42</v>
       </c>
     </row>
     <row r="412">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>20.08</v>
+        <v>20.02</v>
       </c>
     </row>
     <row r="414">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>46.9</v>
+        <v>46.34</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.23</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="417">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>47</v>
+        <v>46.78</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>8.449999999999999</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="420">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>28.3</v>
+        <v>28.42</v>
       </c>
     </row>
     <row r="421">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>39.38</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="422">
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="H422" t="n">
-        <v>4.12</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="423">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>15.37</v>
+        <v>15.41</v>
       </c>
     </row>
     <row r="424">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>47.82</v>
+        <v>47.92</v>
       </c>
     </row>
     <row r="425">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>21.98</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.7</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="427">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.3</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="428">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>8.869999999999999</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="430">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>11.45</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="431">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="432">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>315</v>
+        <v>314.5</v>
       </c>
     </row>
     <row r="433">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.72</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="434">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>7.61</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="435">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>12.95</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="439">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>10.57</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="440">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>6.09</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="442">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>105</v>
+        <v>105.1</v>
       </c>
     </row>
     <row r="444">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="445">
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>27.48</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="447">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>27.36</v>
+        <v>27.48</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>28.98</v>
+        <v>28.78</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>1524</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="450">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>180.5</v>
+        <v>183.9</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>13.36</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="454">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>5.12</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>21.88</v>
+        <v>21.82</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>17.56</v>
+        <v>17.53</v>
       </c>
     </row>
     <row r="457">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="H458" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="459">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>13</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>37.26</v>
+        <v>37.18</v>
       </c>
     </row>
     <row r="461">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>81.8</v>
+        <v>81.55</v>
       </c>
     </row>
     <row r="462">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="464">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>31.98</v>
+        <v>32.12</v>
       </c>
     </row>
     <row r="465">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="H465" t="n">
-        <v>10.96</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="466">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>25.16</v>
+        <v>25.12</v>
       </c>
     </row>
     <row r="469">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>30.8</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>42.68</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="472">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>12.73</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="474">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>13.42</v>
+        <v>13.47</v>
       </c>
     </row>
     <row r="477">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>27.1</v>
+        <v>27.12</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>8.41</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="480">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="482">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.19</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>82</v>
+        <v>81.95</v>
       </c>
     </row>
     <row r="484">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>17.85</v>
+        <v>17.83</v>
       </c>
     </row>
     <row r="488">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>10.67</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="489">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>34.08</v>
+        <v>34.02</v>
       </c>
     </row>
     <row r="494">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>48.76</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="495">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>10.19</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="497">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="499">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>39.7</v>
+        <v>39.94</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.52</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="503">
@@ -17050,7 +17050,7 @@
         </is>
       </c>
       <c r="H503" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="504">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="H504" t="n">
-        <v>8.94</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="505">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>8.57</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="506">
@@ -17248,7 +17248,7 @@
         </is>
       </c>
       <c r="H509" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="510">
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="H512" t="n">
-        <v>34.42</v>
+        <v>34.26</v>
       </c>
     </row>
     <row r="513">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="H513" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="514">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>6.71</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="515">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>9.109999999999999</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="516">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>16.12</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>14.77</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>217.2</v>
+        <v>218</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>146.7</v>
+        <v>148</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>12.6</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>73.09999999999999</v>
+        <v>72.84999999999999</v>
       </c>
     </row>
     <row r="523">
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>7.68</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="526">
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="H528" t="n">
-        <v>17.09</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="529">
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="H529" t="n">
-        <v>13.9</v>
+        <v>13.88</v>
       </c>
     </row>
     <row r="530">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="532">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.36</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="534">
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="H534" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="535">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>6.21</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="536">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.38</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="538">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>153.9</v>
+        <v>153.1</v>
       </c>
     </row>
     <row r="539">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>62.4</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="540">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="H540" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="541">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>25.7</v>
+        <v>25.94</v>
       </c>
     </row>
     <row r="542">
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="H542" t="n">
-        <v>4.37</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="543">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>15.05</v>
+        <v>15.01</v>
       </c>
     </row>
     <row r="544">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>33.44</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="546">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>15.9</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="547">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>27.74</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>55</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="549">
@@ -18634,7 +18634,7 @@
         </is>
       </c>
       <c r="H551" t="n">
-        <v>42.94</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="552">
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="H553" t="n">
-        <v>46.86</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="554">
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="H556" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="557">
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="H557" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="558">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="H558" t="n">
-        <v>119.9</v>
+        <v>119.4</v>
       </c>
     </row>
     <row r="559">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>28.52</v>
+        <v>28.38</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="562">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="H562" t="n">
-        <v>23.82</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="563">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="H563" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="564">
@@ -19063,7 +19063,7 @@
         </is>
       </c>
       <c r="H564" t="n">
-        <v>12.97</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="565">
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="H565" t="n">
-        <v>8.06</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="566">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>6.51</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="569">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="H569" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="570">
@@ -19261,7 +19261,7 @@
         </is>
       </c>
       <c r="H570" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="571">
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>8.48</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="572">
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>4.74</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="573">
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="H573" t="n">
-        <v>18.49</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="574">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>26.58</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="575">
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="H577" t="n">
-        <v>5.91</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="578">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.48</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="581">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.68</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="582">
@@ -19690,7 +19690,7 @@
         </is>
       </c>
       <c r="H583" t="n">
-        <v>6.3</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="584">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>38.2</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>17.61</v>
+        <v>38.02</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>3.82</v>
+        <v>73.69</v>
       </c>
     </row>
     <row r="589">
@@ -19888,7 +19888,7 @@
         </is>
       </c>
       <c r="H589" t="n">
-        <v>17.03</v>
+        <v>17.22</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>47.04</v>
+        <v>17.73</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>18.79</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>12.66</v>
+        <v>182.4</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>44.98</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>8</v>
+        <v>20.44</v>
       </c>
     </row>
     <row r="595">
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="H595" t="n">
-        <v>38.14</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>128.5</v>
+        <v>157.6</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>34.88</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>155.4</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>21.48</v>
+        <v>46.78</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>20.46</v>
+        <v>153.7</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>17.29</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>160.5</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>105.2</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>39.8</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="605">
@@ -20416,7 +20416,7 @@
         </is>
       </c>
       <c r="H605" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>38.2</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>17.81</v>
+        <v>7.98</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>14.4</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>183.7</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>70.40000000000001</v>
+        <v>18.89</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>74.06999999999999</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>65.55</v>
+        <v>34.64</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>378</v>
+        <v>371.25</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2595</v>
+        <v>2607.5</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>94.40000000000001</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>136.4</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>190.1</v>
+        <v>189.2</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>234.3</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>383.25</v>
+        <v>381.75</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>310.25</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -805,7 +805,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>14.45</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="12">
@@ -838,7 +838,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISBTR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2915000</v>
+        <v>419915</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISBTR</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>419915</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>72.09999999999999</v>
+        <v>71.95</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>175.3</v>
+        <v>175.1</v>
       </c>
     </row>
     <row r="16">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>46.78</v>
+        <v>46.46</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>32.74</v>
+        <v>32.64</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>88.2</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>37.9</v>
+        <v>37.78</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>278.25</v>
+        <v>274.75</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>39.24</v>
+        <v>39.18</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>110.8</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="24">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>81.75</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>63.7</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="26">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>95.84999999999999</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>59.25</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1591</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>229.8</v>
+        <v>228.3</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>95.8</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="32">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>44.02</v>
+        <v>43.94</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>45.26</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>13.01</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="36">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>106.1</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="39">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>21.06</v>
+        <v>20.92</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>11082.5</v>
+        <v>11017.5</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1564</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>21.32</v>
+        <v>21.28</v>
       </c>
     </row>
     <row r="45">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>98.55</v>
+        <v>98.59999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>79.05</v>
+        <v>79.75</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>277.25</v>
+        <v>275.5</v>
       </c>
     </row>
     <row r="49">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>108.8</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="51">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>631</v>
+        <v>626</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>443</v>
+        <v>441.5</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>32.14</v>
+        <v>32.86</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>172.6</v>
+        <v>171.9</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>16.93</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>33.52</v>
+        <v>33.16</v>
       </c>
     </row>
     <row r="58">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>116.3</v>
+        <v>116.8</v>
       </c>
     </row>
     <row r="59">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.69</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="61">
@@ -2455,16 +2455,16 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
+          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6.1</v>
+        <v>19.96</v>
       </c>
     </row>
     <row r="62">
@@ -2488,16 +2488,16 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>20.02</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>104</v>
+        <v>103.9</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>110.9</v>
+        <v>111.2</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>261</v>
+        <v>259.5</v>
       </c>
     </row>
     <row r="66">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>32.8</v>
+        <v>32.76</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>202.4</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="68">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.8</v>
+        <v>32.92</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>181.7</v>
+        <v>181.5</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>12.81</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="71">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>93.7</v>
+        <v>91.75</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1311</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="73">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>81.5</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>27.8</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>40.26</v>
+        <v>40.14</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>34.16</v>
+        <v>33.82</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2000</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>170.3</v>
+        <v>169.9</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>36.64</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>217.4</v>
+        <v>217.2</v>
       </c>
     </row>
     <row r="83">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1684</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="84">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>39.92</v>
+        <v>39.62</v>
       </c>
     </row>
     <row r="85">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KRDMB</t>
+          <t>KRDMA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>113.3</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="86">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KRDMA</t>
+          <t>KRDMB</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>41.34</v>
+        <v>113.7</v>
       </c>
     </row>
     <row r="87">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.5</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="88">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>224</v>
+        <v>223.9</v>
       </c>
     </row>
     <row r="90">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1221</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>49.9</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>243.4</v>
+        <v>243.5</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>444</v>
+        <v>442.25</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>110.6</v>
+        <v>111.4</v>
       </c>
     </row>
     <row r="95">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>100.8</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="96">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>134.9</v>
+        <v>134.5</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>612.5</v>
+        <v>613.5</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>11.01</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="99">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>63.85</v>
+        <v>63.45</v>
       </c>
     </row>
     <row r="100">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>354.75</v>
+        <v>354.25</v>
       </c>
     </row>
     <row r="101">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>108.3</v>
+        <v>108.1</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>218</v>
+        <v>217.5</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>113.6</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>203.2</v>
+        <v>202.9</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>83</v>
+        <v>83.15000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1674</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>22.1</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>36.28</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>107.5</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>343.75</v>
+        <v>343</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>8.25</v>
+        <v>8.220000000000001</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>145.4</v>
+        <v>145.7</v>
       </c>
     </row>
     <row r="113">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>324.5</v>
+        <v>342.25</v>
       </c>
     </row>
     <row r="114">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>13.82</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>42.46</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="117">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>13.72</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="119">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>5.86</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="120">
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="121">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>196.9</v>
+        <v>195.9</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>11.88</v>
+        <v>11.85</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>217</v>
+        <v>217.3</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>26.12</v>
+        <v>26.16</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>306.25</v>
+        <v>306.5</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>13.75</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="127">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>15.91</v>
+        <v>15.97</v>
       </c>
     </row>
     <row r="128">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>10.63</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>13.6</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>49.48</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="131">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>15.25</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>113.5</v>
+        <v>113.7</v>
       </c>
     </row>
     <row r="134">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>52.75</v>
+        <v>52.55</v>
       </c>
     </row>
     <row r="135">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>91</v>
+        <v>90.84999999999999</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>28.26</v>
+        <v>28.16</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>232.8</v>
+        <v>232.1</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>13932.5</v>
+        <v>13807.5</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>70.34999999999999</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="141">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>320</v>
+        <v>317.25</v>
       </c>
     </row>
     <row r="142">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>138.7</v>
+        <v>138.5</v>
       </c>
     </row>
     <row r="144">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>9.880000000000001</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="145">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>58.45</v>
+        <v>58.35</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>46.84</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="147">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>6.3</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="148">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>47.38</v>
+        <v>46.94</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>88.5</v>
+        <v>88.25</v>
       </c>
     </row>
     <row r="150">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="152">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>17.7</v>
+        <v>17.63</v>
       </c>
     </row>
     <row r="153">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.15</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>59.8</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>84</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>12.16</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="157">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>35.98</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>14.14</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>84.2</v>
+        <v>83.84999999999999</v>
       </c>
     </row>
     <row r="161">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>38.2</v>
+        <v>38.06</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8.57</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="163">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>152.5</v>
+        <v>151.2</v>
       </c>
     </row>
     <row r="164">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>175.6</v>
+        <v>174.8</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>20.44</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>6.95</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>39.36</v>
+        <v>39.12</v>
       </c>
     </row>
     <row r="168">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>4.86</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>58.65</v>
+        <v>58.15</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>20.98</v>
+        <v>20.84</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>5045</v>
+        <v>5022.5</v>
       </c>
     </row>
     <row r="172">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>71.25</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>3715</v>
+        <v>3705</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5672.5</v>
+        <v>5647.5</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>136.3</v>
+        <v>136.2</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1525</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>16.15</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="179">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>11</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="181">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>629</v>
+        <v>630.5</v>
       </c>
     </row>
     <row r="182">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>93.65000000000001</v>
+        <v>93.05</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>14.77</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="184">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>20.64</v>
+        <v>20.58</v>
       </c>
     </row>
     <row r="186">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>61.35</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>32.16</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>147.1</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="189">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>38.8</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>252.75</v>
+        <v>250.5</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>13.45</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="193">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>28.66</v>
+        <v>28.58</v>
       </c>
     </row>
     <row r="194">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>13.98</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>28.52</v>
+        <v>28.36</v>
       </c>
     </row>
     <row r="196">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="198">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="199">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.6</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>30.74</v>
+        <v>30.68</v>
       </c>
     </row>
     <row r="202">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="203">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>19.21</v>
+        <v>19.24</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>84.75</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>19.82</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>45.26</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="207">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>147.4</v>
+        <v>146.5</v>
       </c>
     </row>
     <row r="208">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>112.1</v>
+        <v>111.7</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>4.52</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>65.65000000000001</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>42.68</v>
+        <v>42.74</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>5.96</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="213">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>41.08</v>
+        <v>41</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>31.84</v>
+        <v>31.78</v>
       </c>
     </row>
     <row r="216">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="217">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>75.90000000000001</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>633.5</v>
+        <v>653.5</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>11.48</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="221">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>14.72</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="222">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>41.12</v>
+        <v>40.96</v>
       </c>
     </row>
     <row r="223">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>55.1</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>7.36</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="225">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>133</v>
+        <v>132.9</v>
       </c>
     </row>
     <row r="227">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>16.64</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="229">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>8.94</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="230">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.15</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>38.78</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>17.75</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>530.5</v>
+        <v>529</v>
       </c>
     </row>
     <row r="234">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>12.27</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>41.68</v>
+        <v>41.66</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>108</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>61.75</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="239">
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="H239" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="240">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>39.84</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="242">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>31.52</v>
+        <v>31.68</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>90.7</v>
+        <v>90.34999999999999</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>21.5</v>
+        <v>21.46</v>
       </c>
     </row>
     <row r="245">
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="246">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.33</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="247">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>86.05</v>
+        <v>85.84999999999999</v>
       </c>
     </row>
     <row r="248">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>6.32</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="249">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="250">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>413.5</v>
+        <v>416.25</v>
       </c>
     </row>
     <row r="251">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>36</v>
+        <v>35.88</v>
       </c>
     </row>
     <row r="252">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>261.25</v>
+        <v>260</v>
       </c>
     </row>
     <row r="253">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>20.28</v>
+        <v>19.91</v>
       </c>
     </row>
     <row r="254">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>24.32</v>
+        <v>24.04</v>
       </c>
     </row>
     <row r="255">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>1140</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>18.66</v>
+        <v>18.68</v>
       </c>
     </row>
     <row r="257">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>4.6</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="258">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>71.90000000000001</v>
+        <v>71.65000000000001</v>
       </c>
     </row>
     <row r="259">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>52.35</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="260">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>13.07</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="261">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="262">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.68</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>126.5</v>
+        <v>125</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>11.54</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="265">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>123.4</v>
+        <v>123</v>
       </c>
     </row>
     <row r="266">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>18.01</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>14.01</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="269">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>5.99</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="270">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>58.65</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>26.94</v>
+        <v>26.82</v>
       </c>
     </row>
     <row r="272">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>12.39</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>7.63</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>39.92</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="276">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>32.72</v>
+        <v>32.64</v>
       </c>
     </row>
     <row r="277">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.27</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="279">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="281">
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>6.39</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="282">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>25.72</v>
+        <v>25.58</v>
       </c>
     </row>
     <row r="284">
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>24.72</v>
+        <v>24.64</v>
       </c>
     </row>
     <row r="285">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>22.76</v>
+        <v>22.66</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>6.24</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="287">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>58.55</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="288">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>6.14</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="289">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>8.1</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>20.72</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>732.5</v>
+        <v>729</v>
       </c>
     </row>
     <row r="292">
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>11.61</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="293">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>44.52</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>54.9</v>
+        <v>54.85</v>
       </c>
     </row>
     <row r="295">
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>1000</v>
+        <v>999.5</v>
       </c>
     </row>
     <row r="296">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>46.56</v>
+        <v>46.62</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>18.75</v>
+        <v>18.73</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>23.86</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>217.7</v>
+        <v>217.1</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>9.699999999999999</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="301">
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="H301" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="302">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>7.57</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="303">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>85.05</v>
+        <v>84.84999999999999</v>
       </c>
     </row>
     <row r="305">
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="308">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="H308" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="309">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>10.1</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="310">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>114.6</v>
+        <v>114.1</v>
       </c>
     </row>
     <row r="311">
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="312">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>7.36</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="313">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>6.33</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>40.4</v>
+        <v>40.02</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>15.12</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>15.48</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>10.14</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>92.2</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>258</v>
+        <v>256.25</v>
       </c>
     </row>
     <row r="320">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>5.85</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="321">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>431</v>
+        <v>427.75</v>
       </c>
     </row>
     <row r="322">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="324">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>6.27</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>246.9</v>
+        <v>243.3</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>12.18</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>8.289999999999999</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>14.33</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>326.5</v>
+        <v>325.25</v>
       </c>
     </row>
     <row r="330">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>39.74</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="331">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>98.59999999999999</v>
+        <v>97.75</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>32.82</v>
+        <v>32.86</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>15.03</v>
+        <v>15</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>17.11</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>63.65</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="336">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="337">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>149.2</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>14.02</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="340">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>22.56</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>27</v>
+        <v>26.74</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>29.66</v>
+        <v>29.54</v>
       </c>
     </row>
     <row r="344">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>17.65</v>
+        <v>17.71</v>
       </c>
     </row>
     <row r="346">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>10.63</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="347">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>12.11</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="348">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="H349" t="n">
-        <v>12.76</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="350">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>5.39</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="351">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="H352" t="n">
-        <v>10.27</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="353">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>264</v>
+        <v>263.75</v>
       </c>
     </row>
     <row r="355">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>38.64</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>12.1</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="358">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>6.91</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>8.83</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>149.4</v>
+        <v>148</v>
       </c>
     </row>
     <row r="363">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>23.54</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="364">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>19.13</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="365">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="H365" t="n">
-        <v>58.45</v>
+        <v>58.05</v>
       </c>
     </row>
     <row r="366">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>20.98</v>
+        <v>20.68</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>125</v>
+        <v>125.9</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>15.08</v>
+        <v>15.04</v>
       </c>
     </row>
     <row r="369">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>22.94</v>
+        <v>22.92</v>
       </c>
     </row>
     <row r="370">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>7.31</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>6.75</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="372">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>15.95</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="373">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>300.5</v>
+        <v>299.75</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>65.5</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>64.2</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="377">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="378">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>89.84999999999999</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>66</v>
+        <v>65.45</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>40.24</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.26</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>19.93</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>100.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="384">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>108.5</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="386">
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>4.88</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="388">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="389">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>34.56</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="390">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="H390" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="391">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>13.05</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="392">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>9.369999999999999</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="393">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>5.73</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="395">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.34</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="396">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="397">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>14.28</v>
+        <v>14.26</v>
       </c>
     </row>
     <row r="398">
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="H398" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="399">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>9.91</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="400">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>12.23</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="403">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>186</v>
+        <v>185.3</v>
       </c>
     </row>
     <row r="404">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>42.84</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="405">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>30.36</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="406">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>90.05</v>
+        <v>90</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>28.14</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>116.8</v>
+        <v>117.2</v>
       </c>
     </row>
     <row r="410">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>6.78</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="411">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>26.42</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="412">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>20.02</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="414">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>46.34</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.21</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="417">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>46.78</v>
+        <v>46.84</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>8.44</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="420">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>28.42</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="421">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>39.5</v>
+        <v>39.36</v>
       </c>
     </row>
     <row r="422">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>15.41</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="424">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>47.92</v>
+        <v>47.56</v>
       </c>
     </row>
     <row r="425">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>22.04</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.68</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="427">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.31</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>21.12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="429">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>8.73</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="430">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>11.43</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="431">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>314.5</v>
+        <v>310.75</v>
       </c>
     </row>
     <row r="433">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.73</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="434">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>7.65</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="435">
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="436">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>10.07</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="437">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>7.35</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="438">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>12.97</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="439">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>10.56</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="440">
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="441">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>6.1</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="442">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="443">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>105.1</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="444">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>39.5</v>
+        <v>39.44</v>
       </c>
     </row>
     <row r="445">
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="H445" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="446">
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>27.54</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="447">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>27.48</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>28.78</v>
+        <v>28.94</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>1527</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="450">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>183.9</v>
+        <v>180.3</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>13.35</v>
+        <v>13.26</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
     </row>
     <row r="454">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>21.82</v>
+        <v>21.78</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>17.53</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="457">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>20.4</v>
+        <v>20.18</v>
       </c>
     </row>
     <row r="458">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="H458" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="459">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>12.98</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="460">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>81.55</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="462">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="464">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>32.12</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="465">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="H465" t="n">
-        <v>10.99</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="466">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="468">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>25.12</v>
+        <v>24.96</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>36.04</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>30.4</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>42.8</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="472">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="473">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>12.75</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="474">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>13.47</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="477">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="478">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>27.12</v>
+        <v>27.06</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>8.59</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.38</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="481">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.18</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>81.95</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="484">
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="485">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>96.8</v>
+        <v>96.55</v>
       </c>
     </row>
     <row r="487">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>17.83</v>
+        <v>17.73</v>
       </c>
     </row>
     <row r="488">
@@ -16588,7 +16588,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="490">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>28.66</v>
+        <v>28.96</v>
       </c>
     </row>
     <row r="491">
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="H491" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="492">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>34.02</v>
+        <v>34.18</v>
       </c>
     </row>
     <row r="494">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>49.04</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="495">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>10.21</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="497">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="499">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="501">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>39.94</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.5</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="503">
@@ -17050,7 +17050,7 @@
         </is>
       </c>
       <c r="H503" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="504">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="H504" t="n">
-        <v>9.1</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="505">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>8.59</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="506">
@@ -17149,7 +17149,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="507">
@@ -17248,7 +17248,7 @@
         </is>
       </c>
       <c r="H509" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="510">
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="512">
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="H512" t="n">
-        <v>34.26</v>
+        <v>34.32</v>
       </c>
     </row>
     <row r="513">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="H513" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="514">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>6.72</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="515">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>9.15</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="516">
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="H516" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="517">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>16.13</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>14.8</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>218</v>
+        <v>217.2</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>148</v>
+        <v>145.8</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>12.46</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>72.84999999999999</v>
+        <v>73.34999999999999</v>
       </c>
     </row>
     <row r="523">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>4.6</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="524">
@@ -17743,7 +17743,7 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="525">
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>7.69</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="526">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>13.97</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="527">
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="H528" t="n">
-        <v>17.27</v>
+        <v>17.37</v>
       </c>
     </row>
     <row r="529">
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="H529" t="n">
-        <v>13.88</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="530">
@@ -17941,7 +17941,7 @@
         </is>
       </c>
       <c r="H530" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="531">
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="533">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.35</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="534">
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="H534" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="535">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>6.28</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="536">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>22.72</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="537">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.4</v>
+        <v>25.42</v>
       </c>
     </row>
     <row r="538">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>153.1</v>
+        <v>152.8</v>
       </c>
     </row>
     <row r="539">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>62.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="540">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="H540" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="541">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>25.94</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="542">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>15.01</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="544">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>34.7</v>
+        <v>33.66</v>
       </c>
     </row>
     <row r="546">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>16.02</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="547">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>27.7</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>53.5</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="549">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="H549" t="n">
-        <v>10.24</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="550">
@@ -18634,7 +18634,7 @@
         </is>
       </c>
       <c r="H551" t="n">
-        <v>43.26</v>
+        <v>42.92</v>
       </c>
     </row>
     <row r="552">
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="H553" t="n">
-        <v>46.4</v>
+        <v>46.56</v>
       </c>
     </row>
     <row r="554">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="H554" t="n">
-        <v>4.7</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="555">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="H558" t="n">
-        <v>119.4</v>
+        <v>119.5</v>
       </c>
     </row>
     <row r="559">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>28.38</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="562">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="H563" t="n">
-        <v>26.8</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="564">
@@ -19063,7 +19063,7 @@
         </is>
       </c>
       <c r="H564" t="n">
-        <v>12.98</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="565">
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="H565" t="n">
-        <v>8.09</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="566">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>6.54</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="569">
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>8.49</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="572">
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="573">
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="H573" t="n">
-        <v>18.48</v>
+        <v>18.54</v>
       </c>
     </row>
     <row r="574">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>26.6</v>
+        <v>26.56</v>
       </c>
     </row>
     <row r="575">
@@ -19459,7 +19459,7 @@
         </is>
       </c>
       <c r="H576" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="577">
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="H577" t="n">
-        <v>5.97</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="578">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.43</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="581">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H582" t="n">
-        <v>10.29</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="583">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>105.8</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>38.02</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>73.69</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>17.22</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>17.73</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>21.12</v>
+        <v>73.73</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>182.4</v>
+        <v>160.3</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>12.64</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>20.44</v>
+        <v>182.3</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>38.2</v>
+        <v>20.42</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>157.6</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>65.2</v>
+        <v>34.74</v>
       </c>
     </row>
     <row r="598">
@@ -20185,7 +20185,7 @@
         </is>
       </c>
       <c r="H598" t="n">
-        <v>39.74</v>
+        <v>40.02</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>46.78</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>153.7</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>128.5</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>3.83</v>
+        <v>38.04</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>38.2</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>70.40000000000001</v>
+        <v>38.02</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>2.47</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>17.8</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>7.98</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>44.98</v>
+        <v>155.2</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>17.29</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="610">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H610" t="n">
-        <v>18.89</v>
+        <v>18.72</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>14.38</v>
+        <v>17.73</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>34.64</v>
+        <v>65.65000000000001</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>371.25</v>
+        <v>369.25</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2607.5</v>
+        <v>2587.5</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>94</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>135.9</v>
+        <v>134.4</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>189.2</v>
+        <v>186.7</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>234</v>
+        <v>233.5</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>381.75</v>
+        <v>377.75</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>308</v>
+        <v>304.5</v>
       </c>
     </row>
     <row r="11">
@@ -805,7 +805,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISBTR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2915000</v>
+        <v>419915</v>
       </c>
     </row>
     <row r="12">
@@ -838,7 +838,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ISBTR</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>419915</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>14.4</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>71.95</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>175.1</v>
+        <v>173.8</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>115.2</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>46.46</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>32.64</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>87.8</v>
+        <v>86.75</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>37.78</v>
+        <v>37.32</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>274.75</v>
+        <v>270.75</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>39.18</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>110.4</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="24">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>81.40000000000001</v>
+        <v>81.34999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>63.75</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="26">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>95.5</v>
+        <v>94.34999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>59.2</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1588</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>228.3</v>
+        <v>218.5</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>486</v>
+        <v>479.75</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>95.2</v>
+        <v>93.84999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>297</v>
+        <v>294.25</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>43.94</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>45.04</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>13.03</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="36">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>106</v>
+        <v>105.2</v>
       </c>
     </row>
     <row r="38">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>20.92</v>
+        <v>20.48</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>674</v>
+        <v>667</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>11017.5</v>
+        <v>10835</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1599</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>21.28</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="45">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>98.59999999999999</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>79.75</v>
+        <v>79.45</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>275.5</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>108.3</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>626</v>
+        <v>617</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>441.5</v>
+        <v>438.5</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>32.86</v>
+        <v>33.08</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>171.9</v>
+        <v>169.5</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>17.17</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>33.16</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="58">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>116.8</v>
+        <v>116.3</v>
       </c>
     </row>
     <row r="59">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>213.4</v>
+        <v>212.9</v>
       </c>
     </row>
     <row r="60">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>9.42</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="61">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>19.96</v>
+        <v>19.65</v>
       </c>
     </row>
     <row r="62">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>6.11</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>103.9</v>
+        <v>102.1</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>111.2</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>259.5</v>
+        <v>257</v>
       </c>
     </row>
     <row r="66">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>32.76</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>202.5</v>
+        <v>201.8</v>
       </c>
     </row>
     <row r="68">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.92</v>
+        <v>32.54</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>181.5</v>
+        <v>180.3</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>12.85</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="71">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>91.75</v>
+        <v>93.84999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1304</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="73">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>81.65000000000001</v>
+        <v>80.75</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>27.78</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>40.14</v>
+        <v>39.82</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>33.82</v>
+        <v>33.58</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1995</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>169.9</v>
+        <v>168.2</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>36.4</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>142</v>
+        <v>140.9</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>217.2</v>
+        <v>217</v>
       </c>
     </row>
     <row r="83">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1693</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="84">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>39.62</v>
+        <v>39.22</v>
       </c>
     </row>
     <row r="85">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>41.24</v>
+        <v>41.26</v>
       </c>
     </row>
     <row r="86">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>113.7</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="87">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.44</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="88">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.43</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="89">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1215</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>49.78</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>243.5</v>
+        <v>242.1</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>442.25</v>
+        <v>440</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>111.4</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="95">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>100.6</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="96">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>134.5</v>
+        <v>133.6</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>613.5</v>
+        <v>611</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>10.98</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="99">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>63.45</v>
+        <v>62.95</v>
       </c>
     </row>
     <row r="100">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>108.1</v>
+        <v>105.3</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>217.5</v>
+        <v>216.7</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>113.2</v>
+        <v>112.3</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>202.9</v>
+        <v>200.8</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>83.15000000000001</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1668</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>22.04</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>36.1</v>
+        <v>35.88</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>105.9</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>343</v>
+        <v>340.5</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>8.220000000000001</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>145.7</v>
+        <v>144.4</v>
       </c>
     </row>
     <row r="113">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>342.25</v>
+        <v>341.5</v>
       </c>
     </row>
     <row r="114">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>49.08</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>13.83</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>42.26</v>
+        <v>41.96</v>
       </c>
     </row>
     <row r="117">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="118">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>13.77</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="119">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>5.84</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="120">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>195.9</v>
+        <v>195.6</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>11.85</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>217.3</v>
+        <v>215.6</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>26.16</v>
+        <v>25.88</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>306.5</v>
+        <v>299.75</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>13.96</v>
+        <v>13.88</v>
       </c>
     </row>
     <row r="127">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>15.97</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="128">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>10.51</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>13.56</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>49.3</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="131">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>15.23</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>113.7</v>
+        <v>113</v>
       </c>
     </row>
     <row r="134">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>52.55</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="135">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>90.84999999999999</v>
+        <v>90.15000000000001</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>28.16</v>
+        <v>27.64</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>232.1</v>
+        <v>232.2</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>13807.5</v>
+        <v>13700</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>70.3</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="141">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>317.25</v>
+        <v>311</v>
       </c>
     </row>
     <row r="142">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>138.5</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="144">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>9.84</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="145">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>58.35</v>
+        <v>57.75</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>46.6</v>
+        <v>46.46</v>
       </c>
     </row>
     <row r="147">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>6.32</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="148">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>46.94</v>
+        <v>46.84</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>88.25</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="150">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="151">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="152">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>17.63</v>
+        <v>18.13</v>
       </c>
     </row>
     <row r="153">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.119999999999999</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="154">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>58.9</v>
+        <v>57.95</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>84.2</v>
+        <v>82.84999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>12.08</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="157">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="158">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>35.9</v>
+        <v>36.24</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>14.1</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>83.84999999999999</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>38.06</v>
+        <v>37.98</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8.5</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="163">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>151.2</v>
+        <v>149.5</v>
       </c>
     </row>
     <row r="164">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>174.8</v>
+        <v>173.7</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>20.3</v>
+        <v>20.26</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>6.89</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>39.12</v>
+        <v>38.76</v>
       </c>
     </row>
     <row r="168">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>4.9</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>58.15</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>20.84</v>
+        <v>20.48</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>5022.5</v>
+        <v>4987.5</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>25.14</v>
+        <v>24.86</v>
       </c>
     </row>
     <row r="173">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>71.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>3705</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5647.5</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>136.2</v>
+        <v>135.7</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1516</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>16.08</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>82.45</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
     <row r="180">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>11.02</v>
+        <v>11</v>
       </c>
     </row>
     <row r="181">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>630.5</v>
+        <v>617.5</v>
       </c>
     </row>
     <row r="182">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>93.05</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>15.02</v>
+        <v>14.95</v>
       </c>
     </row>
     <row r="184">
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>22.96</v>
+        <v>22.72</v>
       </c>
     </row>
     <row r="185">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>20.58</v>
+        <v>20.44</v>
       </c>
     </row>
     <row r="186">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>61.2</v>
+        <v>60.45</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>32.14</v>
+        <v>32.04</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>147.5</v>
+        <v>147.2</v>
       </c>
     </row>
     <row r="189">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>39.1</v>
+        <v>38.78</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>250.5</v>
+        <v>247.1</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>13.41</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="193">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>28.58</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="194">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>14.1</v>
+        <v>14.48</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>28.36</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="196">
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="197">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="199">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.52</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>30.68</v>
+        <v>30.42</v>
       </c>
     </row>
     <row r="202">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="203">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>19.24</v>
+        <v>19.04</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>84.59999999999999</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>19.75</v>
+        <v>19.55</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>45.06</v>
+        <v>44.64</v>
       </c>
     </row>
     <row r="207">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>146.5</v>
+        <v>144.9</v>
       </c>
     </row>
     <row r="208">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>111.7</v>
+        <v>112.1</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>4.51</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>65.5</v>
+        <v>64.95</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>42.74</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>5.89</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="213">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>80.5</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="214">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>31.78</v>
+        <v>31.62</v>
       </c>
     </row>
     <row r="216">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="217">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>12.45</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>75.25</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>653.5</v>
+        <v>649.5</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>11.46</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="221">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>14.71</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="222">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>40.96</v>
+        <v>40.52</v>
       </c>
     </row>
     <row r="223">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>54.4</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>7.33</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="225">
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>8.01</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="226">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>132.9</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="227">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>16.52</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="229">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>8.91</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="230">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.14</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>38.6</v>
+        <v>38.66</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>17.76</v>
+        <v>17.63</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>529</v>
+        <v>525</v>
       </c>
     </row>
     <row r="234">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>12.19</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>41.66</v>
+        <v>41.68</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>107.6</v>
+        <v>108</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>61.7</v>
+        <v>61.45</v>
       </c>
     </row>
     <row r="239">
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="H239" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="240">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="241">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>39.76</v>
+        <v>39.22</v>
       </c>
     </row>
     <row r="242">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>31.68</v>
+        <v>31.64</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>90.34999999999999</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>21.46</v>
+        <v>21.28</v>
       </c>
     </row>
     <row r="245">
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="246">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.36</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="247">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>85.84999999999999</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="248">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>6.31</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="249">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="250">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>416.25</v>
+        <v>413</v>
       </c>
     </row>
     <row r="251">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>35.88</v>
+        <v>35.54</v>
       </c>
     </row>
     <row r="252">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>260</v>
+        <v>257.5</v>
       </c>
     </row>
     <row r="253">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>19.91</v>
+        <v>19.86</v>
       </c>
     </row>
     <row r="254">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>24.04</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="255">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>1135</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>18.68</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="257">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>4.58</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="258">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>71.65000000000001</v>
+        <v>70.65000000000001</v>
       </c>
     </row>
     <row r="259">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>52.2</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="260">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>13.04</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="261">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="262">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.6</v>
+        <v>28.44</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>125</v>
+        <v>124.4</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>11.48</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="265">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>123</v>
+        <v>122.3</v>
       </c>
     </row>
     <row r="266">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>17.67</v>
+        <v>17.56</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>18.07</v>
+        <v>17.87</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>13.97</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="269">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>5.98</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="270">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>59.3</v>
+        <v>58.35</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>26.82</v>
+        <v>26.44</v>
       </c>
     </row>
     <row r="272">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>8.19</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="273">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>12.43</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>7.52</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>39.76</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="276">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>32.64</v>
+        <v>32.56</v>
       </c>
     </row>
     <row r="277">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.26</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>109.7</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="280">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="281">
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>6.38</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="282">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>25.58</v>
+        <v>25.62</v>
       </c>
     </row>
     <row r="284">
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>24.64</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="285">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>22.66</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>6.23</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="287">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>58.3</v>
+        <v>57.65</v>
       </c>
     </row>
     <row r="288">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>6.12</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="289">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>8.06</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>20.74</v>
+        <v>20.56</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>729</v>
+        <v>724.5</v>
       </c>
     </row>
     <row r="292">
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>11.59</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="293">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>44.04</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>54.85</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="295">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>46.62</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>18.73</v>
+        <v>18.72</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>23.84</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>217.1</v>
+        <v>215.3</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>9.66</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="301">
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="H301" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="302">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>7.54</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="303">
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="H303" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="304">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>84.84999999999999</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="305">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>4.99</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="306">
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="308">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="H308" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="309">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>9.98</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="310">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>114.1</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="311">
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="312">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>7.55</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="313">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>6.27</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>40.02</v>
+        <v>39.36</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>15.08</v>
+        <v>14.95</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>15.37</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>10.12</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>91.8</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>256.25</v>
+        <v>253.5</v>
       </c>
     </row>
     <row r="320">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>5.84</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="321">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>427.75</v>
+        <v>427</v>
       </c>
     </row>
     <row r="322">
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="H322" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="323">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="324">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>243.3</v>
+        <v>242.7</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>12.17</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>8.23</v>
+        <v>8.210000000000001</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>14.24</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>325.25</v>
+        <v>324</v>
       </c>
     </row>
     <row r="330">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>39.78</v>
+        <v>39.64</v>
       </c>
     </row>
     <row r="331">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>97.75</v>
+        <v>94.45</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>32.86</v>
+        <v>32.52</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>16.97</v>
+        <v>16.74</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>63.25</v>
+        <v>63</v>
       </c>
     </row>
     <row r="336">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="337">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.81</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="338">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>147.5</v>
+        <v>147.6</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>14.01</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="340">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>22.46</v>
+        <v>22.26</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>26.74</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>29.54</v>
+        <v>28.44</v>
       </c>
     </row>
     <row r="344">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>5.3</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="345">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>17.71</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="346">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>10.56</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="347">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>12.07</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.56</v>
+        <v>25.38</v>
       </c>
     </row>
     <row r="349">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="H349" t="n">
-        <v>12.72</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="350">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>5.33</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="351">
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="H351" t="n">
-        <v>4.23</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="352">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="H352" t="n">
-        <v>10.24</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="353">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>263.75</v>
+        <v>261.5</v>
       </c>
     </row>
     <row r="355">
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="H355" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="356">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>38.46</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>12.07</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="358">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>6.84</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>8.75</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>148</v>
+        <v>149.6</v>
       </c>
     </row>
     <row r="363">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>23.52</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="364">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="H365" t="n">
-        <v>58.05</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="366">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>20.68</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>125.9</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>15.04</v>
+        <v>15</v>
       </c>
     </row>
     <row r="369">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>22.92</v>
+        <v>22.68</v>
       </c>
     </row>
     <row r="370">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>7.34</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>6.71</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="372">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>15.93</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="373">
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="H373" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="374">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>299.75</v>
+        <v>297.5</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>65.2</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="377">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>7.24</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="378">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>89.8</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>65.45</v>
+        <v>64.84999999999999</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>40.2</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>19.87</v>
+        <v>19.72</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="384">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>107.8</v>
+        <v>106.8</v>
       </c>
     </row>
     <row r="386">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="H386" t="n">
-        <v>6.58</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="387">
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="388">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>5.42</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="389">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>34.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="390">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="H390" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="391">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>13.03</v>
+        <v>13</v>
       </c>
     </row>
     <row r="392">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>9.32</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="393">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>4.09</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>5.68</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="395">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.29</v>
+        <v>12.27</v>
       </c>
     </row>
     <row r="396">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="397">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>14.26</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="398">
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="H398" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="399">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>9.84</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>148</v>
+        <v>146.3</v>
       </c>
     </row>
     <row r="401">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="H401" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="402">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>12.16</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="403">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>185.3</v>
+        <v>184</v>
       </c>
     </row>
     <row r="404">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>42.72</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="405">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>30.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="406">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>90</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>27.96</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>117.2</v>
+        <v>116.2</v>
       </c>
     </row>
     <row r="410">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>6.73</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="411">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="412">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>19.99</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="414">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>46.06</v>
+        <v>45.86</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.16</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="417">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>46.84</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>8.43</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="420">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>28.32</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="421">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>39.36</v>
+        <v>38.94</v>
       </c>
     </row>
     <row r="422">
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="H422" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="423">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>15.57</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="424">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>47.56</v>
+        <v>46.82</v>
       </c>
     </row>
     <row r="425">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>22.2</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.72</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="427">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.28</v>
+        <v>11.15</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>21</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="429">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>8.9</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="430">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>11.36</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="431">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="432">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>310.75</v>
+        <v>311</v>
       </c>
     </row>
     <row r="433">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.68</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="434">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>7.6</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="435">
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="436">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>10.05</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="437">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>7.36</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="438">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>12.84</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="439">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>10.51</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="440">
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="441">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>6.09</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="442">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="443">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>104.4</v>
+        <v>103.4</v>
       </c>
     </row>
     <row r="444">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>39.44</v>
+        <v>39.26</v>
       </c>
     </row>
     <row r="445">
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="H445" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="446">
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>27.3</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="447">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>27.36</v>
+        <v>27.14</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>28.94</v>
+        <v>28.26</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>1523</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="450">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>180.3</v>
+        <v>177</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>13.26</v>
+        <v>13.19</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="454">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>21.78</v>
+        <v>21.44</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>17.52</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="457">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>20.18</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="458">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="H458" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="459">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>12.92</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>37.18</v>
+        <v>36.92</v>
       </c>
     </row>
     <row r="461">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>81.5</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="462">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="464">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>32.08</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="465">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="H465" t="n">
-        <v>10.96</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="466">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="468">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>24.96</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>35.8</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>30.8</v>
+        <v>30.68</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="472">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="473">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>12.74</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="474">
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="476">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>13.42</v>
+        <v>13.19</v>
       </c>
     </row>
     <row r="477">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="478">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>27.06</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>8.5</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.34</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="481">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>13.8</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="482">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.16</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="484">
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="485">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="486">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>96.55</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="487">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>17.73</v>
+        <v>17.51</v>
       </c>
     </row>
     <row r="488">
@@ -16588,7 +16588,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="490">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>28.96</v>
+        <v>29.28</v>
       </c>
     </row>
     <row r="491">
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="H491" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="492">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>34.18</v>
+        <v>33.98</v>
       </c>
     </row>
     <row r="494">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>49.1</v>
+        <v>49.02</v>
       </c>
     </row>
     <row r="495">
@@ -16786,7 +16786,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="496">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="499">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="501">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>39.84</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.32</v>
+        <v>24.02</v>
       </c>
     </row>
     <row r="503">
@@ -17050,7 +17050,7 @@
         </is>
       </c>
       <c r="H503" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="504">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="H504" t="n">
-        <v>9.119999999999999</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="505">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>8.52</v>
+        <v>8.470000000000001</v>
       </c>
     </row>
     <row r="506">
@@ -17149,7 +17149,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="507">
@@ -17248,7 +17248,7 @@
         </is>
       </c>
       <c r="H509" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="510">
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>3.33</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="512">
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="H512" t="n">
-        <v>34.32</v>
+        <v>33.96</v>
       </c>
     </row>
     <row r="513">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="H513" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="514">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>6.69</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="515">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>9.16</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="516">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>16.14</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>14.75</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>217.2</v>
+        <v>216.1</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>145.8</v>
+        <v>148.7</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>12.37</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>73.34999999999999</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="523">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="524">
@@ -17743,7 +17743,7 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>4.23</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="525">
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>7.62</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="526">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>13.93</v>
+        <v>13.88</v>
       </c>
     </row>
     <row r="527">
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="H529" t="n">
-        <v>13.78</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="530">
@@ -17941,7 +17941,7 @@
         </is>
       </c>
       <c r="H530" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="531">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="532">
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>5.17</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="533">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="534">
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="H534" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="535">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>6.3</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="536">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>22.76</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="537">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.42</v>
+        <v>25.28</v>
       </c>
     </row>
     <row r="538">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>152.8</v>
+        <v>152.5</v>
       </c>
     </row>
     <row r="539">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>62.4</v>
+        <v>61.85</v>
       </c>
     </row>
     <row r="540">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>25.74</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="542">
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="H542" t="n">
-        <v>4.48</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="543">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>15.25</v>
+        <v>15.01</v>
       </c>
     </row>
     <row r="544">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>33.66</v>
+        <v>33.56</v>
       </c>
     </row>
     <row r="546">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>15.95</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="547">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>27.72</v>
+        <v>27.84</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>53.75</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="549">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="H549" t="n">
-        <v>10.28</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="550">
@@ -18634,7 +18634,7 @@
         </is>
       </c>
       <c r="H551" t="n">
-        <v>42.92</v>
+        <v>42.48</v>
       </c>
     </row>
     <row r="552">
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="H553" t="n">
-        <v>46.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="554">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="H554" t="n">
-        <v>4.69</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="555">
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="H556" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="557">
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="H557" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="558">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="H558" t="n">
-        <v>119.5</v>
+        <v>119</v>
       </c>
     </row>
     <row r="559">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>28.5</v>
+        <v>28.44</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="562">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="H562" t="n">
-        <v>23.8</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="563">
@@ -19063,7 +19063,7 @@
         </is>
       </c>
       <c r="H564" t="n">
-        <v>13.04</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="565">
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="H565" t="n">
-        <v>8.050000000000001</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="566">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>6.47</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="569">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="H569" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="570">
@@ -19261,7 +19261,7 @@
         </is>
       </c>
       <c r="H570" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="571">
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>8.51</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="572">
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="573">
@@ -19558,7 +19558,7 @@
         </is>
       </c>
       <c r="H579" t="n">
-        <v>12.38</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="580">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="581">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.69</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="582">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H582" t="n">
-        <v>10.55</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="583">
@@ -19690,7 +19690,7 @@
         </is>
       </c>
       <c r="H583" t="n">
-        <v>6.33</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="584">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>44.98</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>70.40000000000001</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>105.5</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>128.5</v>
+        <v>66.25</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>3.82</v>
+        <v>37.68</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>73.73</v>
+        <v>104.1</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>160.3</v>
+        <v>38.78</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>17.8</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>182.3</v>
+        <v>40.34</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>20.42</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>14.35</v>
+        <v>17.37</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>34.74</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>40.02</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>38.44</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>12.62</v>
+        <v>17.19</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>45.8</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>38.04</v>
+        <v>73.62</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>7.97</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>38.02</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>20.98</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>17.07</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>17.27</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>155.2</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>2.46</v>
+        <v>16.74</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>18.72</v>
+        <v>153.3</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>17.73</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>65.65000000000001</v>
+        <v>182</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>369.25</v>
+        <v>369.75</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2587.5</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>93.2</v>
+        <v>92.84999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>134.4</v>
+        <v>134.5</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>186.7</v>
+        <v>185.9</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>233.5</v>
+        <v>232.9</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>377.75</v>
+        <v>376.25</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>304.5</v>
+        <v>303.75</v>
       </c>
     </row>
     <row r="11">
@@ -838,7 +838,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>14.28</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2915000</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>71.2</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>173.8</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>115</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="17">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>45.94</v>
+        <v>45.56</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>32.26</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>86.75</v>
+        <v>86.05</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>37.32</v>
+        <v>37.36</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>270.75</v>
+        <v>268.25</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>38.9</v>
+        <v>38.76</v>
       </c>
     </row>
     <row r="23">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>81.34999999999999</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>94.34999999999999</v>
+        <v>94.15000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>58.65</v>
+        <v>58.55</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>218.5</v>
+        <v>217.9</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>479.75</v>
+        <v>474</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>93.84999999999999</v>
+        <v>93.45</v>
       </c>
     </row>
     <row r="32">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>294.25</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>42.86</v>
+        <v>42.76</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>44.48</v>
+        <v>44.34</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>12.95</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="36">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>105.2</v>
+        <v>104.3</v>
       </c>
     </row>
     <row r="38">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>655</v>
+        <v>656.5</v>
       </c>
     </row>
     <row r="39">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>20.48</v>
+        <v>20.42</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>10835</v>
+        <v>10940</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1611</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>21.12</v>
+        <v>21.04</v>
       </c>
     </row>
     <row r="45">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>30.06</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="46">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>98.2</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>79.45</v>
+        <v>79.55</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>273</v>
+        <v>271.5</v>
       </c>
     </row>
     <row r="49">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>617</v>
+        <v>620.5</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>438.5</v>
+        <v>437.5</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>33.08</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>169.5</v>
+        <v>168.6</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>16.63</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>32.9</v>
+        <v>32.94</v>
       </c>
     </row>
     <row r="58">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>116.3</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="59">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>212.9</v>
+        <v>214.7</v>
       </c>
     </row>
     <row r="60">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>9.44</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="61">
@@ -2455,16 +2455,16 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>19.65</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="62">
@@ -2488,16 +2488,16 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
+          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>6.09</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>102.1</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>110.4</v>
+        <v>109.9</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>257</v>
+        <v>257.5</v>
       </c>
     </row>
     <row r="66">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>32.68</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>201.8</v>
+        <v>202.1</v>
       </c>
     </row>
     <row r="68">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.54</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>180.3</v>
+        <v>179</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>12.87</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="71">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>93.84999999999999</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1293</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="73">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>127.9</v>
+        <v>128.2</v>
       </c>
     </row>
     <row r="74">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>80.75</v>
+        <v>79.95</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>27.7</v>
+        <v>27.38</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>39.82</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>33.58</v>
+        <v>33.36</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1985</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>168.2</v>
+        <v>167.2</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>36.18</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>140.9</v>
+        <v>138.3</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>217</v>
+        <v>217.8</v>
       </c>
     </row>
     <row r="83">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1682</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="84">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>39.22</v>
+        <v>38.88</v>
       </c>
     </row>
     <row r="85">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KRDMA</t>
+          <t>KRDMB</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>41.26</v>
+        <v>113</v>
       </c>
     </row>
     <row r="86">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KRDMB</t>
+          <t>KRDMA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>113.6</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="87">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.2</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="88">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.49</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="89">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>223.9</v>
+        <v>223.3</v>
       </c>
     </row>
     <row r="90">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1221</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>49.34</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>242.1</v>
+        <v>243.3</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>440</v>
+        <v>439.5</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>110.5</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="95">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>133.6</v>
+        <v>133</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>611</v>
+        <v>614.5</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>10.89</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>62.95</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="100">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>354.25</v>
+        <v>349</v>
       </c>
     </row>
     <row r="101">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>105.3</v>
+        <v>105.1</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>216.7</v>
+        <v>216.4</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>112.3</v>
+        <v>111.7</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>200.8</v>
+        <v>201.5</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>83.3</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1652</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>35.88</v>
+        <v>35.66</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>105.8</v>
+        <v>105</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>340.5</v>
+        <v>338</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>8.26</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>144.4</v>
+        <v>145.6</v>
       </c>
     </row>
     <row r="113">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>341.5</v>
+        <v>339.5</v>
       </c>
     </row>
     <row r="114">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>48.76</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>13.76</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>41.96</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="117">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>13.53</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="119">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>5.81</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="120">
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="121">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>195.6</v>
+        <v>193.8</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>11.74</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>215.6</v>
+        <v>218</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>25.88</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>299.75</v>
+        <v>300.25</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>13.88</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="127">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>15.9</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="128">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>10.5</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>13.51</v>
+        <v>13.48</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>49.04</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="131">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>15.06</v>
+        <v>14.95</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="134">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>51.95</v>
+        <v>52.55</v>
       </c>
     </row>
     <row r="135">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>90.15000000000001</v>
+        <v>89.95</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>27.64</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>232.2</v>
+        <v>228.1</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>13700</v>
+        <v>13687.5</v>
       </c>
     </row>
     <row r="140">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>311</v>
+        <v>310.75</v>
       </c>
     </row>
     <row r="142">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>144.5</v>
+        <v>145.1</v>
       </c>
     </row>
     <row r="144">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>9.699999999999999</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="145">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>57.75</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>46.46</v>
+        <v>46.18</v>
       </c>
     </row>
     <row r="147">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>6.28</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="148">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>46.84</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>87.8</v>
+        <v>86.05</v>
       </c>
     </row>
     <row r="150">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>57.4</v>
+        <v>57</v>
       </c>
     </row>
     <row r="151">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>18.13</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="153">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>57.95</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>82.84999999999999</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>11.97</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="157">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>36.24</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>13.98</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>83.40000000000001</v>
+        <v>83.45</v>
       </c>
     </row>
     <row r="161">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>37.98</v>
+        <v>37.66</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8.49</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="163">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>149.5</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="164">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>173.7</v>
+        <v>174.2</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>20.26</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>38.76</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="168">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>4.81</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>57.5</v>
+        <v>57.25</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>20.48</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>4987.5</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>24.86</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="173">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>3660</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5610</v>
+        <v>5612.5</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>135.7</v>
+        <v>135.4</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>15.95</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>81.65000000000001</v>
+        <v>80.84999999999999</v>
       </c>
     </row>
     <row r="180">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>617.5</v>
+        <v>612</v>
       </c>
     </row>
     <row r="182">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>91.2</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>14.95</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="184">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>20.44</v>
+        <v>20.24</v>
       </c>
     </row>
     <row r="186">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>60.45</v>
+        <v>60.25</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>32.04</v>
+        <v>32</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>147.2</v>
+        <v>147.1</v>
       </c>
     </row>
     <row r="189">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>38.78</v>
+        <v>38.34</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>247.1</v>
+        <v>246.6</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>13.29</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="193">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>28.4</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="194">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>14.48</v>
+        <v>14</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>28.1</v>
+        <v>28.04</v>
       </c>
     </row>
     <row r="196">
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="197">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="199">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>26.4</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.3</v>
+        <v>23.34</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>30.42</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="202">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="203">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>19.04</v>
+        <v>18.88</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>83.7</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>19.55</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>44.64</v>
+        <v>44.38</v>
       </c>
     </row>
     <row r="207">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>112.1</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>4.48</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>64.95</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>42.1</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>5.85</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="213">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>79.90000000000001</v>
+        <v>79.95</v>
       </c>
     </row>
     <row r="214">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>41</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="216">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="217">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>12.36</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>74.8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>649.5</v>
+        <v>643.5</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>11.3</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="221">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>14.55</v>
+        <v>14.51</v>
       </c>
     </row>
     <row r="222">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>40.52</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="223">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>53.8</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>7.22</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="225">
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>7.94</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="226">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>132.3</v>
+        <v>131.7</v>
       </c>
     </row>
     <row r="227">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>16.42</v>
+        <v>16.47</v>
       </c>
     </row>
     <row r="229">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>8.800000000000001</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="230">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.08</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>38.66</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>17.63</v>
+        <v>17.68</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="234">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>12.02</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>41.68</v>
+        <v>41.48</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>108</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>61.45</v>
+        <v>61.35</v>
       </c>
     </row>
     <row r="239">
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="H239" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="240">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="241">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>39.22</v>
+        <v>39.06</v>
       </c>
     </row>
     <row r="242">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>31.64</v>
+        <v>31.44</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>89.8</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>21.28</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="245">
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="246">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.26</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="247">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>85.3</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="248">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>413</v>
+        <v>411.75</v>
       </c>
     </row>
     <row r="251">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>35.54</v>
+        <v>35.02</v>
       </c>
     </row>
     <row r="252">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>257.5</v>
+        <v>256.5</v>
       </c>
     </row>
     <row r="253">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>19.86</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="254">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>23.78</v>
+        <v>23.86</v>
       </c>
     </row>
     <row r="255">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>1118</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>18.78</v>
+        <v>18.63</v>
       </c>
     </row>
     <row r="257">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>70.65000000000001</v>
+        <v>70.75</v>
       </c>
     </row>
     <row r="259">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>51.8</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="260">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>12.98</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="261">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.44</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>124.4</v>
+        <v>124.1</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>11.43</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="265">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>122.3</v>
+        <v>122.2</v>
       </c>
     </row>
     <row r="266">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>17.56</v>
+        <v>17.54</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>17.87</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>13.83</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="269">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>5.96</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="270">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>58.35</v>
+        <v>58.15</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>26.44</v>
+        <v>26.48</v>
       </c>
     </row>
     <row r="272">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>8.119999999999999</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="273">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>12.37</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>7.46</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>39.52</v>
+        <v>39.24</v>
       </c>
     </row>
     <row r="276">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>32.56</v>
+        <v>32.42</v>
       </c>
     </row>
     <row r="277">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.18</v>
+        <v>11.15</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>108.8</v>
+        <v>109.1</v>
       </c>
     </row>
     <row r="280">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="281">
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>6.35</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="282">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>25.62</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="284">
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>24.44</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="285">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>22.46</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>6.17</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="287">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>57.65</v>
+        <v>57.15</v>
       </c>
     </row>
     <row r="288">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>6.06</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="289">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>7.97</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>20.56</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>724.5</v>
+        <v>718.5</v>
       </c>
     </row>
     <row r="292">
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>11.52</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="293">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>43.26</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>54.55</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="295">
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>999.5</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="296">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>45.84</v>
+        <v>45.88</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>18.72</v>
+        <v>18.62</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>23.6</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>215.3</v>
+        <v>213.7</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>9.58</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="301">
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="H301" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="302">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>7.45</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="303">
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="H303" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="304">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>85.09999999999999</v>
+        <v>86</v>
       </c>
     </row>
     <row r="305">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>4.92</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="306">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="H308" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="309">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>9.869999999999999</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="310">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>114.2</v>
+        <v>113.7</v>
       </c>
     </row>
     <row r="311">
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="312">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>7.37</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="313">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>6.11</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>39.36</v>
+        <v>39.28</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>14.95</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>15.33</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="317">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>90.90000000000001</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>253.5</v>
+        <v>255.5</v>
       </c>
     </row>
     <row r="320">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>5.76</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="321">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>427</v>
+        <v>428.25</v>
       </c>
     </row>
     <row r="322">
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="H322" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="323">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="324">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>6.2</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>242.7</v>
+        <v>243.6</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>12.1</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>8.210000000000001</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>14.23</v>
+        <v>14.22</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>324</v>
+        <v>323.5</v>
       </c>
     </row>
     <row r="330">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>39.64</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="331">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>94.45</v>
+        <v>93.55</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>32.52</v>
+        <v>32.44</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>14.8</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>16.74</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>63</v>
+        <v>62.35</v>
       </c>
     </row>
     <row r="336">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="337">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.76</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="338">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>147.6</v>
+        <v>146.4</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>13.9</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="340">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>22.26</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>26.4</v>
+        <v>25.82</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>28.44</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="344">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="345">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>17.6</v>
+        <v>17.51</v>
       </c>
     </row>
     <row r="346">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>10.45</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="347">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>11.98</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.38</v>
+        <v>25.24</v>
       </c>
     </row>
     <row r="349">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="H349" t="n">
-        <v>12.63</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="350">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>5.26</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="351">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="H352" t="n">
-        <v>10.09</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="353">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>261.5</v>
+        <v>260.25</v>
       </c>
     </row>
     <row r="355">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>37.7</v>
+        <v>37.56</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>12.02</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="358">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="H358" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="359">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>6.79</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>8.69</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>149.6</v>
+        <v>148.9</v>
       </c>
     </row>
     <row r="363">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>23.32</v>
+        <v>23.16</v>
       </c>
     </row>
     <row r="364">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>19.2</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="365">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>20.52</v>
+        <v>20.24</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>127.8</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="369">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>22.68</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="370">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>7.25</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>6.72</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="372">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>15.86</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="373">
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="H373" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="374">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>297.5</v>
+        <v>297</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>64.40000000000001</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>63.6</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="377">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>7.2</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="378">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>89.40000000000001</v>
+        <v>89.15000000000001</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>64.84999999999999</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>39.8</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.3</v>
+        <v>17.23</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>19.72</v>
+        <v>19.63</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>100.2</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="384">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>106.8</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="386">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="H386" t="n">
-        <v>6.55</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="387">
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>4.82</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="388">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>34</v>
+        <v>34.02</v>
       </c>
     </row>
     <row r="390">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="H390" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="391">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="392">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>9.210000000000001</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="393">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>5.59</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="395">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.27</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="396">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="397">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>13.96</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="398">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>9.66</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>146.3</v>
+        <v>145.8</v>
       </c>
     </row>
     <row r="401">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="H401" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="402">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>12.11</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="403">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>184</v>
+        <v>182.8</v>
       </c>
     </row>
     <row r="404">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>42.28</v>
+        <v>41.66</v>
       </c>
     </row>
     <row r="405">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>30</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="406">
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="407">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>89.59999999999999</v>
+        <v>89.05</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>27.8</v>
+        <v>27.86</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>116.2</v>
+        <v>115.4</v>
       </c>
     </row>
     <row r="410">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>6.65</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="411">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>26.2</v>
+        <v>26.04</v>
       </c>
     </row>
     <row r="412">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>19.8</v>
+        <v>19.81</v>
       </c>
     </row>
     <row r="414">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>45.86</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.13</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="417">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>47.08</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="419">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>28.12</v>
+        <v>27.64</v>
       </c>
     </row>
     <row r="421">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>38.94</v>
+        <v>38.96</v>
       </c>
     </row>
     <row r="422">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>15.5</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="424">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>46.82</v>
+        <v>46.48</v>
       </c>
     </row>
     <row r="425">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>21.92</v>
+        <v>22.02</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.67</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="427">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.15</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>20.86</v>
+        <v>20.56</v>
       </c>
     </row>
     <row r="429">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>11.28</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="431">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="432">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>311</v>
+        <v>309.5</v>
       </c>
     </row>
     <row r="433">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.53</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="434">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>7.58</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="435">
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="436">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>9.92</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="437">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>7.32</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="438">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>12.61</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="439">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>10.42</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="440">
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="441">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>6.15</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="442">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="443">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>103.4</v>
+        <v>103</v>
       </c>
     </row>
     <row r="444">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>39.26</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="445">
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="H445" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="446">
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>26.94</v>
+        <v>26.64</v>
       </c>
     </row>
     <row r="447">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>27.14</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>28.26</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="450">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>177</v>
+        <v>174.3</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>13.19</v>
+        <v>13.18</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="454">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>21.44</v>
+        <v>21.06</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>17.33</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="457">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>19.93</v>
+        <v>19.86</v>
       </c>
     </row>
     <row r="458">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="H458" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="459">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>12.82</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>36.92</v>
+        <v>36.86</v>
       </c>
     </row>
     <row r="461">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>81.09999999999999</v>
+        <v>80.75</v>
       </c>
     </row>
     <row r="462">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="464">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>31.9</v>
+        <v>31.88</v>
       </c>
     </row>
     <row r="465">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="H465" t="n">
-        <v>10.89</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="466">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="468">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>24.68</v>
+        <v>24.38</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>35.3</v>
+        <v>35.26</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>30.68</v>
+        <v>30.42</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>42.1</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="472">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>12.64</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="474">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>13.19</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="477">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="478">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>26.9</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>8.51</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.08</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="481">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>13.65</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="482">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.1</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>81.90000000000001</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="484">
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="485">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="486">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>95.3</v>
+        <v>97.15000000000001</v>
       </c>
     </row>
     <row r="487">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>17.51</v>
+        <v>17.38</v>
       </c>
     </row>
     <row r="488">
@@ -16588,7 +16588,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="490">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>29.28</v>
+        <v>29.02</v>
       </c>
     </row>
     <row r="491">
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="H491" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="492">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>33.98</v>
+        <v>33.82</v>
       </c>
     </row>
     <row r="494">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>49.02</v>
+        <v>48.88</v>
       </c>
     </row>
     <row r="495">
@@ -16786,7 +16786,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="496">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>10.18</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="497">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="499">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="501">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.02</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="503">
@@ -17050,7 +17050,7 @@
         </is>
       </c>
       <c r="H503" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="504">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="H504" t="n">
-        <v>9.01</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="505">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>8.470000000000001</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="506">
@@ -17248,7 +17248,7 @@
         </is>
       </c>
       <c r="H509" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="510">
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="512">
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="H512" t="n">
-        <v>33.96</v>
+        <v>33.46</v>
       </c>
     </row>
     <row r="513">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="H513" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="514">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>6.64</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="515">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>9.050000000000001</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="516">
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="H516" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="517">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>16.13</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>14.63</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>216.1</v>
+        <v>216.2</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>148.7</v>
+        <v>149.2</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>12.42</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>71.7</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="523">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>4.56</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="524">
@@ -17743,7 +17743,7 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>4.18</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="525">
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>7.54</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="526">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>13.88</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="527">
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="H528" t="n">
-        <v>17.37</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="529">
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="H529" t="n">
-        <v>13.68</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="530">
@@ -17941,7 +17941,7 @@
         </is>
       </c>
       <c r="H530" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="531">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="532">
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="533">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.3</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="534">
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="H534" t="n">
-        <v>4.37</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="535">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>6.22</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="536">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>22.4</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="537">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.28</v>
+        <v>25.22</v>
       </c>
     </row>
     <row r="538">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>152.5</v>
+        <v>153.9</v>
       </c>
     </row>
     <row r="539">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>61.85</v>
+        <v>61.45</v>
       </c>
     </row>
     <row r="540">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="H540" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="541">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>25.44</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="542">
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="H542" t="n">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="543">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>15.01</v>
+        <v>15</v>
       </c>
     </row>
     <row r="544">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>33.56</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="546">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>15.91</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="547">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>27.84</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>53.55</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="549">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="H549" t="n">
-        <v>10.31</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="550">
@@ -18634,7 +18634,7 @@
         </is>
       </c>
       <c r="H551" t="n">
-        <v>42.48</v>
+        <v>42.32</v>
       </c>
     </row>
     <row r="552">
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="H553" t="n">
-        <v>46.44</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="554">
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="H556" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="557">
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="H557" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="558">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="H558" t="n">
-        <v>119</v>
+        <v>118.9</v>
       </c>
     </row>
     <row r="559">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>28.44</v>
+        <v>28.58</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="562">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="H562" t="n">
-        <v>23.78</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="563">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="H563" t="n">
-        <v>26.62</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="564">
@@ -19063,7 +19063,7 @@
         </is>
       </c>
       <c r="H564" t="n">
-        <v>12.95</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="565">
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="H565" t="n">
-        <v>8.029999999999999</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="566">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>6.5</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="569">
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>8.460000000000001</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="572">
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>4.78</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="573">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>26.56</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="575">
@@ -19459,7 +19459,7 @@
         </is>
       </c>
       <c r="H576" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="577">
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="H577" t="n">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="578">
@@ -19558,7 +19558,7 @@
         </is>
       </c>
       <c r="H579" t="n">
-        <v>12.37</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="580">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.449999999999999</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="581">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.65</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="582">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H582" t="n">
-        <v>10.5</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="583">
@@ -19690,7 +19690,7 @@
         </is>
       </c>
       <c r="H583" t="n">
-        <v>6.17</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="584">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>44.42</v>
+        <v>18.24</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>3.78</v>
+        <v>38</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>44.98</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>66.25</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>37.68</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>104.1</v>
+        <v>40.26</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>38.78</v>
+        <v>37.94</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>7.96</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>40.34</v>
+        <v>44.16</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>20.76</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>17.37</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>163.4</v>
+        <v>37.86</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>18.6</v>
+        <v>181.5</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>70.40000000000001</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>17.19</v>
+        <v>20.84</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>18.5</v>
+        <v>65.55</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>73.62</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>14.32</v>
+        <v>16.61</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>2.44</v>
+        <v>20.28</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>12.56</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>20.36</v>
+        <v>33.88</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>34.3</v>
+        <v>73.72</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>128.5</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>16.74</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="610">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>37.9</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>182</v>
+        <v>103.7</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>369.75</v>
+        <v>370.5</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2585</v>
+        <v>2572.5</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>92.84999999999999</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>134.5</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>185.9</v>
+        <v>187.1</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>232.9</v>
+        <v>233.2</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>376.25</v>
+        <v>378.75</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>303.75</v>
+        <v>305.25</v>
       </c>
     </row>
     <row r="11">
@@ -805,7 +805,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ISBTR</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>419915</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="12">
@@ -838,7 +838,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISBTR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2915000</v>
+        <v>419915</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>14.21</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>70.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>173</v>
+        <v>173.4</v>
       </c>
     </row>
     <row r="16">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>45.56</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>32.08</v>
+        <v>32.22</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>86.05</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>37.36</v>
+        <v>37.78</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>268.25</v>
+        <v>265.75</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>38.76</v>
+        <v>39.16</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>109.6</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="24">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>81</v>
+        <v>81.75</v>
       </c>
     </row>
     <row r="25">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>63.1</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="26">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>94.15000000000001</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>58.55</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="28">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>217.9</v>
+        <v>220.2</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>93.45</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>42.76</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>44.34</v>
+        <v>44.46</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>12.84</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="36">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>104.3</v>
+        <v>105.1</v>
       </c>
     </row>
     <row r="38">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>656.5</v>
+        <v>656</v>
       </c>
     </row>
     <row r="39">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>20.42</v>
+        <v>20.38</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>665</v>
+        <v>671</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>10940</v>
+        <v>10875</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1608</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>21.04</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="45">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>33.4</v>
+        <v>35.72</v>
       </c>
     </row>
     <row r="46">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>97.7</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>79.55</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>271.5</v>
+        <v>273.25</v>
       </c>
     </row>
     <row r="49">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>108</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="51">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>620.5</v>
+        <v>623.5</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>437.5</v>
+        <v>439.5</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>32.68</v>
+        <v>32.84</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>168.6</v>
+        <v>170.2</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>16.66</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>32.94</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="58">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>115.1</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="59">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>214.7</v>
+        <v>212.7</v>
       </c>
     </row>
     <row r="60">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>9.26</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6.08</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="62">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>109.9</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>257.5</v>
+        <v>259.25</v>
       </c>
     </row>
     <row r="66">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>202.1</v>
+        <v>204.3</v>
       </c>
     </row>
     <row r="68">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.68</v>
+        <v>32.64</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>12.72</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="71">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>94.7</v>
+        <v>95.84999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1289</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="73">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>128.2</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="74">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>79.95</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>27.38</v>
+        <v>27.74</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>39.84</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>33.36</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1977</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>167.2</v>
+        <v>168.1</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>36.06</v>
+        <v>36.16</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>138.3</v>
+        <v>139</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>217.8</v>
+        <v>217.7</v>
       </c>
     </row>
     <row r="83">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1685</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="84">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KRDMD</t>
+          <t>KRDMA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>38.88</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="85">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>113</v>
+        <v>113.1</v>
       </c>
     </row>
     <row r="86">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KRDMA</t>
+          <t>KRDMD</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>41.24</v>
+        <v>39.24</v>
       </c>
     </row>
     <row r="87">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.38</v>
+        <v>19.31</v>
       </c>
     </row>
     <row r="89">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>223.3</v>
+        <v>223.2</v>
       </c>
     </row>
     <row r="90">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>49.42</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>243.3</v>
+        <v>246.8</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>439.5</v>
+        <v>441</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>102.3</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="95">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>100.1</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="96">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>133</v>
+        <v>133.9</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>614.5</v>
+        <v>622</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>11</v>
+        <v>11.15</v>
       </c>
     </row>
     <row r="99">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>63.25</v>
+        <v>64.05</v>
       </c>
     </row>
     <row r="100">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>349</v>
+        <v>348.5</v>
       </c>
     </row>
     <row r="101">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>105.1</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>216.4</v>
+        <v>217.2</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>111.7</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>201.5</v>
+        <v>203.5</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>84.5</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1644</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>21.8</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>35.66</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>105</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>338</v>
+        <v>347.75</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>8.19</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>145.6</v>
+        <v>146.3</v>
       </c>
     </row>
     <row r="113">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>339.5</v>
+        <v>344.5</v>
       </c>
     </row>
     <row r="114">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>48.74</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>13.68</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>41.92</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="117">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>13.43</v>
+        <v>13.47</v>
       </c>
     </row>
     <row r="119">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>5.79</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="120">
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="121">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>193.8</v>
+        <v>194.8</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>11.7</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>218</v>
+        <v>218.1</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>25.86</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>300.25</v>
+        <v>304.25</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>13.93</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="127">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>15.91</v>
+        <v>15.97</v>
       </c>
     </row>
     <row r="128">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>10.41</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>13.48</v>
+        <v>13.46</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>48.6</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="131">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>14.95</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>112</v>
+        <v>112.3</v>
       </c>
     </row>
     <row r="134">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>89.95</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>27.54</v>
+        <v>27.84</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>228.1</v>
+        <v>232.5</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>13687.5</v>
+        <v>13747.5</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>69.90000000000001</v>
+        <v>70.25</v>
       </c>
     </row>
     <row r="141">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>310.75</v>
+        <v>313.25</v>
       </c>
     </row>
     <row r="142">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>145.1</v>
+        <v>145</v>
       </c>
     </row>
     <row r="144">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>9.65</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="145">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>58.65</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>46.18</v>
+        <v>46.02</v>
       </c>
     </row>
     <row r="147">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>6.25</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="148">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>46.28</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>86.05</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="150">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>57</v>
+        <v>56.95</v>
       </c>
     </row>
     <row r="151">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>18.2</v>
+        <v>18.08</v>
       </c>
     </row>
     <row r="153">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.08</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>57.6</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>11.89</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="157">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="158">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>36.06</v>
+        <v>36.32</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>14.01</v>
+        <v>14.17</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>83.45</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="161">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>37.66</v>
+        <v>37.72</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8.359999999999999</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="163">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>147.5</v>
+        <v>147.8</v>
       </c>
     </row>
     <row r="164">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>174.2</v>
+        <v>174.1</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>20.16</v>
+        <v>20.28</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>6.8</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="168">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>4.79</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>57.25</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>20.34</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>5000</v>
+        <v>5015</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>24.76</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="173">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>72.59999999999999</v>
+        <v>73.15000000000001</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>3650</v>
+        <v>3667.5</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5612.5</v>
+        <v>5635</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>135.4</v>
+        <v>136</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1506</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>15.82</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>80.84999999999999</v>
+        <v>80.95</v>
       </c>
     </row>
     <row r="180">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>11</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="181">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="182">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>90.7</v>
+        <v>92.55</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>14.93</v>
+        <v>14.96</v>
       </c>
     </row>
     <row r="184">
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>22.72</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="185">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>20.24</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="186">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>60.25</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>147.1</v>
+        <v>150.1</v>
       </c>
     </row>
     <row r="189">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>38.34</v>
+        <v>38.74</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>246.6</v>
+        <v>246.1</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>13.23</v>
+        <v>13.28</v>
       </c>
     </row>
     <row r="193">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>28.32</v>
+        <v>28.36</v>
       </c>
     </row>
     <row r="194">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>14</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>28.04</v>
+        <v>28.42</v>
       </c>
     </row>
     <row r="196">
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="197">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="199">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>26.32</v>
+        <v>26.42</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.34</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>30.26</v>
+        <v>30.36</v>
       </c>
     </row>
     <row r="202">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="203">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>18.88</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>83.8</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>19.5</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>44.38</v>
+        <v>44.34</v>
       </c>
     </row>
     <row r="207">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>144.9</v>
+        <v>145.6</v>
       </c>
     </row>
     <row r="208">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>112.7</v>
+        <v>113.3</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>64.7</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>41.92</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>5.74</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="213">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>79.95</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="214">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>40.8</v>
+        <v>40.82</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>31.5</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="216">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>12.15</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>74</v>
+        <v>74.65000000000001</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>643.5</v>
+        <v>654</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>11.26</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="221">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>14.51</v>
+        <v>14.62</v>
       </c>
     </row>
     <row r="222">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>40.3</v>
+        <v>40.48</v>
       </c>
     </row>
     <row r="223">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>53.35</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>7.16</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="225">
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>7.9</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="226">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>131.7</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="227">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>16.47</v>
+        <v>16.48</v>
       </c>
     </row>
     <row r="229">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>8.789999999999999</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="230">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.06</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>38.5</v>
+        <v>38.66</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>17.68</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="234">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>11.92</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>41.48</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>107.8</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>61.35</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="239">
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="H239" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="240">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="241">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>39.06</v>
+        <v>39.12</v>
       </c>
     </row>
     <row r="242">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>31.44</v>
+        <v>31.42</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>89.3</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>21.16</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="245">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.18</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="247">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>84.09999999999999</v>
+        <v>84.65000000000001</v>
       </c>
     </row>
     <row r="248">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>6.24</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="249">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>3.81</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="250">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>411.75</v>
+        <v>415.5</v>
       </c>
     </row>
     <row r="251">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>256.5</v>
+        <v>257.5</v>
       </c>
     </row>
     <row r="253">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>23.86</v>
+        <v>23.92</v>
       </c>
     </row>
     <row r="255">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>1115</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>18.63</v>
+        <v>18.62</v>
       </c>
     </row>
     <row r="257">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="258">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>70.75</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="259">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>51.25</v>
+        <v>52.05</v>
       </c>
     </row>
     <row r="260">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>12.97</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="261">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="262">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.34</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>124.1</v>
+        <v>124.7</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>11.46</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="265">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>122.2</v>
+        <v>124</v>
       </c>
     </row>
     <row r="266">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>17.54</v>
+        <v>17.51</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>17.8</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>13.85</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="269">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>5.93</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="270">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>58.15</v>
+        <v>58</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>26.48</v>
+        <v>26.54</v>
       </c>
     </row>
     <row r="272">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>8.09</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="273">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>12.35</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>7.45</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>39.24</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="276">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>32.42</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="277">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.15</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>109.1</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="280">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="281">
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>6.34</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="282">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>26.1</v>
+        <v>26.16</v>
       </c>
     </row>
     <row r="284">
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>24.34</v>
+        <v>24.42</v>
       </c>
     </row>
     <row r="285">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>22.38</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>6.14</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="287">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>6.03</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="289">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>7.93</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>718.5</v>
+        <v>723.5</v>
       </c>
     </row>
     <row r="292">
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>11.51</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="293">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>42.26</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>54.5</v>
+        <v>54.45</v>
       </c>
     </row>
     <row r="295">
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>1000</v>
+        <v>998.5</v>
       </c>
     </row>
     <row r="296">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>45.88</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>18.62</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>23.52</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>213.7</v>
+        <v>213.5</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>9.52</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="301">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>7.46</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="303">
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="H303" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="304">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>86</v>
+        <v>85.95</v>
       </c>
     </row>
     <row r="305">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>4.9</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="306">
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="308">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="H308" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="309">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>9.81</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="310">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>113.7</v>
+        <v>113.9</v>
       </c>
     </row>
     <row r="311">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>6.19</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>39.28</v>
+        <v>39.12</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>15.37</v>
+        <v>15.41</v>
       </c>
     </row>
     <row r="317">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>90.2</v>
+        <v>90.65000000000001</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>255.5</v>
+        <v>262.25</v>
       </c>
     </row>
     <row r="320">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>5.74</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="321">
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="H322" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="323">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="324">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>243.6</v>
+        <v>242.5</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>12.08</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>8.279999999999999</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>14.22</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>323.5</v>
+        <v>325.25</v>
       </c>
     </row>
     <row r="330">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>39.4</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="331">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>93.55</v>
+        <v>93.95</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>32.44</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>14.69</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>16.67</v>
+        <v>16.72</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>62.35</v>
+        <v>62.65</v>
       </c>
     </row>
     <row r="336">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="337">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.77</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="338">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>146.4</v>
+        <v>148.1</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>13.89</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="340">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>22.12</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>25.82</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>28.7</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="344">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>5.26</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="345">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>17.51</v>
+        <v>17.53</v>
       </c>
     </row>
     <row r="346">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>10.41</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="347">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>11.97</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.24</v>
+        <v>25.22</v>
       </c>
     </row>
     <row r="349">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="H349" t="n">
-        <v>12.62</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="350">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="351">
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="H351" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="352">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="H352" t="n">
-        <v>10.22</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="353">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>260.25</v>
+        <v>261.75</v>
       </c>
     </row>
     <row r="355">
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="H355" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="356">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>37.56</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>12.01</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="358">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="H358" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="359">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>6.74</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>8.640000000000001</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>148.9</v>
+        <v>149.5</v>
       </c>
     </row>
     <row r="363">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>23.16</v>
+        <v>23.38</v>
       </c>
     </row>
     <row r="364">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>19.38</v>
+        <v>19.36</v>
       </c>
     </row>
     <row r="365">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="H365" t="n">
-        <v>57.7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="366">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>20.24</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>128.7</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>14.9</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="369">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>22.38</v>
+        <v>22.56</v>
       </c>
     </row>
     <row r="370">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>7.16</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>6.69</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="372">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>15.7</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="373">
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="H373" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="374">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>297</v>
+        <v>298.25</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>63.8</v>
+        <v>64.05</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>63.8</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
     <row r="377">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>7.16</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="378">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>89.15000000000001</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>64.3</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>39.74</v>
+        <v>39.72</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.23</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>19.63</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>97.3</v>
+        <v>98.45</v>
       </c>
     </row>
     <row r="384">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>105.8</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="386">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="H386" t="n">
-        <v>6.51</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="387">
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>4.79</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="388">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>5.37</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="389">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>34.02</v>
+        <v>34.14</v>
       </c>
     </row>
     <row r="390">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="H390" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="391">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>12.7</v>
+        <v>12.86</v>
       </c>
     </row>
     <row r="392">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>9.19</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="393">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="394">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.24</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="396">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="397">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>13.76</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="398">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>9.800000000000001</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>145.8</v>
+        <v>146.9</v>
       </c>
     </row>
     <row r="401">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="H401" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="402">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>12.05</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="403">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>182.8</v>
+        <v>183</v>
       </c>
     </row>
     <row r="404">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>41.66</v>
+        <v>42</v>
       </c>
     </row>
     <row r="405">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>29.92</v>
+        <v>30.06</v>
       </c>
     </row>
     <row r="406">
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>4.92</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="407">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>89.05</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>27.86</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>115.4</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="410">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>6.62</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="411">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>26.04</v>
+        <v>26.18</v>
       </c>
     </row>
     <row r="412">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>19.81</v>
+        <v>19.94</v>
       </c>
     </row>
     <row r="414">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>45.42</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.1</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="417">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>47.4</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>8.35</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="420">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>27.64</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="421">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>38.96</v>
+        <v>38.92</v>
       </c>
     </row>
     <row r="422">
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="H422" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="423">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>15.38</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="424">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>46.48</v>
+        <v>46.86</v>
       </c>
     </row>
     <row r="425">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>22.02</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.73</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="427">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.13</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>20.56</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="429">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>8.859999999999999</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="430">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>11.21</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="431">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>309.5</v>
+        <v>307.5</v>
       </c>
     </row>
     <row r="433">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.46</v>
+        <v>14.48</v>
       </c>
     </row>
     <row r="434">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>7.5</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="435">
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="436">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>9.84</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="437">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>7.31</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="438">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>12.56</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="439">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>10.29</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="440">
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="441">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="443">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>103</v>
+        <v>103.9</v>
       </c>
     </row>
     <row r="444">
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="H445" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="446">
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>26.64</v>
+        <v>26.78</v>
       </c>
     </row>
     <row r="447">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>26.88</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>27.96</v>
+        <v>28.54</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>1505</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="450">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>174.3</v>
+        <v>174.2</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>13.18</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="454">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>17.16</v>
+        <v>17.22</v>
       </c>
     </row>
     <row r="457">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>19.86</v>
+        <v>19.69</v>
       </c>
     </row>
     <row r="458">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="H458" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="459">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>12.78</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>36.86</v>
+        <v>36.82</v>
       </c>
     </row>
     <row r="461">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>80.75</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="462">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="464">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>31.88</v>
+        <v>31.86</v>
       </c>
     </row>
     <row r="465">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="468">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>24.38</v>
+        <v>24.64</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>35.26</v>
+        <v>35.28</v>
       </c>
     </row>
     <row r="470">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>41.94</v>
+        <v>42.22</v>
       </c>
     </row>
     <row r="472">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>13.31</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="477">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="478">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>26.88</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="479">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>13.4</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="482">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>10.99</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>82.5</v>
+        <v>82.55</v>
       </c>
     </row>
     <row r="484">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>97.15000000000001</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="487">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>17.38</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="488">
@@ -16588,7 +16588,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="490">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>29.02</v>
+        <v>29.22</v>
       </c>
     </row>
     <row r="491">
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="H491" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="492">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>33.82</v>
+        <v>33.94</v>
       </c>
     </row>
     <row r="494">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>48.88</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="495">
@@ -16786,7 +16786,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="496">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>10.11</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="497">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="499">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="501">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>39.2</v>
+        <v>39.46</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="503">
@@ -17050,7 +17050,7 @@
         </is>
       </c>
       <c r="H503" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="504">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="H504" t="n">
-        <v>8.99</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="505">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>8.460000000000001</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="506">
@@ -17149,7 +17149,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="507">
@@ -17248,7 +17248,7 @@
         </is>
       </c>
       <c r="H509" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="510">
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="512">
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="H512" t="n">
-        <v>33.46</v>
+        <v>33.62</v>
       </c>
     </row>
     <row r="513">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="H513" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="514">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>6.61</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="515">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>9.01</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="516">
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="H516" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="517">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>16.08</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>14.43</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>216.2</v>
+        <v>216.8</v>
       </c>
     </row>
     <row r="520">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>12.49</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>71.5</v>
+        <v>71.25</v>
       </c>
     </row>
     <row r="523">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>4.52</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="524">
@@ -17743,7 +17743,7 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>4.16</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="525">
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>7.51</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="526">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>13.73</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="527">
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="H528" t="n">
-        <v>17.12</v>
+        <v>17.37</v>
       </c>
     </row>
     <row r="529">
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="H529" t="n">
-        <v>13.74</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="530">
@@ -17941,7 +17941,7 @@
         </is>
       </c>
       <c r="H530" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="531">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="532">
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>5.1</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="533">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.26</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="534">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="536">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>22.52</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="537">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.22</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="538">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>153.9</v>
+        <v>153</v>
       </c>
     </row>
     <row r="539">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>61.45</v>
+        <v>61.75</v>
       </c>
     </row>
     <row r="540">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="H540" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="541">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="542">
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="H542" t="n">
-        <v>4.36</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="543">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>15</v>
+        <v>15.07</v>
       </c>
     </row>
     <row r="544">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>33.4</v>
+        <v>33.46</v>
       </c>
     </row>
     <row r="546">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>15.93</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="547">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>53.9</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="549">
@@ -18634,7 +18634,7 @@
         </is>
       </c>
       <c r="H551" t="n">
-        <v>42.32</v>
+        <v>42.44</v>
       </c>
     </row>
     <row r="552">
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="H553" t="n">
-        <v>46.32</v>
+        <v>46.08</v>
       </c>
     </row>
     <row r="554">
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="H557" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="558">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="H558" t="n">
-        <v>118.9</v>
+        <v>118</v>
       </c>
     </row>
     <row r="559">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>28.58</v>
+        <v>28.26</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="562">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="H562" t="n">
-        <v>23.7</v>
+        <v>23.66</v>
       </c>
     </row>
     <row r="563">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="H563" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="564">
@@ -19063,7 +19063,7 @@
         </is>
       </c>
       <c r="H564" t="n">
-        <v>12.6</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="565">
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="H565" t="n">
-        <v>7.91</v>
+        <v>7.98</v>
       </c>
     </row>
     <row r="566">
@@ -19261,7 +19261,7 @@
         </is>
       </c>
       <c r="H570" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="571">
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>8.48</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="572">
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>4.76</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="573">
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="H573" t="n">
-        <v>18.54</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="574">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>26.6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="575">
@@ -19558,7 +19558,7 @@
         </is>
       </c>
       <c r="H579" t="n">
-        <v>12.3</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="580">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.51</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="582">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H582" t="n">
-        <v>10.35</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="583">
@@ -19690,7 +19690,7 @@
         </is>
       </c>
       <c r="H583" t="n">
-        <v>6.31</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="584">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>18.24</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>38</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>161.5</v>
+        <v>38.04</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>128.5</v>
+        <v>73.52</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>2.44</v>
+        <v>17.13</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>40.26</v>
+        <v>18.26</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>37.94</v>
+        <v>161.3</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>17.09</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>44.16</v>
+        <v>18.19</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>12.49</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>18.44</v>
+        <v>38.68</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>37.86</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>181.5</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>44.98</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>20.84</v>
+        <v>16.73</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>65.55</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>17.44</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>16.61</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>20.28</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>70.40000000000001</v>
+        <v>14.22</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>33.88</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>73.72</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>14.1</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>7.94</v>
+        <v>153.2</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>153.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>3.73</v>
+        <v>181.9</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>103.7</v>
+        <v>33.82</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>370.5</v>
+        <v>371.25</v>
       </c>
     </row>
     <row r="3">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>213</v>
+        <v>216.6</v>
       </c>
     </row>
     <row r="4">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2572.5</v>
+        <v>2612.5</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>93.09999999999999</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>135.6</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>187.1</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>233.2</v>
+        <v>233.8</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>378.75</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>305.25</v>
+        <v>307.75</v>
       </c>
     </row>
     <row r="11">
@@ -805,7 +805,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>ISBTR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>14.3</v>
+        <v>419915</v>
       </c>
     </row>
     <row r="12">
@@ -838,7 +838,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ISBTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>419915</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2915000</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>71.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>173.4</v>
+        <v>172.4</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>115.3</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>45.64</v>
+        <v>45.56</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>32.22</v>
+        <v>32.62</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>86.2</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>37.78</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>265.75</v>
+        <v>265.5</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>39.16</v>
+        <v>39.36</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>109.8</v>
+        <v>110.7</v>
       </c>
     </row>
     <row r="24">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>81.75</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="25">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>63.8</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>95.2</v>
+        <v>95.95</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>58.8</v>
+        <v>59.15</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1592</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>220.2</v>
+        <v>217.5</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>476</v>
+        <v>478.75</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>93.59999999999999</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="32">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>294</v>
+        <v>295.5</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>43</v>
+        <v>43.34</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>44.46</v>
+        <v>44.76</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>12.82</v>
+        <v>12.89</v>
       </c>
     </row>
     <row r="36">
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>377</v>
+        <v>374.25</v>
       </c>
     </row>
     <row r="37">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>105.1</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="38">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>656</v>
+        <v>655.5</v>
       </c>
     </row>
     <row r="39">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>20.38</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>671</v>
+        <v>672.5</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>10875</v>
+        <v>10885</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1586</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="44">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>35.72</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="46">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>98.25</v>
+        <v>98.34999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>79.59999999999999</v>
+        <v>79.84999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>273.25</v>
+        <v>275</v>
       </c>
     </row>
     <row r="49">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="50">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>108.5</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="51">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>9.31</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>623.5</v>
+        <v>621.5</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>439.5</v>
+        <v>442.5</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>32.84</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>170.2</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>16.59</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>33.06</v>
+        <v>33.28</v>
       </c>
     </row>
     <row r="58">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>115.6</v>
+        <v>113.9</v>
       </c>
     </row>
     <row r="59">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>212.7</v>
+        <v>211.5</v>
       </c>
     </row>
     <row r="60">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>9.449999999999999</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2455,16 +2455,16 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
+          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6.07</v>
+        <v>19.91</v>
       </c>
     </row>
     <row r="62">
@@ -2488,16 +2488,16 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>19.7</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>102.5</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>110.2</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>259.25</v>
+        <v>260</v>
       </c>
     </row>
     <row r="66">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>32.7</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>204.3</v>
+        <v>205.5</v>
       </c>
     </row>
     <row r="68">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>180</v>
+        <v>179.6</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>12.71</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="71">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>95.84999999999999</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1303</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="73">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>128.1</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="74">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>80.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>27.74</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>40.16</v>
+        <v>40.22</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>33.8</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>168.1</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>36.16</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="81">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1693</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="84">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>41.24</v>
+        <v>41.22</v>
       </c>
     </row>
     <row r="85">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KRDMB</t>
+          <t>KRDMD</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>113.1</v>
+        <v>39.34</v>
       </c>
     </row>
     <row r="86">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KRDMD</t>
+          <t>KRDMB</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>39.24</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="87">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.26</v>
+        <v>25.08</v>
       </c>
     </row>
     <row r="88">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.31</v>
+        <v>19.39</v>
       </c>
     </row>
     <row r="89">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>223.2</v>
+        <v>223.1</v>
       </c>
     </row>
     <row r="90">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1257</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>49.92</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>246.8</v>
+        <v>250.25</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>441</v>
+        <v>441.25</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>106.5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="95">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>100.4</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="96">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>133.9</v>
+        <v>134</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>622</v>
+        <v>618</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>11.15</v>
+        <v>11.12</v>
       </c>
     </row>
     <row r="99">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>64.05</v>
+        <v>65.75</v>
       </c>
     </row>
     <row r="100">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>348.5</v>
+        <v>347.75</v>
       </c>
     </row>
     <row r="101">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>105.9</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>217.2</v>
+        <v>217.1</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>111.8</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>203.5</v>
+        <v>200.5</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>86.2</v>
+        <v>85.75</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1655</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>21.96</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>35.98</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>105.9</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>347.75</v>
+        <v>340</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>8.1</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="112">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>344.5</v>
+        <v>348</v>
       </c>
     </row>
     <row r="114">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>48.96</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>13.79</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>42.12</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="117">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="118">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>13.47</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="119">
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="121">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>194.8</v>
+        <v>197.1</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>11.75</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="123">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>304.25</v>
+        <v>305</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>13.95</v>
+        <v>14</v>
       </c>
     </row>
     <row r="127">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>15.97</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="128">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>10.52</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>13.46</v>
+        <v>13.45</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>48.94</v>
+        <v>49.18</v>
       </c>
     </row>
     <row r="131">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>15.02</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>112.3</v>
+        <v>112.9</v>
       </c>
     </row>
     <row r="134">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>52.55</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="135">
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="136">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>27.84</v>
+        <v>27.98</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>232.5</v>
+        <v>232</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>13747.5</v>
+        <v>13752.5</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>70.25</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="141">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>313.25</v>
+        <v>311.25</v>
       </c>
     </row>
     <row r="142">
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>289.75</v>
+        <v>289.5</v>
       </c>
     </row>
     <row r="143">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>145</v>
+        <v>145.5</v>
       </c>
     </row>
     <row r="144">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>9.699999999999999</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="145">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>58.3</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>46.02</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="147">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>6.28</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="148">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>46.44</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>86.09999999999999</v>
+        <v>86</v>
       </c>
     </row>
     <row r="150">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>56.95</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="151">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="152">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>18.08</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="153">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.109999999999999</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>82.8</v>
+        <v>83.55</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>11.9</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="157">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="158">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>36.32</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>14.17</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>83.2</v>
+        <v>83</v>
       </c>
     </row>
     <row r="161">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>37.72</v>
+        <v>37.58</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8.630000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="163">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>147.8</v>
+        <v>147.9</v>
       </c>
     </row>
     <row r="164">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>174.1</v>
+        <v>174.7</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>20.28</v>
+        <v>20.26</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>6.86</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="168">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>4.81</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>57.7</v>
+        <v>58.25</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>20.8</v>
+        <v>20.64</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>5015</v>
+        <v>5027.5</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>25.1</v>
+        <v>25.22</v>
       </c>
     </row>
     <row r="173">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>73.15000000000001</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>3667.5</v>
+        <v>3675</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5635</v>
+        <v>5622.5</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>136</v>
+        <v>136.2</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1511</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>15.91</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>80.95</v>
+        <v>83.15000000000001</v>
       </c>
     </row>
     <row r="180">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>11.01</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="181">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="182">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>92.55</v>
+        <v>94.95</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>14.96</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="184">
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>22.6</v>
+        <v>22.56</v>
       </c>
     </row>
     <row r="185">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>60.7</v>
+        <v>60.85</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>32.7</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>150.1</v>
+        <v>151.5</v>
       </c>
     </row>
     <row r="189">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>38.74</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>246.1</v>
+        <v>247</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>13.28</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="193">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>14.01</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>28.42</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="196">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="199">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>26.42</v>
+        <v>26.56</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.44</v>
+        <v>23.38</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>30.36</v>
+        <v>30.38</v>
       </c>
     </row>
     <row r="202">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="203">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>84.2</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>19.53</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>44.34</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="207">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>113.3</v>
+        <v>112.9</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>4.48</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>64.90000000000001</v>
+        <v>65.05</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>42.2</v>
+        <v>42.62</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>5.79</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="213">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>80.40000000000001</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="214">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>40.82</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>31.58</v>
+        <v>31.52</v>
       </c>
     </row>
     <row r="216">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>12.19</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>74.65000000000001</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>654</v>
+        <v>663</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>11.35</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="221">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>40.48</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="223">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>53.15</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>7.13</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="225">
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>7.91</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="226">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>16.48</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="229">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>8.85</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="230">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.09</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>38.66</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>17.44</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="234">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>16.22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="235">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>12.03</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>41.54</v>
+        <v>41.68</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>107.6</v>
+        <v>107.3</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>61.4</v>
+        <v>61.65</v>
       </c>
     </row>
     <row r="239">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="241">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>39.12</v>
+        <v>40.06</v>
       </c>
     </row>
     <row r="242">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>31.42</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>89.59999999999999</v>
+        <v>90.05</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>21.24</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="245">
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="246">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.23</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="247">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>84.65000000000001</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="248">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>6.25</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="249">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="250">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>415.5</v>
+        <v>413.75</v>
       </c>
     </row>
     <row r="251">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>35.02</v>
+        <v>35.04</v>
       </c>
     </row>
     <row r="252">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>257.5</v>
+        <v>257.25</v>
       </c>
     </row>
     <row r="253">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>23.92</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="255">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>1125</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>18.62</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="257">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>4.55</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="258">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>71.09999999999999</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="259">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>52.05</v>
+        <v>52</v>
       </c>
     </row>
     <row r="260">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>13.07</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="261">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="262">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.32</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>124.7</v>
+        <v>123.9</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>11.45</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="265">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>124</v>
+        <v>122.5</v>
       </c>
     </row>
     <row r="266">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>17.51</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>18.04</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>13.99</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="269">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>5.95</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="270">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>58</v>
+        <v>57.55</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>26.54</v>
+        <v>26.86</v>
       </c>
     </row>
     <row r="272">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>8.140000000000001</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="273">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>7.47</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>39.2</v>
+        <v>39.32</v>
       </c>
     </row>
     <row r="276">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>32.4</v>
+        <v>32.48</v>
       </c>
     </row>
     <row r="277">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.18</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>111.5</v>
+        <v>111.9</v>
       </c>
     </row>
     <row r="280">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="281">
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>6.35</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="282">
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>21.2</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="283">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>26.16</v>
+        <v>25.68</v>
       </c>
     </row>
     <row r="284">
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>24.42</v>
+        <v>24.46</v>
       </c>
     </row>
     <row r="285">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>6.19</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="287">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>57.15</v>
+        <v>57</v>
       </c>
     </row>
     <row r="288">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>6.1</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="289">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>8.029999999999999</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>20.5</v>
+        <v>20.56</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>723.5</v>
+        <v>723</v>
       </c>
     </row>
     <row r="292">
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>11.54</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="293">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>41.94</v>
+        <v>42.08</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>54.45</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="295">
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>998.5</v>
+        <v>997</v>
       </c>
     </row>
     <row r="296">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>45.62</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>18.64</v>
+        <v>18.66</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>23.6</v>
+        <v>23.64</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>213.5</v>
+        <v>213.2</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="301">
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="H301" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="302">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>7.47</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="303">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>85.95</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="305">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>4.93</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="306">
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="308">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>9.859999999999999</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="310">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>113.9</v>
+        <v>114.1</v>
       </c>
     </row>
     <row r="311">
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="312">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>7.35</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="313">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>6.15</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>39.12</v>
+        <v>39.18</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>15</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>15.41</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>90.65000000000001</v>
+        <v>90.55</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>262.25</v>
+        <v>259</v>
       </c>
     </row>
     <row r="320">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>5.81</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="321">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>428.25</v>
+        <v>432.5</v>
       </c>
     </row>
     <row r="322">
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="H322" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="323">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="324">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>242.5</v>
+        <v>242.6</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>12.07</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>8.25</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>14.24</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>325.25</v>
+        <v>327</v>
       </c>
     </row>
     <row r="330">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>93.95</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>32.68</v>
+        <v>33.26</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>14.83</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>16.72</v>
+        <v>16.76</v>
       </c>
     </row>
     <row r="335">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="337">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>148.1</v>
+        <v>153.1</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>13.84</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="340">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="H340" t="n">
-        <v>205.9</v>
+        <v>198.5</v>
       </c>
     </row>
     <row r="341">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>22.3</v>
+        <v>22.34</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>26.62</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="344">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>5.28</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="345">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>17.53</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="346">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>10.45</v>
+        <v>10.54</v>
       </c>
     </row>
     <row r="347">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>11.92</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.22</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="349">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="H349" t="n">
-        <v>12.65</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="350">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>5.28</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="351">
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="H351" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="352">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="H352" t="n">
-        <v>10.21</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="353">
@@ -12100,7 +12100,7 @@
         </is>
       </c>
       <c r="H353" t="n">
-        <v>34</v>
+        <v>34.96</v>
       </c>
     </row>
     <row r="354">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>261.75</v>
+        <v>261.5</v>
       </c>
     </row>
     <row r="355">
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="H355" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="356">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>37.5</v>
+        <v>37.82</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>11.99</v>
+        <v>12</v>
       </c>
     </row>
     <row r="358">
@@ -12298,7 +12298,7 @@
         </is>
       </c>
       <c r="H359" t="n">
-        <v>16.23</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="360">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>6.78</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>8.710000000000001</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>149.5</v>
+        <v>147.8</v>
       </c>
     </row>
     <row r="363">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>23.38</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="364">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>19.36</v>
+        <v>19.45</v>
       </c>
     </row>
     <row r="365">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>20.3</v>
+        <v>20.24</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>127.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>14.94</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="369">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>22.56</v>
+        <v>22.72</v>
       </c>
     </row>
     <row r="370">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>6.73</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="372">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>15.78</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="373">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>298.25</v>
+        <v>297</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>64.05</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="376">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>7.2</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="378">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>89.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>64.8</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>39.72</v>
+        <v>40</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.2</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>19.73</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>98.45</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="384">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>106.1</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="386">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="H386" t="n">
-        <v>6.85</v>
+        <v>7</v>
       </c>
     </row>
     <row r="387">
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="388">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>5.39</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="389">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>34.14</v>
+        <v>34.76</v>
       </c>
     </row>
     <row r="390">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="H390" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="391">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>12.86</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="392">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>9.23</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="393">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="394">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.14</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="396">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="397">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>13.85</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="398">
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="H398" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="399">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>10.32</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>146.9</v>
+        <v>147</v>
       </c>
     </row>
     <row r="401">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="H401" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="402">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>12.1</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="403">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>183</v>
+        <v>184.6</v>
       </c>
     </row>
     <row r="404">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>42</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="405">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>30.06</v>
+        <v>30.38</v>
       </c>
     </row>
     <row r="406">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>89.7</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>27.88</v>
+        <v>28.04</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>116.6</v>
+        <v>116.1</v>
       </c>
     </row>
     <row r="410">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>6.7</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="411">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>26.18</v>
+        <v>26.22</v>
       </c>
     </row>
     <row r="412">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>19.94</v>
+        <v>20.42</v>
       </c>
     </row>
     <row r="414">
@@ -14113,7 +14113,7 @@
         </is>
       </c>
       <c r="H414" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="415">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>45.84</v>
+        <v>45.76</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.13</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="417">
@@ -14212,7 +14212,7 @@
         </is>
       </c>
       <c r="H417" t="n">
-        <v>298</v>
+        <v>297.75</v>
       </c>
     </row>
     <row r="418">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>46.7</v>
+        <v>48.02</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>8.460000000000001</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="420">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>27.7</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="421">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>38.92</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="422">
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="H422" t="n">
-        <v>4.11</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="423">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>15.48</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="424">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>46.86</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="425">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>22.06</v>
+        <v>21.94</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.71</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="427">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.17</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>20.74</v>
+        <v>20.82</v>
       </c>
     </row>
     <row r="429">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>8.890000000000001</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="430">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>11.25</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="431">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>307.5</v>
+        <v>310.25</v>
       </c>
     </row>
     <row r="433">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.48</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="434">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>7.54</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="435">
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="436">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>9.859999999999999</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="437">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>7.3</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="438">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>12.64</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="439">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>10.35</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="440">
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="441">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>6.08</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="442">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="443">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="445">
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="H445" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="446">
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>26.78</v>
+        <v>26.86</v>
       </c>
     </row>
     <row r="447">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>26.92</v>
+        <v>26.86</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>28.54</v>
+        <v>29.38</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>1516</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="450">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>174.2</v>
+        <v>173</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>13.23</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="454">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>5.12</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>21.06</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>17.22</v>
+        <v>17.26</v>
       </c>
     </row>
     <row r="457">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>19.69</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="458">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="H458" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="459">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>12.82</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>36.82</v>
+        <v>36.92</v>
       </c>
     </row>
     <row r="461">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>81.3</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="462">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="464">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>31.86</v>
+        <v>31.88</v>
       </c>
     </row>
     <row r="465">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="H465" t="n">
-        <v>10.85</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="466">
@@ -15829,7 +15829,7 @@
         </is>
       </c>
       <c r="H466" t="n">
-        <v>96.15000000000001</v>
+        <v>98</v>
       </c>
     </row>
     <row r="467">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="468">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>24.64</v>
+        <v>24.62</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>35.28</v>
+        <v>35.74</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>30.42</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>42.22</v>
+        <v>42.44</v>
       </c>
     </row>
     <row r="472">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>3.09</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="473">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>12.52</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="474">
@@ -16093,7 +16093,7 @@
         </is>
       </c>
       <c r="H474" t="n">
-        <v>393.75</v>
+        <v>381</v>
       </c>
     </row>
     <row r="475">
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="476">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>13.14</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="477">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="478">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>26.92</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>8.49</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.14</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="481">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>13.51</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="482">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.05</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>82.55</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="484">
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="485">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="486">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>98.5</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="487">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>17.52</v>
+        <v>17.63</v>
       </c>
     </row>
     <row r="488">
@@ -16588,7 +16588,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="490">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>29.22</v>
+        <v>29.12</v>
       </c>
     </row>
     <row r="491">
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="H491" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="492">
@@ -16687,7 +16687,7 @@
         </is>
       </c>
       <c r="H492" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="493">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>33.94</v>
+        <v>33.88</v>
       </c>
     </row>
     <row r="494">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="495">
@@ -16786,7 +16786,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="496">
@@ -16852,7 +16852,7 @@
         </is>
       </c>
       <c r="H497" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="498">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="499">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>39.46</v>
+        <v>40.26</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="503">
@@ -17050,7 +17050,7 @@
         </is>
       </c>
       <c r="H503" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="504">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="H504" t="n">
-        <v>8.91</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="505">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>8.48</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="506">
@@ -17149,7 +17149,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="507">
@@ -17182,7 +17182,7 @@
         </is>
       </c>
       <c r="H507" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="508">
@@ -17248,7 +17248,7 @@
         </is>
       </c>
       <c r="H509" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="510">
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="512">
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="H512" t="n">
-        <v>33.62</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="513">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>6.63</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="515">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>9.02</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="516">
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="H516" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="517">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>16.15</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>14.68</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>216.8</v>
+        <v>218.9</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>149.2</v>
+        <v>150.2</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>12.53</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>71.25</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="523">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="524">
@@ -17743,7 +17743,7 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="525">
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>7.53</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="526">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>13.8</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="527">
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="H528" t="n">
-        <v>17.37</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="529">
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="H529" t="n">
-        <v>13.7</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="530">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="532">
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>5.18</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="533">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.28</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="534">
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="H534" t="n">
-        <v>4.34</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="535">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="536">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>22.7</v>
+        <v>22.78</v>
       </c>
     </row>
     <row r="537">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.6</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="538">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="539">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>61.75</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="540">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="H540" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="541">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="542">
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="H542" t="n">
-        <v>4.45</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="543">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>15.07</v>
+        <v>15.01</v>
       </c>
     </row>
     <row r="544">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="H544" t="n">
-        <v>8.85</v>
+        <v>9</v>
       </c>
     </row>
     <row r="545">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>33.46</v>
+        <v>33.48</v>
       </c>
     </row>
     <row r="546">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>27.66</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>52.4</v>
+        <v>53</v>
       </c>
     </row>
     <row r="549">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="H549" t="n">
-        <v>10.2</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="550">
@@ -18601,7 +18601,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>11</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="551">
@@ -18634,7 +18634,7 @@
         </is>
       </c>
       <c r="H551" t="n">
-        <v>42.44</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="552">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="H554" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="555">
@@ -18766,7 +18766,7 @@
         </is>
       </c>
       <c r="H555" t="n">
-        <v>56.8</v>
+        <v>56</v>
       </c>
     </row>
     <row r="556">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="H558" t="n">
-        <v>118</v>
+        <v>119.4</v>
       </c>
     </row>
     <row r="559">
@@ -18898,7 +18898,7 @@
         </is>
       </c>
       <c r="H559" t="n">
-        <v>63.9</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="560">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>28.26</v>
+        <v>27.94</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="562">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="H562" t="n">
-        <v>23.66</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="563">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="H563" t="n">
-        <v>26.4</v>
+        <v>26.74</v>
       </c>
     </row>
     <row r="564">
@@ -19063,7 +19063,7 @@
         </is>
       </c>
       <c r="H564" t="n">
-        <v>12.29</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="565">
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="H565" t="n">
-        <v>7.98</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="566">
@@ -19129,7 +19129,7 @@
         </is>
       </c>
       <c r="H566" t="n">
-        <v>57.85</v>
+        <v>57</v>
       </c>
     </row>
     <row r="567">
@@ -19162,7 +19162,7 @@
         </is>
       </c>
       <c r="H567" t="n">
-        <v>84</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="568">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="569">
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>8.49</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="572">
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>4.73</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="573">
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="H573" t="n">
-        <v>18.5</v>
+        <v>18.79</v>
       </c>
     </row>
     <row r="574">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="575">
@@ -19558,7 +19558,7 @@
         </is>
       </c>
       <c r="H579" t="n">
-        <v>12.29</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="580">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.4</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="581">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.56</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="582">
@@ -19690,7 +19690,7 @@
         </is>
       </c>
       <c r="H583" t="n">
-        <v>6.15</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="584">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="H584" t="n">
-        <v>80.3</v>
+        <v>82</v>
       </c>
     </row>
     <row r="585">
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="H585" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="586">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>20.34</v>
+        <v>37.86</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>3.76</v>
+        <v>182</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>38.04</v>
+        <v>161.1</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>73.52</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>17.13</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>18.26</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>161.3</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>128.5</v>
+        <v>20.64</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>18.19</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>17.6</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>38.68</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>12.54</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>104.2</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>70.40000000000001</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>16.73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>40.7</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>44.98</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>38.32</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>7.94</v>
+        <v>153.7</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>14.22</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>65.3</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>21.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>2.45</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>153.2</v>
+        <v>103.7</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>45.2</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>181.9</v>
+        <v>73.75</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>33.82</v>
+        <v>21.26</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>371.25</v>
+        <v>374.5</v>
       </c>
     </row>
     <row r="3">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>216.6</v>
+        <v>220.1</v>
       </c>
     </row>
     <row r="4">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2612.5</v>
+        <v>2622.5</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>135.9</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>93</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.856891</v>
+        <v>0.8569020000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>187.5</v>
+        <v>195.1</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>380</v>
+        <v>390.25</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>233.8</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>307.75</v>
+        <v>328</v>
       </c>
     </row>
     <row r="11">
@@ -805,7 +805,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISBTR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2915000</v>
+        <v>419915</v>
       </c>
     </row>
     <row r="12">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>14.31</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="13">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1.234359</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISBTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>419915</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>72.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>172.4</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>115</v>
+        <v>114.9</v>
       </c>
     </row>
     <row r="17">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>45.56</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>32.62</v>
+        <v>33.98</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>38.1</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="20">
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20.251426</v>
+        <v>20.428349</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>86.7</v>
+        <v>89.45</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>39.36</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>265.5</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>110.7</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="24">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>82.5</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>64.09999999999999</v>
+        <v>65.84999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>95.95</v>
+        <v>99.84999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1572</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>59.15</v>
+        <v>60.35</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>478.75</v>
+        <v>500</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>217.5</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>93.5</v>
+        <v>95.84999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>295.5</v>
+        <v>306</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>43.34</v>
+        <v>45.54</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>44.76</v>
+        <v>46.26</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>12.89</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="36">
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>105.5</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>655.5</v>
+        <v>669.5</v>
       </c>
     </row>
     <row r="39">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>10885</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>20.4</v>
+        <v>21.04</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>672.5</v>
+        <v>690</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1614</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>21.24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>33.9</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="46">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.716731</v>
+        <v>1.728729</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>275</v>
+        <v>286.25</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>98.34999999999999</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>79.84999999999999</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="50">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>37.1</v>
+        <v>37.52</v>
       </c>
     </row>
     <row r="51">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>108.9</v>
+        <v>110.3</v>
       </c>
     </row>
     <row r="52">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>621.5</v>
+        <v>639.5</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>33.44</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>172</v>
+        <v>180.9</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>442.5</v>
+        <v>452.5</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>9.460000000000001</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>33.28</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="58">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>16.6</v>
+        <v>17.28</v>
       </c>
     </row>
     <row r="59">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>113.9</v>
+        <v>114.6</v>
       </c>
     </row>
     <row r="60">
@@ -2422,16 +2422,16 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
+          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>6.07</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="61">
@@ -2451,20 +2451,20 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.558475</v>
+        <v>1.568751</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>EMLAK KONUT GAYRİMENKUL YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Emlak Konut Gayrimenkul Yatirim Ortakligi A.S. 0 % Certificates 2025-31.12.2199</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>19.91</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="62">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>211.5</v>
+        <v>215.2</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>112.2</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>102.9</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>205.5</v>
+        <v>205.1</v>
       </c>
     </row>
     <row r="66">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1.042486</v>
+        <v>1.05399</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>260</v>
+        <v>263.25</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>32.64</v>
+        <v>33.62</v>
       </c>
     </row>
     <row r="68">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.4</v>
+        <v>32.66</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>12.81</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>179.6</v>
+        <v>182.7</v>
       </c>
     </row>
     <row r="71">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>125.5</v>
+        <v>125.9</v>
       </c>
     </row>
     <row r="73">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1300</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="74">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>40.22</v>
+        <v>42.94</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>27.92</v>
+        <v>28.58</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>79.90000000000001</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1986</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>169</v>
+        <v>173.8</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>36.18</v>
+        <v>37.58</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>33.54</v>
+        <v>34.58</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>217.7</v>
+        <v>223.7</v>
       </c>
     </row>
     <row r="83">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>39.34</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="84">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KRDMB</t>
+          <t>KRDMA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>111.8</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="85">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KRDMA</t>
+          <t>KRDMB</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>41.22</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="86">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3.092177</v>
+        <v>3.092084</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1689</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="87">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.08</v>
+        <v>25.38</v>
       </c>
     </row>
     <row r="88">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.39</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="89">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>5.115027</v>
+        <v>5.172429</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>223.1</v>
+        <v>224.2</v>
       </c>
     </row>
     <row r="90">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1.101892</v>
+        <v>1.1019</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>50.1</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="91">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1.387591</v>
+        <v>1.385348</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1214</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>250.25</v>
+        <v>252.75</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>441.25</v>
+        <v>452.25</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>107</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="95">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>618</v>
+        <v>628.5</v>
       </c>
     </row>
     <row r="96">
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>6.776457</v>
+        <v>6.792446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>100.6</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>134</v>
+        <v>137.4</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>11.12</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="99">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>113.2</v>
+        <v>116.2</v>
       </c>
     </row>
     <row r="100">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>347.75</v>
+        <v>351.75</v>
       </c>
     </row>
     <row r="101">
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>13.804511</v>
+        <v>13.944364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>65.75</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>217.1</v>
+        <v>219.5</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>106.4</v>
+        <v>110.7</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1660</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>200.5</v>
+        <v>203.3</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>85.75</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>36.18</v>
+        <v>37.28</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>146.3</v>
+        <v>156.3</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>21.92</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>105.8</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>348</v>
+        <v>347.5</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>340</v>
+        <v>348.75</v>
       </c>
     </row>
     <row r="113">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>7.82</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="114">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>13.95</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>49.2</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>11.8</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="117">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="118">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>42.04</v>
+        <v>42.76</v>
       </c>
     </row>
     <row r="119">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>3.89</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="120">
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>218.1</v>
+        <v>224.8</v>
       </c>
     </row>
     <row r="121">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>5.84</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>14</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>197.1</v>
+        <v>201</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>13.16</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>16.14</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="126">
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1.077525</v>
+        <v>1.076929</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>26.1</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="127">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>54.1</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="128">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>305</v>
+        <v>315</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>15.3</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>13.45</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="131">
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>49.18</v>
+        <v>50.55</v>
       </c>
     </row>
     <row r="132">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>53.4</v>
+        <v>54</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>232</v>
+        <v>237.9</v>
       </c>
     </row>
     <row r="134">
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>10.66</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="136">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>112.9</v>
+        <v>116.1</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>27.98</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>89.8</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>70.09999999999999</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>13752.5</v>
+        <v>14027.5</v>
       </c>
     </row>
     <row r="141">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>289.5</v>
+        <v>297</v>
       </c>
     </row>
     <row r="142">
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>311.25</v>
+        <v>326.5</v>
       </c>
     </row>
     <row r="143">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>145.5</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="144">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>58.6</v>
+        <v>59.95</v>
       </c>
     </row>
     <row r="145">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>6.29</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>9.630000000000001</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="147">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>46.06</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="148">
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>1.296249</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>57.4</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>86</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="150">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>45.9</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="151">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>17.95</v>
+        <v>18.16</v>
       </c>
     </row>
     <row r="152">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="153">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.119999999999999</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>5.314282</v>
+        <v>5.375927</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>12.01</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>83.55</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="157">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>36.5</v>
+        <v>37.08</v>
       </c>
     </row>
     <row r="158">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>58.4</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>83</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>14.25</v>
+        <v>14.61</v>
       </c>
     </row>
     <row r="161">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>37.58</v>
+        <v>39.26</v>
       </c>
     </row>
     <row r="163">
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>3.361005</v>
+        <v>3.364864</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>6.88</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="164">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>174.7</v>
+        <v>177.9</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>4.83</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>20.26</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>39</v>
+        <v>40.48</v>
       </c>
     </row>
     <row r="168">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>73.09999999999999</v>
+        <v>73.34999999999999</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>147.9</v>
+        <v>148.8</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>5027.5</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>58.25</v>
+        <v>60.95</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>3675</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="173">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>25.22</v>
+        <v>25.48</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>20.64</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5622.5</v>
+        <v>5787.5</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>136.2</v>
+        <v>140.1</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1517</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>14.78</v>
+        <v>15.26</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>11.1</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="180">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>83.15000000000001</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="181">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>16</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="182">
@@ -6444,7 +6444,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>4.455479</v>
+        <v>4.462707</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>94.95</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="183">
@@ -6477,7 +6477,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>4.698963</v>
+        <v>4.725992</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>20.34</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="184">
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>4.737687</v>
+        <v>4.76255</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>32.4</v>
+        <v>32.78</v>
       </c>
     </row>
     <row r="185">
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>5.113011</v>
+        <v>5.144194</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>60.85</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="186">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>22.56</v>
+        <v>22.96</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>151.5</v>
+        <v>153.6</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>606</v>
+        <v>627</v>
       </c>
     </row>
     <row r="189">
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>13.33</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="190">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>28.36</v>
+        <v>28.92</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>39.2</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>28.2</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="193">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="194">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>26.56</v>
+        <v>27.02</v>
       </c>
     </row>
     <row r="196">
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>13.99</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="197">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>247</v>
+        <v>246.4</v>
       </c>
     </row>
     <row r="198">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="199">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>3.64</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.38</v>
+        <v>24</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>30.38</v>
+        <v>31.42</v>
       </c>
     </row>
     <row r="202">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="203">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>145.6</v>
+        <v>144.7</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>19.7</v>
+        <v>20.06</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>85.40000000000001</v>
+        <v>87</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="207">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>4.49</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="208">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>44.3</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>663</v>
+        <v>668</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>65.05</v>
+        <v>66.45</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>112.9</v>
+        <v>116.7</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="213">
@@ -7467,7 +7467,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0</v>
+        <v>5.442006</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>80.2</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="214">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>42.62</v>
+        <v>43.46</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>31.52</v>
+        <v>32.22</v>
       </c>
     </row>
     <row r="216">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>74.75</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="217">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>0</v>
+        <v>8.330444</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>41.5</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>11.4</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="219">
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>0</v>
+        <v>7.262826</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>12.23</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>14.62</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="221">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>40.3</v>
+        <v>41.88</v>
       </c>
     </row>
     <row r="222">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>2800</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="223">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>7.92</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>53.25</v>
+        <v>55.75</v>
       </c>
     </row>
     <row r="225">
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>5.75</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="226">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>16.52</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="227">
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>4.150109</v>
+        <v>4.150114</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="H227" t="n">
-        <v>132.3</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="228">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>8.92</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="229">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>7.1</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="230">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.09</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>17.29</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>526</v>
+        <v>546.5</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>61.65</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="234">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>12.06</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="235">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>40.06</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>107.3</v>
+        <v>110</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>38.44</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="239">
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="H239" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="240">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>41.68</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="241">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="242">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>31.4</v>
+        <v>32.18</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>90.05</v>
+        <v>92.55</v>
       </c>
     </row>
     <row r="245">
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>21.1</v>
+        <v>21.44</v>
       </c>
     </row>
     <row r="246">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.27</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="247">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>6.27</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="248">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="249">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>84.90000000000001</v>
+        <v>86.75</v>
       </c>
     </row>
     <row r="250">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>413.75</v>
+        <v>430.75</v>
       </c>
     </row>
     <row r="251">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>24.06</v>
+        <v>24.78</v>
       </c>
     </row>
     <row r="252">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>257.25</v>
+        <v>262.25</v>
       </c>
     </row>
     <row r="253">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>4.56</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="254">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>35.04</v>
+        <v>35.62</v>
       </c>
     </row>
     <row r="255">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>13.03</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>1133</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="257">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="258">
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>2.002525</v>
+        <v>2.002534</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>26.86</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="259">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>70.8</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="260">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>18.67</v>
+        <v>18.89</v>
       </c>
     </row>
     <row r="261">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>52</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="262">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.06</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>14.01</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>15.41</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="265">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>11.41</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="266">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>122.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>123.9</v>
+        <v>124.1</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>5.98</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="269">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>111.9</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="270">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>17.7</v>
+        <v>17.78</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>8.15</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="272">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>17.44</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="273">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>19.75</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>12.34</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="276">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>39.32</v>
+        <v>40.82</v>
       </c>
     </row>
     <row r="277">
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="H277" t="n">
-        <v>32.48</v>
+        <v>32.88</v>
       </c>
     </row>
     <row r="278">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.25</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>57.55</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="280">
@@ -9711,7 +9711,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>32.424595</v>
+        <v>32.424499</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>7.45</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="282">
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>25.68</v>
+        <v>26.72</v>
       </c>
     </row>
     <row r="283">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>23</v>
+        <v>23.38</v>
       </c>
     </row>
     <row r="284">
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>6.36</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="285">
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>0</v>
+        <v>6.883235</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>24.46</v>
+        <v>25.12</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>7.99</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="287">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>6.15</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="288">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>57</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="289">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>20.56</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>6.07</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>723</v>
+        <v>743.5</v>
       </c>
     </row>
     <row r="292">
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>55.1</v>
+        <v>56.15</v>
       </c>
     </row>
     <row r="293">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>45.2</v>
+        <v>45.92</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>11.57</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="295">
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>18.56</v>
+        <v>19.28</v>
       </c>
     </row>
     <row r="296">
@@ -10206,7 +10206,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>0.844988</v>
+        <v>0.844983</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>7.83</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>86.5</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>997</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>213.2</v>
+        <v>218.2</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>42.08</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="301">
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="H301" t="n">
-        <v>23.64</v>
+        <v>24.28</v>
       </c>
     </row>
     <row r="302">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>18.66</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="303">
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="H303" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="304">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>9.550000000000001</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="305">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="306">
@@ -10549,7 +10549,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>4.95</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="307">
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>3.74</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="308">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="H308" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="309">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>9.890000000000001</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="310">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>7.4</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="311">
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>39.18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="312">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>114.1</v>
+        <v>116</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>14.4</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>8.27</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>242.6</v>
+        <v>245.9</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>432.5</v>
+        <v>434.5</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>5.84</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="320">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>90.55</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="321">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>12.16</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="322">
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="H322" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="323">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>15.06</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="324">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>153.1</v>
+        <v>153.8</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>15.33</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>6.16</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>327</v>
+        <v>333.75</v>
       </c>
     </row>
     <row r="329">
@@ -11295,7 +11295,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>3.233483</v>
+        <v>3.233458</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>6.09</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="330">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>33.26</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="331">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>14.84</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>39.52</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>62.65</v>
+        <v>64.95</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>10.4</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="336">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>16.76</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="337">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.79</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="338">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>22.34</v>
+        <v>22.94</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>13.99</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="340">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="H340" t="n">
-        <v>198.5</v>
+        <v>218.3</v>
       </c>
     </row>
     <row r="341">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>5.35</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>29.1</v>
+        <v>29.96</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>26.5</v>
+        <v>27.04</v>
       </c>
     </row>
     <row r="344">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>17.58</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="345">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>93.7</v>
+        <v>95.05</v>
       </c>
     </row>
     <row r="346">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>34.96</v>
+        <v>36.12</v>
       </c>
     </row>
     <row r="347">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>10.25</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.4</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="349">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="H349" t="n">
-        <v>11.99</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="350">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>12.66</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="351">
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="H351" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
     </row>
     <row r="352">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="H352" t="n">
-        <v>10.54</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="353">
@@ -12100,7 +12100,7 @@
         </is>
       </c>
       <c r="H353" t="n">
-        <v>4.17</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="354">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>5.37</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="355">
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="H355" t="n">
-        <v>261.5</v>
+        <v>267</v>
       </c>
     </row>
     <row r="356">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="358">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="H358" t="n">
-        <v>37.82</v>
+        <v>38.28</v>
       </c>
     </row>
     <row r="359">
@@ -12298,7 +12298,7 @@
         </is>
       </c>
       <c r="H359" t="n">
-        <v>16.18</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="360">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>127</v>
+        <v>126.8</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>19.45</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>8.800000000000001</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="363">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>23.46</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="364">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>12</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="365">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="H365" t="n">
-        <v>147.8</v>
+        <v>148.8</v>
       </c>
     </row>
     <row r="366">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>20.24</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>58</v>
+        <v>59.55</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>14.92</v>
+        <v>15.26</v>
       </c>
     </row>
     <row r="369">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>68.84999999999999</v>
+        <v>69.75</v>
       </c>
     </row>
     <row r="370">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>6.74</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>56.3</v>
+        <v>55.25</v>
       </c>
     </row>
     <row r="372">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>7.24</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="373">
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="H373" t="n">
-        <v>22.72</v>
+        <v>23.54</v>
       </c>
     </row>
     <row r="374">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>15.82</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>297</v>
+        <v>303.5</v>
       </c>
     </row>
     <row r="377">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>63.95</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="378">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>7</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>65.5</v>
+        <v>65.45</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>89.09999999999999</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.17</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>7.18</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>5.68</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="384">
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="H384" t="n">
-        <v>10.67</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="385">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>40</v>
+        <v>40.18</v>
       </c>
     </row>
     <row r="386">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="H386" t="n">
-        <v>19.79</v>
+        <v>20.28</v>
       </c>
     </row>
     <row r="387">
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>34.76</v>
+        <v>35.78</v>
       </c>
     </row>
     <row r="388">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>4.95</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="389">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>106.4</v>
+        <v>109.4</v>
       </c>
     </row>
     <row r="390">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="H390" t="n">
-        <v>4.82</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="391">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>4.01</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="392">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>98.40000000000001</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="393">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>12.85</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="395">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.08</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="396">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>9.19</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="397">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>5.41</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="398">
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="H398" t="n">
-        <v>32.24</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="399">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>3.77</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>48.02</v>
+        <v>49.66</v>
       </c>
     </row>
     <row r="401">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="H401" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="402">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>184.6</v>
+        <v>189.2</v>
       </c>
     </row>
     <row r="403">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>12.12</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="404">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>13.9</v>
+        <v>15.29</v>
       </c>
     </row>
     <row r="405">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="406">
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="407">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>30.38</v>
+        <v>30.68</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>28.04</v>
+        <v>28.56</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>6.71</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="410">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>89.90000000000001</v>
+        <v>92</v>
       </c>
     </row>
     <row r="411">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>42.04</v>
+        <v>43.46</v>
       </c>
     </row>
     <row r="412">
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="H412" t="n">
-        <v>26.22</v>
+        <v>26.86</v>
       </c>
     </row>
     <row r="413">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>20.42</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="414">
@@ -14113,7 +14113,7 @@
         </is>
       </c>
       <c r="H414" t="n">
-        <v>116.1</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="415">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>45.76</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.18</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="417">
@@ -14212,7 +14212,7 @@
         </is>
       </c>
       <c r="H417" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="418">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>8.449999999999999</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>47.08</v>
+        <v>47.82</v>
       </c>
     </row>
     <row r="420">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>297.75</v>
+        <v>297</v>
       </c>
     </row>
     <row r="421">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>15.51</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="422">
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="H422" t="n">
-        <v>4.08</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="423">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>27.68</v>
+        <v>28.86</v>
       </c>
     </row>
     <row r="424">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>21.94</v>
+        <v>22.54</v>
       </c>
     </row>
     <row r="425">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>38.7</v>
+        <v>39.32</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.63</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="427">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.19</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>11.39</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="429">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>8.93</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="430">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>20.82</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="431">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="432">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>7.58</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="433">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.54</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="434">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>9.91</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="435">
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>310.25</v>
+        <v>305</v>
       </c>
     </row>
     <row r="436">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>7.34</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="437">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>29.38</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="438">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>128.8</v>
+        <v>131.9</v>
       </c>
     </row>
     <row r="439">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>103.9</v>
+        <v>106</v>
       </c>
     </row>
     <row r="440">
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="441">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>12.65</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="442">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>6.1</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="443">
@@ -15057,7 +15057,7 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>2.242635</v>
+        <v>2.256101</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="444">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>10.3</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="445">
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="H445" t="n">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="446">
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="447">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>39.3</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>26.86</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>26.86</v>
+        <v>27.46</v>
       </c>
     </row>
     <row r="450">
@@ -15301,7 +15301,7 @@
         </is>
       </c>
       <c r="H450" t="n">
-        <v>1511</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="451">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>13.25</v>
+        <v>13.48</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>19.71</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>5.2</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="454">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>17.26</v>
+        <v>17.83</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>12.81</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="457">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="458">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="H458" t="n">
-        <v>81.8</v>
+        <v>89.95</v>
       </c>
     </row>
     <row r="459">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>173</v>
+        <v>177.2</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>31.88</v>
+        <v>32.94</v>
       </c>
     </row>
     <row r="461">
@@ -15651,7 +15651,7 @@
         </is>
       </c>
       <c r="D461" t="n">
-        <v>1.674045</v>
+        <v>1.674044</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>20.98</v>
+        <v>21.78</v>
       </c>
     </row>
     <row r="462">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="H462" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="463">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>98</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="464">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>36.92</v>
+        <v>36.88</v>
       </c>
     </row>
     <row r="465">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="H465" t="n">
-        <v>10.86</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="466">
@@ -15829,7 +15829,7 @@
         </is>
       </c>
       <c r="H466" t="n">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="467">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>35.74</v>
+        <v>36.32</v>
       </c>
     </row>
     <row r="468">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>24.62</v>
+        <v>25.08</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>42.44</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>8.699999999999999</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="472">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>27.54</v>
+        <v>27.04</v>
       </c>
     </row>
     <row r="473">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="474">
@@ -16093,7 +16093,7 @@
         </is>
       </c>
       <c r="H474" t="n">
-        <v>381</v>
+        <v>394</v>
       </c>
     </row>
     <row r="475">
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>12.58</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="476">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="477">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>10.98</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="478">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>26.88</v>
+        <v>27.34</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>29.12</v>
+        <v>29.38</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.16</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="481">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="482">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.06</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>100.3</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="484">
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>13.43</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="485">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>82.59999999999999</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="486">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="487">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="488">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>13.21</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="489">
@@ -16588,7 +16588,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="490">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>17.63</v>
+        <v>18.19</v>
       </c>
     </row>
     <row r="491">
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="H491" t="n">
-        <v>74</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="492">
@@ -16687,7 +16687,7 @@
         </is>
       </c>
       <c r="H492" t="n">
-        <v>13.75</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="493">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="494">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>33.88</v>
+        <v>34.18</v>
       </c>
     </row>
     <row r="495">
@@ -16786,7 +16786,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>40.26</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="496">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>49.1</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="497">
@@ -16852,7 +16852,7 @@
         </is>
       </c>
       <c r="H497" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="498">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>227</v>
+        <v>249.7</v>
       </c>
     </row>
     <row r="499">
@@ -16918,7 +16918,7 @@
         </is>
       </c>
       <c r="H499" t="n">
-        <v>5.13</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="500">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>10.16</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="501">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>3.54</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.1</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="503">
@@ -17041,16 +17041,16 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>DMSAS</t>
+          <t>SKTAS</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>DEMİSAŞ DÖKÜM EMAYE MAMÜLLERİ SANAYİİ A.Ş.</t>
+          <t>SÖKTAŞ TEKSTİL SANAYİ VE TİCARET A.Ş.</t>
         </is>
       </c>
       <c r="H503" t="n">
-        <v>8.550000000000001</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="504">
@@ -17074,16 +17074,16 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>SKTAS</t>
+          <t>DMSAS</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>SÖKTAŞ TEKSTİL SANAYİ VE TİCARET A.Ş.</t>
+          <t>DEMİSAŞ DÖKÜM EMAYE MAMÜLLERİ SANAYİİ A.Ş.</t>
         </is>
       </c>
       <c r="H504" t="n">
-        <v>3.42</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="505">
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="D505" t="n">
-        <v>1.327064</v>
+        <v>1.341892</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="506">
@@ -17149,7 +17149,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>8.98</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="507">
@@ -17182,7 +17182,7 @@
         </is>
       </c>
       <c r="H507" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="508">
@@ -17215,7 +17215,7 @@
         </is>
       </c>
       <c r="H508" t="n">
-        <v>218.9</v>
+        <v>228.3</v>
       </c>
     </row>
     <row r="509">
@@ -17248,7 +17248,7 @@
         </is>
       </c>
       <c r="H509" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="510">
@@ -17281,7 +17281,7 @@
         </is>
       </c>
       <c r="H510" t="n">
-        <v>14.65</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="511">
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="512">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="H513" t="n">
-        <v>3.24</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="514">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>150.2</v>
+        <v>153.7</v>
       </c>
     </row>
     <row r="515">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>6.64</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="516">
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="H516" t="n">
-        <v>16.28</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="517">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>9.109999999999999</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>33.7</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>4.18</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>70.8</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="523">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>7.54</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="524">
@@ -17743,7 +17743,7 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>12.48</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="525">
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="526">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>17.5</v>
+        <v>17.84</v>
       </c>
     </row>
     <row r="527">
@@ -17842,7 +17842,7 @@
         </is>
       </c>
       <c r="H527" t="n">
-        <v>13.76</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="528">
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="H529" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="530">
@@ -17941,7 +17941,7 @@
         </is>
       </c>
       <c r="H530" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="531">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>5.15</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="532">
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>13.72</v>
+        <v>13.81</v>
       </c>
     </row>
     <row r="533">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.18</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="534">
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="H534" t="n">
-        <v>6.3</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="535">
@@ -18093,7 +18093,7 @@
         </is>
       </c>
       <c r="D535" t="n">
-        <v>2.64268</v>
+        <v>2.644947</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>4.36</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="536">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>22.78</v>
+        <v>23.18</v>
       </c>
     </row>
     <row r="537">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.32</v>
+        <v>25.84</v>
       </c>
     </row>
     <row r="538">
@@ -18205,7 +18205,7 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>9</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="539">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>61.6</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="540">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="H540" t="n">
-        <v>4.49</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="541">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>25.6</v>
+        <v>26.18</v>
       </c>
     </row>
     <row r="542">
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="H542" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="543">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>33.48</v>
+        <v>34.32</v>
       </c>
     </row>
     <row r="544">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>15.01</v>
+        <v>15.28</v>
       </c>
     </row>
     <row r="546">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>10.31</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="547">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>15.96</v>
+        <v>16.17</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>27.7</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="549">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="H549" t="n">
-        <v>159.5</v>
+        <v>162</v>
       </c>
     </row>
     <row r="550">
@@ -18601,7 +18601,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>42.7</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="551">
@@ -18667,7 +18667,7 @@
         </is>
       </c>
       <c r="H552" t="n">
-        <v>53</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="553">
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="H553" t="n">
-        <v>56</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="554">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="H554" t="n">
-        <v>4.62</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="555">
@@ -18766,7 +18766,7 @@
         </is>
       </c>
       <c r="H555" t="n">
-        <v>46.08</v>
+        <v>46.94</v>
       </c>
     </row>
     <row r="556">
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="H556" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="557">
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="H557" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="558">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="H558" t="n">
-        <v>64.8</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="559">
@@ -18898,7 +18898,7 @@
         </is>
       </c>
       <c r="H559" t="n">
-        <v>119.4</v>
+        <v>121.3</v>
       </c>
     </row>
     <row r="560">
@@ -18918,7 +18918,7 @@
         </is>
       </c>
       <c r="D560" t="n">
-        <v>1.341608</v>
+        <v>1.349886</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>27.94</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="562">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="H562" t="n">
-        <v>23.3</v>
+        <v>24.24</v>
       </c>
     </row>
     <row r="563">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="H563" t="n">
-        <v>13.17</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="564">
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="H565" t="n">
-        <v>57</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="566">
@@ -19129,7 +19129,7 @@
         </is>
       </c>
       <c r="H566" t="n">
-        <v>26.74</v>
+        <v>27.04</v>
       </c>
     </row>
     <row r="567">
@@ -19162,7 +19162,7 @@
         </is>
       </c>
       <c r="H567" t="n">
-        <v>4.99</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="568">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>7.97</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="569">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="H569" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="570">
@@ -19261,7 +19261,7 @@
         </is>
       </c>
       <c r="H570" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="571">
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>6.4</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="572">
@@ -19314,7 +19314,7 @@
         </is>
       </c>
       <c r="D572" t="n">
-        <v>0.58184</v>
+        <v>0.584579</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>8.44</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="573">
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="H573" t="n">
-        <v>18.79</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="574">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>26.8</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="575">
@@ -19459,7 +19459,7 @@
         </is>
       </c>
       <c r="H576" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="577">
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="H577" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="578">
@@ -19525,7 +19525,7 @@
         </is>
       </c>
       <c r="H578" t="n">
-        <v>5.9</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="579">
@@ -19558,7 +19558,7 @@
         </is>
       </c>
       <c r="H579" t="n">
-        <v>12.17</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="580">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.390000000000001</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="581">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.54</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="582">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H582" t="n">
-        <v>10.39</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="583">
@@ -19690,7 +19690,7 @@
         </is>
       </c>
       <c r="H583" t="n">
-        <v>82</v>
+        <v>83.84999999999999</v>
       </c>
     </row>
     <row r="584">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="H584" t="n">
-        <v>6.28</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="585">
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="H585" t="n">
-        <v>23</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="586">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>182</v>
+        <v>21.02</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>40</v>
+        <v>18.88</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>13.96</v>
+        <v>44.92</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>128.5</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="590">
@@ -19921,7 +19921,7 @@
         </is>
       </c>
       <c r="H590" t="n">
-        <v>44.98</v>
+        <v>47.64</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>18.05</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>73.75</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>40.1</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>21.26</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>20.64</v>
+        <v>38.68</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>153.7</v>
+        <v>76.34999999999999</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>37.86</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>17.99</v>
+        <v>40.32</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>2.44</v>
+        <v>188.3</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>16.8</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>33.7</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>3.75</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>45.62</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>64</v>
+        <v>17.31</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>161.1</v>
+        <v>141</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>12.6</v>
+        <v>155.5</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>18.25</v>
+        <v>107</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>38.6</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>70.09999999999999</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>17.15</v>
+        <v>18.15</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>103.7</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>7.94</v>
+        <v>166</v>
       </c>
     </row>
     <row r="613">
@@ -20727,7 +20727,7 @@
         </is>
       </c>
       <c r="D616" t="n">
-        <v>0</v>
+        <v>3.694615</v>
       </c>
     </row>
     <row r="617">
@@ -21107,7 +21107,7 @@
         </is>
       </c>
       <c r="D635" t="n">
-        <v>3.764796</v>
+        <v>3.778701</v>
       </c>
     </row>
     <row r="636">
@@ -21287,7 +21287,7 @@
         </is>
       </c>
       <c r="D644" t="n">
-        <v>18.543026</v>
+        <v>18.54404</v>
       </c>
     </row>
     <row r="645">
@@ -21387,7 +21387,7 @@
         </is>
       </c>
       <c r="D649" t="n">
-        <v>4.271822</v>
+        <v>4.281544</v>
       </c>
     </row>
     <row r="650">
@@ -21407,7 +21407,7 @@
         </is>
       </c>
       <c r="D650" t="n">
-        <v>1.1699</v>
+        <v>1.177732</v>
       </c>
     </row>
   </sheetData>

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>374.5</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2622.5</v>
+        <v>2607.5</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>142.5</v>
+        <v>142.1</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>95.90000000000001</v>
+        <v>94.95</v>
       </c>
     </row>
     <row r="7">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>390.25</v>
+        <v>386.75</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>234</v>
+        <v>234.1</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="11">
@@ -805,7 +805,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ISBTR</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>419915</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="12">
@@ -838,7 +838,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>15.03</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISBTR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2915000</v>
+        <v>419915</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>76.40000000000001</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>174.9</v>
+        <v>175.3</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>114.9</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="17">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>47.5</v>
+        <v>47.42</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>33.98</v>
+        <v>34.08</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>40.46</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>89.45</v>
+        <v>89.25</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>40.46</v>
+        <v>40.34</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>114.4</v>
+        <v>113.7</v>
       </c>
     </row>
     <row r="24">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>84.59999999999999</v>
+        <v>83.45</v>
       </c>
     </row>
     <row r="25">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>65.84999999999999</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1559</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>60.35</v>
+        <v>60.15</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>220</v>
+        <v>220.9</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>95.84999999999999</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="32">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>306</v>
+        <v>306.75</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>45.54</v>
+        <v>45.56</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>46.26</v>
+        <v>46.16</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="36">
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>108</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="37">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>669.5</v>
+        <v>666</v>
       </c>
     </row>
     <row r="39">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>11600</v>
+        <v>11612.5</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>21.04</v>
+        <v>20.94</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>690</v>
+        <v>685.5</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1661</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>22</v>
+        <v>22.08</v>
       </c>
     </row>
     <row r="45">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>32.26</v>
+        <v>34.02</v>
       </c>
     </row>
     <row r="46">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>286.25</v>
+        <v>287</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>100.4</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>81.09999999999999</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="49">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>110.3</v>
+        <v>109.4</v>
       </c>
     </row>
     <row r="52">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>639.5</v>
+        <v>636</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>33.7</v>
+        <v>33.92</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>180.9</v>
+        <v>180.7</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>452.5</v>
+        <v>450.25</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>10.05</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>34.24</v>
+        <v>34.16</v>
       </c>
     </row>
     <row r="58">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>17.28</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="59">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>114.6</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>20.7</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="61">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>215.2</v>
+        <v>213.1</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>110.4</v>
+        <v>112.3</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>106.4</v>
+        <v>105.7</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>205.1</v>
+        <v>204.3</v>
       </c>
     </row>
     <row r="66">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>263.25</v>
+        <v>261</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>33.62</v>
+        <v>33.72</v>
       </c>
     </row>
     <row r="68">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.66</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>12.88</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>182.7</v>
+        <v>182.3</v>
       </c>
     </row>
     <row r="71">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>95.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>125.9</v>
+        <v>125.7</v>
       </c>
     </row>
     <row r="73">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1308</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="74">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>42.94</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>28.58</v>
+        <v>28.56</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>82.7</v>
+        <v>83.55</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>2030</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>173.8</v>
+        <v>174.2</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>37.58</v>
+        <v>37.48</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>34.58</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>141</v>
+        <v>141.5</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>223.7</v>
+        <v>224.7</v>
       </c>
     </row>
     <row r="83">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KRDMA</t>
+          <t>KRDMB</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>41.3</v>
+        <v>112.3</v>
       </c>
     </row>
     <row r="85">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KRDMB</t>
+          <t>KRDMA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>111.8</v>
+        <v>41.42</v>
       </c>
     </row>
     <row r="86">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1686</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="87">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.38</v>
+        <v>25.62</v>
       </c>
     </row>
     <row r="88">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.62</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="89">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>224.2</v>
+        <v>224.9</v>
       </c>
     </row>
     <row r="90">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>51.8</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1193</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>252.75</v>
+        <v>253</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>452.25</v>
+        <v>450.75</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>109.8</v>
+        <v>109</v>
       </c>
     </row>
     <row r="95">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>628.5</v>
+        <v>627.5</v>
       </c>
     </row>
     <row r="96">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>103.5</v>
+        <v>103.6</v>
       </c>
     </row>
     <row r="97">
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1.198726</v>
+        <v>1.2158</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>137.4</v>
+        <v>138.4</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>11.39</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="99">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>116.2</v>
+        <v>116.5</v>
       </c>
     </row>
     <row r="100">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>351.75</v>
+        <v>354</v>
       </c>
     </row>
     <row r="101">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>66.90000000000001</v>
+        <v>66.25</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>219.5</v>
+        <v>217.9</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>110.7</v>
+        <v>111.3</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1737</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>203.3</v>
+        <v>203.9</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>84.59999999999999</v>
+        <v>84.95</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>37.28</v>
+        <v>37.48</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>156.3</v>
+        <v>155</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>22.46</v>
+        <v>22.42</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>108.7</v>
+        <v>108</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>347.5</v>
+        <v>351.5</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>348.75</v>
+        <v>350</v>
       </c>
     </row>
     <row r="113">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>14.4</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>50.25</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>12.25</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="117">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="118">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>42.76</v>
+        <v>42.74</v>
       </c>
     </row>
     <row r="119">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="120">
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>224.8</v>
+        <v>225</v>
       </c>
     </row>
     <row r="121">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>6.06</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>14.21</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>201</v>
+        <v>200.1</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>13.42</v>
+        <v>13.48</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>16.42</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>26.24</v>
+        <v>26.34</v>
       </c>
     </row>
     <row r="127">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>315</v>
+        <v>315.75</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>15.38</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>13.56</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="131">
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>50.55</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="132">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>54</v>
+        <v>53.95</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>237.9</v>
+        <v>236.1</v>
       </c>
     </row>
     <row r="134">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>7.241233</v>
+        <v>7.330489</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>10.55</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="136">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>116.1</v>
+        <v>116.7</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>29.7</v>
+        <v>29.32</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>93.09999999999999</v>
+        <v>93.25</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>71.3</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>14027.5</v>
+        <v>14100</v>
       </c>
     </row>
     <row r="141">
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>326.5</v>
+        <v>327.25</v>
       </c>
     </row>
     <row r="143">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>144.5</v>
+        <v>144</v>
       </c>
     </row>
     <row r="144">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>59.95</v>
+        <v>59.75</v>
       </c>
     </row>
     <row r="145">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>9.84</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="147">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>47.8</v>
+        <v>48.08</v>
       </c>
     </row>
     <row r="148">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>58.65</v>
+        <v>58.45</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>87.09999999999999</v>
+        <v>86.75</v>
       </c>
     </row>
     <row r="150">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>47.08</v>
+        <v>46.86</v>
       </c>
     </row>
     <row r="151">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>18.16</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="152">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="153">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.279999999999999</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>12.22</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>9</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>87.09999999999999</v>
+        <v>87.05</v>
       </c>
     </row>
     <row r="157">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>37.08</v>
+        <v>37.02</v>
       </c>
     </row>
     <row r="158">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>58.6</v>
+        <v>58.45</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>83.8</v>
+        <v>83.84999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>39.26</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="163">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>7.13</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="164">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>177.9</v>
+        <v>179.2</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>4.94</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>20.6</v>
+        <v>20.82</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>40.48</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="168">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>73.34999999999999</v>
+        <v>73.95</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>148.8</v>
+        <v>149.5</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>5170</v>
+        <v>5117.5</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>60.95</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>3800</v>
+        <v>3787.5</v>
       </c>
     </row>
     <row r="173">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>25.48</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>21.14</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5787.5</v>
+        <v>5775</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>140.1</v>
+        <v>140.6</v>
       </c>
     </row>
     <row r="177">
@@ -6279,7 +6279,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>7.799288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>15.26</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>11.26</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="180">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>83.2</v>
+        <v>81.84999999999999</v>
       </c>
     </row>
     <row r="181">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>20.86</v>
+        <v>20.84</v>
       </c>
     </row>
     <row r="184">
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>32.78</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="185">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>62.1</v>
+        <v>62.05</v>
       </c>
     </row>
     <row r="186">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>22.96</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>153.6</v>
+        <v>151.8</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="189">
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>13.65</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="190">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>39.76</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="192">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="194">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>27.02</v>
+        <v>27</v>
       </c>
     </row>
     <row r="196">
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>14.01</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="197">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>246.4</v>
+        <v>245.2</v>
       </c>
     </row>
     <row r="198">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>3.76</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>24</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>31.42</v>
+        <v>31.54</v>
       </c>
     </row>
     <row r="202">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>19.6</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="203">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>144.7</v>
+        <v>145</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>20.06</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>87</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>8.75</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="207">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="208">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>44.9</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>668</v>
+        <v>650</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>66.45</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>116.7</v>
+        <v>116.2</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="213">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>81.5</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="214">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>43.46</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>32.22</v>
+        <v>32.36</v>
       </c>
     </row>
     <row r="216">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>77.5</v>
+        <v>76.34999999999999</v>
       </c>
     </row>
     <row r="217">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>40.72</v>
+        <v>40.76</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>11.62</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>12.25</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>14.99</v>
+        <v>15</v>
       </c>
     </row>
     <row r="221">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>41.88</v>
+        <v>41.78</v>
       </c>
     </row>
     <row r="222">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>8.119999999999999</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>55.75</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="225">
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>5.88</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="226">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>16.78</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="227">
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="H227" t="n">
-        <v>135.6</v>
+        <v>134.7</v>
       </c>
     </row>
     <row r="228">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>9.1</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="229">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>7.27</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="230">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.27</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>18.42</v>
+        <v>18.19</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>546.5</v>
+        <v>547.5</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>62.2</v>
+        <v>62.05</v>
       </c>
     </row>
     <row r="234">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>12.41</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="235">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>110</v>
+        <v>111.1</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>38.5</v>
+        <v>38.78</v>
       </c>
     </row>
     <row r="239">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>42.9</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="241">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>32.18</v>
+        <v>32.76</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>92.55</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="245">
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>21.44</v>
+        <v>21.76</v>
       </c>
     </row>
     <row r="246">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.46</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="247">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>6.44</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="248">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="249">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>86.75</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="250">
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1.008109</v>
+        <v>1.009835</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>430.75</v>
+        <v>429.5</v>
       </c>
     </row>
     <row r="251">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>24.78</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="252">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>262.25</v>
+        <v>262.75</v>
       </c>
     </row>
     <row r="253">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="254">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>35.62</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="255">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>13.6</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>1170</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="257">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="258">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>27.2</v>
+        <v>27.14</v>
       </c>
     </row>
     <row r="259">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>72.2</v>
+        <v>72.45</v>
       </c>
     </row>
     <row r="260">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>18.89</v>
+        <v>19.08</v>
       </c>
     </row>
     <row r="261">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>53.5</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="262">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.32</v>
+        <v>28.14</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>14.15</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>15.71</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="265">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>11.53</v>
+        <v>11.72</v>
       </c>
     </row>
     <row r="266">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>126.4</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>124.1</v>
+        <v>126.3</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>6.1</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="269">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>119.1</v>
+        <v>115.4</v>
       </c>
     </row>
     <row r="270">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>17.78</v>
+        <v>17.71</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>8.449999999999999</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="272">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>17.58</v>
+        <v>17.62</v>
       </c>
     </row>
     <row r="273">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>19.71</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>12.56</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="275">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>40.82</v>
+        <v>40.36</v>
       </c>
     </row>
     <row r="277">
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="H277" t="n">
-        <v>32.88</v>
+        <v>33.04</v>
       </c>
     </row>
     <row r="278">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.49</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="280">
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>7.61</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="282">
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>26.72</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="283">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>23.38</v>
+        <v>23.76</v>
       </c>
     </row>
     <row r="284">
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>6.44</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="285">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>25.12</v>
+        <v>25.04</v>
       </c>
     </row>
     <row r="286">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>6.28</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="288">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>58.75</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="289">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>21.08</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>6.16</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>743.5</v>
+        <v>738.5</v>
       </c>
     </row>
     <row r="292">
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>56.15</v>
+        <v>56.05</v>
       </c>
     </row>
     <row r="293">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>45.92</v>
+        <v>46.08</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>11.83</v>
+        <v>11.85</v>
       </c>
     </row>
     <row r="295">
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>19.28</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="296">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>7.84</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>88.40000000000001</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>218.2</v>
+        <v>218.5</v>
       </c>
     </row>
     <row r="300">
@@ -10338,7 +10338,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>0</v>
+        <v>6.770317</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="H301" t="n">
-        <v>24.28</v>
+        <v>24.18</v>
       </c>
     </row>
     <row r="302">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>18.97</v>
+        <v>19</v>
       </c>
     </row>
     <row r="303">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="305">
@@ -10549,7 +10549,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="307">
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="308">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="H308" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="309">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>10.15</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="310">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>7.64</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="311">
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>40</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="312">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="313">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>116</v>
+        <v>116.5</v>
       </c>
     </row>
     <row r="314">
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>1.648886</v>
+        <v>1.655107</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>14.78</v>
+        <v>14.61</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>264</v>
+        <v>263.25</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>8.359999999999999</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>245.9</v>
+        <v>241.8</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>434.5</v>
+        <v>432.5</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>6.01</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="320">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>92.5</v>
+        <v>92.45</v>
       </c>
     </row>
     <row r="321">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>12.35</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="322">
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="H322" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="323">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>15.44</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="324">
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1.394958</v>
+        <v>1.43863</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>153.8</v>
+        <v>158.5</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>15.31</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>6.3</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>333.75</v>
+        <v>333.5</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>6.12</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="330">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>33.38</v>
+        <v>33.28</v>
       </c>
     </row>
     <row r="331">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>14.7</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>64.95</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="336">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>17.49</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="337">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.92</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="338">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>22.94</v>
+        <v>22.96</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>14.25</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="340">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>5.51</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>29.96</v>
+        <v>30.14</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>27.04</v>
+        <v>26.98</v>
       </c>
     </row>
     <row r="344">
@@ -11790,7 +11790,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>4.715346</v>
+        <v>4.834395</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>17.95</v>
+        <v>17.97</v>
       </c>
     </row>
     <row r="345">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>95.05</v>
+        <v>94.55</v>
       </c>
     </row>
     <row r="346">
@@ -11889,7 +11889,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>2.390374</v>
+        <v>2.501208</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>10.49</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.56</v>
+        <v>25.48</v>
       </c>
     </row>
     <row r="349">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="H349" t="n">
-        <v>12.19</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="350">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>12.99</v>
+        <v>12.96</v>
       </c>
     </row>
     <row r="351">
@@ -12021,7 +12021,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>1.087236</v>
+        <v>1.103997</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="H351" t="n">
-        <v>7</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="352">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="H352" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="353">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>5.48</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="355">
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="H355" t="n">
-        <v>267</v>
+        <v>267.75</v>
       </c>
     </row>
     <row r="356">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="357">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="H358" t="n">
-        <v>38.28</v>
+        <v>38.06</v>
       </c>
     </row>
     <row r="359">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>126.8</v>
+        <v>127</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>19.8</v>
+        <v>19.94</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>8.859999999999999</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="363">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="364">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>12.13</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="365">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="H365" t="n">
-        <v>148.8</v>
+        <v>148.5</v>
       </c>
     </row>
     <row r="366">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>20.74</v>
+        <v>21.04</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>59.55</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="368">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>69.75</v>
+        <v>72.55</v>
       </c>
     </row>
     <row r="370">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>6.83</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>55.25</v>
+        <v>54.65</v>
       </c>
     </row>
     <row r="372">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>7.28</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="373">
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="H373" t="n">
-        <v>23.54</v>
+        <v>23.58</v>
       </c>
     </row>
     <row r="374">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>16.02</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>303.5</v>
+        <v>304.5</v>
       </c>
     </row>
     <row r="377">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>66.2</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="378">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>7.09</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>65.45</v>
+        <v>65.55</v>
       </c>
     </row>
     <row r="380">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>95.7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="381">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.52</v>
+        <v>17.48</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>7.37</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>5.73</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="384">
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="H384" t="n">
-        <v>10.12</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="385">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>40.18</v>
+        <v>40.22</v>
       </c>
     </row>
     <row r="386">
@@ -13209,7 +13209,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>0</v>
+        <v>1.404909</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>35.78</v>
+        <v>35.36</v>
       </c>
     </row>
     <row r="388">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>5.01</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="389">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>109.4</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="390">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="H390" t="n">
-        <v>4.92</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="391">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>4.06</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="392">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>99.8</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="393">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>13.12</v>
+        <v>13.18</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="395">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.51</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="396">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>9.460000000000001</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="397">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>5.5</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="398">
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="H398" t="n">
-        <v>34.38</v>
+        <v>34.46</v>
       </c>
     </row>
     <row r="399">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>49.66</v>
+        <v>48.06</v>
       </c>
     </row>
     <row r="401">
@@ -13671,7 +13671,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>5.190158</v>
+        <v>5.190149</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="H401" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="402">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>189.2</v>
+        <v>188.8</v>
       </c>
     </row>
     <row r="403">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>12.42</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="404">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>152</v>
+        <v>152.6</v>
       </c>
     </row>
     <row r="406">
@@ -13836,7 +13836,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>4.493846</v>
+        <v>4.493833</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="407">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>30.68</v>
+        <v>30.52</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>28.56</v>
+        <v>28.62</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>6.79</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="410">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>92</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="411">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>43.46</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="412">
@@ -14034,7 +14034,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>3.863565</v>
+        <v>3.863559</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>7.785777</v>
+        <v>7.786052</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         </is>
       </c>
       <c r="H414" t="n">
-        <v>117.3</v>
+        <v>117.9</v>
       </c>
     </row>
     <row r="415">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>47.14</v>
+        <v>47.18</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.4</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="417">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>8.69</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>47.82</v>
+        <v>47.96</v>
       </c>
     </row>
     <row r="420">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="422">
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="H422" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="423">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>28.86</v>
+        <v>29.32</v>
       </c>
     </row>
     <row r="424">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>22.54</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="425">
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>39.32</v>
+        <v>39.44</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.83</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="427">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.53</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>11.63</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="429">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>8.92</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="430">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>21.24</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="431">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="432">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>7.87</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="433">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.97</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="434">
@@ -14760,7 +14760,7 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>6.812427</v>
+        <v>6.831062</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>10.22</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="435">
@@ -14826,7 +14826,7 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>3.128966</v>
+        <v>3.128336</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>7.52</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="437">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>29.92</v>
+        <v>29.72</v>
       </c>
     </row>
     <row r="438">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>131.9</v>
+        <v>139.8</v>
       </c>
     </row>
     <row r="439">
@@ -14925,7 +14925,7 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>2.097327</v>
+        <v>2.122675</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>106</v>
+        <v>105.1</v>
       </c>
     </row>
     <row r="440">
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="441">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>12.98</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="442">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>6.23</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="443">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="444">
@@ -15090,7 +15090,7 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>2.809969</v>
+        <v>2.823908</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>10.65</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="445">
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="447">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>40.2</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>27.7</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>27.46</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="450">
@@ -15301,7 +15301,7 @@
         </is>
       </c>
       <c r="H450" t="n">
-        <v>1556</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="451">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>13.48</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>20.1</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>5.35</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="454">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>17.83</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>13.1</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="457">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>177.2</v>
+        <v>177.3</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>32.94</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="461">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>21.78</v>
+        <v>23.06</v>
       </c>
     </row>
     <row r="462">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="H462" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="463">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>36.88</v>
+        <v>37.16</v>
       </c>
     </row>
     <row r="465">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="H465" t="n">
-        <v>11.1</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="466">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>36.32</v>
+        <v>36.48</v>
       </c>
     </row>
     <row r="468">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>25.08</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>41.94</v>
+        <v>42.76</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>8.789999999999999</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="472">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>27.04</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="473">
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>12.93</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="476">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="477">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>11.23</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="478">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>27.34</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>29.38</v>
+        <v>29.34</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.46</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="481">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="482">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.34</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>102.9</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="484">
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>13.62</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="485">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>87.2</v>
+        <v>86.55</v>
       </c>
     </row>
     <row r="486">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="488">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>13.39</v>
+        <v>13.55</v>
       </c>
     </row>
     <row r="489">
@@ -16588,7 +16588,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="490">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>18.19</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="491">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>34.18</v>
+        <v>34.22</v>
       </c>
     </row>
     <row r="495">
@@ -16786,7 +16786,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>41.46</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="496">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="497">
@@ -16852,7 +16852,7 @@
         </is>
       </c>
       <c r="H497" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="498">
@@ -16918,7 +16918,7 @@
         </is>
       </c>
       <c r="H499" t="n">
-        <v>5.47</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="500">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>10.4</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="501">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.68</v>
+        <v>24.74</v>
       </c>
     </row>
     <row r="503">
@@ -17041,16 +17041,16 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>SKTAS</t>
+          <t>DMSAS</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>SÖKTAŞ TEKSTİL SANAYİ VE TİCARET A.Ş.</t>
+          <t>DEMİSAŞ DÖKÜM EMAYE MAMÜLLERİ SANAYİİ A.Ş.</t>
         </is>
       </c>
       <c r="H503" t="n">
-        <v>3.47</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="504">
@@ -17074,16 +17074,16 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>DMSAS</t>
+          <t>SKTAS</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>DEMİSAŞ DÖKÜM EMAYE MAMÜLLERİ SANAYİİ A.Ş.</t>
+          <t>SÖKTAŞ TEKSTİL SANAYİ VE TİCARET A.Ş.</t>
         </is>
       </c>
       <c r="H504" t="n">
-        <v>8.68</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="505">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="506">
@@ -17182,7 +17182,7 @@
         </is>
       </c>
       <c r="H507" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="508">
@@ -17215,7 +17215,7 @@
         </is>
       </c>
       <c r="H508" t="n">
-        <v>228.3</v>
+        <v>226.4</v>
       </c>
     </row>
     <row r="509">
@@ -17281,7 +17281,7 @@
         </is>
       </c>
       <c r="H510" t="n">
-        <v>14.86</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="511">
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="512">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>153.7</v>
+        <v>154.3</v>
       </c>
     </row>
     <row r="515">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="516">
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="H516" t="n">
-        <v>16.78</v>
+        <v>16.76</v>
       </c>
     </row>
     <row r="517">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>9.279999999999999</v>
+        <v>9.220000000000001</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>35.1</v>
+        <v>35.08</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>71.5</v>
+        <v>72.25</v>
       </c>
     </row>
     <row r="523">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>7.72</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="524">
@@ -17743,7 +17743,7 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>12.47</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="525">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>17.84</v>
+        <v>17.92</v>
       </c>
     </row>
     <row r="527">
@@ -17842,7 +17842,7 @@
         </is>
       </c>
       <c r="H527" t="n">
-        <v>14.15</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="528">
@@ -17941,7 +17941,7 @@
         </is>
       </c>
       <c r="H530" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="531">
@@ -17961,7 +17961,7 @@
         </is>
       </c>
       <c r="D531" t="n">
-        <v>0</v>
+        <v>4.239865</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>13.81</v>
+        <v>13.63</v>
       </c>
     </row>
     <row r="533">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.41</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="534">
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="H534" t="n">
-        <v>6.31</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="535">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="536">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>23.18</v>
+        <v>22.98</v>
       </c>
     </row>
     <row r="537">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.84</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="538">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>63.1</v>
+        <v>63.05</v>
       </c>
     </row>
     <row r="540">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="H540" t="n">
-        <v>4.59</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="541">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>34.32</v>
+        <v>34.06</v>
       </c>
     </row>
     <row r="544">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="H544" t="n">
-        <v>154</v>
+        <v>155.9</v>
       </c>
     </row>
     <row r="545">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>15.28</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="546">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>10.49</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="547">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>16.17</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>28.1</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="549">
@@ -18588,7 +18588,7 @@
         </is>
       </c>
       <c r="D550" t="n">
-        <v>0</v>
+        <v>5.246168</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>43.88</v>
+        <v>44.12</v>
       </c>
     </row>
     <row r="551">
@@ -18621,7 +18621,7 @@
         </is>
       </c>
       <c r="D551" t="n">
-        <v>0</v>
+        <v>6.174458</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         </is>
       </c>
       <c r="H552" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="553">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="H554" t="n">
-        <v>4.76</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="555">
@@ -18766,7 +18766,7 @@
         </is>
       </c>
       <c r="H555" t="n">
-        <v>46.94</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="556">
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="H556" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="557">
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="H557" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="558">
@@ -18898,7 +18898,7 @@
         </is>
       </c>
       <c r="H559" t="n">
-        <v>121.3</v>
+        <v>121.2</v>
       </c>
     </row>
     <row r="560">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>28.28</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="562">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="H562" t="n">
-        <v>24.24</v>
+        <v>24</v>
       </c>
     </row>
     <row r="563">
@@ -19083,7 +19083,7 @@
         </is>
       </c>
       <c r="D565" t="n">
-        <v>0</v>
+        <v>12.553125</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         </is>
       </c>
       <c r="H567" t="n">
-        <v>4.81</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="568">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>8.119999999999999</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="569">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="H569" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="570">
@@ -19261,7 +19261,7 @@
         </is>
       </c>
       <c r="H570" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="571">
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>8.51</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="573">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>27.16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="575">
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="H577" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="578">
@@ -19558,7 +19558,7 @@
         </is>
       </c>
       <c r="H579" t="n">
-        <v>12.34</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="580">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.550000000000001</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="581">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.68</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="582">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H582" t="n">
-        <v>10.57</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="583">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="H584" t="n">
-        <v>6.22</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="585">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>21.02</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>18.88</v>
+        <v>141.3</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>44.92</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="589">
@@ -19888,7 +19888,7 @@
         </is>
       </c>
       <c r="H589" t="n">
-        <v>18.67</v>
+        <v>18.88</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>47.64</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>2.48</v>
+        <v>18.01</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>72.5</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>3.87</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>17.49</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>38.68</v>
+        <v>12.89</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>76.34999999999999</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>12.82</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>40.32</v>
+        <v>76.38</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>188.3</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>39.8</v>
+        <v>155.9</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>39.1</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="602">
@@ -20304,20 +20304,20 @@
         </is>
       </c>
       <c r="D602" t="n">
-        <v>0</v>
+        <v>3.842808</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>14.4</v>
+        <v>33.92</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>33.9</v>
+        <v>45.16</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>17.31</v>
+        <v>21.38</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>141</v>
+        <v>38.64</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>155.5</v>
+        <v>17.51</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>107</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>21.2</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>64.8</v>
+        <v>165.5</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>18.15</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>8.1</v>
+        <v>188.9</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>166</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>379</v>
+        <v>372.5</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2607.5</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>142.1</v>
+        <v>140.8</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>94.95</v>
+        <v>94.45</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>195.1</v>
+        <v>193.9</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>386.75</v>
+        <v>385.75</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>234.1</v>
+        <v>233.2</v>
       </c>
     </row>
     <row r="10">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.169641</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>327</v>
+        <v>327.75</v>
       </c>
     </row>
     <row r="11">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>15.03</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="12">
@@ -838,7 +838,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISBTR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2915000</v>
+        <v>419915</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISBTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>419915</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>76.7</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>175.3</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>114.3</v>
+        <v>114.8</v>
       </c>
     </row>
     <row r="17">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>47.42</v>
+        <v>47.06</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>34.08</v>
+        <v>33.66</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>40.5</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>89.25</v>
+        <v>88.95</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>40.34</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>113.7</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="24">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>83.45</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>65.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>99.84999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1562</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="28">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>60.15</v>
+        <v>59.55</v>
       </c>
     </row>
     <row r="29">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>6.715756</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>498</v>
+        <v>495.5</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>220.9</v>
+        <v>221.7</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>95.8</v>
+        <v>95.15000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>15.389279</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>17.930897</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>45.56</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>46.16</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6.57</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="36">
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>107.5</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="37">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>666</v>
+        <v>676</v>
       </c>
     </row>
     <row r="39">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>11612.5</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>20.94</v>
+        <v>20.96</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>685.5</v>
+        <v>680.5</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1684</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>22.08</v>
+        <v>22.18</v>
       </c>
     </row>
     <row r="45">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>34.02</v>
+        <v>34.16</v>
       </c>
     </row>
     <row r="46">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>287</v>
+        <v>286.5</v>
       </c>
     </row>
     <row r="47">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>80.8</v>
+        <v>80.65000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>109.4</v>
+        <v>109.3</v>
       </c>
     </row>
     <row r="52">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>636</v>
+        <v>628.5</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>33.92</v>
+        <v>34.04</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>180.7</v>
+        <v>180.6</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>450.25</v>
+        <v>449</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>10.21</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>34.16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>17.24</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="59">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>20.86</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="61">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>213.1</v>
+        <v>211.8</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>112.3</v>
+        <v>111.9</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>105.7</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>204.3</v>
+        <v>203.6</v>
       </c>
     </row>
     <row r="66">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>261</v>
+        <v>259.75</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>33.72</v>
+        <v>33.78</v>
       </c>
     </row>
     <row r="68">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.68</v>
+        <v>32.72</v>
       </c>
     </row>
     <row r="69">
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1.280674</v>
+        <v>1.280858</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>12.97</v>
+        <v>12.89</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>182.3</v>
+        <v>183</v>
       </c>
     </row>
     <row r="71">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3.45984</v>
+        <v>3.453432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>95.59999999999999</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>125.7</v>
+        <v>126</v>
       </c>
     </row>
     <row r="73">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1368</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="74">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>42.9</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>28.56</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="76">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>83.55</v>
+        <v>83.34999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>2024</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>174.2</v>
+        <v>173.3</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>37.48</v>
+        <v>37.36</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>34.62</v>
+        <v>34.46</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>141.5</v>
+        <v>139.6</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>224.7</v>
+        <v>224.3</v>
       </c>
     </row>
     <row r="83">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>40.4</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="84">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>112.3</v>
+        <v>112.1</v>
       </c>
     </row>
     <row r="85">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>41.42</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="86">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1695</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="87">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.62</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="88">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.53</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="89">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>224.9</v>
+        <v>224</v>
       </c>
     </row>
     <row r="90">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>51.65</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1199</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>253</v>
+        <v>252.75</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>450.75</v>
+        <v>450.5</v>
       </c>
     </row>
     <row r="94">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>109</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="95">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>627.5</v>
+        <v>630</v>
       </c>
     </row>
     <row r="96">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>103.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>138.4</v>
+        <v>138.9</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>11.5</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="99">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>116.5</v>
+        <v>116.2</v>
       </c>
     </row>
     <row r="100">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>354</v>
+        <v>353.5</v>
       </c>
     </row>
     <row r="101">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>66.25</v>
+        <v>66.84999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>217.9</v>
+        <v>216.8</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>111.3</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1725</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>203.9</v>
+        <v>202.8</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>84.95</v>
+        <v>85.25</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>37.48</v>
+        <v>37.62</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>155</v>
+        <v>154.1</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>22.42</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>108</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>351.5</v>
+        <v>352.5</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>350</v>
+        <v>348.75</v>
       </c>
     </row>
     <row r="113">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>14.37</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>50.4</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>12.22</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="117">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>42.74</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="119">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="120">
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="121">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>6.02</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>14.72</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>200.1</v>
+        <v>199.5</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>13.48</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>16.38</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>26.34</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="127">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>315.75</v>
+        <v>314.75</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>15.36</v>
+        <v>15.26</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>13.67</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="131">
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>50.8</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="132">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>53.95</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>236.1</v>
+        <v>235.3</v>
       </c>
     </row>
     <row r="134">
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>10.59</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="136">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>116.7</v>
+        <v>116.3</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>29.32</v>
+        <v>29.34</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>93.25</v>
+        <v>92.55</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84999999999999</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>14100</v>
+        <v>14020</v>
       </c>
     </row>
     <row r="141">
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>327.25</v>
+        <v>330.25</v>
       </c>
     </row>
     <row r="143">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>59.75</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="145">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>6.39</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>9.91</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="147">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>48.08</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="148">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>58.45</v>
+        <v>58.15</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>86.75</v>
+        <v>88.25</v>
       </c>
     </row>
     <row r="150">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>46.86</v>
+        <v>46.78</v>
       </c>
     </row>
     <row r="151">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>18.39</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="152">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="153">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.289999999999999</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="154">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>12.36</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>8.960000000000001</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>87.05</v>
+        <v>86.34999999999999</v>
       </c>
     </row>
     <row r="157">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>37.02</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="158">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>58.45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>83.84999999999999</v>
+        <v>84.34999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>14.61</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="161">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="162">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>39.52</v>
+        <v>39.92</v>
       </c>
     </row>
     <row r="163">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>7.12</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="164">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>4.95</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>20.82</v>
+        <v>20.84</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>40.46</v>
+        <v>40.64</v>
       </c>
     </row>
     <row r="168">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>149.5</v>
+        <v>149.4</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>5117.5</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>62.2</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>3787.5</v>
+        <v>3757.5</v>
       </c>
     </row>
     <row r="173">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>25.44</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>21.16</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5775</v>
+        <v>5742.5</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>140.6</v>
+        <v>139.6</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1554</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>15.09</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>11.9</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="180">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>81.84999999999999</v>
+        <v>80.95</v>
       </c>
     </row>
     <row r="181">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>16.18</v>
+        <v>16.09</v>
       </c>
     </row>
     <row r="182">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>93.8</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>20.84</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="184">
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>32.16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="185">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>62.05</v>
+        <v>61.75</v>
       </c>
     </row>
     <row r="186">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>151.8</v>
+        <v>152</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>626</v>
+        <v>623.5</v>
       </c>
     </row>
     <row r="189">
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>13.69</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="190">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>28.92</v>
+        <v>28.96</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>39.7</v>
+        <v>39.62</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>28.9</v>
+        <v>28.74</v>
       </c>
     </row>
     <row r="193">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="194">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>27</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="196">
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>14.2</v>
+        <v>14.26</v>
       </c>
     </row>
     <row r="197">
@@ -6939,7 +6939,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>2.731275</v>
+        <v>2.790137</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>245.2</v>
+        <v>242.6</v>
       </c>
     </row>
     <row r="198">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.96</v>
+        <v>23.92</v>
       </c>
     </row>
     <row r="201">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>19.57</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="203">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>145</v>
+        <v>144.2</v>
       </c>
     </row>
     <row r="204">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>86.7</v>
+        <v>87.05</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>8.67</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="207">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="208">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>44.4</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>650</v>
+        <v>650.5</v>
       </c>
     </row>
     <row r="210">
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>0</v>
+        <v>12.456489</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>66.2</v>
+        <v>65.95</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>116.2</v>
+        <v>116.9</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="213">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>81.7</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="214">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>43.78</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>32.36</v>
+        <v>32.52</v>
       </c>
     </row>
     <row r="216">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>76.34999999999999</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="217">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>40.76</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>11.64</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>12.3</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>15</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="221">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>41.78</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="222">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>8.07</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>55.8</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="225">
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>5.91</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="226">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>16.81</v>
+        <v>16.74</v>
       </c>
     </row>
     <row r="227">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>9.119999999999999</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="229">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>7.24</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="230">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.24</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>18.19</v>
+        <v>18.32</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>547.5</v>
+        <v>542</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>62.05</v>
+        <v>62</v>
       </c>
     </row>
     <row r="234">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>12.5</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="235">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>40.7</v>
+        <v>41.42</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>111.1</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>38.78</v>
+        <v>38.34</v>
       </c>
     </row>
     <row r="239">
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="H239" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="240">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>4.1</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>32.76</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>92.59999999999999</v>
+        <v>92.34999999999999</v>
       </c>
     </row>
     <row r="245">
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>21.76</v>
+        <v>21.62</v>
       </c>
     </row>
     <row r="246">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.44</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="247">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>6.43</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="248">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="249">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>87.09999999999999</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="250">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>429.5</v>
+        <v>427.5</v>
       </c>
     </row>
     <row r="251">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="252">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>262.75</v>
+        <v>263</v>
       </c>
     </row>
     <row r="253">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>4.7</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="254">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>13.41</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="257">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>27.14</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="259">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>72.45</v>
+        <v>72</v>
       </c>
     </row>
     <row r="260">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>19.08</v>
+        <v>19.14</v>
       </c>
     </row>
     <row r="261">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>53.75</v>
+        <v>54</v>
       </c>
     </row>
     <row r="262">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.14</v>
+        <v>28.24</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>14.18</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>15.43</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="265">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>11.72</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="266">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>124.5</v>
+        <v>125.2</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>126.3</v>
+        <v>125.7</v>
       </c>
     </row>
     <row r="268">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>115.4</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="270">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>17.71</v>
+        <v>17.64</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>8.41</v>
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="272">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>5.616324</v>
+        <v>5.616416</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>17.62</v>
+        <v>17.64</v>
       </c>
     </row>
     <row r="273">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>19.77</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>12.58</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="276">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>40.36</v>
+        <v>40.08</v>
       </c>
     </row>
     <row r="277">
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="H277" t="n">
-        <v>33.04</v>
+        <v>32.98</v>
       </c>
     </row>
     <row r="278">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.6</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>58.6</v>
+        <v>58.35</v>
       </c>
     </row>
     <row r="280">
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>7.64</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="282">
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>26.6</v>
+        <v>26.46</v>
       </c>
     </row>
     <row r="283">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>23.76</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="284">
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="285">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>25.04</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>8.130000000000001</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="287">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>58.85</v>
+        <v>58.55</v>
       </c>
     </row>
     <row r="289">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>21.24</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>6.14</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>738.5</v>
+        <v>736</v>
       </c>
     </row>
     <row r="292">
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>56.05</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="293">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>46.08</v>
+        <v>45.92</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>11.85</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="295">
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>19.37</v>
+        <v>18.98</v>
       </c>
     </row>
     <row r="296">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>7.75</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>89.2</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>218.5</v>
+        <v>217.5</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="301">
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="H301" t="n">
-        <v>24.18</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="302">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="303">
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="H303" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="304">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>9.800000000000001</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="305">
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>5.946804</v>
+        <v>6.061398</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="307">
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="308">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="310">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>7.62</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="311">
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>39.68</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="312">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>116.5</v>
+        <v>115.2</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>14.61</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>263.25</v>
+        <v>262.25</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>8.33</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>241.8</v>
+        <v>240.6</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>432.5</v>
+        <v>440.75</v>
       </c>
     </row>
     <row r="319">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>92.45</v>
+        <v>92.15000000000001</v>
       </c>
     </row>
     <row r="321">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>12.4</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="322">
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="H322" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="323">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>15.36</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="324">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>158.5</v>
+        <v>155.4</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>15.34</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>6.32</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="327">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>333.5</v>
+        <v>332</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>6.15</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="330">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>33.28</v>
+        <v>33.22</v>
       </c>
     </row>
     <row r="331">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>15.02</v>
+        <v>14.81</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>40.4</v>
+        <v>40.32</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>64.59999999999999</v>
+        <v>64.05</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>10.1</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="336">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>17.41</v>
+        <v>17.37</v>
       </c>
     </row>
     <row r="337">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.94</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="338">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>22.96</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>14.28</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="340">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>5.48</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>30.14</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>26.98</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="344">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>17.97</v>
+        <v>18</v>
       </c>
     </row>
     <row r="345">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>94.55</v>
+        <v>94.05</v>
       </c>
     </row>
     <row r="346">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>10.47</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.48</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="349">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="H349" t="n">
-        <v>12.15</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="350">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="H352" t="n">
-        <v>10.5</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="353">
@@ -12100,7 +12100,7 @@
         </is>
       </c>
       <c r="H353" t="n">
-        <v>4.26</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="354">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="355">
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="H355" t="n">
-        <v>267.75</v>
+        <v>266.25</v>
       </c>
     </row>
     <row r="356">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="357">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="H358" t="n">
-        <v>38.06</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="359">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>127</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>19.94</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="362">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>9.15</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="363">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>24</v>
+        <v>23.94</v>
       </c>
     </row>
     <row r="364">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>12.24</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="365">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="H365" t="n">
-        <v>148.5</v>
+        <v>148.3</v>
       </c>
     </row>
     <row r="366">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>21.04</v>
+        <v>21</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>59.8</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>15.26</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="369">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>72.55</v>
+        <v>71</v>
       </c>
     </row>
     <row r="370">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>6.85</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>54.65</v>
+        <v>53.95</v>
       </c>
     </row>
     <row r="372">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>7.3</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="373">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>16.2</v>
+        <v>16.17</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>304.5</v>
+        <v>302.5</v>
       </c>
     </row>
     <row r="377">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>66.40000000000001</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="378">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>7.13</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>65.55</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="380">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.48</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>7.4</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>5.8</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="384">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>40.22</v>
+        <v>40.18</v>
       </c>
     </row>
     <row r="386">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="H386" t="n">
-        <v>20.28</v>
+        <v>20.18</v>
       </c>
     </row>
     <row r="387">
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>35.36</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="388">
@@ -13242,7 +13242,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>0</v>
+        <v>5.500132</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="H388" t="n">
-        <v>4.96</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="389">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="H390" t="n">
-        <v>4.94</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="391">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="392">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>99.2</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="393">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>13.18</v>
+        <v>13.19</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="395">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.53</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="396">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>9.43</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="397">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>5.49</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="398">
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="H398" t="n">
-        <v>34.46</v>
+        <v>33.96</v>
       </c>
     </row>
     <row r="399">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>48.06</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="401">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>188.8</v>
+        <v>189.5</v>
       </c>
     </row>
     <row r="403">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>12.49</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="404">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>152.6</v>
+        <v>152</v>
       </c>
     </row>
     <row r="406">
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="407">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>30.52</v>
+        <v>30.58</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>28.62</v>
+        <v>28.68</v>
       </c>
     </row>
     <row r="409">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="410">
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>0</v>
+        <v>19.312947</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>43.48</v>
+        <v>43.34</v>
       </c>
     </row>
     <row r="412">
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="H412" t="n">
-        <v>26.86</v>
+        <v>26.84</v>
       </c>
     </row>
     <row r="413">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>20.7</v>
+        <v>20.64</v>
       </c>
     </row>
     <row r="414">
@@ -14113,7 +14113,7 @@
         </is>
       </c>
       <c r="H414" t="n">
-        <v>117.9</v>
+        <v>119.6</v>
       </c>
     </row>
     <row r="415">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>47.18</v>
+        <v>46.78</v>
       </c>
     </row>
     <row r="416">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>10.41</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="417">
@@ -14199,7 +14199,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>3.547692</v>
+        <v>3.625551</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>4.753512</v>
+        <v>4.799405</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>8.66</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="419">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>47.96</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="420">
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="H422" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="423">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>29.32</v>
+        <v>29.38</v>
       </c>
     </row>
     <row r="424">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>22.46</v>
+        <v>22.58</v>
       </c>
     </row>
     <row r="425">
@@ -14463,7 +14463,7 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>4.701503</v>
+        <v>4.717436</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>39.44</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="426">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>7.8</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="427">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.51</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>11.62</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="429">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>8.859999999999999</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="430">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>21.3</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="431">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="432">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>7.9</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="433">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.98</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="434">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>10.21</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="435">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>7.5</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="437">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>29.72</v>
+        <v>29.22</v>
       </c>
     </row>
     <row r="438">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>139.8</v>
+        <v>137.9</v>
       </c>
     </row>
     <row r="439">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>105.1</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="440">
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="441">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>12.97</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="442">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>6.27</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="443">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="444">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>10.63</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="445">
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="H445" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="446">
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="447">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>41.4</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>27.68</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>27.54</v>
+        <v>27.44</v>
       </c>
     </row>
     <row r="450">
@@ -15301,7 +15301,7 @@
         </is>
       </c>
       <c r="H450" t="n">
-        <v>1559</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="451">
@@ -15321,7 +15321,7 @@
         </is>
       </c>
       <c r="D451" t="n">
-        <v>4.088745</v>
+        <v>4.101698</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>13.5</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>20.16</v>
+        <v>20.08</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>5.36</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="454">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>17.8</v>
+        <v>17.79</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>13.12</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="457">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>177.3</v>
+        <v>177.9</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>32.82</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="461">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="H462" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="463">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>37.16</v>
+        <v>37.22</v>
       </c>
     </row>
     <row r="465">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="H465" t="n">
-        <v>11.07</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="466">
@@ -15829,7 +15829,7 @@
         </is>
       </c>
       <c r="H466" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="467">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>36.48</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="468">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>25.2</v>
+        <v>26.16</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>42.76</v>
+        <v>42.62</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>8.74</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="472">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>27.32</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="473">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>30</v>
+        <v>30.02</v>
       </c>
     </row>
     <row r="474">
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>12.94</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="476">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>11.19</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="478">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>27.32</v>
+        <v>27.38</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>29.34</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.47</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="481">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.39</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>102.2</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="484">
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>13.7</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="485">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>86.55</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="486">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="488">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>13.55</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="489">
@@ -16588,7 +16588,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="490">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>18.25</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="491">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="494">
@@ -16740,7 +16740,7 @@
         </is>
       </c>
       <c r="D494" t="n">
-        <v>5.351563</v>
+        <v>4.988244</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>34.22</v>
+        <v>34.18</v>
       </c>
     </row>
     <row r="495">
@@ -16786,7 +16786,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>41.32</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="496">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="497">
@@ -16852,7 +16852,7 @@
         </is>
       </c>
       <c r="H497" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="498">
@@ -16918,7 +16918,7 @@
         </is>
       </c>
       <c r="H499" t="n">
-        <v>5.34</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="500">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="502">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.74</v>
+        <v>24.66</v>
       </c>
     </row>
     <row r="503">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="506">
@@ -17149,7 +17149,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>8.789999999999999</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="507">
@@ -17182,7 +17182,7 @@
         </is>
       </c>
       <c r="H507" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="508">
@@ -17215,7 +17215,7 @@
         </is>
       </c>
       <c r="H508" t="n">
-        <v>226.4</v>
+        <v>226.6</v>
       </c>
     </row>
     <row r="509">
@@ -17281,7 +17281,7 @@
         </is>
       </c>
       <c r="H510" t="n">
-        <v>15.92</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="511">
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="512">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>154.3</v>
+        <v>155</v>
       </c>
     </row>
     <row r="515">
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="516">
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="H516" t="n">
-        <v>16.76</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="517">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>9.220000000000001</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>35.08</v>
+        <v>34.72</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="520">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>72.25</v>
+        <v>71.65000000000001</v>
       </c>
     </row>
     <row r="523">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>7.71</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="524">
@@ -17743,7 +17743,7 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>12.56</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="525">
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>4.6</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="526">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>17.92</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="527">
@@ -17842,7 +17842,7 @@
         </is>
       </c>
       <c r="H527" t="n">
-        <v>14.24</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="528">
@@ -17941,7 +17941,7 @@
         </is>
       </c>
       <c r="H530" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="531">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="532">
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>13.63</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="533">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.47</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="534">
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="H534" t="n">
-        <v>6.29</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="535">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="536">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>22.98</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="537">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.74</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="538">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>63.05</v>
+        <v>62.95</v>
       </c>
     </row>
     <row r="540">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="H540" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="541">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>26.18</v>
+        <v>26.08</v>
       </c>
     </row>
     <row r="542">
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="H542" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="543">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>34.06</v>
+        <v>34.18</v>
       </c>
     </row>
     <row r="544">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="H544" t="n">
-        <v>155.9</v>
+        <v>155.5</v>
       </c>
     </row>
     <row r="545">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>15.09</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="546">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>10.47</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="547">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>16.18</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>28.28</v>
+        <v>28</v>
       </c>
     </row>
     <row r="549">
@@ -18601,7 +18601,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>44.12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="551">
@@ -18667,7 +18667,7 @@
         </is>
       </c>
       <c r="H552" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="553">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="H554" t="n">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="555">
@@ -18766,7 +18766,7 @@
         </is>
       </c>
       <c r="H555" t="n">
-        <v>47.28</v>
+        <v>47</v>
       </c>
     </row>
     <row r="556">
@@ -18898,7 +18898,7 @@
         </is>
       </c>
       <c r="H559" t="n">
-        <v>121.2</v>
+        <v>122</v>
       </c>
     </row>
     <row r="560">
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="561">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>28.1</v>
+        <v>28.24</v>
       </c>
     </row>
     <row r="562">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="H563" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="564">
@@ -19129,7 +19129,7 @@
         </is>
       </c>
       <c r="H566" t="n">
-        <v>27.04</v>
+        <v>27.12</v>
       </c>
     </row>
     <row r="567">
@@ -19162,7 +19162,7 @@
         </is>
       </c>
       <c r="H567" t="n">
-        <v>4.98</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="568">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>8.140000000000001</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="569">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="H569" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="570">
@@ -19261,7 +19261,7 @@
         </is>
       </c>
       <c r="H570" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="571">
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>6.51</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="572">
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>8.529999999999999</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="573">
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="H573" t="n">
-        <v>18.99</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="574">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>27</v>
+        <v>27.12</v>
       </c>
     </row>
     <row r="575">
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="H577" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="578">
@@ -19525,7 +19525,7 @@
         </is>
       </c>
       <c r="H578" t="n">
-        <v>5.96</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="579">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.59</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="581">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.67</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="582">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H582" t="n">
-        <v>10.67</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="583">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="H584" t="n">
-        <v>6.32</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="585">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>108.2</v>
+        <v>18.62</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>141.3</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>17.47</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>18.88</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>8.09</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>18.01</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>47.68</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>41.18</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>63.8</v>
+        <v>114</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>12.89</v>
+        <v>41.48</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>39.8</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>18.75</v>
+        <v>33.96</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>76.38</v>
+        <v>38.52</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>3.88</v>
+        <v>166.6</v>
       </c>
     </row>
     <row r="600">
@@ -20251,7 +20251,7 @@
         </is>
       </c>
       <c r="H600" t="n">
-        <v>155.9</v>
+        <v>156.3</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>2.49</v>
+        <v>188.6</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>33.92</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>45.16</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>21.38</v>
+        <v>141.3</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>38.64</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>17.51</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>39.4</v>
+        <v>21.06</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>14.64</v>
+        <v>76.31</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>165.5</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>72.5</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>188.9</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>21.4</v>
+        <v>44.46</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>372.5</v>
+        <v>372.75</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2610</v>
+        <v>2612.5</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>140.8</v>
+        <v>141.9</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>94.45</v>
+        <v>94.84999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>193.9</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>385.75</v>
+        <v>388.25</v>
       </c>
     </row>
     <row r="9">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>327.75</v>
+        <v>327.5</v>
       </c>
     </row>
     <row r="11">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>14.84</v>
+        <v>14.95</v>
       </c>
     </row>
     <row r="12">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>76.59999999999999</v>
+        <v>77.55</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>174.9</v>
+        <v>174.3</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>114.8</v>
+        <v>114.7</v>
       </c>
     </row>
     <row r="17">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>47.06</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>33.66</v>
+        <v>33.88</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>39.98</v>
+        <v>40.38</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>88.95</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>39.76</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>112.7</v>
+        <v>113.4</v>
       </c>
     </row>
     <row r="24">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>83</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="25">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>64.90000000000001</v>
+        <v>65.05</v>
       </c>
     </row>
     <row r="26">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>59.55</v>
+        <v>59.75</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>495.5</v>
+        <v>495.25</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>221.7</v>
+        <v>219.6</v>
       </c>
     </row>
     <row r="31">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>306.75</v>
+        <v>308.25</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>45.42</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>45.96</v>
+        <v>46.38</v>
       </c>
     </row>
     <row r="35">
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>107.2</v>
+        <v>107.3</v>
       </c>
     </row>
     <row r="37">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>676</v>
+        <v>685.5</v>
       </c>
     </row>
     <row r="39">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>11500</v>
+        <v>11487.5</v>
       </c>
     </row>
     <row r="41">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>20.96</v>
+        <v>21.02</v>
       </c>
     </row>
     <row r="42">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>680.5</v>
+        <v>685</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1680</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>22.18</v>
+        <v>22.58</v>
       </c>
     </row>
     <row r="45">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>34.16</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="46">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>286.5</v>
+        <v>287.25</v>
       </c>
     </row>
     <row r="47">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>100.5</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>80.65000000000001</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>109.3</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="52">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>628.5</v>
+        <v>631.5</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>34.04</v>
+        <v>33.88</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>180.6</v>
+        <v>180.7</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>449</v>
+        <v>448.25</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>10.23</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="57">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>34</v>
+        <v>34.02</v>
       </c>
     </row>
     <row r="58">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>17.17</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="59">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>115</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="60">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>20.6</v>
+        <v>20.78</v>
       </c>
     </row>
     <row r="61">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6.13</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="62">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>211.8</v>
+        <v>211.9</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>111.9</v>
+        <v>115.7</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>105.5</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>203.6</v>
+        <v>201.6</v>
       </c>
     </row>
     <row r="66">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>259.75</v>
+        <v>260.5</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>33.78</v>
+        <v>33.82</v>
       </c>
     </row>
     <row r="68">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.72</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>12.89</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>183</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="71">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>96.2</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>126</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="73">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1357</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="74">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>43.92</v>
+        <v>42.68</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>28.4</v>
+        <v>28.42</v>
       </c>
     </row>
     <row r="76">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="78">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>173.3</v>
+        <v>174.1</v>
       </c>
     </row>
     <row r="79">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>37.36</v>
+        <v>37.42</v>
       </c>
     </row>
     <row r="80">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>34.46</v>
+        <v>34.36</v>
       </c>
     </row>
     <row r="81">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>139.6</v>
+        <v>140</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>224.3</v>
+        <v>224.4</v>
       </c>
     </row>
     <row r="83">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KRDMD</t>
+          <t>KRDMB</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>39.98</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="84">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KRDMB</t>
+          <t>KRDMD</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>112.1</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="85">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1687</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="87">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.78</v>
+        <v>25.88</v>
       </c>
     </row>
     <row r="88">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.48</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="89">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>224</v>
+        <v>224.4</v>
       </c>
     </row>
     <row r="90">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>51.25</v>
+        <v>51.55</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1213</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>252.75</v>
+        <v>254</v>
       </c>
     </row>
     <row r="93">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>105.5</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="95">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="96">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>101.9</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>138.9</v>
+        <v>139.4</v>
       </c>
     </row>
     <row r="98">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>11.58</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="99">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>66.84999999999999</v>
+        <v>66.15000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>216.8</v>
+        <v>215.9</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>110.5</v>
+        <v>111.3</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1719</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>202.8</v>
+        <v>203.6</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>85.25</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>37.62</v>
+        <v>37.76</v>
       </c>
     </row>
     <row r="108">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>154.1</v>
+        <v>150.8</v>
       </c>
     </row>
     <row r="109">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>22.46</v>
+        <v>22.56</v>
       </c>
     </row>
     <row r="110">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>352.5</v>
+        <v>357.75</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>348.75</v>
+        <v>348</v>
       </c>
     </row>
     <row r="113">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>14.25</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>50.25</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>12.14</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="117">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>42.7</v>
+        <v>42.76</v>
       </c>
     </row>
     <row r="119">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120">
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>224</v>
+        <v>224.2</v>
       </c>
     </row>
     <row r="121">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>14.8</v>
+        <v>14.66</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>199.5</v>
+        <v>200.1</v>
       </c>
     </row>
     <row r="124">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>16.24</v>
+        <v>16.26</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>26.32</v>
+        <v>26.48</v>
       </c>
     </row>
     <row r="127">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>314.75</v>
+        <v>313</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>15.26</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="130">
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>50.75</v>
+        <v>50.95</v>
       </c>
     </row>
     <row r="132">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>53.75</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>235.3</v>
+        <v>233</v>
       </c>
     </row>
     <row r="134">
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>10.76</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="136">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>116.3</v>
+        <v>116</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>29.34</v>
+        <v>29.22</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>92.55</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>70.84999999999999</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>14020</v>
+        <v>13950</v>
       </c>
     </row>
     <row r="141">
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>330.25</v>
+        <v>326.5</v>
       </c>
     </row>
     <row r="143">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>144</v>
+        <v>143.9</v>
       </c>
     </row>
     <row r="144">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>59.25</v>
+        <v>59.55</v>
       </c>
     </row>
     <row r="145">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>6.41</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="146">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>9.960000000000001</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="147">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>47.76</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="148">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>58.15</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>88.25</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="150">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>46.78</v>
+        <v>46.94</v>
       </c>
     </row>
     <row r="151">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>18.37</v>
+        <v>18.27</v>
       </c>
     </row>
     <row r="152">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="153">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.27</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="154">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>12.22</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>8.92</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>86.34999999999999</v>
+        <v>86.84999999999999</v>
       </c>
     </row>
     <row r="157">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>36.9</v>
+        <v>36.88</v>
       </c>
     </row>
     <row r="158">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>58</v>
+        <v>58.55</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>84.34999999999999</v>
+        <v>84.45</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>14.59</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="161">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>39.92</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="163">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>7.07</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="164">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>179.2</v>
+        <v>180.8</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>4.94</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>20.84</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>40.64</v>
+        <v>40.66</v>
       </c>
     </row>
     <row r="168">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>73.95</v>
+        <v>74.05</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>149.4</v>
+        <v>150.5</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>5080</v>
+        <v>5085</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>62.1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>3757.5</v>
+        <v>3762.5</v>
       </c>
     </row>
     <row r="173">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>25.32</v>
+        <v>25.36</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>21.1</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5742.5</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>139.6</v>
+        <v>140.5</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1539</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>15.08</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>11.92</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="180">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>80.95</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="181">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>16.09</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="182">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>93.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>20.86</v>
+        <v>20.72</v>
       </c>
     </row>
     <row r="184">
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>32</v>
+        <v>31.98</v>
       </c>
     </row>
     <row r="185">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>61.75</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="186">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>152</v>
+        <v>152.1</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>623.5</v>
+        <v>624.5</v>
       </c>
     </row>
     <row r="189">
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>13.64</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="190">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>28.96</v>
+        <v>29.12</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>39.62</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>28.74</v>
+        <v>28.76</v>
       </c>
     </row>
     <row r="193">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>26.92</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="196">
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>14.26</v>
+        <v>14.27</v>
       </c>
     </row>
     <row r="197">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>242.6</v>
+        <v>240.4</v>
       </c>
     </row>
     <row r="198">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="199">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>23.92</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>31.54</v>
+        <v>31.76</v>
       </c>
     </row>
     <row r="202">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>19.37</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="203">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>20.1</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>87.05</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="206">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>8.529999999999999</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="207">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>45.14</v>
+        <v>45.12</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>650.5</v>
+        <v>643</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>65.95</v>
+        <v>66.05</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>116.9</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="213">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>81.25</v>
+        <v>81</v>
       </c>
     </row>
     <row r="214">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>43.22</v>
+        <v>43.44</v>
       </c>
     </row>
     <row r="215">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>32.52</v>
+        <v>32.36</v>
       </c>
     </row>
     <row r="216">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>76.40000000000001</v>
+        <v>76.25</v>
       </c>
     </row>
     <row r="217">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>41.38</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>11.56</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>12.15</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>14.93</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="221">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>55.1</v>
+        <v>55.05</v>
       </c>
     </row>
     <row r="225">
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>5.97</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="226">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>16.74</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="227">
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="H227" t="n">
-        <v>134.7</v>
+        <v>134</v>
       </c>
     </row>
     <row r="228">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>9.16</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="229">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>7.22</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="230">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.2</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>18.32</v>
+        <v>18.29</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>542</v>
+        <v>542.5</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>62</v>
+        <v>62.65</v>
       </c>
     </row>
     <row r="234">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>12.61</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="235">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="236">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>41.42</v>
+        <v>41.28</v>
       </c>
     </row>
     <row r="237">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>110.4</v>
+        <v>110.9</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>38.34</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="239">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>42.82</v>
+        <v>42.92</v>
       </c>
     </row>
     <row r="241">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>33.5</v>
+        <v>33.14</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>92.34999999999999</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="245">
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>21.62</v>
+        <v>21.68</v>
       </c>
     </row>
     <row r="246">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.41</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="247">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="248">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="249">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>86.59999999999999</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="250">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>427.5</v>
+        <v>427</v>
       </c>
     </row>
     <row r="251">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>25</v>
+        <v>25.04</v>
       </c>
     </row>
     <row r="252">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>263</v>
+        <v>263.5</v>
       </c>
     </row>
     <row r="253">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="255">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>13.38</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="257">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="258">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>27.4</v>
+        <v>26.98</v>
       </c>
     </row>
     <row r="259">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>72</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="260">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>19.14</v>
+        <v>19.13</v>
       </c>
     </row>
     <row r="261">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>54</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="262">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.24</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>14.19</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>15.33</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="265">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>11.61</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="266">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>125.2</v>
+        <v>125.3</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>125.7</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="268">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>114.3</v>
+        <v>114.1</v>
       </c>
     </row>
     <row r="270">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>17.64</v>
+        <v>17.68</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>8.369999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="272">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>17.64</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="273">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>40.08</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="277">
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="H277" t="n">
-        <v>32.98</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="278">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>11.57</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="279">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>58.35</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="280">
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>7.6</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="282">
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>26.46</v>
+        <v>26.64</v>
       </c>
     </row>
     <row r="283">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>23.5</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="284">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>24.94</v>
+        <v>25.04</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>8.140000000000001</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="287">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>58.55</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="289">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>21.16</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>6.13</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="291">
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>55.9</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="293">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>45.92</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>11.78</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="295">
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>18.98</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="296">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>7.72</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>89.8</v>
+        <v>89.34999999999999</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>217.5</v>
+        <v>216.8</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>42.2</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="301">
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="H301" t="n">
-        <v>24.06</v>
+        <v>24.08</v>
       </c>
     </row>
     <row r="302">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>19.1</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="303">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>9.75</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="305">
@@ -10549,7 +10549,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="307">
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="308">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="H308" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="309">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>10.11</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="310">
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>39.7</v>
+        <v>39.54</v>
       </c>
     </row>
     <row r="312">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="313">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>115.2</v>
+        <v>114.5</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>14.54</v>
+        <v>14.22</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>262.25</v>
+        <v>261</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>8.48</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>240.6</v>
+        <v>238.9</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>440.75</v>
+        <v>438.5</v>
       </c>
     </row>
     <row r="319">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>6.02</v>
+        <v>6</v>
       </c>
     </row>
     <row r="320">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>92.15000000000001</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="321">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>12.36</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="322">
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="H322" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="323">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>15.4</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="324">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>155.4</v>
+        <v>156.2</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>15.35</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>6.24</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="327">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>332</v>
+        <v>332.75</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>6.17</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="330">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>33.22</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="331">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>14.81</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>40.32</v>
+        <v>40.26</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>64.05</v>
+        <v>63.85</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>10.11</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="336">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>17.37</v>
+        <v>17.34</v>
       </c>
     </row>
     <row r="337">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.95</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="338">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>22.9</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="339">
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>14.39</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="340">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>5.47</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="H342" t="n">
-        <v>29.9</v>
+        <v>29.98</v>
       </c>
     </row>
     <row r="343">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>27.1</v>
+        <v>27.26</v>
       </c>
     </row>
     <row r="344">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>18</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="345">
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>94.05</v>
+        <v>94.34999999999999</v>
       </c>
     </row>
     <row r="346">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>10.45</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="348">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>25.44</v>
+        <v>25.52</v>
       </c>
     </row>
     <row r="349">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="H349" t="n">
-        <v>12.16</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="350">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>12.96</v>
+        <v>13</v>
       </c>
     </row>
     <row r="351">
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="H351" t="n">
-        <v>6.97</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="352">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="H352" t="n">
-        <v>10.51</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="353">
@@ -12100,7 +12100,7 @@
         </is>
       </c>
       <c r="H353" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="354">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="357">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="H357" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="358">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="H358" t="n">
-        <v>37.9</v>
+        <v>37.94</v>
       </c>
     </row>
     <row r="359">
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="H360" t="n">
-        <v>127.3</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="361">
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>19.82</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="362">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H363" t="n">
-        <v>23.94</v>
+        <v>24.02</v>
       </c>
     </row>
     <row r="364">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="H364" t="n">
-        <v>12.26</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="365">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="H365" t="n">
-        <v>148.3</v>
+        <v>147.8</v>
       </c>
     </row>
     <row r="366">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>21</v>
+        <v>20.96</v>
       </c>
     </row>
     <row r="367">
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>59.3</v>
+        <v>59.45</v>
       </c>
     </row>
     <row r="368">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H368" t="n">
-        <v>15.19</v>
+        <v>15.21</v>
       </c>
     </row>
     <row r="369">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="H369" t="n">
-        <v>71</v>
+        <v>71.05</v>
       </c>
     </row>
     <row r="370">
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>6.8</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="371">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>53.95</v>
+        <v>54.15</v>
       </c>
     </row>
     <row r="372">
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="H373" t="n">
-        <v>23.58</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="374">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="H374" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="375">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="H375" t="n">
-        <v>16.17</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="376">
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H376" t="n">
-        <v>302.5</v>
+        <v>302.25</v>
       </c>
     </row>
     <row r="377">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H377" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="378">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="H378" t="n">
-        <v>7.1</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="379">
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>65.2</v>
+        <v>64.55</v>
       </c>
     </row>
     <row r="380">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="H381" t="n">
-        <v>17.43</v>
+        <v>17.36</v>
       </c>
     </row>
     <row r="382">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H382" t="n">
-        <v>7.35</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="383">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="H383" t="n">
-        <v>5.85</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="384">
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>40.18</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="386">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="H386" t="n">
-        <v>20.18</v>
+        <v>20.22</v>
       </c>
     </row>
     <row r="387">
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>35.5</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="388">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="H389" t="n">
-        <v>108.6</v>
+        <v>114.6</v>
       </c>
     </row>
     <row r="390">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="H390" t="n">
-        <v>4.92</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="391">
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H391" t="n">
-        <v>4.02</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="392">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>98.7</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="393">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="H393" t="n">
-        <v>13.19</v>
+        <v>13.18</v>
       </c>
     </row>
     <row r="394">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="H394" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="395">
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="H395" t="n">
-        <v>12.48</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="396">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>9.4</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="397">
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>5.44</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="398">
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="H398" t="n">
-        <v>33.96</v>
+        <v>33.88</v>
       </c>
     </row>
     <row r="399">
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="400">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>47.02</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="401">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="H401" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="402">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>189.5</v>
+        <v>189.2</v>
       </c>
     </row>
     <row r="403">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>12.43</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="404">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>152</v>
+        <v>151.5</v>
       </c>
     </row>
     <row r="406">
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="407">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>30.58</v>
+        <v>30.64</v>
       </c>
     </row>
     <row r="408">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>28.68</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="409">
@@ -13981,7 +13981,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>91.90000000000001</v>
+        <v>92.15000000000001</v>
       </c>
     </row>
     <row r="411">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>43.34</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="412">
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="H412" t="n">
-        <v>26.84</v>
+        <v>26.74</v>
       </c>
     </row>
     <row r="413">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>20.64</v>
+        <v>20.62</v>
       </c>
     </row>
     <row r="414">
@@ -14113,7 +14113,7 @@
         </is>
       </c>
       <c r="H414" t="n">
-        <v>119.6</v>
+        <v>117.7</v>
       </c>
     </row>
     <row r="415">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>46.78</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="416">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="419">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>29.38</v>
+        <v>29.52</v>
       </c>
     </row>
     <row r="424">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>22.58</v>
+        <v>22.56</v>
       </c>
     </row>
     <row r="425">
@@ -14463,7 +14463,7 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>4.717436</v>
+        <v>4.717444</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>39.74</v>
+        <v>39.88</v>
       </c>
     </row>
     <row r="426">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>11.47</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="428">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>11.56</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="429">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>8.83</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="430">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>21.14</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="431">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="432">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>14.87</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="434">
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>10.12</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="435">
@@ -14806,7 +14806,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>305</v>
+        <v>305.25</v>
       </c>
     </row>
     <row r="436">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>7.48</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="437">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>29.22</v>
+        <v>29.12</v>
       </c>
     </row>
     <row r="438">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>137.9</v>
+        <v>138.7</v>
       </c>
     </row>
     <row r="439">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>104.8</v>
+        <v>105</v>
       </c>
     </row>
     <row r="440">
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>12.92</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="442">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>6.29</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="443">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>10.53</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="445">
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="H445" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="446">
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="447">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>41.04</v>
+        <v>41</v>
       </c>
     </row>
     <row r="448">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>27.66</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="449">
@@ -15268,7 +15268,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>27.44</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="450">
@@ -15301,7 +15301,7 @@
         </is>
       </c>
       <c r="H450" t="n">
-        <v>1549</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="451">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>13.42</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="452">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>20.08</v>
+        <v>20.04</v>
       </c>
     </row>
     <row r="453">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>5.41</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="454">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="455">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>17.79</v>
+        <v>17.81</v>
       </c>
     </row>
     <row r="456">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>13.1</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="457">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="458">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>177.9</v>
+        <v>176.6</v>
       </c>
     </row>
     <row r="460">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>32.7</v>
+        <v>32.64</v>
       </c>
     </row>
     <row r="461">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>37.22</v>
+        <v>37.28</v>
       </c>
     </row>
     <row r="465">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="H465" t="n">
-        <v>11.04</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="466">
@@ -15829,7 +15829,7 @@
         </is>
       </c>
       <c r="H466" t="n">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="467">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>36.3</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="468">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="469">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>26.16</v>
+        <v>25.84</v>
       </c>
     </row>
     <row r="470">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>42.62</v>
+        <v>42.68</v>
       </c>
     </row>
     <row r="471">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>8.789999999999999</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="472">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>26.94</v>
+        <v>26.98</v>
       </c>
     </row>
     <row r="473">
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>12.92</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="476">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="477">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>11.6</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="478">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>27.38</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="479">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>30.5</v>
+        <v>30.98</v>
       </c>
     </row>
     <row r="480">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>12.37</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="481">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="482">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>11.34</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="483">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>101.5</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="484">
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>13.76</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="485">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>86.3</v>
+        <v>90.05</v>
       </c>
     </row>
     <row r="486">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="487">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="488">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>13.73</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="489">
@@ -16588,7 +16588,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="490">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>18.09</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="491">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>34.18</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="495">
@@ -16786,7 +16786,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>40.94</v>
+        <v>40.74</v>
       </c>
     </row>
     <row r="496">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>49.5</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="497">
@@ -16852,7 +16852,7 @@
         </is>
       </c>
       <c r="H497" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="498">
@@ -16918,7 +16918,7 @@
         </is>
       </c>
       <c r="H499" t="n">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="500">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>10.31</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="501">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>24.66</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="503">
@@ -17050,7 +17050,7 @@
         </is>
       </c>
       <c r="H503" t="n">
-        <v>8.640000000000001</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="504">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="506">
@@ -17149,7 +17149,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>8.98</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="507">
@@ -17182,7 +17182,7 @@
         </is>
       </c>
       <c r="H507" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="508">
@@ -17215,7 +17215,7 @@
         </is>
       </c>
       <c r="H508" t="n">
-        <v>226.6</v>
+        <v>220.8</v>
       </c>
     </row>
     <row r="509">
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="512">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="515">
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="H516" t="n">
-        <v>16.6</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="517">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>9.35</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="518">
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>34.72</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="519">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="520">
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="521">
@@ -17644,7 +17644,7 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>4.27</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="522">
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>71.65000000000001</v>
+        <v>72.25</v>
       </c>
     </row>
     <row r="523">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>7.67</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="524">
@@ -17743,7 +17743,7 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>12.58</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="525">
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>4.59</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="526">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>17.65</v>
+        <v>17.51</v>
       </c>
     </row>
     <row r="527">
@@ -17842,7 +17842,7 @@
         </is>
       </c>
       <c r="H527" t="n">
-        <v>14.08</v>
+        <v>14</v>
       </c>
     </row>
     <row r="528">
@@ -17941,7 +17941,7 @@
         </is>
       </c>
       <c r="H530" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="531">
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>13.56</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="533">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="H533" t="n">
-        <v>5.38</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="534">
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="H534" t="n">
-        <v>6.31</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="535">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="536">
@@ -18172,7 +18172,7 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>25.66</v>
+        <v>25.84</v>
       </c>
     </row>
     <row r="538">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>62.95</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="540">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="H540" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="541">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>26.08</v>
+        <v>26</v>
       </c>
     </row>
     <row r="542">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>34.18</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="544">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="H544" t="n">
-        <v>155.5</v>
+        <v>154.5</v>
       </c>
     </row>
     <row r="545">
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>15.08</v>
+        <v>15.07</v>
       </c>
     </row>
     <row r="546">
@@ -18502,7 +18502,7 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>16.16</v>
+        <v>16.17</v>
       </c>
     </row>
     <row r="548">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="549">
@@ -18601,7 +18601,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>44</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="551">
@@ -18667,7 +18667,7 @@
         </is>
       </c>
       <c r="H552" t="n">
-        <v>52.5</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="553">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="H554" t="n">
-        <v>4.74</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="555">
@@ -18766,7 +18766,7 @@
         </is>
       </c>
       <c r="H555" t="n">
-        <v>47</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="556">
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="H557" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="558">
@@ -18898,7 +18898,7 @@
         </is>
       </c>
       <c r="H559" t="n">
-        <v>122</v>
+        <v>123.1</v>
       </c>
     </row>
     <row r="560">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>28.24</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="562">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="H562" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="563">
@@ -19129,7 +19129,7 @@
         </is>
       </c>
       <c r="H566" t="n">
-        <v>27.12</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="567">
@@ -19162,7 +19162,7 @@
         </is>
       </c>
       <c r="H567" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="568">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>8.130000000000001</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="569">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="H569" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="570">
@@ -19294,7 +19294,7 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="572">
@@ -19327,7 +19327,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>8.51</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="573">
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="H573" t="n">
-        <v>19.1</v>
+        <v>19.14</v>
       </c>
     </row>
     <row r="574">
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>27.12</v>
+        <v>27.24</v>
       </c>
     </row>
     <row r="575">
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="H577" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="578">
@@ -19525,7 +19525,7 @@
         </is>
       </c>
       <c r="H578" t="n">
-        <v>5.93</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="579">
@@ -19558,7 +19558,7 @@
         </is>
       </c>
       <c r="H579" t="n">
-        <v>12.37</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="580">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="H580" t="n">
-        <v>9.84</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="581">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>7.68</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="582">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H582" t="n">
-        <v>10.66</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="583">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="H584" t="n">
-        <v>6.33</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="585">
@@ -19780,16 +19780,16 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>ATATR</t>
+          <t>VERTU</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
+          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H586" t="n">
-        <v>18.62</v>
+        <v>41.64</v>
       </c>
     </row>
     <row r="587">
@@ -19813,16 +19813,16 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Formul Plastik Ve Metal Sanayi AS</t>
+          <t>Enpara Bank A.S.</t>
         </is>
       </c>
       <c r="H587" t="n">
-        <v>46.7</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="588">
@@ -19846,16 +19846,16 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>VAKFA</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>VAKIF FAKTORİNG A.Ş.</t>
+          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
         </is>
       </c>
       <c r="H588" t="n">
-        <v>12.87</v>
+        <v>34.06</v>
       </c>
     </row>
     <row r="589">
@@ -19879,16 +19879,16 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
+          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H589" t="n">
-        <v>21.4</v>
+        <v>114</v>
       </c>
     </row>
     <row r="590">
@@ -19912,16 +19912,16 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Marmara Holding AS</t>
+          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H590" t="n">
-        <v>2.48</v>
+        <v>141.3</v>
       </c>
     </row>
     <row r="591">
@@ -19945,16 +19945,16 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>VAKFA</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
+          <t>VAKIF FAKTORİNG A.Ş.</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>38.6</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="592">
@@ -19978,16 +19978,16 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>EKDMR</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Ekinciler Demir ve Celik Sanayi AS</t>
+          <t>DOF Robotik Sanayi Anonim Sirketi</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>62.9</v>
+        <v>156.7</v>
       </c>
     </row>
     <row r="593">
@@ -20011,16 +20011,16 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>MEYSU</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
+          <t>Netcad Yazilim A.S.</t>
         </is>
       </c>
       <c r="H593" t="n">
-        <v>17.33</v>
+        <v>165.2</v>
       </c>
     </row>
     <row r="594">
@@ -20044,16 +20044,16 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>İŞ GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>DARPHANE ALTIN SERTİFİKASI</t>
         </is>
       </c>
       <c r="H594" t="n">
-        <v>114</v>
+        <v>76.51000000000001</v>
       </c>
     </row>
     <row r="595">
@@ -20077,16 +20077,16 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>VERTU</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>VERUSATURK GİRİŞİM SERMAYESİ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H595" t="n">
-        <v>41.48</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="596">
@@ -20110,16 +20110,16 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
         </is>
       </c>
       <c r="H596" t="n">
-        <v>17.52</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="597">
@@ -20143,16 +20143,16 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>ATATR</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Akhan Un Fabrikasi Ve Tarim Urunleri Gida Sanayi Ticaret Anonim Sirketi</t>
+          <t>Ata Turizm Isletmecilik Tasimacilik Madencilik Kuyumculu</t>
         </is>
       </c>
       <c r="H597" t="n">
-        <v>33.96</v>
+        <v>18.61</v>
       </c>
     </row>
     <row r="598">
@@ -20176,16 +20176,16 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>EKDMR</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Ecogreen Enerji Holding A.S.</t>
+          <t>Ekinciler Demir ve Celik Sanayi AS</t>
         </is>
       </c>
       <c r="H598" t="n">
-        <v>38.52</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="599">
@@ -20209,16 +20209,16 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Netcad Yazilim A.S.</t>
+          <t>Best Brands Grup Enerji Yatirim as</t>
         </is>
       </c>
       <c r="H599" t="n">
-        <v>166.6</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="600">
@@ -20242,16 +20242,16 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>DOFRB</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>DOF Robotik Sanayi Anonim Sirketi</t>
+          <t>Agaoglu Avrasya Gayrimenkul Yatirim Ortakligi AS</t>
         </is>
       </c>
       <c r="H600" t="n">
-        <v>156.3</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="601">
@@ -20275,16 +20275,16 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Metropal Kurumsal Hizmetler A.S.</t>
+          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
         </is>
       </c>
       <c r="H601" t="n">
-        <v>188.6</v>
+        <v>18.22</v>
       </c>
     </row>
     <row r="602">
@@ -20308,16 +20308,16 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>ZGYO</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Savur Gayrimenkul Yatirim Ortakligi A.S</t>
         </is>
       </c>
       <c r="H602" t="n">
-        <v>39.84</v>
+        <v>21.62</v>
       </c>
     </row>
     <row r="603">
@@ -20341,16 +20341,16 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
+          <t>Ucay Muhendislik Enerji ve Iklimlendirme Teknolojileri</t>
         </is>
       </c>
       <c r="H603" t="n">
-        <v>3.86</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="604">
@@ -20374,16 +20374,16 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Empa Elektronik Sanayi ve Ticaret A.S.</t>
+          <t>Ecogreen Enerji Holding A.S.</t>
         </is>
       </c>
       <c r="H604" t="n">
-        <v>141.3</v>
+        <v>38.72</v>
       </c>
     </row>
     <row r="605">
@@ -20407,16 +20407,16 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Zeray Gayrimenkul Yatirim Ortakligi AS</t>
+          <t>Marmara Holding AS</t>
         </is>
       </c>
       <c r="H605" t="n">
-        <v>15.16</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="606">
@@ -20440,16 +20440,16 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>ZGYO</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>AVRASYA PETROL VE TURİSTİK TESİSLER YATIRIMLAR A.Ş.</t>
+          <t>Z Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H606" t="n">
-        <v>18.25</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="607">
@@ -20473,16 +20473,16 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
+          <t>Meka Global Makine Imalat Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H607" t="n">
-        <v>21.06</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="608">
@@ -20506,16 +20506,16 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>DARPHANE ALTIN SERTİFİKASI</t>
+          <t>Gentas Kimya Sanayi ve Ticaret Pazarlama</t>
         </is>
       </c>
       <c r="H608" t="n">
-        <v>76.31</v>
+        <v>20.94</v>
       </c>
     </row>
     <row r="609">
@@ -20539,16 +20539,16 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Enpara Bank A.S.</t>
+          <t>Formul Plastik Ve Metal Sanayi AS</t>
         </is>
       </c>
       <c r="H609" t="n">
-        <v>72.5</v>
+        <v>46.38</v>
       </c>
     </row>
     <row r="610">
@@ -20572,16 +20572,16 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
+          <t>Metropal Kurumsal Hizmetler A.S.</t>
         </is>
       </c>
       <c r="H610" t="n">
-        <v>18.78</v>
+        <v>187</v>
       </c>
     </row>
     <row r="611">
@@ -20605,16 +20605,16 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>MEYSU</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>İŞ YATIRIM ORTAKLIĞI A.Ş.</t>
+          <t>Meysu Gida Sanayi Ve Ticaret A.S.</t>
         </is>
       </c>
       <c r="H611" t="n">
-        <v>8.119999999999999</v>
+        <v>17.26</v>
       </c>
     </row>
     <row r="612">
@@ -20638,16 +20638,16 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Best Brands Grup Enerji Yatirim as</t>
+          <t>Luxera Gayrimenkul Yatirim Ortakligi A.S.</t>
         </is>
       </c>
       <c r="H612" t="n">
-        <v>44.46</v>
+        <v>18.61</v>
       </c>
     </row>
     <row r="613">

--- a/FonHisseFiyatlari.xlsx
+++ b/FonHisseFiyatlari.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2612.5</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>141.9</v>
+        <v>140.8</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>94.84999999999999</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>196</v>
+        <v>195.1</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>388.25</v>
+        <v>388.75</v>
       </c>
     </row>
     <row r="9">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>233.2</v>
+        <v>233.5</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>327.5</v>
+        <v>327.25</v>
       </c>
     </row>
     <row r="11">
@@ -805,7 +805,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>ISKUR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>14.95</v>
+        <v>2915000</v>
       </c>
     </row>
     <row r="12">
@@ -871,7 +871,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISKUR</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2915000</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>77.55</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>174.3</v>
+        <v>172.2</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>114.7</v>
+        <v>114.6</v>
       </c>
     </row>
     <row r="17">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>47.16</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="18">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>33.88</v>
+        <v>33.68</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>40.38</v>
+        <v>40.08</v>
       </c>
     </row>
     <row r="20">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>89.90000000000001</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>40</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="22">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>271</v>
+        <v>279.25</v>
       </c>
     </row>
     <row r="23">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>113.4</v>
+        <v>112.9</v>
       </c>
     </row>
     <row r="24">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="25">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>65.05</v>
+        <v>64.95</v>
       </c>
     </row>
     <row r="26">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>101</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="27">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1549</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="28">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>495.25</v>
+        <v>494.25</v>
       </c>
     </row>
     <row r="30">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>219.6</v>
+        <v>221.2</v>
       </c>
     </row>
     <row r="31">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>95.15000000000001</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>308.25</v>
+        <v>307</v>
       </c>
     </row>
     <row r="33">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>45.6</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>46.38</v>
+        <v>46.26</v>
       </c>
     </row>
     <row r="35">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="36">
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>107.3</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="37">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>685.5</v>
+        <v>702.5</v>
       </c>
     </row>
     <row r="39">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>11487.5</v>
+        <v>11405</v>
       </c>
     </row>
     <row r="41">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>685</v>
+        <v>688.5</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1689</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="44">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>22.58</v>
+        <v>22.48</v>
       </c>
     </row>
     <row r="45">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>33.2</v>
+        <v>33.56</v>
       </c>
     </row>
     <row r="46">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>287.25</v>
+        <v>287</v>
       </c>
     </row>
     <row r="47">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="49">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>108.8</v>
+        <v>107.7</v>
       </c>
     </row>
     <row r="52">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>631.5</v>
+        <v>634.5</v>
       </c>
     </row>
     <row r="53">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>33.88</v>
+        <v>34.14</v>
       </c>
     </row>
     <row r="54">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>180.7</v>
+        <v>180.4</v>
       </c>
     </row>
     <row r="55">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>448.25</v>
+        <v>448</v>
       </c>
     </row>
     <row r="56">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>10.16</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="57">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>17.14</v>
+        <v>17.23</v>
       </c>
     </row>
     <row r="59">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>114.3</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="60">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>20.78</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="61">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>211.9</v>
+        <v>211.5</v>
       </c>
     </row>
     <row r="63">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>115.7</v>
+        <v>113.3</v>
       </c>
     </row>
     <row r="64">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>105.9</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="65">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>201.6</v>
+        <v>202.7</v>
       </c>
     </row>
     <row r="66">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>260.5</v>
+        <v>260</v>
       </c>
     </row>
     <row r="67">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>33.82</v>
+        <v>33.66</v>
       </c>
     </row>
     <row r="68">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.8</v>
+        <v>32.72</v>
       </c>
     </row>
     <row r="69">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>13.01</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="70">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>182.9</v>
+        <v>183.2</v>
       </c>
     </row>
     <row r="71">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>100.4</v>
+        <v>99.05</v>
       </c>
     </row>
     <row r="72">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>125.8</v>
+        <v>126</v>
       </c>
     </row>
     <row r="73">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1371</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="74">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>42.68</v>
+        <v>43.16</v>
       </c>
     </row>
     <row r="75">
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>28.42</v>
+        <v>28.48</v>
       </c>
     </row>
     <row r="76">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="78">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>37.42</v>
+        <v>37.38</v>
       </c>
     </row>
     <row r="80">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>140</v>
+        <v>139.5</v>
       </c>
     </row>
     <row r="82">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>224.4</v>
+        <v>225.6</v>
       </c>
     </row>
     <row r="83">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>40.58</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="85">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>41.34</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="86">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>25.88</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="88">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>51.55</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="91">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1205</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="92">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>254</v>
+        <v>253.75</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>450.5</v>
+        <v>450.25</v>
       </c>
     </row>
     <row r="94">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>628</v>
+        <v>645.5</v>
       </c>
     </row>
     <row r="96">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>102</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="97">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>139.4</v>
+        <v>138.7</v>
       </c>
     </row>
     <row r="98">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>116.2</v>
+        <v>116.1</v>
       </c>
     </row>
     <row r="100">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>353.5</v>
+        <v>353.25</v>
       </c>
     </row>
     <row r="101">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>66.15000000000001</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="102">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>215.9</v>
+        <v>217.3</v>
       </c>
     </row>
     <row r="103">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>111.3</v>
+        <v>110.7</v>
       </c>
     </row>
     <row r="104">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1722</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="105">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>203.6</v>
+        <v>203.1</v>
       </c>
     </row>
     <row r="106">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>86.2</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="107">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>37.76</v>
+        <v>38.02</v>
       </c>
     </row>
     <row r="108">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>22.56</v>
+        <v>22.64</v>
       </c>
     </row>
     <row r="110">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>107.5</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="111">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>357.75</v>
+        <v>355.5</v>
       </c>
     </row>
     <row r="112">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="113">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>14.28</v>
+        <v>14.26</v>
       </c>
     </row>
     <row r="115">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>50.4</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="116">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>12.25</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="117">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="118">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>42.76</v>
+        <v>42.58</v>
       </c>
     </row>
     <row r="119">
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>224.2</v>
+        <v>224</v>
       </c>
     </row>
     <row r="121">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>5.99</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="122">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>14.66</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="123">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>200.1</v>
+        <v>199.9</v>
       </c>
     </row>
     <row r="124">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>13.43</v>
+        <v>13.45</v>
       </c>
     </row>
     <row r="125">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>16.26</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="126">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>26.48</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="127">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>313</v>
+        <v>313.5</v>
       </c>
     </row>
     <row r="129">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>15.35</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="130">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>13.79</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="131">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>53.7</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="133">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>233</v>
+        <v>233.4</v>
       </c>
     </row>
     <row r="134">
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>10.56</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="136">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>116</v>
+        <v>115.9</v>
       </c>
     </row>
     <row r="137">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>29.22</v>
+        <v>29.12</v>
       </c>
     </row>
     <row r="138">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>92.5</v>
+        <v>92.34999999999999</v>
       </c>
     </row>
     <row r="139">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>70.7</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="140">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>13950</v>
+        <v>13925</v>
       </c>
     </row>
     <row r="141">
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>326.5</v>
+        <v>327.75</v>
       </c>
     </row>
     <row r="143">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>143.9</v>
+        <v>143.8</v>
       </c>
     </row>
     <row r="144">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>59.55</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="145">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>9.94</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="147">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>47.5</v>
+        <v>47.46</v>
       </c>
     </row>
     <row r="148">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>58.3</v>
+        <v>58.05</v>
       </c>
     </row>
     <row r="149">
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>87.8</v>
+        <v>87.75</v>
       </c>
     </row>
     <row r="150">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>18.27</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="152">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="153">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.26</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="154">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>12.16</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="155">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>8.949999999999999</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="156">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>86.84999999999999</v>
+        <v>86.55</v>
       </c>
     </row>
     <row r="157">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>36.88</v>
+        <v>36.96</v>
       </c>
     </row>
     <row r="158">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>58.55</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="159">
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>84.45</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="160">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>14.52</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="161">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>40.16</v>
+        <v>40.76</v>
       </c>
     </row>
     <row r="163">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>180.8</v>
+        <v>181.4</v>
       </c>
     </row>
     <row r="165">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>4.97</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="166">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>20.86</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="167">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>40.66</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="168">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>74.05</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="169">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>150.5</v>
+        <v>149.6</v>
       </c>
     </row>
     <row r="170">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>5085</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="171">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>62</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="172">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>3762.5</v>
+        <v>3752.5</v>
       </c>
     </row>
     <row r="173">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>25.36</v>
+        <v>25.22</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>20.98</v>
+        <v>21</v>
       </c>
     </row>
     <row r="175">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5740</v>
+        <v>5715</v>
       </c>
     </row>
     <row r="176">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>140.5</v>
+        <v>139.7</v>
       </c>
     </row>
     <row r="177">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>1548</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="178">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>14.98</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="179">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>11.98</v>
+        <v>11.85</v>
       </c>
     </row>
     <row r="180">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>80.2</v>
+        <v>80.05</v>
       </c>
     </row>
     <row r="181">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>16.07</v>
+        <v>16</v>
       </c>
     </row>
     <row r="182">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>94.09999999999999</v>
+        <v>93.45</v>
       </c>
     </row>
     <row r="183">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>20.72</v>
+        <v>20.78</v>
       </c>
     </row>
     <row r="184">
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>31.98</v>
+        <v>31.96</v>
       </c>
     </row>
     <row r="185">
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>61.9</v>
+        <v>61.75</v>
       </c>
     </row>
     <row r="186">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>22.8</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>152.1</v>
+        <v>151.4</v>
       </c>
     </row>
     <row r="188">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>624.5</v>
+        <v>625</v>
       </c>
     </row>
     <row r="189">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>29.12</v>
+        <v>28.96</v>
       </c>
     </row>
     <row r="191">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>39.7</v>
+        <v>39.92</v>
       </c>
     </row>
     <row r="192">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>28.76</v>
+        <v>28.64</v>
       </c>
     </row>
     <row r="193">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="194">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="195">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>26.94</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="196">
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>14.27</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="197">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>240.4</v>
+        <v>237.2</v>
       </c>
     </row>
     <row r="198">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="200">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>24.06</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="201">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
     </row>
     <row r="202">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>19.4</v>
+        <v>19.29</v>
       </c>
     </row>
     <row r="203">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>144.2</v>
+        <v>143.9</v>
       </c>
     </row>
     <row r="204">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>20.12</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="205">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>86.7</v>
+        <v>86.55</v>
       </c>
     </row>
     <row r="206">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>4.6</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="208">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>45.12</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="209">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>643</v>
+        <v>643.5</v>
       </c>
     </row>
     <row r="210">
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>66.05</v>
+        <v>66</v>
       </c>
     </row>
     <row r="211">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>117.3</v>
+        <v>114.9</v>
       </c>
     </row>
     <row r="212">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="213">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="214">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>32.36</v>
+        <v>32.28</v>
       </c>
     </row>
     <row r="216">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>76.25</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="217">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>41.18</v>
+        <v>41.28</v>
       </c>
     </row>
     <row r="218">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>11.55</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="219">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>12.19</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="220">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>14.94</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="221">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>41.7</v>
+        <v>41.68</v>
       </c>
     </row>
     <row r="222">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>8.02</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="224">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>55.05</v>
+        <v>55.15</v>
       </c>
     </row>
     <row r="225">
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>5.98</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="226">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>16.75</v>
+        <v>16.71</v>
       </c>
     </row>
     <row r="227">
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="H227" t="n">
-        <v>134</v>
+        <v>134.2</v>
       </c>
     </row>
     <row r="228">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>9.140000000000001</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="229">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>7.24</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="230">
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>7.22</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="231">
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>18.29</v>
+        <v>18.35</v>
       </c>
     </row>
     <row r="232">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>542.5</v>
+        <v>538.5</v>
       </c>
     </row>
     <row r="233">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>62.65</v>
+        <v>62.95</v>
       </c>
     </row>
     <row r="234">
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>110.9</v>
+        <v>110.3</v>
       </c>
     </row>
     <row r="238">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>38.5</v>
+        <v>38.48</v>
       </c>
     </row>
     <row r="239">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>42.92</v>
+        <v>42.74</v>
       </c>
     </row>
     <row r="241">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="243">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>33.14</v>
+        <v>33.94</v>
       </c>
     </row>
     <row r="244">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>92.40000000000001</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="245">
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>21.68</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="246">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>7.44</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="247">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="249">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>86.5</v>
+        <v>86.45</v>
       </c>
     </row>
     <row r="250">
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="251">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>25.04</v>
+        <v>25.02</v>
       </c>
     </row>
     <row r="252">
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>263.5</v>
+        <v>263.25</v>
       </c>
     </row>
     <row r="253">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>35.7</v>
+        <v>35.68</v>
       </c>
     </row>
     <row r="255">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>13.33</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="256">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>1167</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="257">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>26.98</v>
+        <v>27.08</v>
       </c>
     </row>
     <row r="259">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="260">
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>19.13</v>
+        <v>19.08</v>
       </c>
     </row>
     <row r="261">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>53.8</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="262">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>28.32</v>
+        <v>28.36</v>
       </c>
     </row>
     <row r="263">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>14.14</v>
+        <v>14.11</v>
       </c>
     </row>
     <row r="264">
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>15.17</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="265">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>11.5</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="266">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>125.3</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="267">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>124.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="268">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>6.09</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="269">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>114.1</v>
+        <v>116.5</v>
       </c>
     </row>
     <row r="270">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>17.68</v>
+        <v>17.66</v>
       </c>
     </row>
     <row r="271">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>8.4</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="272">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>17.67</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="273">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>19.48</v>
+        <v>19.45</v>
       </c>
     </row>
     <row r="274">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>12.56</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="275">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="276">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>40.16</v>
+        <v>40.44</v>
       </c>
     </row>
     <row r="277">
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="H277" t="n">
-        <v>32.9</v>
+        <v>32.94</v>
       </c>
     </row>
     <row r="278">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>58.5</v>
+        <v>58.45</v>
       </c>
     </row>
     <row r="280">
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>7.68</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="282">
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>26.64</v>
+        <v>26.78</v>
       </c>
     </row>
     <row r="283">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>23.46</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="284">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>25.04</v>
+        <v>25.02</v>
       </c>
     </row>
     <row r="286">
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>8.130000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="287">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>6.3</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="288">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>58.65</v>
+        <v>58.55</v>
       </c>
     </row>
     <row r="289">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>21.12</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="290">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>6.16</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="291">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="292">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>45.62</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="294">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>11.82</v>
+        <v>11.79</v>
       </c>
     </row>
     <row r="295">
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>18.95</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="296">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="297">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>89.34999999999999</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="298">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="299">
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>216.8</v>
+        <v>216.4</v>
       </c>
     </row>
     <row r="300">
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>42.24</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="301">
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="H301" t="n">
-        <v>24.08</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="302">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>19.16</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="303">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>9.800000000000001</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="305">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="306">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>10.09</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="310">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>7.59</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="311">
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>39.54</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="312">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>114.5</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="314">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>14.22</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="315">
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>261</v>
+        <v>261.5</v>
       </c>
     </row>
     <row r="316">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>8.43</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="317">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>238.9</v>
+        <v>238.5</v>
       </c>
     </row>
     <row r="318">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>438.5</v>
+        <v>442</v>
       </c>
     </row>
     <row r="319">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>91.90000000000001</v>
+        <v>91.45</v>
       </c>
     </row>
     <row r="321">
@@ -11044,7 +11044,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>12.37</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="322">
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="H322" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="323">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>15.38</v>
+        <v>15.24</v>
       </c>
     </row>
     <row r="324">
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>156.2</v>
+        <v>155.2</v>
       </c>
     </row>
     <row r="325">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>15.34</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="326">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>6.27</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="327">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="328">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="H328" t="n">
-        <v>332.75</v>
+        <v>333</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>6.29</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="330">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="H330" t="n">
-        <v>33.3</v>
+        <v>33.26</v>
       </c>
     </row>
     <row r="331">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H331" t="n">
-        <v>14.98</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H332" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="333">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="H333" t="n">
-        <v>40.26</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="334">
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="H334" t="n">
-        <v>63.85</v>
+        <v>63.65</v>
       </c>
     </row>
     <row r="335">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="336">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="H336" t="n">
-        <v>17.34</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="337">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>6.96</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="338">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>22.86</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="339">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>5.46</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="342">
@@ -11737,7 +11737,7 @@
         </is>
       </